--- a/apportion/pop.xlsx
+++ b/apportion/pop.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10411"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/user/Google Drive/GitHub/R Functions/apportion/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0263A944-4CE9-8D44-823F-F119DDAF8248}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8C63575-32E8-F042-A0FD-16E20B0C84EE}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38400" yWindow="500" windowWidth="38400" windowHeight="21100"/>
+    <workbookView xWindow="-38400" yWindow="500" windowWidth="38400" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="pop" sheetId="1" r:id="rId1"/>
@@ -31,9 +31,6 @@
     <t>house2010</t>
   </si>
   <si>
-    <t>pop2019</t>
-  </si>
-  <si>
     <t>pop2020</t>
   </si>
   <si>
@@ -215,12 +212,15 @@
   </si>
   <si>
     <t>Wyoming</t>
+  </si>
+  <si>
+    <t>pop2020est</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
@@ -1055,7 +1055,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L52"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
@@ -1070,36 +1070,36 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>10</v>
-      </c>
-      <c r="L1" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B2">
         <v>4802982</v>
@@ -1132,7 +1132,7 @@
         <v>0</v>
       </c>
       <c r="K2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L2">
         <f>E2-B2</f>
@@ -1141,7 +1141,7 @@
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B3">
         <v>721523</v>
@@ -1174,7 +1174,7 @@
         <v>0</v>
       </c>
       <c r="K3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L3">
         <f t="shared" ref="L3:L52" si="3">E3-B3</f>
@@ -1183,7 +1183,7 @@
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B4">
         <v>6412700</v>
@@ -1216,7 +1216,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L4">
         <f t="shared" si="3"/>
@@ -1225,7 +1225,7 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B5">
         <v>2926229</v>
@@ -1258,7 +1258,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L5">
         <f t="shared" si="3"/>
@@ -1267,7 +1267,7 @@
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B6">
         <v>37341989</v>
@@ -1300,7 +1300,7 @@
         <v>-1</v>
       </c>
       <c r="K6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L6">
         <f t="shared" si="3"/>
@@ -1309,7 +1309,7 @@
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B7">
         <v>5044930</v>
@@ -1342,7 +1342,7 @@
         <v>1</v>
       </c>
       <c r="K7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L7">
         <f t="shared" si="3"/>
@@ -1351,7 +1351,7 @@
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B8">
         <v>3581628</v>
@@ -1384,7 +1384,7 @@
         <v>0</v>
       </c>
       <c r="K8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L8">
         <f t="shared" si="3"/>
@@ -1393,7 +1393,7 @@
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B9">
         <v>900877</v>
@@ -1426,7 +1426,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L9">
         <f t="shared" si="3"/>
@@ -1435,7 +1435,7 @@
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B10">
         <v>601723</v>
@@ -1467,7 +1467,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L10">
         <f t="shared" si="3"/>
@@ -1476,7 +1476,7 @@
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B11">
         <v>18900773</v>
@@ -1509,7 +1509,7 @@
         <v>1</v>
       </c>
       <c r="K11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L11">
         <f t="shared" si="3"/>
@@ -1518,7 +1518,7 @@
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B12">
         <v>9727566</v>
@@ -1551,7 +1551,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L12">
         <f t="shared" si="3"/>
@@ -1560,7 +1560,7 @@
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B13">
         <v>1366862</v>
@@ -1593,7 +1593,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L13">
         <f t="shared" si="3"/>
@@ -1602,7 +1602,7 @@
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B14">
         <v>1573499</v>
@@ -1635,7 +1635,7 @@
         <v>0</v>
       </c>
       <c r="K14" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L14">
         <f t="shared" si="3"/>
@@ -1644,7 +1644,7 @@
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B15">
         <v>12864380</v>
@@ -1677,7 +1677,7 @@
         <v>-1</v>
       </c>
       <c r="K15" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L15">
         <f t="shared" si="3"/>
@@ -1686,7 +1686,7 @@
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B16">
         <v>6501582</v>
@@ -1719,7 +1719,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L16">
         <f t="shared" si="3"/>
@@ -1728,7 +1728,7 @@
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B17">
         <v>3053787</v>
@@ -1761,7 +1761,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L17">
         <f t="shared" si="3"/>
@@ -1770,7 +1770,7 @@
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B18">
         <v>2863813</v>
@@ -1803,7 +1803,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L18">
         <f t="shared" si="3"/>
@@ -1812,7 +1812,7 @@
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B19">
         <v>4350606</v>
@@ -1845,7 +1845,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L19">
         <f t="shared" si="3"/>
@@ -1854,7 +1854,7 @@
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B20">
         <v>4553962</v>
@@ -1887,7 +1887,7 @@
         <v>0</v>
       </c>
       <c r="K20" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L20">
         <f t="shared" si="3"/>
@@ -1896,7 +1896,7 @@
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B21">
         <v>1333074</v>
@@ -1929,7 +1929,7 @@
         <v>0</v>
       </c>
       <c r="K21" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L21">
         <f t="shared" si="3"/>
@@ -1938,7 +1938,7 @@
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B22">
         <v>5789929</v>
@@ -1971,7 +1971,7 @@
         <v>0</v>
       </c>
       <c r="K22" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L22">
         <f t="shared" si="3"/>
@@ -1980,7 +1980,7 @@
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B23">
         <v>6559644</v>
@@ -2013,7 +2013,7 @@
         <v>0</v>
       </c>
       <c r="K23" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L23">
         <f t="shared" si="3"/>
@@ -2022,7 +2022,7 @@
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B24">
         <v>9911626</v>
@@ -2055,7 +2055,7 @@
         <v>-1</v>
       </c>
       <c r="K24" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L24">
         <f t="shared" si="3"/>
@@ -2064,7 +2064,7 @@
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B25">
         <v>5314879</v>
@@ -2097,7 +2097,7 @@
         <v>0</v>
       </c>
       <c r="K25" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L25">
         <f t="shared" si="3"/>
@@ -2106,7 +2106,7 @@
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B26">
         <v>2978240</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="K26" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L26">
         <f t="shared" si="3"/>
@@ -2148,7 +2148,7 @@
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B27">
         <v>6011478</v>
@@ -2181,7 +2181,7 @@
         <v>0</v>
       </c>
       <c r="K27" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L27">
         <f t="shared" si="3"/>
@@ -2190,7 +2190,7 @@
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B28">
         <v>994416</v>
@@ -2223,7 +2223,7 @@
         <v>1</v>
       </c>
       <c r="K28" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L28">
         <f t="shared" si="3"/>
@@ -2232,7 +2232,7 @@
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B29">
         <v>1831825</v>
@@ -2265,7 +2265,7 @@
         <v>0</v>
       </c>
       <c r="K29" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L29">
         <f t="shared" si="3"/>
@@ -2274,7 +2274,7 @@
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B30">
         <v>2709432</v>
@@ -2307,7 +2307,7 @@
         <v>0</v>
       </c>
       <c r="K30" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L30">
         <f t="shared" si="3"/>
@@ -2316,7 +2316,7 @@
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B31">
         <v>1321445</v>
@@ -2349,7 +2349,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L31">
         <f t="shared" si="3"/>
@@ -2358,7 +2358,7 @@
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B32">
         <v>8807501</v>
@@ -2391,7 +2391,7 @@
         <v>0</v>
       </c>
       <c r="K32" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L32">
         <f t="shared" si="3"/>
@@ -2400,7 +2400,7 @@
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B33">
         <v>2067273</v>
@@ -2433,7 +2433,7 @@
         <v>0</v>
       </c>
       <c r="K33" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L33">
         <f t="shared" si="3"/>
@@ -2442,7 +2442,7 @@
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B34">
         <v>19421055</v>
@@ -2475,7 +2475,7 @@
         <v>-1</v>
       </c>
       <c r="K34" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L34">
         <f t="shared" si="3"/>
@@ -2484,7 +2484,7 @@
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B35">
         <v>9565781</v>
@@ -2517,7 +2517,7 @@
         <v>1</v>
       </c>
       <c r="K35" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L35">
         <f t="shared" si="3"/>
@@ -2526,7 +2526,7 @@
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B36">
         <v>675905</v>
@@ -2559,7 +2559,7 @@
         <v>0</v>
       </c>
       <c r="K36" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L36">
         <f t="shared" si="3"/>
@@ -2568,7 +2568,7 @@
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B37">
         <v>11568495</v>
@@ -2601,7 +2601,7 @@
         <v>-1</v>
       </c>
       <c r="K37" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L37">
         <f t="shared" si="3"/>
@@ -2610,7 +2610,7 @@
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B38">
         <v>3764882</v>
@@ -2643,7 +2643,7 @@
         <v>0</v>
       </c>
       <c r="K38" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L38">
         <f t="shared" si="3"/>
@@ -2652,7 +2652,7 @@
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B39">
         <v>3848606</v>
@@ -2685,7 +2685,7 @@
         <v>1</v>
       </c>
       <c r="K39" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L39">
         <f t="shared" si="3"/>
@@ -2694,7 +2694,7 @@
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B40">
         <v>12734905</v>
@@ -2727,7 +2727,7 @@
         <v>-1</v>
       </c>
       <c r="K40" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L40">
         <f t="shared" si="3"/>
@@ -2736,7 +2736,7 @@
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B41">
         <v>1055247</v>
@@ -2769,7 +2769,7 @@
         <v>0</v>
       </c>
       <c r="K41" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L41">
         <f t="shared" si="3"/>
@@ -2778,7 +2778,7 @@
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B42">
         <v>4645975</v>
@@ -2811,7 +2811,7 @@
         <v>0</v>
       </c>
       <c r="K42" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L42">
         <f t="shared" si="3"/>
@@ -2820,7 +2820,7 @@
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B43">
         <v>819761</v>
@@ -2853,7 +2853,7 @@
         <v>0</v>
       </c>
       <c r="K43" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L43">
         <f t="shared" si="3"/>
@@ -2862,7 +2862,7 @@
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B44">
         <v>6375431</v>
@@ -2895,7 +2895,7 @@
         <v>0</v>
       </c>
       <c r="K44" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L44">
         <f t="shared" si="3"/>
@@ -2904,7 +2904,7 @@
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B45">
         <v>25268418</v>
@@ -2937,7 +2937,7 @@
         <v>2</v>
       </c>
       <c r="K45" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L45">
         <f t="shared" si="3"/>
@@ -2946,7 +2946,7 @@
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B46">
         <v>2770765</v>
@@ -2979,7 +2979,7 @@
         <v>0</v>
       </c>
       <c r="K46" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L46">
         <f t="shared" si="3"/>
@@ -2988,7 +2988,7 @@
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B47">
         <v>630337</v>
@@ -3021,7 +3021,7 @@
         <v>0</v>
       </c>
       <c r="K47" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L47">
         <f t="shared" si="3"/>
@@ -3030,7 +3030,7 @@
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B48">
         <v>8037736</v>
@@ -3063,7 +3063,7 @@
         <v>0</v>
       </c>
       <c r="K48" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L48">
         <f t="shared" si="3"/>
@@ -3072,7 +3072,7 @@
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B49">
         <v>6753369</v>
@@ -3105,7 +3105,7 @@
         <v>0</v>
       </c>
       <c r="K49" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L49">
         <f t="shared" si="3"/>
@@ -3114,7 +3114,7 @@
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B50">
         <v>1859815</v>
@@ -3147,7 +3147,7 @@
         <v>-1</v>
       </c>
       <c r="K50" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L50">
         <f t="shared" si="3"/>
@@ -3156,7 +3156,7 @@
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B51">
         <v>5698230</v>
@@ -3189,7 +3189,7 @@
         <v>0</v>
       </c>
       <c r="K51" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L51">
         <f t="shared" si="3"/>
@@ -3198,7 +3198,7 @@
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B52">
         <v>568300</v>
@@ -3231,7 +3231,7 @@
         <v>0</v>
       </c>
       <c r="K52" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L52">
         <f t="shared" si="3"/>

--- a/apportion/pop.xlsx
+++ b/apportion/pop.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/user/Google Drive/GitHub/R Functions/apportion/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8C63575-32E8-F042-A0FD-16E20B0C84EE}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{7AD16E79-4AA1-3947-9E00-8B25696DE3CB}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38400" yWindow="500" windowWidth="38400" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="123">
   <si>
     <t>state</t>
   </si>
@@ -215,13 +215,187 @@
   </si>
   <si>
     <t>pop2020est</t>
+  </si>
+  <si>
+    <t>popestdiff</t>
+  </si>
+  <si>
+    <t>pop_per_diff</t>
+  </si>
+  <si>
+    <t>WY</t>
+  </si>
+  <si>
+    <t>WI</t>
+  </si>
+  <si>
+    <t>WV</t>
+  </si>
+  <si>
+    <t>WA</t>
+  </si>
+  <si>
+    <t>VT</t>
+  </si>
+  <si>
+    <t>VA</t>
+  </si>
+  <si>
+    <t>UT</t>
+  </si>
+  <si>
+    <t>TX</t>
+  </si>
+  <si>
+    <t>TN</t>
+  </si>
+  <si>
+    <t>SD</t>
+  </si>
+  <si>
+    <t>SC</t>
+  </si>
+  <si>
+    <t>RI</t>
+  </si>
+  <si>
+    <t>PA</t>
+  </si>
+  <si>
+    <t>OR</t>
+  </si>
+  <si>
+    <t>OK</t>
+  </si>
+  <si>
+    <t>OH</t>
+  </si>
+  <si>
+    <t>ND</t>
+  </si>
+  <si>
+    <t>NC</t>
+  </si>
+  <si>
+    <t>NY</t>
+  </si>
+  <si>
+    <t>NM</t>
+  </si>
+  <si>
+    <t>NJ</t>
+  </si>
+  <si>
+    <t>NH</t>
+  </si>
+  <si>
+    <t>NV</t>
+  </si>
+  <si>
+    <t>NE</t>
+  </si>
+  <si>
+    <t>MT</t>
+  </si>
+  <si>
+    <t>MO</t>
+  </si>
+  <si>
+    <t>MS</t>
+  </si>
+  <si>
+    <t>MN</t>
+  </si>
+  <si>
+    <t>MI</t>
+  </si>
+  <si>
+    <t>MA</t>
+  </si>
+  <si>
+    <t>MD</t>
+  </si>
+  <si>
+    <t>ME</t>
+  </si>
+  <si>
+    <t>LA</t>
+  </si>
+  <si>
+    <t>KY</t>
+  </si>
+  <si>
+    <t>KS</t>
+  </si>
+  <si>
+    <t>IA</t>
+  </si>
+  <si>
+    <t>IN</t>
+  </si>
+  <si>
+    <t>IL</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>HI</t>
+  </si>
+  <si>
+    <t>GA</t>
+  </si>
+  <si>
+    <t>FL</t>
+  </si>
+  <si>
+    <t>DC</t>
+  </si>
+  <si>
+    <t>DE</t>
+  </si>
+  <si>
+    <t>CT</t>
+  </si>
+  <si>
+    <t>CO</t>
+  </si>
+  <si>
+    <t>CA</t>
+  </si>
+  <si>
+    <t>AR</t>
+  </si>
+  <si>
+    <t>AZ</t>
+  </si>
+  <si>
+    <t>AL</t>
+  </si>
+  <si>
+    <t>AK</t>
+  </si>
+  <si>
+    <t>new_death</t>
+  </si>
+  <si>
+    <t>tot_death</t>
+  </si>
+  <si>
+    <t>tot_cases</t>
+  </si>
+  <si>
+    <t>abv</t>
+  </si>
+  <si>
+    <t>covid_effect</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -352,6 +526,13 @@
     <font>
       <sz val="12"/>
       <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -654,7 +835,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="42">
+  <cellStyleXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
@@ -697,12 +878,15 @@
     <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="42">
+  <cellStyles count="43">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
     <cellStyle name="20% - Accent2" xfId="23" builtinId="34" customBuiltin="1"/>
     <cellStyle name="20% - Accent3" xfId="27" builtinId="38" customBuiltin="1"/>
@@ -742,6 +926,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Note" xfId="15" builtinId="10" customBuiltin="1"/>
     <cellStyle name="Output" xfId="10" builtinId="21" customBuiltin="1"/>
+    <cellStyle name="Percent" xfId="42" builtinId="5"/>
     <cellStyle name="Title" xfId="1" builtinId="15" customBuiltin="1"/>
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
     <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
@@ -1056,10 +1241,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L52"/>
+  <dimension ref="A1:S52"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1096,8 +1281,29 @@
       <c r="L1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M1" t="s">
+        <v>65</v>
+      </c>
+      <c r="N1" t="s">
+        <v>66</v>
+      </c>
+      <c r="O1" t="s">
+        <v>121</v>
+      </c>
+      <c r="P1" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>119</v>
+      </c>
+      <c r="R1" t="s">
+        <v>118</v>
+      </c>
+      <c r="S1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -1138,8 +1344,32 @@
         <f>E2-B2</f>
         <v>227071</v>
       </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M2" s="2">
+        <f>(E2-D2)/D2</f>
+        <v>2.2050247768377815E-2</v>
+      </c>
+      <c r="N2">
+        <f>E2/D2*100</f>
+        <v>102.20502477683777</v>
+      </c>
+      <c r="O2" t="s">
+        <v>117</v>
+      </c>
+      <c r="P2">
+        <v>143</v>
+      </c>
+      <c r="Q2">
+        <v>3</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <f>P2+E2</f>
+        <v>5030196</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -1180,8 +1410,32 @@
         <f t="shared" ref="L3:L52" si="3">E3-B3</f>
         <v>14558</v>
       </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M3" s="2">
+        <f t="shared" ref="M3:M52" si="4">(E3-D3)/D3</f>
+        <v>6.7331548037496683E-3</v>
+      </c>
+      <c r="N3">
+        <f t="shared" ref="N3:N52" si="5">E3/D3*100</f>
+        <v>100.67331548037497</v>
+      </c>
+      <c r="O3" t="s">
+        <v>116</v>
+      </c>
+      <c r="P3">
+        <v>1106</v>
+      </c>
+      <c r="Q3">
+        <v>17</v>
+      </c>
+      <c r="R3">
+        <v>4</v>
+      </c>
+      <c r="S3">
+        <f t="shared" ref="S3:S52" si="6">P3+E3</f>
+        <v>737187</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -1222,8 +1476,32 @@
         <f t="shared" si="3"/>
         <v>746223</v>
       </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M4" s="2">
+        <f t="shared" si="4"/>
+        <v>-3.5367715610570026E-2</v>
+      </c>
+      <c r="N4">
+        <f t="shared" si="5"/>
+        <v>96.463228438942991</v>
+      </c>
+      <c r="O4" t="s">
+        <v>115</v>
+      </c>
+      <c r="P4">
+        <v>1413</v>
+      </c>
+      <c r="Q4">
+        <v>29</v>
+      </c>
+      <c r="R4">
+        <v>5</v>
+      </c>
+      <c r="S4">
+        <f t="shared" si="6"/>
+        <v>7160336</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -1264,8 +1542,32 @@
         <f t="shared" si="3"/>
         <v>87527</v>
       </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M5" s="2">
+        <f t="shared" si="4"/>
+        <v>-5.5323802302045654E-3</v>
+      </c>
+      <c r="N5">
+        <f t="shared" si="5"/>
+        <v>99.446761976979545</v>
+      </c>
+      <c r="O5" t="s">
+        <v>114</v>
+      </c>
+      <c r="P5">
+        <v>614</v>
+      </c>
+      <c r="Q5">
+        <v>10</v>
+      </c>
+      <c r="R5">
+        <v>2</v>
+      </c>
+      <c r="S5">
+        <f t="shared" si="6"/>
+        <v>3014370</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -1306,8 +1608,32 @@
         <f t="shared" si="3"/>
         <v>2234768</v>
       </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M6" s="2">
+        <f t="shared" si="4"/>
+        <v>5.3007159760250422E-3</v>
+      </c>
+      <c r="N6">
+        <f t="shared" si="5"/>
+        <v>100.5300715976025</v>
+      </c>
+      <c r="O6" t="s">
+        <v>113</v>
+      </c>
+      <c r="P6">
+        <v>8155</v>
+      </c>
+      <c r="Q6">
+        <v>172</v>
+      </c>
+      <c r="R6">
+        <v>0</v>
+      </c>
+      <c r="S6">
+        <f t="shared" si="6"/>
+        <v>39584912</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -1348,8 +1674,32 @@
         <f t="shared" si="3"/>
         <v>737241</v>
       </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M7" s="2">
+        <f t="shared" si="4"/>
+        <v>-4.3989731596862725E-3</v>
+      </c>
+      <c r="N7">
+        <f t="shared" si="5"/>
+        <v>99.560102684031364</v>
+      </c>
+      <c r="O7" t="s">
+        <v>112</v>
+      </c>
+      <c r="P7">
+        <v>3342</v>
+      </c>
+      <c r="Q7">
+        <v>80</v>
+      </c>
+      <c r="R7">
+        <v>11</v>
+      </c>
+      <c r="S7">
+        <f t="shared" si="6"/>
+        <v>5785513</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>19</v>
       </c>
@@ -1390,8 +1740,32 @@
         <f t="shared" si="3"/>
         <v>26670</v>
       </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M8" s="2">
+        <f t="shared" si="4"/>
+        <v>1.4419992544291464E-2</v>
+      </c>
+      <c r="N8">
+        <f t="shared" si="5"/>
+        <v>101.44199925442913</v>
+      </c>
+      <c r="O8" t="s">
+        <v>111</v>
+      </c>
+      <c r="P8">
+        <v>3557</v>
+      </c>
+      <c r="Q8">
+        <v>85</v>
+      </c>
+      <c r="R8">
+        <v>16</v>
+      </c>
+      <c r="S8">
+        <f t="shared" si="6"/>
+        <v>3611855</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>20</v>
       </c>
@@ -1432,8 +1806,32 @@
         <f t="shared" si="3"/>
         <v>89960</v>
       </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M9" s="2">
+        <f t="shared" si="4"/>
+        <v>4.0818435989132653E-3</v>
+      </c>
+      <c r="N9">
+        <f t="shared" si="5"/>
+        <v>100.40818435989132</v>
+      </c>
+      <c r="O9" t="s">
+        <v>110</v>
+      </c>
+      <c r="P9">
+        <v>368</v>
+      </c>
+      <c r="Q9">
+        <v>11</v>
+      </c>
+      <c r="R9">
+        <v>1</v>
+      </c>
+      <c r="S9">
+        <f t="shared" si="6"/>
+        <v>991205</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>21</v>
       </c>
@@ -1473,8 +1871,32 @@
         <f t="shared" si="3"/>
         <v>89810</v>
       </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M10" s="2">
+        <f t="shared" si="4"/>
+        <v>-2.9857635069919865E-2</v>
+      </c>
+      <c r="N10">
+        <f t="shared" si="5"/>
+        <v>97.014236493008013</v>
+      </c>
+      <c r="O10" t="s">
+        <v>109</v>
+      </c>
+      <c r="P10">
+        <v>586</v>
+      </c>
+      <c r="Q10">
+        <v>11</v>
+      </c>
+      <c r="R10">
+        <v>2</v>
+      </c>
+      <c r="S10">
+        <f t="shared" si="6"/>
+        <v>692119</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>22</v>
       </c>
@@ -1515,8 +1937,32 @@
         <f t="shared" si="3"/>
         <v>2669754</v>
       </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M11" s="2">
+        <f t="shared" si="4"/>
+        <v>-7.4901147142230323E-3</v>
+      </c>
+      <c r="N11">
+        <f t="shared" si="5"/>
+        <v>99.250988528577693</v>
+      </c>
+      <c r="O11" t="s">
+        <v>108</v>
+      </c>
+      <c r="P11">
+        <v>7495</v>
+      </c>
+      <c r="Q11">
+        <v>101</v>
+      </c>
+      <c r="R11">
+        <v>16</v>
+      </c>
+      <c r="S11">
+        <f t="shared" si="6"/>
+        <v>21578022</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>23</v>
       </c>
@@ -1557,8 +2003,32 @@
         <f t="shared" si="3"/>
         <v>997708</v>
       </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M12" s="2">
+        <f t="shared" si="4"/>
+        <v>1.4245542280651841E-3</v>
+      </c>
+      <c r="N12">
+        <f t="shared" si="5"/>
+        <v>100.14245542280651</v>
+      </c>
+      <c r="O12" t="s">
+        <v>107</v>
+      </c>
+      <c r="P12">
+        <v>4806</v>
+      </c>
+      <c r="Q12">
+        <v>154</v>
+      </c>
+      <c r="R12">
+        <v>24</v>
+      </c>
+      <c r="S12">
+        <f t="shared" si="6"/>
+        <v>10730080</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>24</v>
       </c>
@@ -1599,8 +2069,32 @@
         <f t="shared" si="3"/>
         <v>93275</v>
       </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M13" s="2">
+        <f t="shared" si="4"/>
+        <v>3.7761743731014652E-2</v>
+      </c>
+      <c r="N13">
+        <f t="shared" si="5"/>
+        <v>103.77617437310147</v>
+      </c>
+      <c r="O13" t="s">
+        <v>106</v>
+      </c>
+      <c r="P13">
+        <v>311</v>
+      </c>
+      <c r="Q13">
+        <v>1</v>
+      </c>
+      <c r="R13">
+        <v>0</v>
+      </c>
+      <c r="S13">
+        <f t="shared" si="6"/>
+        <v>1460448</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>25</v>
       </c>
@@ -1641,8 +2135,32 @@
         <f t="shared" si="3"/>
         <v>267878</v>
       </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M14" s="2">
+        <f t="shared" si="4"/>
+        <v>7.9171805116061908E-3</v>
+      </c>
+      <c r="N14">
+        <f t="shared" si="5"/>
+        <v>100.79171805116063</v>
+      </c>
+      <c r="O14" t="s">
+        <v>105</v>
+      </c>
+      <c r="P14">
+        <v>669</v>
+      </c>
+      <c r="Q14">
+        <v>9</v>
+      </c>
+      <c r="R14">
+        <v>0</v>
+      </c>
+      <c r="S14">
+        <f t="shared" si="6"/>
+        <v>1842046</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>26</v>
       </c>
@@ -1683,8 +2201,32 @@
         <f t="shared" si="3"/>
         <v>-41641</v>
       </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M15" s="2">
+        <f t="shared" si="4"/>
+        <v>1.8685874035652746E-2</v>
+      </c>
+      <c r="N15">
+        <f t="shared" si="5"/>
+        <v>101.86858740356529</v>
+      </c>
+      <c r="O15" t="s">
+        <v>104</v>
+      </c>
+      <c r="P15">
+        <v>6980</v>
+      </c>
+      <c r="Q15">
+        <v>141</v>
+      </c>
+      <c r="R15">
+        <v>42</v>
+      </c>
+      <c r="S15">
+        <f t="shared" si="6"/>
+        <v>12829719</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>27</v>
       </c>
@@ -1725,8 +2267,32 @@
         <f t="shared" si="3"/>
         <v>288698</v>
       </c>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M16" s="2">
+        <f t="shared" si="4"/>
+        <v>5.2297921243863576E-3</v>
+      </c>
+      <c r="N16">
+        <f t="shared" si="5"/>
+        <v>100.52297921243864</v>
+      </c>
+      <c r="O16" t="s">
+        <v>103</v>
+      </c>
+      <c r="P16">
+        <v>2565</v>
+      </c>
+      <c r="Q16">
+        <v>65</v>
+      </c>
+      <c r="R16">
+        <v>16</v>
+      </c>
+      <c r="S16">
+        <f t="shared" si="6"/>
+        <v>6792845</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>28</v>
       </c>
@@ -1767,8 +2333,32 @@
         <f t="shared" si="3"/>
         <v>138619</v>
       </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M17" s="2">
+        <f t="shared" si="4"/>
+        <v>9.1178896186923531E-3</v>
+      </c>
+      <c r="N17">
+        <f t="shared" si="5"/>
+        <v>100.91178896186923</v>
+      </c>
+      <c r="O17" t="s">
+        <v>102</v>
+      </c>
+      <c r="P17">
+        <v>549</v>
+      </c>
+      <c r="Q17">
+        <v>9</v>
+      </c>
+      <c r="R17">
+        <v>2</v>
+      </c>
+      <c r="S17">
+        <f t="shared" si="6"/>
+        <v>3192955</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>29</v>
       </c>
@@ -1809,8 +2399,32 @@
         <f t="shared" si="3"/>
         <v>77052</v>
       </c>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M18" s="2">
+        <f t="shared" si="4"/>
+        <v>9.2868259886986267E-3</v>
+      </c>
+      <c r="N18">
+        <f t="shared" si="5"/>
+        <v>100.92868259886987</v>
+      </c>
+      <c r="O18" t="s">
+        <v>101</v>
+      </c>
+      <c r="P18">
+        <v>482</v>
+      </c>
+      <c r="Q18">
+        <v>10</v>
+      </c>
+      <c r="R18">
+        <v>1</v>
+      </c>
+      <c r="S18">
+        <f t="shared" si="6"/>
+        <v>2941347</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>30</v>
       </c>
@@ -1851,8 +2465,32 @@
         <f t="shared" si="3"/>
         <v>158736</v>
       </c>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M19" s="2">
+        <f t="shared" si="4"/>
+        <v>7.1675677776385557E-3</v>
+      </c>
+      <c r="N19">
+        <f t="shared" si="5"/>
+        <v>100.71675677776386</v>
+      </c>
+      <c r="O19" t="s">
+        <v>100</v>
+      </c>
+      <c r="P19">
+        <v>680</v>
+      </c>
+      <c r="Q19">
+        <v>20</v>
+      </c>
+      <c r="R19">
+        <v>2</v>
+      </c>
+      <c r="S19">
+        <f t="shared" si="6"/>
+        <v>4510022</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>31</v>
       </c>
@@ -1893,8 +2531,32 @@
         <f t="shared" si="3"/>
         <v>107506</v>
       </c>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M20" s="2">
+        <f t="shared" si="4"/>
+        <v>3.4766188235121902E-3</v>
+      </c>
+      <c r="N20">
+        <f t="shared" si="5"/>
+        <v>100.34766188235122</v>
+      </c>
+      <c r="O20" t="s">
+        <v>99</v>
+      </c>
+      <c r="P20">
+        <v>6424</v>
+      </c>
+      <c r="Q20">
+        <v>273</v>
+      </c>
+      <c r="R20">
+        <v>34</v>
+      </c>
+      <c r="S20">
+        <f t="shared" si="6"/>
+        <v>4667892</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>32</v>
       </c>
@@ -1935,8 +2597,32 @@
         <f t="shared" si="3"/>
         <v>30508</v>
       </c>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M21" s="2">
+        <f t="shared" si="4"/>
+        <v>9.9552565250592348E-3</v>
+      </c>
+      <c r="N21">
+        <f t="shared" si="5"/>
+        <v>100.99552565250592</v>
+      </c>
+      <c r="O21" t="s">
+        <v>98</v>
+      </c>
+      <c r="P21">
+        <v>344</v>
+      </c>
+      <c r="Q21">
+        <v>7</v>
+      </c>
+      <c r="R21">
+        <v>2</v>
+      </c>
+      <c r="S21">
+        <f t="shared" si="6"/>
+        <v>1363926</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>33</v>
       </c>
@@ -1977,8 +2663,32 @@
         <f t="shared" si="3"/>
         <v>395349</v>
       </c>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M22" s="2">
+        <f t="shared" si="4"/>
+        <v>2.1380487671162299E-2</v>
+      </c>
+      <c r="N22">
+        <f t="shared" si="5"/>
+        <v>102.13804876711623</v>
+      </c>
+      <c r="O22" t="s">
+        <v>97</v>
+      </c>
+      <c r="P22">
+        <v>1985</v>
+      </c>
+      <c r="Q22">
+        <v>31</v>
+      </c>
+      <c r="R22">
+        <v>13</v>
+      </c>
+      <c r="S22">
+        <f t="shared" si="6"/>
+        <v>6187263</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>34</v>
       </c>
@@ -2019,8 +2729,32 @@
         <f t="shared" si="3"/>
         <v>473825</v>
       </c>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M23" s="2">
+        <f t="shared" si="4"/>
+        <v>2.0293537140531167E-2</v>
+      </c>
+      <c r="N23">
+        <f t="shared" si="5"/>
+        <v>102.0293537140531</v>
+      </c>
+      <c r="O23" t="s">
+        <v>96</v>
+      </c>
+      <c r="P23">
+        <v>7738</v>
+      </c>
+      <c r="Q23">
+        <v>122</v>
+      </c>
+      <c r="R23">
+        <v>33</v>
+      </c>
+      <c r="S23">
+        <f t="shared" si="6"/>
+        <v>7041207</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>35</v>
       </c>
@@ -2061,8 +2795,32 @@
         <f t="shared" si="3"/>
         <v>172816</v>
       </c>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M24" s="2">
+        <f t="shared" si="4"/>
+        <v>1.1828259614279959E-2</v>
+      </c>
+      <c r="N24">
+        <f t="shared" si="5"/>
+        <v>101.18282596142801</v>
+      </c>
+      <c r="O24" t="s">
+        <v>95</v>
+      </c>
+      <c r="P24">
+        <v>9334</v>
+      </c>
+      <c r="Q24">
+        <v>337</v>
+      </c>
+      <c r="R24">
+        <v>78</v>
+      </c>
+      <c r="S24">
+        <f t="shared" si="6"/>
+        <v>10093776</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>36</v>
       </c>
@@ -2103,8 +2861,32 @@
         <f t="shared" si="3"/>
         <v>394873</v>
       </c>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M25" s="2">
+        <f t="shared" si="4"/>
+        <v>9.2640678254911936E-3</v>
+      </c>
+      <c r="N25">
+        <f t="shared" si="5"/>
+        <v>100.92640678254912</v>
+      </c>
+      <c r="O25" t="s">
+        <v>94</v>
+      </c>
+      <c r="P25">
+        <v>742</v>
+      </c>
+      <c r="Q25">
+        <v>18</v>
+      </c>
+      <c r="R25">
+        <v>1</v>
+      </c>
+      <c r="S25">
+        <f t="shared" si="6"/>
+        <v>5710494</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>37</v>
       </c>
@@ -2145,8 +2927,32 @@
         <f t="shared" si="3"/>
         <v>-14326</v>
       </c>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M26" s="2">
+        <f t="shared" si="4"/>
+        <v>-9.6805094806298806E-4</v>
+      </c>
+      <c r="N26">
+        <f t="shared" si="5"/>
+        <v>99.9031949051937</v>
+      </c>
+      <c r="O26" t="s">
+        <v>93</v>
+      </c>
+      <c r="P26">
+        <v>1177</v>
+      </c>
+      <c r="Q26">
+        <v>26</v>
+      </c>
+      <c r="R26">
+        <v>4</v>
+      </c>
+      <c r="S26">
+        <f t="shared" si="6"/>
+        <v>2965091</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>38</v>
       </c>
@@ -2187,8 +2993,32 @@
         <f t="shared" si="3"/>
         <v>148803</v>
       </c>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M27" s="2">
+        <f t="shared" si="4"/>
+        <v>1.4196426655534509E-3</v>
+      </c>
+      <c r="N27">
+        <f t="shared" si="5"/>
+        <v>100.14196426655535</v>
+      </c>
+      <c r="O27" t="s">
+        <v>92</v>
+      </c>
+      <c r="P27">
+        <v>2819</v>
+      </c>
+      <c r="Q27">
+        <v>18</v>
+      </c>
+      <c r="R27">
+        <v>4</v>
+      </c>
+      <c r="S27">
+        <f t="shared" si="6"/>
+        <v>6163100</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>39</v>
       </c>
@@ -2229,8 +3059,32 @@
         <f t="shared" si="3"/>
         <v>90991</v>
       </c>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M28" s="2">
+        <f t="shared" si="4"/>
+        <v>4.4698341719285163E-3</v>
+      </c>
+      <c r="N28">
+        <f t="shared" si="5"/>
+        <v>100.44698341719285</v>
+      </c>
+      <c r="O28" t="s">
+        <v>91</v>
+      </c>
+      <c r="P28">
+        <v>228</v>
+      </c>
+      <c r="Q28">
+        <v>5</v>
+      </c>
+      <c r="R28">
+        <v>0</v>
+      </c>
+      <c r="S28">
+        <f t="shared" si="6"/>
+        <v>1085635</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>40</v>
       </c>
@@ -2271,8 +3125,32 @@
         <f t="shared" si="3"/>
         <v>131508</v>
       </c>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M29" s="2">
+        <f t="shared" si="4"/>
+        <v>1.330596546570105E-2</v>
+      </c>
+      <c r="N29">
+        <f t="shared" si="5"/>
+        <v>101.33059654657011</v>
+      </c>
+      <c r="O29" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="P29" s="3">
+        <v>214</v>
+      </c>
+      <c r="Q29" s="3">
+        <v>4</v>
+      </c>
+      <c r="R29" s="3">
+        <v>1</v>
+      </c>
+      <c r="S29">
+        <f t="shared" si="6"/>
+        <v>1963547</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>41</v>
       </c>
@@ -2313,8 +3191,32 @@
         <f t="shared" si="3"/>
         <v>399030</v>
       </c>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M30" s="2">
+        <f t="shared" si="4"/>
+        <v>-9.4947548943538438E-3</v>
+      </c>
+      <c r="N30">
+        <f t="shared" si="5"/>
+        <v>99.050524510564614</v>
+      </c>
+      <c r="O30" t="s">
+        <v>89</v>
+      </c>
+      <c r="P30">
+        <v>1279</v>
+      </c>
+      <c r="Q30">
+        <v>32</v>
+      </c>
+      <c r="R30">
+        <v>6</v>
+      </c>
+      <c r="S30">
+        <f t="shared" si="6"/>
+        <v>3109741</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>42</v>
       </c>
@@ -2355,8 +3257,32 @@
         <f t="shared" si="3"/>
         <v>57644</v>
       </c>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M31" s="2">
+        <f t="shared" si="4"/>
+        <v>9.3787853836160371E-3</v>
+      </c>
+      <c r="N31">
+        <f t="shared" si="5"/>
+        <v>100.9378785383616</v>
+      </c>
+      <c r="O31" t="s">
+        <v>88</v>
+      </c>
+      <c r="P31">
+        <v>415</v>
+      </c>
+      <c r="Q31">
+        <v>4</v>
+      </c>
+      <c r="R31">
+        <v>1</v>
+      </c>
+      <c r="S31">
+        <f t="shared" si="6"/>
+        <v>1379504</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>43</v>
       </c>
@@ -2397,8 +3323,32 @@
         <f t="shared" si="3"/>
         <v>486992</v>
       </c>
-    </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M32" s="2">
+        <f t="shared" si="4"/>
+        <v>4.6397746727759967E-2</v>
+      </c>
+      <c r="N32">
+        <f t="shared" si="5"/>
+        <v>104.63977467277599</v>
+      </c>
+      <c r="O32" t="s">
+        <v>87</v>
+      </c>
+      <c r="P32">
+        <v>22255</v>
+      </c>
+      <c r="Q32">
+        <v>355</v>
+      </c>
+      <c r="R32">
+        <v>88</v>
+      </c>
+      <c r="S32">
+        <f t="shared" si="6"/>
+        <v>9316748</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>44</v>
       </c>
@@ -2439,8 +3389,32 @@
         <f t="shared" si="3"/>
         <v>52947</v>
       </c>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M33" s="2">
+        <f t="shared" si="4"/>
+        <v>6.5996651029592386E-3</v>
+      </c>
+      <c r="N33">
+        <f t="shared" si="5"/>
+        <v>100.65996651029592</v>
+      </c>
+      <c r="O33" t="s">
+        <v>86</v>
+      </c>
+      <c r="P33">
+        <v>363</v>
+      </c>
+      <c r="Q33">
+        <v>6</v>
+      </c>
+      <c r="R33">
+        <v>1</v>
+      </c>
+      <c r="S33">
+        <f t="shared" si="6"/>
+        <v>2120583</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>45</v>
       </c>
@@ -2481,8 +3455,32 @@
         <f t="shared" si="3"/>
         <v>794696</v>
       </c>
-    </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M34" s="2">
+        <f t="shared" si="4"/>
+        <v>4.5456129811919009E-2</v>
+      </c>
+      <c r="N34">
+        <f t="shared" si="5"/>
+        <v>104.54561298119189</v>
+      </c>
+      <c r="O34" t="s">
+        <v>85</v>
+      </c>
+      <c r="P34">
+        <v>84735</v>
+      </c>
+      <c r="Q34">
+        <v>1672</v>
+      </c>
+      <c r="R34">
+        <v>365</v>
+      </c>
+      <c r="S34">
+        <f t="shared" si="6"/>
+        <v>20300486</v>
+      </c>
+    </row>
+    <row r="35" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>46</v>
       </c>
@@ -2523,8 +3521,32 @@
         <f t="shared" si="3"/>
         <v>888167</v>
       </c>
-    </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M35" s="2">
+        <f t="shared" si="4"/>
+        <v>-1.3855056347983548E-2</v>
+      </c>
+      <c r="N35">
+        <f t="shared" si="5"/>
+        <v>98.614494365201637</v>
+      </c>
+      <c r="O35" t="s">
+        <v>84</v>
+      </c>
+      <c r="P35">
+        <v>1584</v>
+      </c>
+      <c r="Q35">
+        <v>9</v>
+      </c>
+      <c r="R35">
+        <v>1</v>
+      </c>
+      <c r="S35">
+        <f t="shared" si="6"/>
+        <v>10455532</v>
+      </c>
+    </row>
+    <row r="36" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>47</v>
       </c>
@@ -2565,8 +3587,32 @@
         <f t="shared" si="3"/>
         <v>103797</v>
       </c>
-    </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M36" s="2">
+        <f t="shared" si="4"/>
+        <v>1.8806782619830684E-2</v>
+      </c>
+      <c r="N36">
+        <f t="shared" si="5"/>
+        <v>101.88067826198306</v>
+      </c>
+      <c r="O36" t="s">
+        <v>83</v>
+      </c>
+      <c r="P36">
+        <v>147</v>
+      </c>
+      <c r="Q36">
+        <v>3</v>
+      </c>
+      <c r="R36">
+        <v>0</v>
+      </c>
+      <c r="S36">
+        <f t="shared" si="6"/>
+        <v>779849</v>
+      </c>
+    </row>
+    <row r="37" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>48</v>
       </c>
@@ -2607,8 +3653,32 @@
         <f t="shared" si="3"/>
         <v>240353</v>
       </c>
-    </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M37" s="2">
+        <f t="shared" si="4"/>
+        <v>9.8887243775600854E-3</v>
+      </c>
+      <c r="N37">
+        <f t="shared" si="5"/>
+        <v>100.988872437756</v>
+      </c>
+      <c r="O37" t="s">
+        <v>82</v>
+      </c>
+      <c r="P37">
+        <v>2547</v>
+      </c>
+      <c r="Q37">
+        <v>65</v>
+      </c>
+      <c r="R37">
+        <v>10</v>
+      </c>
+      <c r="S37">
+        <f t="shared" si="6"/>
+        <v>11811395</v>
+      </c>
+    </row>
+    <row r="38" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>49</v>
       </c>
@@ -2649,8 +3719,32 @@
         <f t="shared" si="3"/>
         <v>198634</v>
       </c>
-    </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M38" s="2">
+        <f t="shared" si="4"/>
+        <v>-4.3375888612868377E-3</v>
+      </c>
+      <c r="N38">
+        <f t="shared" si="5"/>
+        <v>99.566241113871314</v>
+      </c>
+      <c r="O38" t="s">
+        <v>81</v>
+      </c>
+      <c r="P38">
+        <v>1744</v>
+      </c>
+      <c r="Q38">
+        <v>36</v>
+      </c>
+      <c r="R38">
+        <v>5</v>
+      </c>
+      <c r="S38">
+        <f t="shared" si="6"/>
+        <v>3965260</v>
+      </c>
+    </row>
+    <row r="39" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>50</v>
       </c>
@@ -2691,8 +3785,32 @@
         <f t="shared" si="3"/>
         <v>392894</v>
       </c>
-    </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M39" s="2">
+        <f t="shared" si="4"/>
+        <v>-1.6503568189325161E-6</v>
+      </c>
+      <c r="N39">
+        <f t="shared" si="5"/>
+        <v>99.999834964318097</v>
+      </c>
+      <c r="O39" t="s">
+        <v>80</v>
+      </c>
+      <c r="P39">
+        <v>736</v>
+      </c>
+      <c r="Q39">
+        <v>18</v>
+      </c>
+      <c r="R39">
+        <v>0</v>
+      </c>
+      <c r="S39">
+        <f t="shared" si="6"/>
+        <v>4242236</v>
+      </c>
+    </row>
+    <row r="40" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>51</v>
       </c>
@@ -2733,8 +3851,32 @@
         <f t="shared" si="3"/>
         <v>276939</v>
       </c>
-    </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M40" s="2">
+        <f t="shared" si="4"/>
+        <v>1.7881988420162816E-2</v>
+      </c>
+      <c r="N40">
+        <f t="shared" si="5"/>
+        <v>101.78819884201629</v>
+      </c>
+      <c r="O40" t="s">
+        <v>79</v>
+      </c>
+      <c r="P40">
+        <v>5805</v>
+      </c>
+      <c r="Q40">
+        <v>74</v>
+      </c>
+      <c r="R40">
+        <v>11</v>
+      </c>
+      <c r="S40">
+        <f t="shared" si="6"/>
+        <v>13017649</v>
+      </c>
+    </row>
+    <row r="41" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>52</v>
       </c>
@@ -2775,8 +3917,32 @@
         <f t="shared" si="3"/>
         <v>42916</v>
       </c>
-    </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M41" s="2">
+        <f t="shared" si="4"/>
+        <v>3.8820385479484451E-2</v>
+      </c>
+      <c r="N41">
+        <f t="shared" si="5"/>
+        <v>103.88203854794844</v>
+      </c>
+      <c r="O41" t="s">
+        <v>78</v>
+      </c>
+      <c r="P41">
+        <v>682</v>
+      </c>
+      <c r="Q41">
+        <v>12</v>
+      </c>
+      <c r="R41">
+        <v>1</v>
+      </c>
+      <c r="S41">
+        <f t="shared" si="6"/>
+        <v>1098845</v>
+      </c>
+    </row>
+    <row r="42" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>53</v>
       </c>
@@ -2817,8 +3983,32 @@
         <f t="shared" si="3"/>
         <v>478737</v>
       </c>
-    </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M42" s="2">
+        <f t="shared" si="4"/>
+        <v>-1.7885642885067957E-2</v>
+      </c>
+      <c r="N42">
+        <f t="shared" si="5"/>
+        <v>98.211435711493195</v>
+      </c>
+      <c r="O42" t="s">
+        <v>77</v>
+      </c>
+      <c r="P42">
+        <v>1349</v>
+      </c>
+      <c r="Q42">
+        <v>32</v>
+      </c>
+      <c r="R42">
+        <v>2</v>
+      </c>
+      <c r="S42">
+        <f t="shared" si="6"/>
+        <v>5126061</v>
+      </c>
+    </row>
+    <row r="43" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>54</v>
       </c>
@@ -2859,8 +4049,32 @@
         <f t="shared" si="3"/>
         <v>68009</v>
       </c>
-    </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M43" s="2">
+        <f t="shared" si="4"/>
+        <v>-5.5415097953774826E-3</v>
+      </c>
+      <c r="N43">
+        <f t="shared" si="5"/>
+        <v>99.445849020462248</v>
+      </c>
+      <c r="O43" t="s">
+        <v>76</v>
+      </c>
+      <c r="P43">
+        <v>129</v>
+      </c>
+      <c r="Q43">
+        <v>2</v>
+      </c>
+      <c r="R43">
+        <v>1</v>
+      </c>
+      <c r="S43">
+        <f t="shared" si="6"/>
+        <v>887899</v>
+      </c>
+    </row>
+    <row r="44" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>55</v>
       </c>
@@ -2901,8 +4115,32 @@
         <f t="shared" si="3"/>
         <v>541466</v>
       </c>
-    </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M44" s="2">
+        <f t="shared" si="4"/>
+        <v>4.3652859935349106E-3</v>
+      </c>
+      <c r="N44">
+        <f t="shared" si="5"/>
+        <v>100.43652859935348</v>
+      </c>
+      <c r="O44" t="s">
+        <v>75</v>
+      </c>
+      <c r="P44">
+        <v>2240</v>
+      </c>
+      <c r="Q44">
+        <v>23</v>
+      </c>
+      <c r="R44">
+        <v>0</v>
+      </c>
+      <c r="S44">
+        <f t="shared" si="6"/>
+        <v>6919137</v>
+      </c>
+    </row>
+    <row r="45" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>56</v>
       </c>
@@ -2943,8 +4181,32 @@
         <f t="shared" si="3"/>
         <v>3914872</v>
       </c>
-    </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M45" s="2">
+        <f t="shared" si="4"/>
+        <v>-6.0444282111371851E-3</v>
+      </c>
+      <c r="N45">
+        <f t="shared" si="5"/>
+        <v>99.395557178886278</v>
+      </c>
+      <c r="O45" t="s">
+        <v>74</v>
+      </c>
+      <c r="P45">
+        <v>3996</v>
+      </c>
+      <c r="Q45">
+        <v>122</v>
+      </c>
+      <c r="R45">
+        <v>21</v>
+      </c>
+      <c r="S45">
+        <f t="shared" si="6"/>
+        <v>29187286</v>
+      </c>
+    </row>
+    <row r="46" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>57</v>
       </c>
@@ -2985,8 +4247,32 @@
         <f t="shared" si="3"/>
         <v>504487</v>
       </c>
-    </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M46" s="2">
+        <f t="shared" si="4"/>
+        <v>7.8073675973782406E-3</v>
+      </c>
+      <c r="N46">
+        <f t="shared" si="5"/>
+        <v>100.78073675973782</v>
+      </c>
+      <c r="O46" t="s">
+        <v>73</v>
+      </c>
+      <c r="P46">
+        <v>1012</v>
+      </c>
+      <c r="Q46">
+        <v>7</v>
+      </c>
+      <c r="R46">
+        <v>2</v>
+      </c>
+      <c r="S46">
+        <f t="shared" si="6"/>
+        <v>3276264</v>
+      </c>
+    </row>
+    <row r="47" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>58</v>
       </c>
@@ -3027,8 +4313,32 @@
         <f t="shared" si="3"/>
         <v>13166</v>
       </c>
-    </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M47" s="2">
+        <f t="shared" si="4"/>
+        <v>3.233511992517811E-2</v>
+      </c>
+      <c r="N47">
+        <f t="shared" si="5"/>
+        <v>103.2335119925178</v>
+      </c>
+      <c r="O47" t="s">
+        <v>72</v>
+      </c>
+      <c r="P47">
+        <v>1706</v>
+      </c>
+      <c r="Q47">
+        <v>41</v>
+      </c>
+      <c r="R47">
+        <v>7</v>
+      </c>
+      <c r="S47">
+        <f t="shared" si="6"/>
+        <v>645209</v>
+      </c>
+    </row>
+    <row r="48" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>59</v>
       </c>
@@ -3069,8 +4379,32 @@
         <f t="shared" si="3"/>
         <v>616806</v>
       </c>
-    </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M48" s="2">
+        <f t="shared" si="4"/>
+        <v>7.4475910368156312E-3</v>
+      </c>
+      <c r="N48">
+        <f t="shared" si="5"/>
+        <v>100.74475910368157</v>
+      </c>
+      <c r="O48" t="s">
+        <v>71</v>
+      </c>
+      <c r="P48">
+        <v>321</v>
+      </c>
+      <c r="Q48">
+        <v>16</v>
+      </c>
+      <c r="R48">
+        <v>3</v>
+      </c>
+      <c r="S48">
+        <f t="shared" si="6"/>
+        <v>8654863</v>
+      </c>
+    </row>
+    <row r="49" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>60</v>
       </c>
@@ -3111,8 +4445,32 @@
         <f t="shared" si="3"/>
         <v>962577</v>
       </c>
-    </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M49" s="2">
+        <f t="shared" si="4"/>
+        <v>2.9029277795656967E-3</v>
+      </c>
+      <c r="N49">
+        <f t="shared" si="5"/>
+        <v>100.29029277795658</v>
+      </c>
+      <c r="O49" t="s">
+        <v>70</v>
+      </c>
+      <c r="P49">
+        <v>5319</v>
+      </c>
+      <c r="Q49">
+        <v>246</v>
+      </c>
+      <c r="R49">
+        <v>51</v>
+      </c>
+      <c r="S49">
+        <f t="shared" si="6"/>
+        <v>7721265</v>
+      </c>
+    </row>
+    <row r="50" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>61</v>
       </c>
@@ -3153,8 +4511,32 @@
         <f t="shared" si="3"/>
         <v>-64770</v>
       </c>
-    </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M50" s="2">
+        <f t="shared" si="4"/>
+        <v>5.7474645433880905E-3</v>
+      </c>
+      <c r="N50">
+        <f t="shared" si="5"/>
+        <v>100.57474645433882</v>
+      </c>
+      <c r="O50" t="s">
+        <v>69</v>
+      </c>
+      <c r="P50">
+        <v>191</v>
+      </c>
+      <c r="Q50">
+        <v>2</v>
+      </c>
+      <c r="R50">
+        <v>1</v>
+      </c>
+      <c r="S50">
+        <f t="shared" si="6"/>
+        <v>1795236</v>
+      </c>
+    </row>
+    <row r="51" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>62</v>
       </c>
@@ -3195,8 +4577,32 @@
         <f t="shared" si="3"/>
         <v>199243</v>
       </c>
-    </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M51" s="2">
+        <f t="shared" si="4"/>
+        <v>1.1112949420118283E-2</v>
+      </c>
+      <c r="N51">
+        <f t="shared" si="5"/>
+        <v>101.11129494201182</v>
+      </c>
+      <c r="O51" t="s">
+        <v>68</v>
+      </c>
+      <c r="P51">
+        <v>1550</v>
+      </c>
+      <c r="Q51">
+        <v>24</v>
+      </c>
+      <c r="R51">
+        <v>8</v>
+      </c>
+      <c r="S51">
+        <f t="shared" si="6"/>
+        <v>5899023</v>
+      </c>
+    </row>
+    <row r="52" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>63</v>
       </c>
@@ -3236,6 +4642,30 @@
       <c r="L52">
         <f t="shared" si="3"/>
         <v>9419</v>
+      </c>
+      <c r="M52" s="2">
+        <f t="shared" si="4"/>
+        <v>-7.914783421027324E-3</v>
+      </c>
+      <c r="N52">
+        <f t="shared" si="5"/>
+        <v>99.208521657897265</v>
+      </c>
+      <c r="O52" t="s">
+        <v>67</v>
+      </c>
+      <c r="P52">
+        <v>137</v>
+      </c>
+      <c r="Q52">
+        <v>0</v>
+      </c>
+      <c r="R52">
+        <v>0</v>
+      </c>
+      <c r="S52">
+        <f t="shared" si="6"/>
+        <v>577856</v>
       </c>
     </row>
   </sheetData>

--- a/apportion/pop.xlsx
+++ b/apportion/pop.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/user/Google Drive/GitHub/R Functions/apportion/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{7AD16E79-4AA1-3947-9E00-8B25696DE3CB}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12F7B794-1EFF-7346-A4B0-7922CC83E623}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38400" yWindow="500" windowWidth="38400" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="124">
   <si>
     <t>state</t>
   </si>
@@ -389,6 +389,9 @@
   </si>
   <si>
     <t>covid_effect</t>
+  </si>
+  <si>
+    <t>popchange_per</t>
   </si>
 </sst>
 </file>
@@ -1241,10 +1244,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S52"/>
+  <dimension ref="A1:T52"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1282,28 +1285,31 @@
         <v>10</v>
       </c>
       <c r="M1" t="s">
+        <v>123</v>
+      </c>
+      <c r="N1" t="s">
         <v>65</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>66</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>121</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>120</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>119</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>118</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -1344,32 +1350,36 @@
         <f>E2-B2</f>
         <v>227071</v>
       </c>
-      <c r="M2" s="2">
+      <c r="M2">
+        <f>L2/B2*100</f>
+        <v>4.7277087442759518</v>
+      </c>
+      <c r="N2" s="2">
         <f>(E2-D2)/D2</f>
         <v>2.2050247768377815E-2</v>
       </c>
-      <c r="N2">
+      <c r="O2">
         <f>E2/D2*100</f>
         <v>102.20502477683777</v>
       </c>
-      <c r="O2" t="s">
+      <c r="P2" t="s">
         <v>117</v>
       </c>
-      <c r="P2">
+      <c r="Q2">
         <v>143</v>
       </c>
-      <c r="Q2">
+      <c r="R2">
         <v>3</v>
       </c>
-      <c r="R2">
-        <v>0</v>
-      </c>
       <c r="S2">
-        <f>P2+E2</f>
+        <v>0</v>
+      </c>
+      <c r="T2">
+        <f>Q2+E2</f>
         <v>5030196</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -1410,32 +1420,36 @@
         <f t="shared" ref="L3:L52" si="3">E3-B3</f>
         <v>14558</v>
       </c>
-      <c r="M3" s="2">
-        <f t="shared" ref="M3:M52" si="4">(E3-D3)/D3</f>
+      <c r="M3">
+        <f t="shared" ref="M3:M52" si="4">L3/B3*100</f>
+        <v>2.0176764981850894</v>
+      </c>
+      <c r="N3" s="2">
+        <f t="shared" ref="N3:N52" si="5">(E3-D3)/D3</f>
         <v>6.7331548037496683E-3</v>
       </c>
-      <c r="N3">
-        <f t="shared" ref="N3:N52" si="5">E3/D3*100</f>
+      <c r="O3">
+        <f t="shared" ref="O3:O52" si="6">E3/D3*100</f>
         <v>100.67331548037497</v>
       </c>
-      <c r="O3" t="s">
+      <c r="P3" t="s">
         <v>116</v>
       </c>
-      <c r="P3">
+      <c r="Q3">
         <v>1106</v>
       </c>
-      <c r="Q3">
+      <c r="R3">
         <v>17</v>
       </c>
-      <c r="R3">
+      <c r="S3">
         <v>4</v>
       </c>
-      <c r="S3">
-        <f t="shared" ref="S3:S52" si="6">P3+E3</f>
+      <c r="T3">
+        <f t="shared" ref="T3:T52" si="7">Q3+E3</f>
         <v>737187</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -1476,32 +1490,36 @@
         <f t="shared" si="3"/>
         <v>746223</v>
       </c>
-      <c r="M4" s="2">
+      <c r="M4">
         <f t="shared" si="4"/>
+        <v>11.636642911722053</v>
+      </c>
+      <c r="N4" s="2">
+        <f t="shared" si="5"/>
         <v>-3.5367715610570026E-2</v>
       </c>
-      <c r="N4">
-        <f t="shared" si="5"/>
+      <c r="O4">
+        <f t="shared" si="6"/>
         <v>96.463228438942991</v>
       </c>
-      <c r="O4" t="s">
+      <c r="P4" t="s">
         <v>115</v>
       </c>
-      <c r="P4">
+      <c r="Q4">
         <v>1413</v>
       </c>
-      <c r="Q4">
+      <c r="R4">
         <v>29</v>
       </c>
-      <c r="R4">
+      <c r="S4">
         <v>5</v>
       </c>
-      <c r="S4">
-        <f t="shared" si="6"/>
+      <c r="T4">
+        <f t="shared" si="7"/>
         <v>7160336</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -1542,32 +1560,36 @@
         <f t="shared" si="3"/>
         <v>87527</v>
       </c>
-      <c r="M5" s="2">
+      <c r="M5">
         <f t="shared" si="4"/>
+        <v>2.9911192869730976</v>
+      </c>
+      <c r="N5" s="2">
+        <f t="shared" si="5"/>
         <v>-5.5323802302045654E-3</v>
       </c>
-      <c r="N5">
-        <f t="shared" si="5"/>
+      <c r="O5">
+        <f t="shared" si="6"/>
         <v>99.446761976979545</v>
       </c>
-      <c r="O5" t="s">
+      <c r="P5" t="s">
         <v>114</v>
       </c>
-      <c r="P5">
+      <c r="Q5">
         <v>614</v>
       </c>
-      <c r="Q5">
+      <c r="R5">
         <v>10</v>
       </c>
-      <c r="R5">
+      <c r="S5">
         <v>2</v>
       </c>
-      <c r="S5">
-        <f t="shared" si="6"/>
+      <c r="T5">
+        <f t="shared" si="7"/>
         <v>3014370</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -1608,32 +1630,36 @@
         <f t="shared" si="3"/>
         <v>2234768</v>
       </c>
-      <c r="M6" s="2">
+      <c r="M6">
         <f t="shared" si="4"/>
+        <v>5.9845981958807819</v>
+      </c>
+      <c r="N6" s="2">
+        <f t="shared" si="5"/>
         <v>5.3007159760250422E-3</v>
       </c>
-      <c r="N6">
-        <f t="shared" si="5"/>
+      <c r="O6">
+        <f t="shared" si="6"/>
         <v>100.5300715976025</v>
       </c>
-      <c r="O6" t="s">
+      <c r="P6" t="s">
         <v>113</v>
       </c>
-      <c r="P6">
+      <c r="Q6">
         <v>8155</v>
       </c>
-      <c r="Q6">
+      <c r="R6">
         <v>172</v>
       </c>
-      <c r="R6">
-        <v>0</v>
-      </c>
       <c r="S6">
-        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="T6">
+        <f t="shared" si="7"/>
         <v>39584912</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -1674,32 +1700,36 @@
         <f t="shared" si="3"/>
         <v>737241</v>
       </c>
-      <c r="M7" s="2">
+      <c r="M7">
         <f t="shared" si="4"/>
+        <v>14.613503061489455</v>
+      </c>
+      <c r="N7" s="2">
+        <f t="shared" si="5"/>
         <v>-4.3989731596862725E-3</v>
       </c>
-      <c r="N7">
-        <f t="shared" si="5"/>
+      <c r="O7">
+        <f t="shared" si="6"/>
         <v>99.560102684031364</v>
       </c>
-      <c r="O7" t="s">
+      <c r="P7" t="s">
         <v>112</v>
       </c>
-      <c r="P7">
+      <c r="Q7">
         <v>3342</v>
       </c>
-      <c r="Q7">
+      <c r="R7">
         <v>80</v>
       </c>
-      <c r="R7">
+      <c r="S7">
         <v>11</v>
       </c>
-      <c r="S7">
-        <f t="shared" si="6"/>
+      <c r="T7">
+        <f t="shared" si="7"/>
         <v>5785513</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>19</v>
       </c>
@@ -1740,32 +1770,36 @@
         <f t="shared" si="3"/>
         <v>26670</v>
       </c>
-      <c r="M8" s="2">
+      <c r="M8">
         <f t="shared" si="4"/>
+        <v>0.74463344601951964</v>
+      </c>
+      <c r="N8" s="2">
+        <f t="shared" si="5"/>
         <v>1.4419992544291464E-2</v>
       </c>
-      <c r="N8">
-        <f t="shared" si="5"/>
+      <c r="O8">
+        <f t="shared" si="6"/>
         <v>101.44199925442913</v>
       </c>
-      <c r="O8" t="s">
+      <c r="P8" t="s">
         <v>111</v>
       </c>
-      <c r="P8">
+      <c r="Q8">
         <v>3557</v>
       </c>
-      <c r="Q8">
+      <c r="R8">
         <v>85</v>
       </c>
-      <c r="R8">
+      <c r="S8">
         <v>16</v>
       </c>
-      <c r="S8">
-        <f t="shared" si="6"/>
+      <c r="T8">
+        <f t="shared" si="7"/>
         <v>3611855</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>20</v>
       </c>
@@ -1806,32 +1840,36 @@
         <f t="shared" si="3"/>
         <v>89960</v>
       </c>
-      <c r="M9" s="2">
+      <c r="M9">
         <f t="shared" si="4"/>
+        <v>9.9858249239352332</v>
+      </c>
+      <c r="N9" s="2">
+        <f t="shared" si="5"/>
         <v>4.0818435989132653E-3</v>
       </c>
-      <c r="N9">
-        <f t="shared" si="5"/>
+      <c r="O9">
+        <f t="shared" si="6"/>
         <v>100.40818435989132</v>
       </c>
-      <c r="O9" t="s">
+      <c r="P9" t="s">
         <v>110</v>
       </c>
-      <c r="P9">
+      <c r="Q9">
         <v>368</v>
       </c>
-      <c r="Q9">
+      <c r="R9">
         <v>11</v>
       </c>
-      <c r="R9">
+      <c r="S9">
         <v>1</v>
       </c>
-      <c r="S9">
-        <f t="shared" si="6"/>
+      <c r="T9">
+        <f t="shared" si="7"/>
         <v>991205</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>21</v>
       </c>
@@ -1871,32 +1909,36 @@
         <f t="shared" si="3"/>
         <v>89810</v>
       </c>
-      <c r="M10" s="2">
+      <c r="M10">
         <f t="shared" si="4"/>
+        <v>14.925472351896138</v>
+      </c>
+      <c r="N10" s="2">
+        <f t="shared" si="5"/>
         <v>-2.9857635069919865E-2</v>
       </c>
-      <c r="N10">
-        <f t="shared" si="5"/>
+      <c r="O10">
+        <f t="shared" si="6"/>
         <v>97.014236493008013</v>
       </c>
-      <c r="O10" t="s">
+      <c r="P10" t="s">
         <v>109</v>
       </c>
-      <c r="P10">
+      <c r="Q10">
         <v>586</v>
       </c>
-      <c r="Q10">
+      <c r="R10">
         <v>11</v>
       </c>
-      <c r="R10">
+      <c r="S10">
         <v>2</v>
       </c>
-      <c r="S10">
-        <f t="shared" si="6"/>
+      <c r="T10">
+        <f t="shared" si="7"/>
         <v>692119</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>22</v>
       </c>
@@ -1937,32 +1979,36 @@
         <f t="shared" si="3"/>
         <v>2669754</v>
       </c>
-      <c r="M11" s="2">
+      <c r="M11">
         <f t="shared" si="4"/>
+        <v>14.12510483036858</v>
+      </c>
+      <c r="N11" s="2">
+        <f t="shared" si="5"/>
         <v>-7.4901147142230323E-3</v>
       </c>
-      <c r="N11">
-        <f t="shared" si="5"/>
+      <c r="O11">
+        <f t="shared" si="6"/>
         <v>99.250988528577693</v>
       </c>
-      <c r="O11" t="s">
+      <c r="P11" t="s">
         <v>108</v>
       </c>
-      <c r="P11">
+      <c r="Q11">
         <v>7495</v>
       </c>
-      <c r="Q11">
+      <c r="R11">
         <v>101</v>
       </c>
-      <c r="R11">
+      <c r="S11">
         <v>16</v>
       </c>
-      <c r="S11">
-        <f t="shared" si="6"/>
+      <c r="T11">
+        <f t="shared" si="7"/>
         <v>21578022</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>23</v>
       </c>
@@ -2003,32 +2049,36 @@
         <f t="shared" si="3"/>
         <v>997708</v>
       </c>
-      <c r="M12" s="2">
+      <c r="M12">
         <f t="shared" si="4"/>
+        <v>10.256501986211145</v>
+      </c>
+      <c r="N12" s="2">
+        <f t="shared" si="5"/>
         <v>1.4245542280651841E-3</v>
       </c>
-      <c r="N12">
-        <f t="shared" si="5"/>
+      <c r="O12">
+        <f t="shared" si="6"/>
         <v>100.14245542280651</v>
       </c>
-      <c r="O12" t="s">
+      <c r="P12" t="s">
         <v>107</v>
       </c>
-      <c r="P12">
+      <c r="Q12">
         <v>4806</v>
       </c>
-      <c r="Q12">
+      <c r="R12">
         <v>154</v>
       </c>
-      <c r="R12">
+      <c r="S12">
         <v>24</v>
       </c>
-      <c r="S12">
-        <f t="shared" si="6"/>
+      <c r="T12">
+        <f t="shared" si="7"/>
         <v>10730080</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>24</v>
       </c>
@@ -2069,32 +2119,36 @@
         <f t="shared" si="3"/>
         <v>93275</v>
       </c>
-      <c r="M13" s="2">
+      <c r="M13">
         <f t="shared" si="4"/>
+        <v>6.8240246637919553</v>
+      </c>
+      <c r="N13" s="2">
+        <f t="shared" si="5"/>
         <v>3.7761743731014652E-2</v>
       </c>
-      <c r="N13">
-        <f t="shared" si="5"/>
+      <c r="O13">
+        <f t="shared" si="6"/>
         <v>103.77617437310147</v>
       </c>
-      <c r="O13" t="s">
+      <c r="P13" t="s">
         <v>106</v>
       </c>
-      <c r="P13">
+      <c r="Q13">
         <v>311</v>
       </c>
-      <c r="Q13">
+      <c r="R13">
         <v>1</v>
       </c>
-      <c r="R13">
-        <v>0</v>
-      </c>
       <c r="S13">
-        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="T13">
+        <f t="shared" si="7"/>
         <v>1460448</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>25</v>
       </c>
@@ -2135,32 +2189,36 @@
         <f t="shared" si="3"/>
         <v>267878</v>
       </c>
-      <c r="M14" s="2">
+      <c r="M14">
         <f t="shared" si="4"/>
+        <v>17.024351461297403</v>
+      </c>
+      <c r="N14" s="2">
+        <f t="shared" si="5"/>
         <v>7.9171805116061908E-3</v>
       </c>
-      <c r="N14">
-        <f t="shared" si="5"/>
+      <c r="O14">
+        <f t="shared" si="6"/>
         <v>100.79171805116063</v>
       </c>
-      <c r="O14" t="s">
+      <c r="P14" t="s">
         <v>105</v>
       </c>
-      <c r="P14">
+      <c r="Q14">
         <v>669</v>
       </c>
-      <c r="Q14">
+      <c r="R14">
         <v>9</v>
       </c>
-      <c r="R14">
-        <v>0</v>
-      </c>
       <c r="S14">
-        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="T14">
+        <f t="shared" si="7"/>
         <v>1842046</v>
       </c>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>26</v>
       </c>
@@ -2201,32 +2259,36 @@
         <f t="shared" si="3"/>
         <v>-41641</v>
       </c>
-      <c r="M15" s="2">
+      <c r="M15">
         <f t="shared" si="4"/>
+        <v>-0.32369224167818428</v>
+      </c>
+      <c r="N15" s="2">
+        <f t="shared" si="5"/>
         <v>1.8685874035652746E-2</v>
       </c>
-      <c r="N15">
-        <f t="shared" si="5"/>
+      <c r="O15">
+        <f t="shared" si="6"/>
         <v>101.86858740356529</v>
       </c>
-      <c r="O15" t="s">
+      <c r="P15" t="s">
         <v>104</v>
       </c>
-      <c r="P15">
+      <c r="Q15">
         <v>6980</v>
       </c>
-      <c r="Q15">
+      <c r="R15">
         <v>141</v>
       </c>
-      <c r="R15">
+      <c r="S15">
         <v>42</v>
       </c>
-      <c r="S15">
-        <f t="shared" si="6"/>
+      <c r="T15">
+        <f t="shared" si="7"/>
         <v>12829719</v>
       </c>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>27</v>
       </c>
@@ -2267,32 +2329,36 @@
         <f t="shared" si="3"/>
         <v>288698</v>
       </c>
-      <c r="M16" s="2">
+      <c r="M16">
         <f t="shared" si="4"/>
+        <v>4.4404269606997193</v>
+      </c>
+      <c r="N16" s="2">
+        <f t="shared" si="5"/>
         <v>5.2297921243863576E-3</v>
       </c>
-      <c r="N16">
-        <f t="shared" si="5"/>
+      <c r="O16">
+        <f t="shared" si="6"/>
         <v>100.52297921243864</v>
       </c>
-      <c r="O16" t="s">
+      <c r="P16" t="s">
         <v>103</v>
       </c>
-      <c r="P16">
+      <c r="Q16">
         <v>2565</v>
       </c>
-      <c r="Q16">
+      <c r="R16">
         <v>65</v>
       </c>
-      <c r="R16">
+      <c r="S16">
         <v>16</v>
       </c>
-      <c r="S16">
-        <f t="shared" si="6"/>
+      <c r="T16">
+        <f t="shared" si="7"/>
         <v>6792845</v>
       </c>
     </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>28</v>
       </c>
@@ -2333,32 +2399,36 @@
         <f t="shared" si="3"/>
         <v>138619</v>
       </c>
-      <c r="M17" s="2">
+      <c r="M17">
         <f t="shared" si="4"/>
+        <v>4.5392491355814926</v>
+      </c>
+      <c r="N17" s="2">
+        <f t="shared" si="5"/>
         <v>9.1178896186923531E-3</v>
       </c>
-      <c r="N17">
-        <f t="shared" si="5"/>
+      <c r="O17">
+        <f t="shared" si="6"/>
         <v>100.91178896186923</v>
       </c>
-      <c r="O17" t="s">
+      <c r="P17" t="s">
         <v>102</v>
       </c>
-      <c r="P17">
+      <c r="Q17">
         <v>549</v>
       </c>
-      <c r="Q17">
+      <c r="R17">
         <v>9</v>
       </c>
-      <c r="R17">
+      <c r="S17">
         <v>2</v>
       </c>
-      <c r="S17">
-        <f t="shared" si="6"/>
+      <c r="T17">
+        <f t="shared" si="7"/>
         <v>3192955</v>
       </c>
     </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>29</v>
       </c>
@@ -2399,32 +2469,36 @@
         <f t="shared" si="3"/>
         <v>77052</v>
       </c>
-      <c r="M18" s="2">
+      <c r="M18">
         <f t="shared" si="4"/>
+        <v>2.6905388026383008</v>
+      </c>
+      <c r="N18" s="2">
+        <f t="shared" si="5"/>
         <v>9.2868259886986267E-3</v>
       </c>
-      <c r="N18">
-        <f t="shared" si="5"/>
+      <c r="O18">
+        <f t="shared" si="6"/>
         <v>100.92868259886987</v>
       </c>
-      <c r="O18" t="s">
+      <c r="P18" t="s">
         <v>101</v>
       </c>
-      <c r="P18">
+      <c r="Q18">
         <v>482</v>
       </c>
-      <c r="Q18">
+      <c r="R18">
         <v>10</v>
       </c>
-      <c r="R18">
+      <c r="S18">
         <v>1</v>
       </c>
-      <c r="S18">
-        <f t="shared" si="6"/>
+      <c r="T18">
+        <f t="shared" si="7"/>
         <v>2941347</v>
       </c>
     </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>30</v>
       </c>
@@ -2465,32 +2539,36 @@
         <f t="shared" si="3"/>
         <v>158736</v>
       </c>
-      <c r="M19" s="2">
+      <c r="M19">
         <f t="shared" si="4"/>
+        <v>3.6485951612258156</v>
+      </c>
+      <c r="N19" s="2">
+        <f t="shared" si="5"/>
         <v>7.1675677776385557E-3</v>
       </c>
-      <c r="N19">
-        <f t="shared" si="5"/>
+      <c r="O19">
+        <f t="shared" si="6"/>
         <v>100.71675677776386</v>
       </c>
-      <c r="O19" t="s">
+      <c r="P19" t="s">
         <v>100</v>
       </c>
-      <c r="P19">
+      <c r="Q19">
         <v>680</v>
       </c>
-      <c r="Q19">
+      <c r="R19">
         <v>20</v>
       </c>
-      <c r="R19">
+      <c r="S19">
         <v>2</v>
       </c>
-      <c r="S19">
-        <f t="shared" si="6"/>
+      <c r="T19">
+        <f t="shared" si="7"/>
         <v>4510022</v>
       </c>
     </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>31</v>
       </c>
@@ -2531,32 +2609,36 @@
         <f t="shared" si="3"/>
         <v>107506</v>
       </c>
-      <c r="M20" s="2">
+      <c r="M20">
         <f t="shared" si="4"/>
+        <v>2.3607135940089092</v>
+      </c>
+      <c r="N20" s="2">
+        <f t="shared" si="5"/>
         <v>3.4766188235121902E-3</v>
       </c>
-      <c r="N20">
-        <f t="shared" si="5"/>
+      <c r="O20">
+        <f t="shared" si="6"/>
         <v>100.34766188235122</v>
       </c>
-      <c r="O20" t="s">
+      <c r="P20" t="s">
         <v>99</v>
       </c>
-      <c r="P20">
+      <c r="Q20">
         <v>6424</v>
       </c>
-      <c r="Q20">
+      <c r="R20">
         <v>273</v>
       </c>
-      <c r="R20">
+      <c r="S20">
         <v>34</v>
       </c>
-      <c r="S20">
-        <f t="shared" si="6"/>
+      <c r="T20">
+        <f t="shared" si="7"/>
         <v>4667892</v>
       </c>
     </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>32</v>
       </c>
@@ -2597,32 +2679,36 @@
         <f t="shared" si="3"/>
         <v>30508</v>
       </c>
-      <c r="M21" s="2">
+      <c r="M21">
         <f t="shared" si="4"/>
+        <v>2.2885451220262341</v>
+      </c>
+      <c r="N21" s="2">
+        <f t="shared" si="5"/>
         <v>9.9552565250592348E-3</v>
       </c>
-      <c r="N21">
-        <f t="shared" si="5"/>
+      <c r="O21">
+        <f t="shared" si="6"/>
         <v>100.99552565250592</v>
       </c>
-      <c r="O21" t="s">
+      <c r="P21" t="s">
         <v>98</v>
       </c>
-      <c r="P21">
+      <c r="Q21">
         <v>344</v>
       </c>
-      <c r="Q21">
+      <c r="R21">
         <v>7</v>
       </c>
-      <c r="R21">
+      <c r="S21">
         <v>2</v>
       </c>
-      <c r="S21">
-        <f t="shared" si="6"/>
+      <c r="T21">
+        <f t="shared" si="7"/>
         <v>1363926</v>
       </c>
     </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>33</v>
       </c>
@@ -2663,32 +2749,36 @@
         <f t="shared" si="3"/>
         <v>395349</v>
       </c>
-      <c r="M22" s="2">
+      <c r="M22">
         <f t="shared" si="4"/>
+        <v>6.8282184462020172</v>
+      </c>
+      <c r="N22" s="2">
+        <f t="shared" si="5"/>
         <v>2.1380487671162299E-2</v>
       </c>
-      <c r="N22">
-        <f t="shared" si="5"/>
+      <c r="O22">
+        <f t="shared" si="6"/>
         <v>102.13804876711623</v>
       </c>
-      <c r="O22" t="s">
+      <c r="P22" t="s">
         <v>97</v>
       </c>
-      <c r="P22">
+      <c r="Q22">
         <v>1985</v>
       </c>
-      <c r="Q22">
+      <c r="R22">
         <v>31</v>
       </c>
-      <c r="R22">
+      <c r="S22">
         <v>13</v>
       </c>
-      <c r="S22">
-        <f t="shared" si="6"/>
+      <c r="T22">
+        <f t="shared" si="7"/>
         <v>6187263</v>
       </c>
     </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>34</v>
       </c>
@@ -2729,32 +2819,36 @@
         <f t="shared" si="3"/>
         <v>473825</v>
       </c>
-      <c r="M23" s="2">
+      <c r="M23">
         <f t="shared" si="4"/>
+        <v>7.223334071178253</v>
+      </c>
+      <c r="N23" s="2">
+        <f t="shared" si="5"/>
         <v>2.0293537140531167E-2</v>
       </c>
-      <c r="N23">
-        <f t="shared" si="5"/>
+      <c r="O23">
+        <f t="shared" si="6"/>
         <v>102.0293537140531</v>
       </c>
-      <c r="O23" t="s">
+      <c r="P23" t="s">
         <v>96</v>
       </c>
-      <c r="P23">
+      <c r="Q23">
         <v>7738</v>
       </c>
-      <c r="Q23">
+      <c r="R23">
         <v>122</v>
       </c>
-      <c r="R23">
+      <c r="S23">
         <v>33</v>
       </c>
-      <c r="S23">
-        <f t="shared" si="6"/>
+      <c r="T23">
+        <f t="shared" si="7"/>
         <v>7041207</v>
       </c>
     </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>35</v>
       </c>
@@ -2795,32 +2889,36 @@
         <f t="shared" si="3"/>
         <v>172816</v>
       </c>
-      <c r="M24" s="2">
+      <c r="M24">
         <f t="shared" si="4"/>
+        <v>1.743568613262849</v>
+      </c>
+      <c r="N24" s="2">
+        <f t="shared" si="5"/>
         <v>1.1828259614279959E-2</v>
       </c>
-      <c r="N24">
-        <f t="shared" si="5"/>
+      <c r="O24">
+        <f t="shared" si="6"/>
         <v>101.18282596142801</v>
       </c>
-      <c r="O24" t="s">
+      <c r="P24" t="s">
         <v>95</v>
       </c>
-      <c r="P24">
+      <c r="Q24">
         <v>9334</v>
       </c>
-      <c r="Q24">
+      <c r="R24">
         <v>337</v>
       </c>
-      <c r="R24">
+      <c r="S24">
         <v>78</v>
       </c>
-      <c r="S24">
-        <f t="shared" si="6"/>
+      <c r="T24">
+        <f t="shared" si="7"/>
         <v>10093776</v>
       </c>
     </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>36</v>
       </c>
@@ -2861,32 +2959,36 @@
         <f t="shared" si="3"/>
         <v>394873</v>
       </c>
-      <c r="M25" s="2">
+      <c r="M25">
         <f t="shared" si="4"/>
+        <v>7.4295764776582871</v>
+      </c>
+      <c r="N25" s="2">
+        <f t="shared" si="5"/>
         <v>9.2640678254911936E-3</v>
       </c>
-      <c r="N25">
-        <f t="shared" si="5"/>
+      <c r="O25">
+        <f t="shared" si="6"/>
         <v>100.92640678254912</v>
       </c>
-      <c r="O25" t="s">
+      <c r="P25" t="s">
         <v>94</v>
       </c>
-      <c r="P25">
+      <c r="Q25">
         <v>742</v>
       </c>
-      <c r="Q25">
+      <c r="R25">
         <v>18</v>
       </c>
-      <c r="R25">
+      <c r="S25">
         <v>1</v>
       </c>
-      <c r="S25">
-        <f t="shared" si="6"/>
+      <c r="T25">
+        <f t="shared" si="7"/>
         <v>5710494</v>
       </c>
     </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>37</v>
       </c>
@@ -2927,32 +3029,36 @@
         <f t="shared" si="3"/>
         <v>-14326</v>
       </c>
-      <c r="M26" s="2">
+      <c r="M26">
         <f t="shared" si="4"/>
+        <v>-0.48102234876974315</v>
+      </c>
+      <c r="N26" s="2">
+        <f t="shared" si="5"/>
         <v>-9.6805094806298806E-4</v>
       </c>
-      <c r="N26">
-        <f t="shared" si="5"/>
+      <c r="O26">
+        <f t="shared" si="6"/>
         <v>99.9031949051937</v>
       </c>
-      <c r="O26" t="s">
+      <c r="P26" t="s">
         <v>93</v>
       </c>
-      <c r="P26">
+      <c r="Q26">
         <v>1177</v>
       </c>
-      <c r="Q26">
+      <c r="R26">
         <v>26</v>
       </c>
-      <c r="R26">
+      <c r="S26">
         <v>4</v>
       </c>
-      <c r="S26">
-        <f t="shared" si="6"/>
+      <c r="T26">
+        <f t="shared" si="7"/>
         <v>2965091</v>
       </c>
     </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>38</v>
       </c>
@@ -2993,32 +3099,36 @@
         <f t="shared" si="3"/>
         <v>148803</v>
       </c>
-      <c r="M27" s="2">
+      <c r="M27">
         <f t="shared" si="4"/>
+        <v>2.4753147229350252</v>
+      </c>
+      <c r="N27" s="2">
+        <f t="shared" si="5"/>
         <v>1.4196426655534509E-3</v>
       </c>
-      <c r="N27">
-        <f t="shared" si="5"/>
+      <c r="O27">
+        <f t="shared" si="6"/>
         <v>100.14196426655535</v>
       </c>
-      <c r="O27" t="s">
+      <c r="P27" t="s">
         <v>92</v>
       </c>
-      <c r="P27">
+      <c r="Q27">
         <v>2819</v>
       </c>
-      <c r="Q27">
+      <c r="R27">
         <v>18</v>
       </c>
-      <c r="R27">
+      <c r="S27">
         <v>4</v>
       </c>
-      <c r="S27">
-        <f t="shared" si="6"/>
+      <c r="T27">
+        <f t="shared" si="7"/>
         <v>6163100</v>
       </c>
     </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>39</v>
       </c>
@@ -3059,32 +3169,36 @@
         <f t="shared" si="3"/>
         <v>90991</v>
       </c>
-      <c r="M28" s="2">
+      <c r="M28">
         <f t="shared" si="4"/>
+        <v>9.1501946871329505</v>
+      </c>
+      <c r="N28" s="2">
+        <f t="shared" si="5"/>
         <v>4.4698341719285163E-3</v>
       </c>
-      <c r="N28">
-        <f t="shared" si="5"/>
+      <c r="O28">
+        <f t="shared" si="6"/>
         <v>100.44698341719285</v>
       </c>
-      <c r="O28" t="s">
+      <c r="P28" t="s">
         <v>91</v>
       </c>
-      <c r="P28">
+      <c r="Q28">
         <v>228</v>
       </c>
-      <c r="Q28">
+      <c r="R28">
         <v>5</v>
       </c>
-      <c r="R28">
-        <v>0</v>
-      </c>
       <c r="S28">
-        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="T28">
+        <f t="shared" si="7"/>
         <v>1085635</v>
       </c>
     </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>40</v>
       </c>
@@ -3125,32 +3239,36 @@
         <f t="shared" si="3"/>
         <v>131508</v>
       </c>
-      <c r="M29" s="2">
+      <c r="M29">
         <f t="shared" si="4"/>
+        <v>7.1790700530891334</v>
+      </c>
+      <c r="N29" s="2">
+        <f t="shared" si="5"/>
         <v>1.330596546570105E-2</v>
       </c>
-      <c r="N29">
-        <f t="shared" si="5"/>
+      <c r="O29">
+        <f t="shared" si="6"/>
         <v>101.33059654657011</v>
       </c>
-      <c r="O29" s="3" t="s">
+      <c r="P29" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>214</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>4</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>1</v>
       </c>
-      <c r="S29">
-        <f t="shared" si="6"/>
+      <c r="T29">
+        <f t="shared" si="7"/>
         <v>1963547</v>
       </c>
     </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>41</v>
       </c>
@@ -3191,32 +3309,36 @@
         <f t="shared" si="3"/>
         <v>399030</v>
       </c>
-      <c r="M30" s="2">
+      <c r="M30">
         <f t="shared" si="4"/>
+        <v>14.72744102823027</v>
+      </c>
+      <c r="N30" s="2">
+        <f t="shared" si="5"/>
         <v>-9.4947548943538438E-3</v>
       </c>
-      <c r="N30">
-        <f t="shared" si="5"/>
+      <c r="O30">
+        <f t="shared" si="6"/>
         <v>99.050524510564614</v>
       </c>
-      <c r="O30" t="s">
+      <c r="P30" t="s">
         <v>89</v>
       </c>
-      <c r="P30">
+      <c r="Q30">
         <v>1279</v>
       </c>
-      <c r="Q30">
+      <c r="R30">
         <v>32</v>
       </c>
-      <c r="R30">
+      <c r="S30">
         <v>6</v>
       </c>
-      <c r="S30">
-        <f t="shared" si="6"/>
+      <c r="T30">
+        <f t="shared" si="7"/>
         <v>3109741</v>
       </c>
     </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>42</v>
       </c>
@@ -3257,32 +3379,36 @@
         <f t="shared" si="3"/>
         <v>57644</v>
       </c>
-      <c r="M31" s="2">
+      <c r="M31">
         <f t="shared" si="4"/>
+        <v>4.3621944159613149</v>
+      </c>
+      <c r="N31" s="2">
+        <f t="shared" si="5"/>
         <v>9.3787853836160371E-3</v>
       </c>
-      <c r="N31">
-        <f t="shared" si="5"/>
+      <c r="O31">
+        <f t="shared" si="6"/>
         <v>100.9378785383616</v>
       </c>
-      <c r="O31" t="s">
+      <c r="P31" t="s">
         <v>88</v>
       </c>
-      <c r="P31">
+      <c r="Q31">
         <v>415</v>
       </c>
-      <c r="Q31">
+      <c r="R31">
         <v>4</v>
       </c>
-      <c r="R31">
+      <c r="S31">
         <v>1</v>
       </c>
-      <c r="S31">
-        <f t="shared" si="6"/>
+      <c r="T31">
+        <f t="shared" si="7"/>
         <v>1379504</v>
       </c>
     </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>43</v>
       </c>
@@ -3323,32 +3449,36 @@
         <f t="shared" si="3"/>
         <v>486992</v>
       </c>
-      <c r="M32" s="2">
+      <c r="M32">
         <f t="shared" si="4"/>
+        <v>5.5292869112362295</v>
+      </c>
+      <c r="N32" s="2">
+        <f t="shared" si="5"/>
         <v>4.6397746727759967E-2</v>
       </c>
-      <c r="N32">
-        <f t="shared" si="5"/>
+      <c r="O32">
+        <f t="shared" si="6"/>
         <v>104.63977467277599</v>
       </c>
-      <c r="O32" t="s">
+      <c r="P32" t="s">
         <v>87</v>
       </c>
-      <c r="P32">
+      <c r="Q32">
         <v>22255</v>
       </c>
-      <c r="Q32">
+      <c r="R32">
         <v>355</v>
       </c>
-      <c r="R32">
+      <c r="S32">
         <v>88</v>
       </c>
-      <c r="S32">
-        <f t="shared" si="6"/>
+      <c r="T32">
+        <f t="shared" si="7"/>
         <v>9316748</v>
       </c>
     </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>44</v>
       </c>
@@ -3389,32 +3519,36 @@
         <f t="shared" si="3"/>
         <v>52947</v>
       </c>
-      <c r="M33" s="2">
+      <c r="M33">
         <f t="shared" si="4"/>
+        <v>2.5612001898152785</v>
+      </c>
+      <c r="N33" s="2">
+        <f t="shared" si="5"/>
         <v>6.5996651029592386E-3</v>
       </c>
-      <c r="N33">
-        <f t="shared" si="5"/>
+      <c r="O33">
+        <f t="shared" si="6"/>
         <v>100.65996651029592</v>
       </c>
-      <c r="O33" t="s">
+      <c r="P33" t="s">
         <v>86</v>
       </c>
-      <c r="P33">
+      <c r="Q33">
         <v>363</v>
       </c>
-      <c r="Q33">
+      <c r="R33">
         <v>6</v>
       </c>
-      <c r="R33">
+      <c r="S33">
         <v>1</v>
       </c>
-      <c r="S33">
-        <f t="shared" si="6"/>
+      <c r="T33">
+        <f t="shared" si="7"/>
         <v>2120583</v>
       </c>
     </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>45</v>
       </c>
@@ -3455,32 +3589,36 @@
         <f t="shared" si="3"/>
         <v>794696</v>
       </c>
-      <c r="M34" s="2">
+      <c r="M34">
         <f t="shared" si="4"/>
+        <v>4.0919301242903643</v>
+      </c>
+      <c r="N34" s="2">
+        <f t="shared" si="5"/>
         <v>4.5456129811919009E-2</v>
       </c>
-      <c r="N34">
-        <f t="shared" si="5"/>
+      <c r="O34">
+        <f t="shared" si="6"/>
         <v>104.54561298119189</v>
       </c>
-      <c r="O34" t="s">
+      <c r="P34" t="s">
         <v>85</v>
       </c>
-      <c r="P34">
+      <c r="Q34">
         <v>84735</v>
       </c>
-      <c r="Q34">
+      <c r="R34">
         <v>1672</v>
       </c>
-      <c r="R34">
+      <c r="S34">
         <v>365</v>
       </c>
-      <c r="S34">
-        <f t="shared" si="6"/>
+      <c r="T34">
+        <f t="shared" si="7"/>
         <v>20300486</v>
       </c>
     </row>
-    <row r="35" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>46</v>
       </c>
@@ -3521,32 +3659,36 @@
         <f t="shared" si="3"/>
         <v>888167</v>
       </c>
-      <c r="M35" s="2">
+      <c r="M35">
         <f t="shared" si="4"/>
+        <v>9.2848351849159005</v>
+      </c>
+      <c r="N35" s="2">
+        <f t="shared" si="5"/>
         <v>-1.3855056347983548E-2</v>
       </c>
-      <c r="N35">
-        <f t="shared" si="5"/>
+      <c r="O35">
+        <f t="shared" si="6"/>
         <v>98.614494365201637</v>
       </c>
-      <c r="O35" t="s">
+      <c r="P35" t="s">
         <v>84</v>
       </c>
-      <c r="P35">
+      <c r="Q35">
         <v>1584</v>
       </c>
-      <c r="Q35">
+      <c r="R35">
         <v>9</v>
       </c>
-      <c r="R35">
+      <c r="S35">
         <v>1</v>
       </c>
-      <c r="S35">
-        <f t="shared" si="6"/>
+      <c r="T35">
+        <f t="shared" si="7"/>
         <v>10455532</v>
       </c>
     </row>
-    <row r="36" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>47</v>
       </c>
@@ -3587,32 +3729,36 @@
         <f t="shared" si="3"/>
         <v>103797</v>
       </c>
-      <c r="M36" s="2">
+      <c r="M36">
         <f t="shared" si="4"/>
+        <v>15.356743921113175</v>
+      </c>
+      <c r="N36" s="2">
+        <f t="shared" si="5"/>
         <v>1.8806782619830684E-2</v>
       </c>
-      <c r="N36">
-        <f t="shared" si="5"/>
+      <c r="O36">
+        <f t="shared" si="6"/>
         <v>101.88067826198306</v>
       </c>
-      <c r="O36" t="s">
+      <c r="P36" t="s">
         <v>83</v>
       </c>
-      <c r="P36">
+      <c r="Q36">
         <v>147</v>
       </c>
-      <c r="Q36">
+      <c r="R36">
         <v>3</v>
       </c>
-      <c r="R36">
-        <v>0</v>
-      </c>
       <c r="S36">
-        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="T36">
+        <f t="shared" si="7"/>
         <v>779849</v>
       </c>
     </row>
-    <row r="37" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>48</v>
       </c>
@@ -3653,32 +3799,36 @@
         <f t="shared" si="3"/>
         <v>240353</v>
       </c>
-      <c r="M37" s="2">
+      <c r="M37">
         <f t="shared" si="4"/>
+        <v>2.0776514144666183</v>
+      </c>
+      <c r="N37" s="2">
+        <f t="shared" si="5"/>
         <v>9.8887243775600854E-3</v>
       </c>
-      <c r="N37">
-        <f t="shared" si="5"/>
+      <c r="O37">
+        <f t="shared" si="6"/>
         <v>100.988872437756</v>
       </c>
-      <c r="O37" t="s">
+      <c r="P37" t="s">
         <v>82</v>
       </c>
-      <c r="P37">
+      <c r="Q37">
         <v>2547</v>
       </c>
-      <c r="Q37">
+      <c r="R37">
         <v>65</v>
       </c>
-      <c r="R37">
+      <c r="S37">
         <v>10</v>
       </c>
-      <c r="S37">
-        <f t="shared" si="6"/>
+      <c r="T37">
+        <f t="shared" si="7"/>
         <v>11811395</v>
       </c>
     </row>
-    <row r="38" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>49</v>
       </c>
@@ -3719,32 +3869,36 @@
         <f t="shared" si="3"/>
         <v>198634</v>
       </c>
-      <c r="M38" s="2">
+      <c r="M38">
         <f t="shared" si="4"/>
+        <v>5.2759688085841736</v>
+      </c>
+      <c r="N38" s="2">
+        <f t="shared" si="5"/>
         <v>-4.3375888612868377E-3</v>
       </c>
-      <c r="N38">
-        <f t="shared" si="5"/>
+      <c r="O38">
+        <f t="shared" si="6"/>
         <v>99.566241113871314</v>
       </c>
-      <c r="O38" t="s">
+      <c r="P38" t="s">
         <v>81</v>
       </c>
-      <c r="P38">
+      <c r="Q38">
         <v>1744</v>
       </c>
-      <c r="Q38">
+      <c r="R38">
         <v>36</v>
       </c>
-      <c r="R38">
+      <c r="S38">
         <v>5</v>
       </c>
-      <c r="S38">
-        <f t="shared" si="6"/>
+      <c r="T38">
+        <f t="shared" si="7"/>
         <v>3965260</v>
       </c>
     </row>
-    <row r="39" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>50</v>
       </c>
@@ -3785,32 +3939,36 @@
         <f t="shared" si="3"/>
         <v>392894</v>
       </c>
-      <c r="M39" s="2">
+      <c r="M39">
         <f t="shared" si="4"/>
+        <v>10.208735318710204</v>
+      </c>
+      <c r="N39" s="2">
+        <f t="shared" si="5"/>
         <v>-1.6503568189325161E-6</v>
       </c>
-      <c r="N39">
-        <f t="shared" si="5"/>
+      <c r="O39">
+        <f t="shared" si="6"/>
         <v>99.999834964318097</v>
       </c>
-      <c r="O39" t="s">
+      <c r="P39" t="s">
         <v>80</v>
       </c>
-      <c r="P39">
+      <c r="Q39">
         <v>736</v>
       </c>
-      <c r="Q39">
+      <c r="R39">
         <v>18</v>
       </c>
-      <c r="R39">
-        <v>0</v>
-      </c>
       <c r="S39">
-        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="T39">
+        <f t="shared" si="7"/>
         <v>4242236</v>
       </c>
     </row>
-    <row r="40" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>51</v>
       </c>
@@ -3851,32 +4009,36 @@
         <f t="shared" si="3"/>
         <v>276939</v>
       </c>
-      <c r="M40" s="2">
+      <c r="M40">
         <f t="shared" si="4"/>
+        <v>2.1746451975888319</v>
+      </c>
+      <c r="N40" s="2">
+        <f t="shared" si="5"/>
         <v>1.7881988420162816E-2</v>
       </c>
-      <c r="N40">
-        <f t="shared" si="5"/>
+      <c r="O40">
+        <f t="shared" si="6"/>
         <v>101.78819884201629</v>
       </c>
-      <c r="O40" t="s">
+      <c r="P40" t="s">
         <v>79</v>
       </c>
-      <c r="P40">
+      <c r="Q40">
         <v>5805</v>
       </c>
-      <c r="Q40">
+      <c r="R40">
         <v>74</v>
       </c>
-      <c r="R40">
+      <c r="S40">
         <v>11</v>
       </c>
-      <c r="S40">
-        <f t="shared" si="6"/>
+      <c r="T40">
+        <f t="shared" si="7"/>
         <v>13017649</v>
       </c>
     </row>
-    <row r="41" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>52</v>
       </c>
@@ -3917,32 +4079,36 @@
         <f t="shared" si="3"/>
         <v>42916</v>
       </c>
-      <c r="M41" s="2">
+      <c r="M41">
         <f t="shared" si="4"/>
+        <v>4.0669151392991401</v>
+      </c>
+      <c r="N41" s="2">
+        <f t="shared" si="5"/>
         <v>3.8820385479484451E-2</v>
       </c>
-      <c r="N41">
-        <f t="shared" si="5"/>
+      <c r="O41">
+        <f t="shared" si="6"/>
         <v>103.88203854794844</v>
       </c>
-      <c r="O41" t="s">
+      <c r="P41" t="s">
         <v>78</v>
       </c>
-      <c r="P41">
+      <c r="Q41">
         <v>682</v>
       </c>
-      <c r="Q41">
+      <c r="R41">
         <v>12</v>
       </c>
-      <c r="R41">
+      <c r="S41">
         <v>1</v>
       </c>
-      <c r="S41">
-        <f t="shared" si="6"/>
+      <c r="T41">
+        <f t="shared" si="7"/>
         <v>1098845</v>
       </c>
     </row>
-    <row r="42" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>53</v>
       </c>
@@ -3983,32 +4149,36 @@
         <f t="shared" si="3"/>
         <v>478737</v>
       </c>
-      <c r="M42" s="2">
+      <c r="M42">
         <f t="shared" si="4"/>
+        <v>10.304338701779498</v>
+      </c>
+      <c r="N42" s="2">
+        <f t="shared" si="5"/>
         <v>-1.7885642885067957E-2</v>
       </c>
-      <c r="N42">
-        <f t="shared" si="5"/>
+      <c r="O42">
+        <f t="shared" si="6"/>
         <v>98.211435711493195</v>
       </c>
-      <c r="O42" t="s">
+      <c r="P42" t="s">
         <v>77</v>
       </c>
-      <c r="P42">
+      <c r="Q42">
         <v>1349</v>
       </c>
-      <c r="Q42">
+      <c r="R42">
         <v>32</v>
       </c>
-      <c r="R42">
+      <c r="S42">
         <v>2</v>
       </c>
-      <c r="S42">
-        <f t="shared" si="6"/>
+      <c r="T42">
+        <f t="shared" si="7"/>
         <v>5126061</v>
       </c>
     </row>
-    <row r="43" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>54</v>
       </c>
@@ -4049,32 +4219,36 @@
         <f t="shared" si="3"/>
         <v>68009</v>
       </c>
-      <c r="M43" s="2">
+      <c r="M43">
         <f t="shared" si="4"/>
+        <v>8.2961985261557949</v>
+      </c>
+      <c r="N43" s="2">
+        <f t="shared" si="5"/>
         <v>-5.5415097953774826E-3</v>
       </c>
-      <c r="N43">
-        <f t="shared" si="5"/>
+      <c r="O43">
+        <f t="shared" si="6"/>
         <v>99.445849020462248</v>
       </c>
-      <c r="O43" t="s">
+      <c r="P43" t="s">
         <v>76</v>
       </c>
-      <c r="P43">
+      <c r="Q43">
         <v>129</v>
       </c>
-      <c r="Q43">
+      <c r="R43">
         <v>2</v>
       </c>
-      <c r="R43">
+      <c r="S43">
         <v>1</v>
       </c>
-      <c r="S43">
-        <f t="shared" si="6"/>
+      <c r="T43">
+        <f t="shared" si="7"/>
         <v>887899</v>
       </c>
     </row>
-    <row r="44" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>55</v>
       </c>
@@ -4115,32 +4289,36 @@
         <f t="shared" si="3"/>
         <v>541466</v>
       </c>
-      <c r="M44" s="2">
+      <c r="M44">
         <f t="shared" si="4"/>
+        <v>8.4930101196295578</v>
+      </c>
+      <c r="N44" s="2">
+        <f t="shared" si="5"/>
         <v>4.3652859935349106E-3</v>
       </c>
-      <c r="N44">
-        <f t="shared" si="5"/>
+      <c r="O44">
+        <f t="shared" si="6"/>
         <v>100.43652859935348</v>
       </c>
-      <c r="O44" t="s">
+      <c r="P44" t="s">
         <v>75</v>
       </c>
-      <c r="P44">
+      <c r="Q44">
         <v>2240</v>
       </c>
-      <c r="Q44">
+      <c r="R44">
         <v>23</v>
       </c>
-      <c r="R44">
-        <v>0</v>
-      </c>
       <c r="S44">
-        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="T44">
+        <f t="shared" si="7"/>
         <v>6919137</v>
       </c>
     </row>
-    <row r="45" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>56</v>
       </c>
@@ -4181,32 +4359,36 @@
         <f t="shared" si="3"/>
         <v>3914872</v>
       </c>
-      <c r="M45" s="2">
+      <c r="M45">
         <f t="shared" si="4"/>
+        <v>15.493142467407338</v>
+      </c>
+      <c r="N45" s="2">
+        <f t="shared" si="5"/>
         <v>-6.0444282111371851E-3</v>
       </c>
-      <c r="N45">
-        <f t="shared" si="5"/>
+      <c r="O45">
+        <f t="shared" si="6"/>
         <v>99.395557178886278</v>
       </c>
-      <c r="O45" t="s">
+      <c r="P45" t="s">
         <v>74</v>
       </c>
-      <c r="P45">
+      <c r="Q45">
         <v>3996</v>
       </c>
-      <c r="Q45">
+      <c r="R45">
         <v>122</v>
       </c>
-      <c r="R45">
+      <c r="S45">
         <v>21</v>
       </c>
-      <c r="S45">
-        <f t="shared" si="6"/>
+      <c r="T45">
+        <f t="shared" si="7"/>
         <v>29187286</v>
       </c>
     </row>
-    <row r="46" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>57</v>
       </c>
@@ -4247,32 +4429,36 @@
         <f t="shared" si="3"/>
         <v>504487</v>
       </c>
-      <c r="M46" s="2">
+      <c r="M46">
         <f t="shared" si="4"/>
+        <v>18.207498651094554</v>
+      </c>
+      <c r="N46" s="2">
+        <f t="shared" si="5"/>
         <v>7.8073675973782406E-3</v>
       </c>
-      <c r="N46">
-        <f t="shared" si="5"/>
+      <c r="O46">
+        <f t="shared" si="6"/>
         <v>100.78073675973782</v>
       </c>
-      <c r="O46" t="s">
+      <c r="P46" t="s">
         <v>73</v>
       </c>
-      <c r="P46">
+      <c r="Q46">
         <v>1012</v>
       </c>
-      <c r="Q46">
+      <c r="R46">
         <v>7</v>
       </c>
-      <c r="R46">
+      <c r="S46">
         <v>2</v>
       </c>
-      <c r="S46">
-        <f t="shared" si="6"/>
+      <c r="T46">
+        <f t="shared" si="7"/>
         <v>3276264</v>
       </c>
     </row>
-    <row r="47" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>58</v>
       </c>
@@ -4313,32 +4499,36 @@
         <f t="shared" si="3"/>
         <v>13166</v>
       </c>
-      <c r="M47" s="2">
+      <c r="M47">
         <f t="shared" si="4"/>
+        <v>2.0887239682899783</v>
+      </c>
+      <c r="N47" s="2">
+        <f t="shared" si="5"/>
         <v>3.233511992517811E-2</v>
       </c>
-      <c r="N47">
-        <f t="shared" si="5"/>
+      <c r="O47">
+        <f t="shared" si="6"/>
         <v>103.2335119925178</v>
       </c>
-      <c r="O47" t="s">
+      <c r="P47" t="s">
         <v>72</v>
       </c>
-      <c r="P47">
+      <c r="Q47">
         <v>1706</v>
       </c>
-      <c r="Q47">
+      <c r="R47">
         <v>41</v>
       </c>
-      <c r="R47">
+      <c r="S47">
         <v>7</v>
       </c>
-      <c r="S47">
-        <f t="shared" si="6"/>
+      <c r="T47">
+        <f t="shared" si="7"/>
         <v>645209</v>
       </c>
     </row>
-    <row r="48" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>59</v>
       </c>
@@ -4379,32 +4569,36 @@
         <f t="shared" si="3"/>
         <v>616806</v>
       </c>
-      <c r="M48" s="2">
+      <c r="M48">
         <f t="shared" si="4"/>
+        <v>7.6738773206783604</v>
+      </c>
+      <c r="N48" s="2">
+        <f t="shared" si="5"/>
         <v>7.4475910368156312E-3</v>
       </c>
-      <c r="N48">
-        <f t="shared" si="5"/>
+      <c r="O48">
+        <f t="shared" si="6"/>
         <v>100.74475910368157</v>
       </c>
-      <c r="O48" t="s">
+      <c r="P48" t="s">
         <v>71</v>
       </c>
-      <c r="P48">
+      <c r="Q48">
         <v>321</v>
       </c>
-      <c r="Q48">
+      <c r="R48">
         <v>16</v>
       </c>
-      <c r="R48">
+      <c r="S48">
         <v>3</v>
       </c>
-      <c r="S48">
-        <f t="shared" si="6"/>
+      <c r="T48">
+        <f t="shared" si="7"/>
         <v>8654863</v>
       </c>
     </row>
-    <row r="49" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>60</v>
       </c>
@@ -4445,32 +4639,36 @@
         <f t="shared" si="3"/>
         <v>962577</v>
       </c>
-      <c r="M49" s="2">
+      <c r="M49">
         <f t="shared" si="4"/>
+        <v>14.25328602657429</v>
+      </c>
+      <c r="N49" s="2">
+        <f t="shared" si="5"/>
         <v>2.9029277795656967E-3</v>
       </c>
-      <c r="N49">
-        <f t="shared" si="5"/>
+      <c r="O49">
+        <f t="shared" si="6"/>
         <v>100.29029277795658</v>
       </c>
-      <c r="O49" t="s">
+      <c r="P49" t="s">
         <v>70</v>
       </c>
-      <c r="P49">
+      <c r="Q49">
         <v>5319</v>
       </c>
-      <c r="Q49">
+      <c r="R49">
         <v>246</v>
       </c>
-      <c r="R49">
+      <c r="S49">
         <v>51</v>
       </c>
-      <c r="S49">
-        <f t="shared" si="6"/>
+      <c r="T49">
+        <f t="shared" si="7"/>
         <v>7721265</v>
       </c>
     </row>
-    <row r="50" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>61</v>
       </c>
@@ -4511,32 +4709,36 @@
         <f t="shared" si="3"/>
         <v>-64770</v>
       </c>
-      <c r="M50" s="2">
+      <c r="M50">
         <f t="shared" si="4"/>
+        <v>-3.4826044525934035</v>
+      </c>
+      <c r="N50" s="2">
+        <f t="shared" si="5"/>
         <v>5.7474645433880905E-3</v>
       </c>
-      <c r="N50">
-        <f t="shared" si="5"/>
+      <c r="O50">
+        <f t="shared" si="6"/>
         <v>100.57474645433882</v>
       </c>
-      <c r="O50" t="s">
+      <c r="P50" t="s">
         <v>69</v>
       </c>
-      <c r="P50">
+      <c r="Q50">
         <v>191</v>
       </c>
-      <c r="Q50">
+      <c r="R50">
         <v>2</v>
       </c>
-      <c r="R50">
+      <c r="S50">
         <v>1</v>
       </c>
-      <c r="S50">
-        <f t="shared" si="6"/>
+      <c r="T50">
+        <f t="shared" si="7"/>
         <v>1795236</v>
       </c>
     </row>
-    <row r="51" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>62</v>
       </c>
@@ -4577,32 +4779,36 @@
         <f t="shared" si="3"/>
         <v>199243</v>
       </c>
-      <c r="M51" s="2">
+      <c r="M51">
         <f t="shared" si="4"/>
+        <v>3.4965770072461098</v>
+      </c>
+      <c r="N51" s="2">
+        <f t="shared" si="5"/>
         <v>1.1112949420118283E-2</v>
       </c>
-      <c r="N51">
-        <f t="shared" si="5"/>
+      <c r="O51">
+        <f t="shared" si="6"/>
         <v>101.11129494201182</v>
       </c>
-      <c r="O51" t="s">
+      <c r="P51" t="s">
         <v>68</v>
       </c>
-      <c r="P51">
+      <c r="Q51">
         <v>1550</v>
       </c>
-      <c r="Q51">
+      <c r="R51">
         <v>24</v>
       </c>
-      <c r="R51">
+      <c r="S51">
         <v>8</v>
       </c>
-      <c r="S51">
-        <f t="shared" si="6"/>
+      <c r="T51">
+        <f t="shared" si="7"/>
         <v>5899023</v>
       </c>
     </row>
-    <row r="52" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>63</v>
       </c>
@@ -4643,28 +4849,32 @@
         <f t="shared" si="3"/>
         <v>9419</v>
       </c>
-      <c r="M52" s="2">
+      <c r="M52">
         <f t="shared" si="4"/>
+        <v>1.6573992609537216</v>
+      </c>
+      <c r="N52" s="2">
+        <f t="shared" si="5"/>
         <v>-7.914783421027324E-3</v>
       </c>
-      <c r="N52">
-        <f t="shared" si="5"/>
+      <c r="O52">
+        <f t="shared" si="6"/>
         <v>99.208521657897265</v>
       </c>
-      <c r="O52" t="s">
+      <c r="P52" t="s">
         <v>67</v>
       </c>
-      <c r="P52">
+      <c r="Q52">
         <v>137</v>
       </c>
-      <c r="Q52">
-        <v>0</v>
-      </c>
       <c r="R52">
         <v>0</v>
       </c>
       <c r="S52">
-        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="T52">
+        <f t="shared" si="7"/>
         <v>577856</v>
       </c>
     </row>

--- a/apportion/pop.xlsx
+++ b/apportion/pop.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/user/Google Drive/GitHub/R Functions/apportion/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12F7B794-1EFF-7346-A4B0-7922CC83E623}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{296885F4-AEA0-FA4E-8A6D-F0582FB5BC0B}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38400" yWindow="500" windowWidth="38400" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4703,7 +4703,7 @@
         <v>-1</v>
       </c>
       <c r="K50" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="L50">
         <f t="shared" si="3"/>

--- a/apportion/pop.xlsx
+++ b/apportion/pop.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/user/Google Drive/GitHub/R Functions/apportion/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{848E51B3-F7F6-BE46-931F-2DA7DCB26CA6}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83A3C4D6-0D34-2043-B0CF-EBDF49C09E7B}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="35840" yWindow="-6380" windowWidth="21600" windowHeight="37900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="35840" windowHeight="21900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="pop" sheetId="1" r:id="rId1"/>
@@ -421,9 +421,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="169" formatCode="0.000"/>
+    <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -554,13 +554,6 @@
     <font>
       <sz val="12"/>
       <color theme="0"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -909,14 +902,13 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="43" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="44">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1277,8 +1269,8 @@
   <dimension ref="A1:AA52"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="26" max="26" width="17.1640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="10.83203125" style="6"/>
+    <col min="26" max="26" width="17.1640625" style="4" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="10.83203125" style="5"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:27" x14ac:dyDescent="0.2">
@@ -1357,10 +1349,10 @@
       <c r="Y1" t="s">
         <v>124</v>
       </c>
-      <c r="Z1" s="5" t="s">
+      <c r="Z1" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="AA1" s="6" t="s">
+      <c r="AA1" s="5" t="s">
         <v>128</v>
       </c>
     </row>
@@ -1369,7 +1361,7 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C2">
         <v>4802982</v>
@@ -1381,15 +1373,15 @@
         <v>4921532</v>
       </c>
       <c r="F2">
-        <f>D2-C2</f>
+        <f t="shared" ref="F2:F33" si="0">D2-C2</f>
         <v>227071</v>
       </c>
       <c r="G2">
-        <f>F2/C2*100</f>
+        <f t="shared" ref="G2:G33" si="1">F2/C2*100</f>
         <v>4.7277087442759518</v>
       </c>
       <c r="H2" s="2">
-        <f>(D2-E2)/E2</f>
+        <f t="shared" ref="H2:H33" si="2">(D2-E2)/E2</f>
         <v>2.2050247768377815E-2</v>
       </c>
       <c r="I2">
@@ -1399,37 +1391,37 @@
         <v>7</v>
       </c>
       <c r="K2">
-        <f>J2-I2</f>
+        <f t="shared" ref="K2:K33" si="3">J2-I2</f>
         <v>0</v>
       </c>
       <c r="L2">
         <v>9</v>
       </c>
       <c r="M2">
-        <f>J2+2</f>
+        <f t="shared" ref="M2:M9" si="4">J2+2</f>
         <v>9</v>
       </c>
       <c r="N2">
-        <f>M2-L2</f>
+        <f t="shared" ref="N2:N9" si="5">M2-L2</f>
         <v>0</v>
       </c>
       <c r="O2" t="s">
         <v>9</v>
       </c>
       <c r="P2">
-        <v>143</v>
+        <v>3364</v>
       </c>
       <c r="Q2">
-        <v>3</v>
+        <v>56</v>
       </c>
       <c r="R2">
-        <v>0</v>
-      </c>
-      <c r="S2" s="4">
+        <v>7</v>
+      </c>
+      <c r="S2" s="3">
         <v>50645.33</v>
       </c>
       <c r="T2">
-        <f>D2/S2</f>
+        <f t="shared" ref="T2:T33" si="6">D2/S2</f>
         <v>99.319186981307055</v>
       </c>
       <c r="U2">
@@ -1447,11 +1439,11 @@
       <c r="Y2">
         <v>43</v>
       </c>
-      <c r="Z2" s="5">
+      <c r="Z2" s="4">
         <v>1240000</v>
       </c>
-      <c r="AA2" s="6">
-        <f>Z2/D2</f>
+      <c r="AA2" s="5">
+        <f t="shared" ref="AA2:AA33" si="7">Z2/D2</f>
         <v>0.2465182772428044</v>
       </c>
     </row>
@@ -1460,7 +1452,7 @@
         <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C3">
         <v>721523</v>
@@ -1472,15 +1464,15 @@
         <v>731158</v>
       </c>
       <c r="F3">
-        <f>D3-C3</f>
+        <f t="shared" si="0"/>
         <v>14558</v>
       </c>
       <c r="G3">
-        <f>F3/C3*100</f>
+        <f t="shared" si="1"/>
         <v>2.0176764981850894</v>
       </c>
       <c r="H3" s="2">
-        <f>(D3-E3)/E3</f>
+        <f t="shared" si="2"/>
         <v>6.7331548037496683E-3</v>
       </c>
       <c r="I3">
@@ -1490,37 +1482,37 @@
         <v>1</v>
       </c>
       <c r="K3">
-        <f>J3-I3</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L3">
         <v>3</v>
       </c>
       <c r="M3">
-        <f>J3+2</f>
+        <f t="shared" si="4"/>
         <v>3</v>
       </c>
       <c r="N3">
-        <f>M3-L3</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="O3" t="s">
         <v>9</v>
       </c>
       <c r="P3">
-        <v>1106</v>
+        <v>141</v>
       </c>
       <c r="Q3">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="R3">
-        <v>4</v>
-      </c>
-      <c r="S3" s="4">
+        <v>0</v>
+      </c>
+      <c r="S3" s="3">
         <v>570640.94999999995</v>
       </c>
       <c r="T3">
-        <f>D3/S3</f>
+        <f t="shared" si="6"/>
         <v>1.289919694687176</v>
       </c>
       <c r="U3">
@@ -1538,11 +1530,11 @@
       <c r="Y3">
         <v>32</v>
       </c>
-      <c r="Z3" s="5">
+      <c r="Z3" s="4">
         <v>600000</v>
       </c>
-      <c r="AA3" s="6">
-        <f>Z3/D3</f>
+      <c r="AA3" s="5">
+        <f t="shared" si="7"/>
         <v>0.81512768295880478</v>
       </c>
     </row>
@@ -1563,15 +1555,15 @@
         <v>7421401</v>
       </c>
       <c r="F4">
-        <f>D4-C4</f>
+        <f t="shared" si="0"/>
         <v>746223</v>
       </c>
       <c r="G4">
-        <f>F4/C4*100</f>
+        <f t="shared" si="1"/>
         <v>11.636642911722053</v>
       </c>
       <c r="H4" s="2">
-        <f>(D4-E4)/E4</f>
+        <f t="shared" si="2"/>
         <v>-3.5367715610570026E-2</v>
       </c>
       <c r="I4">
@@ -1581,18 +1573,18 @@
         <v>9</v>
       </c>
       <c r="K4">
-        <f>J4-I4</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L4">
         <v>11</v>
       </c>
       <c r="M4">
-        <f>J4+2</f>
+        <f t="shared" si="4"/>
         <v>11</v>
       </c>
       <c r="N4">
-        <f>M4-L4</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="O4" t="s">
@@ -1607,11 +1599,11 @@
       <c r="R4">
         <v>5</v>
       </c>
-      <c r="S4" s="4">
+      <c r="S4" s="3">
         <v>113594.08</v>
       </c>
       <c r="T4">
-        <f>D4/S4</f>
+        <f t="shared" si="6"/>
         <v>63.021972623925471</v>
       </c>
       <c r="U4">
@@ -1629,11 +1621,11 @@
       <c r="Y4">
         <v>25</v>
       </c>
-      <c r="Z4" s="5">
-        <v>0</v>
-      </c>
-      <c r="AA4" s="6">
-        <f>Z4/D4</f>
+      <c r="Z4" s="4">
+        <v>0</v>
+      </c>
+      <c r="AA4" s="5">
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -1654,15 +1646,15 @@
         <v>3030522</v>
       </c>
       <c r="F5">
-        <f>D5-C5</f>
+        <f t="shared" si="0"/>
         <v>87527</v>
       </c>
       <c r="G5">
-        <f>F5/C5*100</f>
+        <f t="shared" si="1"/>
         <v>2.9911192869730976</v>
       </c>
       <c r="H5" s="2">
-        <f>(D5-E5)/E5</f>
+        <f t="shared" si="2"/>
         <v>-5.5323802302045654E-3</v>
       </c>
       <c r="I5">
@@ -1672,18 +1664,18 @@
         <v>4</v>
       </c>
       <c r="K5">
-        <f>J5-I5</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L5">
         <v>6</v>
       </c>
       <c r="M5">
-        <f>J5+2</f>
+        <f t="shared" si="4"/>
         <v>6</v>
       </c>
       <c r="N5">
-        <f>M5-L5</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="O5" t="s">
@@ -1698,11 +1690,11 @@
       <c r="R5">
         <v>2</v>
       </c>
-      <c r="S5" s="4">
+      <c r="S5" s="3">
         <v>52035.48</v>
       </c>
       <c r="T5">
-        <f>D5/S5</f>
+        <f t="shared" si="6"/>
         <v>57.917328714946031</v>
       </c>
       <c r="U5">
@@ -1720,11 +1712,11 @@
       <c r="Y5">
         <v>46</v>
       </c>
-      <c r="Z5" s="5">
-        <v>0</v>
-      </c>
-      <c r="AA5" s="6">
-        <f>Z5/D5</f>
+      <c r="Z5" s="4">
+        <v>0</v>
+      </c>
+      <c r="AA5" s="5">
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -1745,15 +1737,15 @@
         <v>39368078</v>
       </c>
       <c r="F6">
-        <f>D6-C6</f>
+        <f t="shared" si="0"/>
         <v>2234768</v>
       </c>
       <c r="G6">
-        <f>F6/C6*100</f>
+        <f t="shared" si="1"/>
         <v>5.9845981958807819</v>
       </c>
       <c r="H6" s="2">
-        <f>(D6-E6)/E6</f>
+        <f t="shared" si="2"/>
         <v>5.3007159760250422E-3</v>
       </c>
       <c r="I6">
@@ -1763,18 +1755,18 @@
         <v>52</v>
       </c>
       <c r="K6">
-        <f>J6-I6</f>
+        <f t="shared" si="3"/>
         <v>-1</v>
       </c>
       <c r="L6">
         <v>55</v>
       </c>
       <c r="M6">
-        <f>J6+2</f>
+        <f t="shared" si="4"/>
         <v>54</v>
       </c>
       <c r="N6">
-        <f>M6-L6</f>
+        <f t="shared" si="5"/>
         <v>-1</v>
       </c>
       <c r="O6" t="s">
@@ -1789,11 +1781,11 @@
       <c r="R6">
         <v>0</v>
       </c>
-      <c r="S6" s="4">
+      <c r="S6" s="3">
         <v>155779.22</v>
       </c>
       <c r="T6">
-        <f>D6/S6</f>
+        <f t="shared" si="6"/>
         <v>254.05671565180515</v>
       </c>
       <c r="U6">
@@ -1811,11 +1803,11 @@
       <c r="Y6">
         <v>6</v>
       </c>
-      <c r="Z6" s="5">
+      <c r="Z6" s="4">
         <v>187000000</v>
       </c>
-      <c r="AA6" s="6">
-        <f>Z6/D6</f>
+      <c r="AA6" s="5">
+        <f t="shared" si="7"/>
         <v>4.7249955320998129</v>
       </c>
     </row>
@@ -1836,15 +1828,15 @@
         <v>5807719</v>
       </c>
       <c r="F7">
-        <f>D7-C7</f>
+        <f t="shared" si="0"/>
         <v>737241</v>
       </c>
       <c r="G7">
-        <f>F7/C7*100</f>
+        <f t="shared" si="1"/>
         <v>14.613503061489455</v>
       </c>
       <c r="H7" s="2">
-        <f>(D7-E7)/E7</f>
+        <f t="shared" si="2"/>
         <v>-4.3989731596862725E-3</v>
       </c>
       <c r="I7">
@@ -1854,18 +1846,18 @@
         <v>8</v>
       </c>
       <c r="K7">
-        <f>J7-I7</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="L7">
         <v>9</v>
       </c>
       <c r="M7">
-        <f>J7+2</f>
+        <f t="shared" si="4"/>
         <v>10</v>
       </c>
       <c r="N7">
-        <f>M7-L7</f>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="O7" t="s">
@@ -1880,11 +1872,11 @@
       <c r="R7">
         <v>11</v>
       </c>
-      <c r="S7" s="4">
+      <c r="S7" s="3">
         <v>103641.89</v>
       </c>
       <c r="T7">
-        <f>D7/S7</f>
+        <f t="shared" si="6"/>
         <v>55.789903098061991</v>
       </c>
       <c r="U7">
@@ -1902,11 +1894,11 @@
       <c r="Y7">
         <v>15</v>
       </c>
-      <c r="Z7" s="5">
+      <c r="Z7" s="4">
         <v>6000000</v>
       </c>
-      <c r="AA7" s="6">
-        <f>Z7/D7</f>
+      <c r="AA7" s="5">
+        <f t="shared" si="7"/>
         <v>1.0376725281905361</v>
       </c>
     </row>
@@ -1927,15 +1919,15 @@
         <v>3557006</v>
       </c>
       <c r="F8">
-        <f>D8-C8</f>
+        <f t="shared" si="0"/>
         <v>26670</v>
       </c>
       <c r="G8">
-        <f>F8/C8*100</f>
+        <f t="shared" si="1"/>
         <v>0.74463344601951964</v>
       </c>
       <c r="H8" s="2">
-        <f>(D8-E8)/E8</f>
+        <f t="shared" si="2"/>
         <v>1.4419992544291464E-2</v>
       </c>
       <c r="I8">
@@ -1945,18 +1937,18 @@
         <v>5</v>
       </c>
       <c r="K8">
-        <f>J8-I8</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L8">
         <v>7</v>
       </c>
       <c r="M8">
-        <f>J8+2</f>
+        <f t="shared" si="4"/>
         <v>7</v>
       </c>
       <c r="N8">
-        <f>M8-L8</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="O8" t="s">
@@ -1971,11 +1963,11 @@
       <c r="R8">
         <v>16</v>
       </c>
-      <c r="S8" s="4">
+      <c r="S8" s="3">
         <v>4842.3599999999997</v>
       </c>
       <c r="T8">
-        <f>D8/S8</f>
+        <f t="shared" si="6"/>
         <v>745.15277674522349</v>
       </c>
       <c r="U8">
@@ -1993,11 +1985,11 @@
       <c r="Y8">
         <v>9</v>
       </c>
-      <c r="Z8" s="5">
+      <c r="Z8" s="4">
         <v>500000</v>
       </c>
-      <c r="AA8" s="6">
-        <f>Z8/D8</f>
+      <c r="AA8" s="5">
+        <f t="shared" si="7"/>
         <v>0.13856948622314455</v>
       </c>
     </row>
@@ -2018,15 +2010,15 @@
         <v>986809</v>
       </c>
       <c r="F9">
-        <f>D9-C9</f>
+        <f t="shared" si="0"/>
         <v>89960</v>
       </c>
       <c r="G9">
-        <f>F9/C9*100</f>
+        <f t="shared" si="1"/>
         <v>9.9858249239352332</v>
       </c>
       <c r="H9" s="2">
-        <f>(D9-E9)/E9</f>
+        <f t="shared" si="2"/>
         <v>4.0818435989132653E-3</v>
       </c>
       <c r="I9">
@@ -2036,18 +2028,18 @@
         <v>1</v>
       </c>
       <c r="K9">
-        <f>J9-I9</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L9">
         <v>3</v>
       </c>
       <c r="M9">
-        <f>J9+2</f>
+        <f t="shared" si="4"/>
         <v>3</v>
       </c>
       <c r="N9">
-        <f>M9-L9</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="O9" t="s">
@@ -2062,11 +2054,11 @@
       <c r="R9">
         <v>1</v>
       </c>
-      <c r="S9" s="4">
+      <c r="S9" s="3">
         <v>1948.54</v>
       </c>
       <c r="T9">
-        <f>D9/S9</f>
+        <f t="shared" si="6"/>
         <v>508.50226323298472</v>
       </c>
       <c r="U9">
@@ -2084,11 +2076,11 @@
       <c r="Y9">
         <v>11</v>
       </c>
-      <c r="Z9" s="5">
-        <v>0</v>
-      </c>
-      <c r="AA9" s="6">
-        <f>Z9/D9</f>
+      <c r="Z9" s="4">
+        <v>0</v>
+      </c>
+      <c r="AA9" s="5">
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -2110,15 +2102,15 @@
         <v>712816</v>
       </c>
       <c r="F10">
-        <f>D10-C10</f>
+        <f t="shared" si="0"/>
         <v>89810</v>
       </c>
       <c r="G10">
-        <f>F10/C10*100</f>
+        <f t="shared" si="1"/>
         <v>14.925472351896138</v>
       </c>
       <c r="H10" s="2">
-        <f>(D10-E10)/E10</f>
+        <f t="shared" si="2"/>
         <v>-2.9857635069919865E-2</v>
       </c>
       <c r="I10">
@@ -2128,7 +2120,7 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <f>J10-I10</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L10">
@@ -2156,7 +2148,7 @@
         <v>61.05</v>
       </c>
       <c r="T10">
-        <f>D10/S10</f>
+        <f t="shared" si="6"/>
         <v>11327.321867321867</v>
       </c>
       <c r="U10">
@@ -2174,11 +2166,11 @@
       <c r="Y10">
         <v>1</v>
       </c>
-      <c r="Z10" s="5">
-        <v>0</v>
-      </c>
-      <c r="AA10" s="6">
-        <f>Z10/D10</f>
+      <c r="Z10" s="4">
+        <v>0</v>
+      </c>
+      <c r="AA10" s="5">
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -2199,15 +2191,15 @@
         <v>21733312</v>
       </c>
       <c r="F11">
-        <f>D11-C11</f>
+        <f t="shared" si="0"/>
         <v>2669754</v>
       </c>
       <c r="G11">
-        <f>F11/C11*100</f>
+        <f t="shared" si="1"/>
         <v>14.12510483036858</v>
       </c>
       <c r="H11" s="2">
-        <f>(D11-E11)/E11</f>
+        <f t="shared" si="2"/>
         <v>-7.4901147142230323E-3</v>
       </c>
       <c r="I11">
@@ -2217,18 +2209,18 @@
         <v>28</v>
       </c>
       <c r="K11">
-        <f>J11-I11</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="L11">
         <v>29</v>
       </c>
       <c r="M11">
-        <f>J11+2</f>
+        <f t="shared" ref="M11:M52" si="8">J11+2</f>
         <v>30</v>
       </c>
       <c r="N11">
-        <f>M11-L11</f>
+        <f t="shared" ref="N11:N52" si="9">M11-L11</f>
         <v>1</v>
       </c>
       <c r="O11" t="s">
@@ -2243,11 +2235,11 @@
       <c r="R11">
         <v>16</v>
       </c>
-      <c r="S11" s="4">
+      <c r="S11" s="3">
         <v>53624.76</v>
       </c>
       <c r="T11">
-        <f>D11/S11</f>
+        <f t="shared" si="6"/>
         <v>402.24939002058005</v>
       </c>
       <c r="U11">
@@ -2265,11 +2257,11 @@
       <c r="Y11">
         <v>28</v>
       </c>
-      <c r="Z11" s="5">
-        <v>0</v>
-      </c>
-      <c r="AA11" s="6">
-        <f>Z11/D11</f>
+      <c r="Z11" s="4">
+        <v>0</v>
+      </c>
+      <c r="AA11" s="5">
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -2290,15 +2282,15 @@
         <v>10710017</v>
       </c>
       <c r="F12">
-        <f>D12-C12</f>
+        <f t="shared" si="0"/>
         <v>997708</v>
       </c>
       <c r="G12">
-        <f>F12/C12*100</f>
+        <f t="shared" si="1"/>
         <v>10.256501986211145</v>
       </c>
       <c r="H12" s="2">
-        <f>(D12-E12)/E12</f>
+        <f t="shared" si="2"/>
         <v>1.4245542280651841E-3</v>
       </c>
       <c r="I12">
@@ -2308,18 +2300,18 @@
         <v>14</v>
       </c>
       <c r="K12">
-        <f>J12-I12</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L12">
         <v>16</v>
       </c>
       <c r="M12">
-        <f>J12+2</f>
+        <f t="shared" si="8"/>
         <v>16</v>
       </c>
       <c r="N12">
-        <f>M12-L12</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="O12" t="s">
@@ -2334,11 +2326,11 @@
       <c r="R12">
         <v>24</v>
       </c>
-      <c r="S12" s="4">
+      <c r="S12" s="3">
         <v>57513.49</v>
       </c>
       <c r="T12">
-        <f>D12/S12</f>
+        <f t="shared" si="6"/>
         <v>186.48275387217851</v>
       </c>
       <c r="U12">
@@ -2356,11 +2348,11 @@
       <c r="Y12">
         <v>26</v>
       </c>
-      <c r="Z12" s="5">
+      <c r="Z12" s="4">
         <v>3750886</v>
       </c>
-      <c r="AA12" s="6">
-        <f>Z12/D12</f>
+      <c r="AA12" s="5">
+        <f t="shared" si="7"/>
         <v>0.34972402569855093</v>
       </c>
     </row>
@@ -2381,15 +2373,15 @@
         <v>1407006</v>
       </c>
       <c r="F13">
-        <f>D13-C13</f>
+        <f t="shared" si="0"/>
         <v>93275</v>
       </c>
       <c r="G13">
-        <f>F13/C13*100</f>
+        <f t="shared" si="1"/>
         <v>6.8240246637919553</v>
       </c>
       <c r="H13" s="2">
-        <f>(D13-E13)/E13</f>
+        <f t="shared" si="2"/>
         <v>3.7761743731014652E-2</v>
       </c>
       <c r="I13">
@@ -2399,18 +2391,18 @@
         <v>2</v>
       </c>
       <c r="K13">
-        <f>J13-I13</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L13">
         <v>4</v>
       </c>
       <c r="M13">
-        <f>J13+2</f>
+        <f t="shared" si="8"/>
         <v>4</v>
       </c>
       <c r="N13">
-        <f>M13-L13</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="O13" t="s">
@@ -2425,11 +2417,11 @@
       <c r="R13">
         <v>0</v>
       </c>
-      <c r="S13" s="4">
+      <c r="S13" s="3">
         <v>6422.63</v>
       </c>
       <c r="T13">
-        <f>D13/S13</f>
+        <f t="shared" si="6"/>
         <v>227.34253724720247</v>
       </c>
       <c r="U13">
@@ -2447,11 +2439,11 @@
       <c r="Y13">
         <v>5</v>
       </c>
-      <c r="Z13" s="5">
+      <c r="Z13" s="4">
         <v>750000</v>
       </c>
-      <c r="AA13" s="6">
-        <f>Z13/D13</f>
+      <c r="AA13" s="5">
+        <f t="shared" si="7"/>
         <v>0.51365043143211908</v>
       </c>
     </row>
@@ -2472,15 +2464,15 @@
         <v>1826913</v>
       </c>
       <c r="F14">
-        <f>D14-C14</f>
+        <f t="shared" si="0"/>
         <v>267878</v>
       </c>
       <c r="G14">
-        <f>F14/C14*100</f>
+        <f t="shared" si="1"/>
         <v>17.024351461297403</v>
       </c>
       <c r="H14" s="2">
-        <f>(D14-E14)/E14</f>
+        <f t="shared" si="2"/>
         <v>7.9171805116061908E-3</v>
       </c>
       <c r="I14">
@@ -2490,18 +2482,18 @@
         <v>2</v>
       </c>
       <c r="K14">
-        <f>J14-I14</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L14">
         <v>4</v>
       </c>
       <c r="M14">
-        <f>J14+2</f>
+        <f t="shared" si="8"/>
         <v>4</v>
       </c>
       <c r="N14">
-        <f>M14-L14</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="O14" t="s">
@@ -2516,11 +2508,11 @@
       <c r="R14">
         <v>0</v>
       </c>
-      <c r="S14" s="4">
+      <c r="S14" s="3">
         <v>82643.12</v>
       </c>
       <c r="T14">
-        <f>D14/S14</f>
+        <f t="shared" si="6"/>
         <v>22.281068284934065</v>
       </c>
       <c r="U14">
@@ -2538,11 +2530,11 @@
       <c r="Y14">
         <v>47</v>
       </c>
-      <c r="Z14" s="5">
-        <v>0</v>
-      </c>
-      <c r="AA14" s="6">
-        <f>Z14/D14</f>
+      <c r="Z14" s="4">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="5">
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -2563,15 +2555,15 @@
         <v>12587530</v>
       </c>
       <c r="F15">
-        <f>D15-C15</f>
+        <f t="shared" si="0"/>
         <v>-41641</v>
       </c>
       <c r="G15">
-        <f>F15/C15*100</f>
+        <f t="shared" si="1"/>
         <v>-0.32369224167818428</v>
       </c>
       <c r="H15" s="2">
-        <f>(D15-E15)/E15</f>
+        <f t="shared" si="2"/>
         <v>1.8685874035652746E-2</v>
       </c>
       <c r="I15">
@@ -2581,18 +2573,18 @@
         <v>17</v>
       </c>
       <c r="K15">
-        <f>J15-I15</f>
+        <f t="shared" si="3"/>
         <v>-1</v>
       </c>
       <c r="L15">
         <v>20</v>
       </c>
       <c r="M15">
-        <f>J15+2</f>
+        <f t="shared" si="8"/>
         <v>19</v>
       </c>
       <c r="N15">
-        <f>M15-L15</f>
+        <f t="shared" si="9"/>
         <v>-1</v>
       </c>
       <c r="O15" t="s">
@@ -2607,11 +2599,11 @@
       <c r="R15">
         <v>42</v>
       </c>
-      <c r="S15" s="4">
+      <c r="S15" s="3">
         <v>55518.93</v>
       </c>
       <c r="T15">
-        <f>D15/S15</f>
+        <f t="shared" si="6"/>
         <v>230.96156572181778</v>
       </c>
       <c r="U15">
@@ -2629,11 +2621,11 @@
       <c r="Y15">
         <v>12</v>
       </c>
-      <c r="Z15" s="5">
+      <c r="Z15" s="4">
         <v>30500000</v>
       </c>
-      <c r="AA15" s="6">
-        <f>Z15/D15</f>
+      <c r="AA15" s="5">
+        <f t="shared" si="7"/>
         <v>2.3785869774000701</v>
       </c>
     </row>
@@ -2654,15 +2646,15 @@
         <v>6754953</v>
       </c>
       <c r="F16">
-        <f>D16-C16</f>
+        <f t="shared" si="0"/>
         <v>288698</v>
       </c>
       <c r="G16">
-        <f>F16/C16*100</f>
+        <f t="shared" si="1"/>
         <v>4.4404269606997193</v>
       </c>
       <c r="H16" s="2">
-        <f>(D16-E16)/E16</f>
+        <f t="shared" si="2"/>
         <v>5.2297921243863576E-3</v>
       </c>
       <c r="I16">
@@ -2672,18 +2664,18 @@
         <v>9</v>
       </c>
       <c r="K16">
-        <f>J16-I16</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L16">
         <v>11</v>
       </c>
       <c r="M16">
-        <f>J16+2</f>
+        <f t="shared" si="8"/>
         <v>11</v>
       </c>
       <c r="N16">
-        <f>M16-L16</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="O16" t="s">
@@ -2698,11 +2690,11 @@
       <c r="R16">
         <v>16</v>
       </c>
-      <c r="S16" s="4">
+      <c r="S16" s="3">
         <v>35826.11</v>
       </c>
       <c r="T16">
-        <f>D16/S16</f>
+        <f t="shared" si="6"/>
         <v>189.53439265384938</v>
       </c>
       <c r="U16">
@@ -2720,11 +2712,11 @@
       <c r="Y16">
         <v>36</v>
       </c>
-      <c r="Z16" s="5">
-        <v>0</v>
-      </c>
-      <c r="AA16" s="6">
-        <f>Z16/D16</f>
+      <c r="Z16" s="4">
+        <v>0</v>
+      </c>
+      <c r="AA16" s="5">
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -2745,15 +2737,15 @@
         <v>3163561</v>
       </c>
       <c r="F17">
-        <f>D17-C17</f>
+        <f t="shared" si="0"/>
         <v>138619</v>
       </c>
       <c r="G17">
-        <f>F17/C17*100</f>
+        <f t="shared" si="1"/>
         <v>4.5392491355814926</v>
       </c>
       <c r="H17" s="2">
-        <f>(D17-E17)/E17</f>
+        <f t="shared" si="2"/>
         <v>9.1178896186923531E-3</v>
       </c>
       <c r="I17">
@@ -2763,18 +2755,18 @@
         <v>4</v>
       </c>
       <c r="K17">
-        <f>J17-I17</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L17">
         <v>6</v>
       </c>
       <c r="M17">
-        <f>J17+2</f>
+        <f t="shared" si="8"/>
         <v>6</v>
       </c>
       <c r="N17">
-        <f>M17-L17</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="O17" t="s">
@@ -2789,11 +2781,11 @@
       <c r="R17">
         <v>2</v>
       </c>
-      <c r="S17" s="4">
+      <c r="S17" s="3">
         <v>55857.13</v>
       </c>
       <c r="T17">
-        <f>D17/S17</f>
+        <f t="shared" si="6"/>
         <v>57.153061748786591</v>
       </c>
       <c r="U17">
@@ -2811,11 +2803,11 @@
       <c r="Y17">
         <v>31</v>
       </c>
-      <c r="Z17" s="5">
-        <v>0</v>
-      </c>
-      <c r="AA17" s="6">
-        <f>Z17/D17</f>
+      <c r="Z17" s="4">
+        <v>0</v>
+      </c>
+      <c r="AA17" s="5">
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -2836,15 +2828,15 @@
         <v>2913805</v>
       </c>
       <c r="F18">
-        <f>D18-C18</f>
+        <f t="shared" si="0"/>
         <v>77052</v>
       </c>
       <c r="G18">
-        <f>F18/C18*100</f>
+        <f t="shared" si="1"/>
         <v>2.6905388026383008</v>
       </c>
       <c r="H18" s="2">
-        <f>(D18-E18)/E18</f>
+        <f t="shared" si="2"/>
         <v>9.2868259886986267E-3</v>
       </c>
       <c r="I18">
@@ -2854,18 +2846,18 @@
         <v>4</v>
       </c>
       <c r="K18">
-        <f>J18-I18</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L18">
         <v>6</v>
       </c>
       <c r="M18">
-        <f>J18+2</f>
+        <f t="shared" si="8"/>
         <v>6</v>
       </c>
       <c r="N18">
-        <f>M18-L18</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="O18" t="s">
@@ -2880,11 +2872,11 @@
       <c r="R18">
         <v>1</v>
       </c>
-      <c r="S18" s="4">
+      <c r="S18" s="3">
         <v>81758.720000000001</v>
       </c>
       <c r="T18">
-        <f>D18/S18</f>
+        <f t="shared" si="6"/>
         <v>35.97004698703698</v>
       </c>
       <c r="U18">
@@ -2902,11 +2894,11 @@
       <c r="Y18">
         <v>34</v>
       </c>
-      <c r="Z18" s="5">
-        <v>0</v>
-      </c>
-      <c r="AA18" s="6">
-        <f>Z18/D18</f>
+      <c r="Z18" s="4">
+        <v>0</v>
+      </c>
+      <c r="AA18" s="5">
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -2927,15 +2919,15 @@
         <v>4477251</v>
       </c>
       <c r="F19">
-        <f>D19-C19</f>
+        <f t="shared" si="0"/>
         <v>158736</v>
       </c>
       <c r="G19">
-        <f>F19/C19*100</f>
+        <f t="shared" si="1"/>
         <v>3.6485951612258156</v>
       </c>
       <c r="H19" s="2">
-        <f>(D19-E19)/E19</f>
+        <f t="shared" si="2"/>
         <v>7.1675677776385557E-3</v>
       </c>
       <c r="I19">
@@ -2945,18 +2937,18 @@
         <v>6</v>
       </c>
       <c r="K19">
-        <f>J19-I19</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L19">
         <v>8</v>
       </c>
       <c r="M19">
-        <f>J19+2</f>
+        <f t="shared" si="8"/>
         <v>8</v>
       </c>
       <c r="N19">
-        <f>M19-L19</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="O19" t="s">
@@ -2971,11 +2963,11 @@
       <c r="R19">
         <v>2</v>
       </c>
-      <c r="S19" s="4">
+      <c r="S19" s="3">
         <v>39486.339999999997</v>
       </c>
       <c r="T19">
-        <f>D19/S19</f>
+        <f t="shared" si="6"/>
         <v>114.2000499413215</v>
       </c>
       <c r="U19">
@@ -2993,11 +2985,11 @@
       <c r="Y19">
         <v>44</v>
       </c>
-      <c r="Z19" s="5">
-        <v>0</v>
-      </c>
-      <c r="AA19" s="6">
-        <f>Z19/D19</f>
+      <c r="Z19" s="4">
+        <v>0</v>
+      </c>
+      <c r="AA19" s="5">
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -3018,15 +3010,15 @@
         <v>4645318</v>
       </c>
       <c r="F20">
-        <f>D20-C20</f>
+        <f t="shared" si="0"/>
         <v>107506</v>
       </c>
       <c r="G20">
-        <f>F20/C20*100</f>
+        <f t="shared" si="1"/>
         <v>2.3607135940089092</v>
       </c>
       <c r="H20" s="2">
-        <f>(D20-E20)/E20</f>
+        <f t="shared" si="2"/>
         <v>3.4766188235121902E-3</v>
       </c>
       <c r="I20">
@@ -3036,18 +3028,18 @@
         <v>6</v>
       </c>
       <c r="K20">
-        <f>J20-I20</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L20">
         <v>8</v>
       </c>
       <c r="M20">
-        <f>J20+2</f>
+        <f t="shared" si="8"/>
         <v>8</v>
       </c>
       <c r="N20">
-        <f>M20-L20</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="O20" t="s">
@@ -3062,11 +3054,11 @@
       <c r="R20">
         <v>34</v>
       </c>
-      <c r="S20" s="4">
+      <c r="S20" s="3">
         <v>43203.9</v>
       </c>
       <c r="T20">
-        <f>D20/S20</f>
+        <f t="shared" si="6"/>
         <v>107.89461136610352</v>
       </c>
       <c r="U20">
@@ -3084,11 +3076,11 @@
       <c r="Y20">
         <v>39</v>
       </c>
-      <c r="Z20" s="5">
-        <v>0</v>
-      </c>
-      <c r="AA20" s="6">
-        <f>Z20/D20</f>
+      <c r="Z20" s="4">
+        <v>0</v>
+      </c>
+      <c r="AA20" s="5">
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -3109,15 +3101,15 @@
         <v>1350141</v>
       </c>
       <c r="F21">
-        <f>D21-C21</f>
+        <f t="shared" si="0"/>
         <v>30508</v>
       </c>
       <c r="G21">
-        <f>F21/C21*100</f>
+        <f t="shared" si="1"/>
         <v>2.2885451220262341</v>
       </c>
       <c r="H21" s="2">
-        <f>(D21-E21)/E21</f>
+        <f t="shared" si="2"/>
         <v>9.9552565250592348E-3</v>
       </c>
       <c r="I21">
@@ -3127,18 +3119,18 @@
         <v>2</v>
       </c>
       <c r="K21">
-        <f>J21-I21</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L21">
         <v>4</v>
       </c>
       <c r="M21">
-        <f>J21+2</f>
+        <f t="shared" si="8"/>
         <v>4</v>
       </c>
       <c r="N21">
-        <f>M21-L21</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="O21" t="s">
@@ -3153,11 +3145,11 @@
       <c r="R21">
         <v>2</v>
       </c>
-      <c r="S21" s="4">
+      <c r="S21" s="3">
         <v>30842.92</v>
       </c>
       <c r="T21">
-        <f>D21/S21</f>
+        <f t="shared" si="6"/>
         <v>44.210535189275205</v>
       </c>
       <c r="U21">
@@ -3175,11 +3167,11 @@
       <c r="Y21">
         <v>18</v>
       </c>
-      <c r="Z21" s="5">
-        <v>0</v>
-      </c>
-      <c r="AA21" s="6">
-        <f>Z21/D21</f>
+      <c r="Z21" s="4">
+        <v>0</v>
+      </c>
+      <c r="AA21" s="5">
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -3200,15 +3192,15 @@
         <v>6055802</v>
       </c>
       <c r="F22">
-        <f>D22-C22</f>
+        <f t="shared" si="0"/>
         <v>395349</v>
       </c>
       <c r="G22">
-        <f>F22/C22*100</f>
+        <f t="shared" si="1"/>
         <v>6.8282184462020172</v>
       </c>
       <c r="H22" s="2">
-        <f>(D22-E22)/E22</f>
+        <f t="shared" si="2"/>
         <v>2.1380487671162299E-2</v>
       </c>
       <c r="I22">
@@ -3218,18 +3210,18 @@
         <v>8</v>
       </c>
       <c r="K22">
-        <f>J22-I22</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L22">
         <v>10</v>
       </c>
       <c r="M22">
-        <f>J22+2</f>
+        <f t="shared" si="8"/>
         <v>10</v>
       </c>
       <c r="N22">
-        <f>M22-L22</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="O22" t="s">
@@ -3244,11 +3236,11 @@
       <c r="R22">
         <v>13</v>
       </c>
-      <c r="S22" s="4">
+      <c r="S22" s="3">
         <v>9707.24</v>
       </c>
       <c r="T22">
-        <f>D22/S22</f>
+        <f t="shared" si="6"/>
         <v>637.18193842946096</v>
       </c>
       <c r="U22">
@@ -3266,11 +3258,11 @@
       <c r="Y22">
         <v>4</v>
       </c>
-      <c r="Z22" s="5">
+      <c r="Z22" s="4">
         <v>5000000</v>
       </c>
-      <c r="AA22" s="6">
-        <f>Z22/D22</f>
+      <c r="AA22" s="5">
+        <f t="shared" si="7"/>
         <v>0.80837110312584171</v>
       </c>
     </row>
@@ -3291,15 +3283,15 @@
         <v>6893574</v>
       </c>
       <c r="F23">
-        <f>D23-C23</f>
+        <f t="shared" si="0"/>
         <v>473825</v>
       </c>
       <c r="G23">
-        <f>F23/C23*100</f>
+        <f t="shared" si="1"/>
         <v>7.223334071178253</v>
       </c>
       <c r="H23" s="2">
-        <f>(D23-E23)/E23</f>
+        <f t="shared" si="2"/>
         <v>2.0293537140531167E-2</v>
       </c>
       <c r="I23">
@@ -3309,18 +3301,18 @@
         <v>9</v>
       </c>
       <c r="K23">
-        <f>J23-I23</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L23">
         <v>11</v>
       </c>
       <c r="M23">
-        <f>J23+2</f>
+        <f t="shared" si="8"/>
         <v>11</v>
       </c>
       <c r="N23">
-        <f>M23-L23</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="O23" t="s">
@@ -3335,11 +3327,11 @@
       <c r="R23">
         <v>33</v>
       </c>
-      <c r="S23" s="4">
+      <c r="S23" s="3">
         <v>7800.06</v>
       </c>
       <c r="T23">
-        <f>D23/S23</f>
+        <f t="shared" si="6"/>
         <v>901.71985856519052</v>
       </c>
       <c r="U23">
@@ -3357,11 +3349,11 @@
       <c r="Y23">
         <v>3</v>
       </c>
-      <c r="Z23" s="5">
+      <c r="Z23" s="4">
         <v>6650000</v>
       </c>
-      <c r="AA23" s="6">
-        <f>Z23/D23</f>
+      <c r="AA23" s="5">
+        <f t="shared" si="7"/>
         <v>0.94547939288564431</v>
       </c>
     </row>
@@ -3382,15 +3374,15 @@
         <v>9966555</v>
       </c>
       <c r="F24">
-        <f>D24-C24</f>
+        <f t="shared" si="0"/>
         <v>172816</v>
       </c>
       <c r="G24">
-        <f>F24/C24*100</f>
+        <f t="shared" si="1"/>
         <v>1.743568613262849</v>
       </c>
       <c r="H24" s="2">
-        <f>(D24-E24)/E24</f>
+        <f t="shared" si="2"/>
         <v>1.1828259614279959E-2</v>
       </c>
       <c r="I24">
@@ -3400,18 +3392,18 @@
         <v>13</v>
       </c>
       <c r="K24">
-        <f>J24-I24</f>
+        <f t="shared" si="3"/>
         <v>-1</v>
       </c>
       <c r="L24">
         <v>16</v>
       </c>
       <c r="M24">
-        <f>J24+2</f>
+        <f t="shared" si="8"/>
         <v>15</v>
       </c>
       <c r="N24">
-        <f>M24-L24</f>
+        <f t="shared" si="9"/>
         <v>-1</v>
       </c>
       <c r="O24" t="s">
@@ -3426,11 +3418,11 @@
       <c r="R24">
         <v>78</v>
       </c>
-      <c r="S24" s="4">
+      <c r="S24" s="3">
         <v>56538.9</v>
       </c>
       <c r="T24">
-        <f>D24/S24</f>
+        <f t="shared" si="6"/>
         <v>178.36289704964193</v>
       </c>
       <c r="U24">
@@ -3448,11 +3440,11 @@
       <c r="Y24">
         <v>21</v>
       </c>
-      <c r="Z24" s="5">
+      <c r="Z24" s="4">
         <v>16000000</v>
       </c>
-      <c r="AA24" s="6">
-        <f>Z24/D24</f>
+      <c r="AA24" s="5">
+        <f t="shared" si="7"/>
         <v>1.5866024119133215</v>
       </c>
     </row>
@@ -3473,15 +3465,15 @@
         <v>5657342</v>
       </c>
       <c r="F25">
-        <f>D25-C25</f>
+        <f t="shared" si="0"/>
         <v>394873</v>
       </c>
       <c r="G25">
-        <f>F25/C25*100</f>
+        <f t="shared" si="1"/>
         <v>7.4295764776582871</v>
       </c>
       <c r="H25" s="2">
-        <f>(D25-E25)/E25</f>
+        <f t="shared" si="2"/>
         <v>9.2640678254911936E-3</v>
       </c>
       <c r="I25">
@@ -3491,18 +3483,18 @@
         <v>8</v>
       </c>
       <c r="K25">
-        <f>J25-I25</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L25">
         <v>10</v>
       </c>
       <c r="M25">
-        <f>J25+2</f>
+        <f t="shared" si="8"/>
         <v>10</v>
       </c>
       <c r="N25">
-        <f>M25-L25</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="O25" t="s">
@@ -3517,11 +3509,11 @@
       <c r="R25">
         <v>1</v>
       </c>
-      <c r="S25" s="4">
+      <c r="S25" s="3">
         <v>79626.740000000005</v>
       </c>
       <c r="T25">
-        <f>D25/S25</f>
+        <f t="shared" si="6"/>
         <v>71.706464436444335</v>
       </c>
       <c r="U25">
@@ -3539,11 +3531,11 @@
       <c r="Y25">
         <v>20</v>
       </c>
-      <c r="Z25" s="5">
+      <c r="Z25" s="4">
         <v>2170000</v>
       </c>
-      <c r="AA25" s="6">
-        <f>Z25/D25</f>
+      <c r="AA25" s="5">
+        <f t="shared" si="7"/>
         <v>0.38005153288619192</v>
       </c>
     </row>
@@ -3564,15 +3556,15 @@
         <v>2966786</v>
       </c>
       <c r="F26">
-        <f>D26-C26</f>
+        <f t="shared" si="0"/>
         <v>-14326</v>
       </c>
       <c r="G26">
-        <f>F26/C26*100</f>
+        <f t="shared" si="1"/>
         <v>-0.48102234876974315</v>
       </c>
       <c r="H26" s="2">
-        <f>(D26-E26)/E26</f>
+        <f t="shared" si="2"/>
         <v>-9.6805094806298806E-4</v>
       </c>
       <c r="I26">
@@ -3582,18 +3574,18 @@
         <v>4</v>
       </c>
       <c r="K26">
-        <f>J26-I26</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L26">
         <v>6</v>
       </c>
       <c r="M26">
-        <f>J26+2</f>
+        <f t="shared" si="8"/>
         <v>6</v>
       </c>
       <c r="N26">
-        <f>M26-L26</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="O26" t="s">
@@ -3608,11 +3600,11 @@
       <c r="R26">
         <v>4</v>
       </c>
-      <c r="S26" s="4">
+      <c r="S26" s="3">
         <v>46923.27</v>
       </c>
       <c r="T26">
-        <f>D26/S26</f>
+        <f t="shared" si="6"/>
         <v>63.165120418930741</v>
       </c>
       <c r="U26">
@@ -3630,11 +3622,11 @@
       <c r="Y26">
         <v>37</v>
       </c>
-      <c r="Z26" s="5">
+      <c r="Z26" s="4">
         <v>400000</v>
       </c>
-      <c r="AA26" s="6">
-        <f>Z26/D26</f>
+      <c r="AA26" s="5">
+        <f t="shared" si="7"/>
         <v>0.13495668227890553</v>
       </c>
     </row>
@@ -3655,15 +3647,15 @@
         <v>6151548</v>
       </c>
       <c r="F27">
-        <f>D27-C27</f>
+        <f t="shared" si="0"/>
         <v>148803</v>
       </c>
       <c r="G27">
-        <f>F27/C27*100</f>
+        <f t="shared" si="1"/>
         <v>2.4753147229350252</v>
       </c>
       <c r="H27" s="2">
-        <f>(D27-E27)/E27</f>
+        <f t="shared" si="2"/>
         <v>1.4196426655534509E-3</v>
       </c>
       <c r="I27">
@@ -3673,18 +3665,18 @@
         <v>8</v>
       </c>
       <c r="K27">
-        <f>J27-I27</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L27">
         <v>10</v>
       </c>
       <c r="M27">
-        <f>J27+2</f>
+        <f t="shared" si="8"/>
         <v>10</v>
       </c>
       <c r="N27">
-        <f>M27-L27</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="O27" t="s">
@@ -3699,11 +3691,11 @@
       <c r="R27">
         <v>4</v>
       </c>
-      <c r="S27" s="4">
+      <c r="S27" s="3">
         <v>68741.52</v>
       </c>
       <c r="T27">
-        <f>D27/S27</f>
+        <f t="shared" si="6"/>
         <v>89.615140893014868</v>
       </c>
       <c r="U27">
@@ -3721,11 +3713,11 @@
       <c r="Y27">
         <v>35</v>
       </c>
-      <c r="Z27" s="5">
+      <c r="Z27" s="4">
         <v>501650</v>
       </c>
-      <c r="AA27" s="6">
-        <f>Z27/D27</f>
+      <c r="AA27" s="5">
+        <f t="shared" si="7"/>
         <v>8.1432973593250052E-2</v>
       </c>
     </row>
@@ -3746,15 +3738,15 @@
         <v>1080577</v>
       </c>
       <c r="F28">
-        <f>D28-C28</f>
+        <f t="shared" si="0"/>
         <v>90991</v>
       </c>
       <c r="G28">
-        <f>F28/C28*100</f>
+        <f t="shared" si="1"/>
         <v>9.1501946871329505</v>
       </c>
       <c r="H28" s="2">
-        <f>(D28-E28)/E28</f>
+        <f t="shared" si="2"/>
         <v>4.4698341719285163E-3</v>
       </c>
       <c r="I28">
@@ -3764,18 +3756,18 @@
         <v>2</v>
       </c>
       <c r="K28">
-        <f>J28-I28</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="L28">
         <v>3</v>
       </c>
       <c r="M28">
-        <f>J28+2</f>
+        <f t="shared" si="8"/>
         <v>4</v>
       </c>
       <c r="N28">
-        <f>M28-L28</f>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="O28" t="s">
@@ -3790,11 +3782,11 @@
       <c r="R28">
         <v>0</v>
       </c>
-      <c r="S28" s="4">
+      <c r="S28" s="3">
         <v>145545.79999999999</v>
       </c>
       <c r="T28">
-        <f>D28/S28</f>
+        <f t="shared" si="6"/>
         <v>7.4574944794009861</v>
       </c>
       <c r="U28">
@@ -3812,11 +3804,11 @@
       <c r="Y28">
         <v>38</v>
       </c>
-      <c r="Z28" s="5">
+      <c r="Z28" s="4">
         <v>635500</v>
       </c>
-      <c r="AA28" s="6">
-        <f>Z28/D28</f>
+      <c r="AA28" s="5">
+        <f t="shared" si="7"/>
         <v>0.58549465776432252</v>
       </c>
     </row>
@@ -3824,7 +3816,7 @@
       <c r="A29" t="s">
         <v>37</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="B29" t="s">
         <v>85</v>
       </c>
       <c r="C29">
@@ -3837,15 +3829,15 @@
         <v>1937552</v>
       </c>
       <c r="F29">
-        <f>D29-C29</f>
+        <f t="shared" si="0"/>
         <v>131508</v>
       </c>
       <c r="G29">
-        <f>F29/C29*100</f>
+        <f t="shared" si="1"/>
         <v>7.1790700530891334</v>
       </c>
       <c r="H29" s="2">
-        <f>(D29-E29)/E29</f>
+        <f t="shared" si="2"/>
         <v>1.330596546570105E-2</v>
       </c>
       <c r="I29">
@@ -3855,37 +3847,37 @@
         <v>3</v>
       </c>
       <c r="K29">
-        <f>J29-I29</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L29">
         <v>5</v>
       </c>
       <c r="M29">
-        <f>J29+2</f>
+        <f t="shared" si="8"/>
         <v>5</v>
       </c>
       <c r="N29">
-        <f>M29-L29</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="O29" t="s">
         <v>9</v>
       </c>
-      <c r="P29" s="3">
+      <c r="P29">
         <v>214</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="Q29">
         <v>4</v>
       </c>
-      <c r="R29" s="3">
+      <c r="R29">
         <v>1</v>
       </c>
-      <c r="S29" s="4">
+      <c r="S29" s="3">
         <v>76824.17</v>
       </c>
       <c r="T29">
-        <f>D29/S29</f>
+        <f t="shared" si="6"/>
         <v>25.556188892115593</v>
       </c>
       <c r="U29">
@@ -3903,8 +3895,8 @@
       <c r="Y29">
         <v>40</v>
       </c>
-      <c r="AA29" s="6">
-        <f>Z29/D29</f>
+      <c r="AA29" s="5">
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -3925,15 +3917,15 @@
         <v>3138259</v>
       </c>
       <c r="F30">
-        <f>D30-C30</f>
+        <f t="shared" si="0"/>
         <v>399030</v>
       </c>
       <c r="G30">
-        <f>F30/C30*100</f>
+        <f t="shared" si="1"/>
         <v>14.72744102823027</v>
       </c>
       <c r="H30" s="2">
-        <f>(D30-E30)/E30</f>
+        <f t="shared" si="2"/>
         <v>-9.4947548943538438E-3</v>
       </c>
       <c r="I30">
@@ -3943,18 +3935,18 @@
         <v>4</v>
       </c>
       <c r="K30">
-        <f>J30-I30</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L30">
         <v>6</v>
       </c>
       <c r="M30">
-        <f>J30+2</f>
+        <f t="shared" si="8"/>
         <v>6</v>
       </c>
       <c r="N30">
-        <f>M30-L30</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="O30" t="s">
@@ -3969,11 +3961,11 @@
       <c r="R30">
         <v>6</v>
       </c>
-      <c r="S30" s="4">
+      <c r="S30" s="3">
         <v>109781.18</v>
       </c>
       <c r="T30">
-        <f>D30/S30</f>
+        <f t="shared" si="6"/>
         <v>28.315071854756891</v>
       </c>
       <c r="U30">
@@ -3991,11 +3983,11 @@
       <c r="Y30">
         <v>22</v>
       </c>
-      <c r="Z30" s="5">
+      <c r="Z30" s="4">
         <v>5000000</v>
       </c>
-      <c r="AA30" s="6">
-        <f>Z30/D30</f>
+      <c r="AA30" s="5">
+        <f t="shared" si="7"/>
         <v>1.6085125055413256</v>
       </c>
     </row>
@@ -4016,15 +4008,15 @@
         <v>1366275</v>
       </c>
       <c r="F31">
-        <f>D31-C31</f>
+        <f t="shared" si="0"/>
         <v>57644</v>
       </c>
       <c r="G31">
-        <f>F31/C31*100</f>
+        <f t="shared" si="1"/>
         <v>4.3621944159613149</v>
       </c>
       <c r="H31" s="2">
-        <f>(D31-E31)/E31</f>
+        <f t="shared" si="2"/>
         <v>9.3787853836160371E-3</v>
       </c>
       <c r="I31">
@@ -4034,18 +4026,18 @@
         <v>2</v>
       </c>
       <c r="K31">
-        <f>J31-I31</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L31">
         <v>4</v>
       </c>
       <c r="M31">
-        <f>J31+2</f>
+        <f t="shared" si="8"/>
         <v>4</v>
       </c>
       <c r="N31">
-        <f>M31-L31</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="O31" t="s">
@@ -4060,11 +4052,11 @@
       <c r="R31">
         <v>1</v>
       </c>
-      <c r="S31" s="4">
+      <c r="S31" s="3">
         <v>8952.65</v>
       </c>
       <c r="T31">
-        <f>D31/S31</f>
+        <f t="shared" si="6"/>
         <v>154.0425460617806</v>
       </c>
       <c r="U31">
@@ -4082,8 +4074,8 @@
       <c r="Y31">
         <v>19</v>
       </c>
-      <c r="AA31" s="6">
-        <f>Z31/D31</f>
+      <c r="AA31" s="5">
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
@@ -4104,15 +4096,15 @@
         <v>8882371</v>
       </c>
       <c r="F32">
-        <f>D32-C32</f>
+        <f t="shared" si="0"/>
         <v>486992</v>
       </c>
       <c r="G32">
-        <f>F32/C32*100</f>
+        <f t="shared" si="1"/>
         <v>5.5292869112362295</v>
       </c>
       <c r="H32" s="2">
-        <f>(D32-E32)/E32</f>
+        <f t="shared" si="2"/>
         <v>4.6397746727759967E-2</v>
       </c>
       <c r="I32">
@@ -4122,18 +4114,18 @@
         <v>12</v>
       </c>
       <c r="K32">
-        <f>J32-I32</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L32">
         <v>14</v>
       </c>
       <c r="M32">
-        <f>J32+2</f>
+        <f t="shared" si="8"/>
         <v>14</v>
       </c>
       <c r="N32">
-        <f>M32-L32</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="O32" t="s">
@@ -4148,11 +4140,11 @@
       <c r="R32">
         <v>88</v>
       </c>
-      <c r="S32" s="4">
+      <c r="S32" s="3">
         <v>7354.22</v>
       </c>
       <c r="T32">
-        <f>D32/S32</f>
+        <f t="shared" si="6"/>
         <v>1263.8312424703095</v>
       </c>
       <c r="U32">
@@ -4170,11 +4162,11 @@
       <c r="Y32">
         <v>14</v>
       </c>
-      <c r="Z32" s="5">
+      <c r="Z32" s="4">
         <v>9000000</v>
       </c>
-      <c r="AA32" s="6">
-        <f>Z32/D32</f>
+      <c r="AA32" s="5">
+        <f t="shared" si="7"/>
         <v>0.96831532392353192</v>
       </c>
     </row>
@@ -4195,15 +4187,15 @@
         <v>2106319</v>
       </c>
       <c r="F33">
-        <f>D33-C33</f>
+        <f t="shared" si="0"/>
         <v>52947</v>
       </c>
       <c r="G33">
-        <f>F33/C33*100</f>
+        <f t="shared" si="1"/>
         <v>2.5612001898152785</v>
       </c>
       <c r="H33" s="2">
-        <f>(D33-E33)/E33</f>
+        <f t="shared" si="2"/>
         <v>6.5996651029592386E-3</v>
       </c>
       <c r="I33">
@@ -4213,18 +4205,18 @@
         <v>3</v>
       </c>
       <c r="K33">
-        <f>J33-I33</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L33">
         <v>5</v>
       </c>
       <c r="M33">
-        <f>J33+2</f>
+        <f t="shared" si="8"/>
         <v>5</v>
       </c>
       <c r="N33">
-        <f>M33-L33</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="O33" t="s">
@@ -4239,11 +4231,11 @@
       <c r="R33">
         <v>1</v>
       </c>
-      <c r="S33" s="4">
+      <c r="S33" s="3">
         <v>121298.15</v>
       </c>
       <c r="T33">
-        <f>D33/S33</f>
+        <f t="shared" si="6"/>
         <v>17.479409207807375</v>
       </c>
       <c r="U33">
@@ -4261,11 +4253,11 @@
       <c r="Y33">
         <v>16</v>
       </c>
-      <c r="Z33" s="5">
+      <c r="Z33" s="4">
         <v>11500000</v>
       </c>
-      <c r="AA33" s="6">
-        <f>Z33/D33</f>
+      <c r="AA33" s="5">
+        <f t="shared" si="7"/>
         <v>5.4239654375489339</v>
       </c>
     </row>
@@ -4286,15 +4278,15 @@
         <v>19336776</v>
       </c>
       <c r="F34">
-        <f>D34-C34</f>
+        <f t="shared" ref="F34:F52" si="10">D34-C34</f>
         <v>794696</v>
       </c>
       <c r="G34">
-        <f>F34/C34*100</f>
+        <f t="shared" ref="G34:G52" si="11">F34/C34*100</f>
         <v>4.0919301242903643</v>
       </c>
       <c r="H34" s="2">
-        <f>(D34-E34)/E34</f>
+        <f t="shared" ref="H34:H52" si="12">(D34-E34)/E34</f>
         <v>4.5456129811919009E-2</v>
       </c>
       <c r="I34">
@@ -4304,37 +4296,37 @@
         <v>26</v>
       </c>
       <c r="K34">
-        <f>J34-I34</f>
+        <f t="shared" ref="K34:K52" si="13">J34-I34</f>
         <v>-1</v>
       </c>
       <c r="L34">
         <v>29</v>
       </c>
       <c r="M34">
-        <f>J34+2</f>
+        <f t="shared" si="8"/>
         <v>28</v>
       </c>
       <c r="N34">
-        <f>M34-L34</f>
+        <f t="shared" si="9"/>
         <v>-1</v>
       </c>
       <c r="O34" t="s">
         <v>12</v>
       </c>
       <c r="P34">
-        <v>84735</v>
+        <v>133197</v>
       </c>
       <c r="Q34">
-        <v>1672</v>
+        <v>3069</v>
       </c>
       <c r="R34">
-        <v>365</v>
-      </c>
-      <c r="S34" s="4">
+        <v>666</v>
+      </c>
+      <c r="S34" s="3">
         <v>47126.400000000001</v>
       </c>
       <c r="T34">
-        <f>D34/S34</f>
+        <f t="shared" ref="T34:T52" si="14">D34/S34</f>
         <v>428.96870968289534</v>
       </c>
       <c r="U34">
@@ -4352,11 +4344,11 @@
       <c r="Y34">
         <v>7</v>
       </c>
-      <c r="Z34" s="5">
+      <c r="Z34" s="4">
         <v>20000000</v>
       </c>
-      <c r="AA34" s="6">
-        <f>Z34/D34</f>
+      <c r="AA34" s="5">
+        <f t="shared" ref="AA34:AA52" si="15">Z34/D34</f>
         <v>0.98932757927222192</v>
       </c>
     </row>
@@ -4377,15 +4369,15 @@
         <v>10600823</v>
       </c>
       <c r="F35">
-        <f>D35-C35</f>
+        <f t="shared" si="10"/>
         <v>888167</v>
       </c>
       <c r="G35">
-        <f>F35/C35*100</f>
+        <f t="shared" si="11"/>
         <v>9.2848351849159005</v>
       </c>
       <c r="H35" s="2">
-        <f>(D35-E35)/E35</f>
+        <f t="shared" si="12"/>
         <v>-1.3855056347983548E-2</v>
       </c>
       <c r="I35">
@@ -4395,18 +4387,18 @@
         <v>14</v>
       </c>
       <c r="K35">
-        <f>J35-I35</f>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="L35">
         <v>15</v>
       </c>
       <c r="M35">
-        <f>J35+2</f>
+        <f t="shared" si="8"/>
         <v>16</v>
       </c>
       <c r="N35">
-        <f>M35-L35</f>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="O35" t="s">
@@ -4421,11 +4413,11 @@
       <c r="R35">
         <v>1</v>
       </c>
-      <c r="S35" s="4">
+      <c r="S35" s="3">
         <v>48617.91</v>
       </c>
       <c r="T35">
-        <f>D35/S35</f>
+        <f t="shared" si="14"/>
         <v>215.02257090031225</v>
       </c>
       <c r="U35">
@@ -4443,11 +4435,11 @@
       <c r="Y35">
         <v>27</v>
       </c>
-      <c r="Z35" s="5">
-        <v>0</v>
-      </c>
-      <c r="AA35" s="6">
-        <f>Z35/D35</f>
+      <c r="Z35" s="4">
+        <v>0</v>
+      </c>
+      <c r="AA35" s="5">
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
@@ -4468,15 +4460,15 @@
         <v>765309</v>
       </c>
       <c r="F36">
-        <f>D36-C36</f>
+        <f t="shared" si="10"/>
         <v>103797</v>
       </c>
       <c r="G36">
-        <f>F36/C36*100</f>
+        <f t="shared" si="11"/>
         <v>15.356743921113175</v>
       </c>
       <c r="H36" s="2">
-        <f>(D36-E36)/E36</f>
+        <f t="shared" si="12"/>
         <v>1.8806782619830684E-2</v>
       </c>
       <c r="I36">
@@ -4486,18 +4478,18 @@
         <v>1</v>
       </c>
       <c r="K36">
-        <f>J36-I36</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="L36">
         <v>3</v>
       </c>
       <c r="M36">
-        <f>J36+2</f>
+        <f t="shared" si="8"/>
         <v>3</v>
       </c>
       <c r="N36">
-        <f>M36-L36</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="O36" t="s">
@@ -4512,11 +4504,11 @@
       <c r="R36">
         <v>0</v>
       </c>
-      <c r="S36" s="4">
+      <c r="S36" s="3">
         <v>69000.800000000003</v>
       </c>
       <c r="T36">
-        <f>D36/S36</f>
+        <f t="shared" si="14"/>
         <v>11.299897972197423</v>
       </c>
       <c r="U36">
@@ -4534,11 +4526,11 @@
       <c r="Y36">
         <v>49</v>
       </c>
-      <c r="Z36" s="5">
+      <c r="Z36" s="4">
         <v>1000000</v>
       </c>
-      <c r="AA36" s="6">
-        <f>Z36/D36</f>
+      <c r="AA36" s="5">
+        <f t="shared" si="15"/>
         <v>1.2825412785910515</v>
       </c>
     </row>
@@ -4559,15 +4551,15 @@
         <v>11693217</v>
       </c>
       <c r="F37">
-        <f>D37-C37</f>
+        <f t="shared" si="10"/>
         <v>240353</v>
       </c>
       <c r="G37">
-        <f>F37/C37*100</f>
+        <f t="shared" si="11"/>
         <v>2.0776514144666183</v>
       </c>
       <c r="H37" s="2">
-        <f>(D37-E37)/E37</f>
+        <f t="shared" si="12"/>
         <v>9.8887243775600854E-3</v>
       </c>
       <c r="I37">
@@ -4577,18 +4569,18 @@
         <v>15</v>
       </c>
       <c r="K37">
-        <f>J37-I37</f>
+        <f t="shared" si="13"/>
         <v>-1</v>
       </c>
       <c r="L37">
         <v>18</v>
       </c>
       <c r="M37">
-        <f>J37+2</f>
+        <f t="shared" si="8"/>
         <v>17</v>
       </c>
       <c r="N37">
-        <f>M37-L37</f>
+        <f t="shared" si="9"/>
         <v>-1</v>
       </c>
       <c r="O37" t="s">
@@ -4603,11 +4595,11 @@
       <c r="R37">
         <v>10</v>
       </c>
-      <c r="S37" s="4">
+      <c r="S37" s="3">
         <v>40860.69</v>
       </c>
       <c r="T37">
-        <f>D37/S37</f>
+        <f t="shared" si="14"/>
         <v>289.00265756647769</v>
       </c>
       <c r="U37">
@@ -4625,11 +4617,11 @@
       <c r="Y37">
         <v>30</v>
       </c>
-      <c r="Z37" s="5">
-        <v>0</v>
-      </c>
-      <c r="AA37" s="6">
-        <f>Z37/D37</f>
+      <c r="Z37" s="4">
+        <v>0</v>
+      </c>
+      <c r="AA37" s="5">
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
@@ -4650,15 +4642,15 @@
         <v>3980783</v>
       </c>
       <c r="F38">
-        <f>D38-C38</f>
+        <f t="shared" si="10"/>
         <v>198634</v>
       </c>
       <c r="G38">
-        <f>F38/C38*100</f>
+        <f t="shared" si="11"/>
         <v>5.2759688085841736</v>
       </c>
       <c r="H38" s="2">
-        <f>(D38-E38)/E38</f>
+        <f t="shared" si="12"/>
         <v>-4.3375888612868377E-3</v>
       </c>
       <c r="I38">
@@ -4668,18 +4660,18 @@
         <v>5</v>
       </c>
       <c r="K38">
-        <f>J38-I38</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="L38">
         <v>7</v>
       </c>
       <c r="M38">
-        <f>J38+2</f>
+        <f t="shared" si="8"/>
         <v>7</v>
       </c>
       <c r="N38">
-        <f>M38-L38</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="O38" t="s">
@@ -4694,11 +4686,11 @@
       <c r="R38">
         <v>5</v>
       </c>
-      <c r="S38" s="4">
+      <c r="S38" s="3">
         <v>68594.92</v>
       </c>
       <c r="T38">
-        <f>D38/S38</f>
+        <f t="shared" si="14"/>
         <v>57.781480027967085</v>
       </c>
       <c r="U38">
@@ -4716,11 +4708,11 @@
       <c r="Y38">
         <v>48</v>
       </c>
-      <c r="Z38" s="5">
-        <v>0</v>
-      </c>
-      <c r="AA38" s="6">
-        <f>Z38/D38</f>
+      <c r="Z38" s="4">
+        <v>0</v>
+      </c>
+      <c r="AA38" s="5">
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
@@ -4741,15 +4733,15 @@
         <v>4241507</v>
       </c>
       <c r="F39">
-        <f>D39-C39</f>
+        <f t="shared" si="10"/>
         <v>392894</v>
       </c>
       <c r="G39">
-        <f>F39/C39*100</f>
+        <f t="shared" si="11"/>
         <v>10.208735318710204</v>
       </c>
       <c r="H39" s="2">
-        <f>(D39-E39)/E39</f>
+        <f t="shared" si="12"/>
         <v>-1.6503568189325161E-6</v>
       </c>
       <c r="I39">
@@ -4759,18 +4751,18 @@
         <v>6</v>
       </c>
       <c r="K39">
-        <f>J39-I39</f>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="L39">
         <v>7</v>
       </c>
       <c r="M39">
-        <f>J39+2</f>
+        <f t="shared" si="8"/>
         <v>8</v>
       </c>
       <c r="N39">
-        <f>M39-L39</f>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="O39" t="s">
@@ -4785,11 +4777,11 @@
       <c r="R39">
         <v>0</v>
       </c>
-      <c r="S39" s="4">
+      <c r="S39" s="3">
         <v>95988.01</v>
       </c>
       <c r="T39">
-        <f>D39/S39</f>
+        <f t="shared" si="14"/>
         <v>44.187810540087249</v>
       </c>
       <c r="U39">
@@ -4807,11 +4799,11 @@
       <c r="Y39">
         <v>13</v>
       </c>
-      <c r="Z39" s="5">
+      <c r="Z39" s="4">
         <v>7730772</v>
       </c>
-      <c r="AA39" s="6">
-        <f>Z39/D39</f>
+      <c r="AA39" s="5">
+        <f t="shared" si="15"/>
         <v>1.8226504774254391</v>
       </c>
     </row>
@@ -4832,15 +4824,15 @@
         <v>12783254</v>
       </c>
       <c r="F40">
-        <f>D40-C40</f>
+        <f t="shared" si="10"/>
         <v>276939</v>
       </c>
       <c r="G40">
-        <f>F40/C40*100</f>
+        <f t="shared" si="11"/>
         <v>2.1746451975888319</v>
       </c>
       <c r="H40" s="2">
-        <f>(D40-E40)/E40</f>
+        <f t="shared" si="12"/>
         <v>1.7881988420162816E-2</v>
       </c>
       <c r="I40">
@@ -4850,18 +4842,18 @@
         <v>17</v>
       </c>
       <c r="K40">
-        <f>J40-I40</f>
+        <f t="shared" si="13"/>
         <v>-1</v>
       </c>
       <c r="L40">
         <v>20</v>
       </c>
       <c r="M40">
-        <f>J40+2</f>
+        <f t="shared" si="8"/>
         <v>19</v>
       </c>
       <c r="N40">
-        <f>M40-L40</f>
+        <f t="shared" si="9"/>
         <v>-1</v>
       </c>
       <c r="O40" t="s">
@@ -4876,11 +4868,11 @@
       <c r="R40">
         <v>11</v>
       </c>
-      <c r="S40" s="4">
+      <c r="S40" s="3">
         <v>44742.7</v>
       </c>
       <c r="T40">
-        <f>D40/S40</f>
+        <f t="shared" si="14"/>
         <v>290.81490388376204</v>
       </c>
       <c r="U40">
@@ -4898,11 +4890,11 @@
       <c r="Y40">
         <v>23</v>
       </c>
-      <c r="Z40" s="5">
+      <c r="Z40" s="4">
         <v>4000000</v>
       </c>
-      <c r="AA40" s="6">
-        <f>Z40/D40</f>
+      <c r="AA40" s="5">
+        <f t="shared" si="15"/>
         <v>0.30741223150231434</v>
       </c>
     </row>
@@ -4923,15 +4915,15 @@
         <v>1057125</v>
       </c>
       <c r="F41">
-        <f>D41-C41</f>
+        <f t="shared" si="10"/>
         <v>42916</v>
       </c>
       <c r="G41">
-        <f>F41/C41*100</f>
+        <f t="shared" si="11"/>
         <v>4.0669151392991401</v>
       </c>
       <c r="H41" s="2">
-        <f>(D41-E41)/E41</f>
+        <f t="shared" si="12"/>
         <v>3.8820385479484451E-2</v>
       </c>
       <c r="I41">
@@ -4941,18 +4933,18 @@
         <v>2</v>
       </c>
       <c r="K41">
-        <f>J41-I41</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="L41">
         <v>4</v>
       </c>
       <c r="M41">
-        <f>J41+2</f>
+        <f t="shared" si="8"/>
         <v>4</v>
       </c>
       <c r="N41">
-        <f>M41-L41</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="O41" t="s">
@@ -4967,11 +4959,11 @@
       <c r="R41">
         <v>1</v>
       </c>
-      <c r="S41" s="4">
+      <c r="S41" s="3">
         <v>1033.81</v>
       </c>
       <c r="T41">
-        <f>D41/S41</f>
+        <f t="shared" si="14"/>
         <v>1062.2483821978894</v>
       </c>
       <c r="U41">
@@ -4989,11 +4981,11 @@
       <c r="Y41">
         <v>8</v>
       </c>
-      <c r="Z41" s="5">
+      <c r="Z41" s="4">
         <v>500000</v>
       </c>
-      <c r="AA41" s="6">
-        <f>Z41/D41</f>
+      <c r="AA41" s="5">
+        <f t="shared" si="15"/>
         <v>0.45530581525693364</v>
       </c>
     </row>
@@ -5014,15 +5006,15 @@
         <v>5218040</v>
       </c>
       <c r="F42">
-        <f>D42-C42</f>
+        <f t="shared" si="10"/>
         <v>478737</v>
       </c>
       <c r="G42">
-        <f>F42/C42*100</f>
+        <f t="shared" si="11"/>
         <v>10.304338701779498</v>
       </c>
       <c r="H42" s="2">
-        <f>(D42-E42)/E42</f>
+        <f t="shared" si="12"/>
         <v>-1.7885642885067957E-2</v>
       </c>
       <c r="I42">
@@ -5032,18 +5024,18 @@
         <v>7</v>
       </c>
       <c r="K42">
-        <f>J42-I42</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="L42">
         <v>9</v>
       </c>
       <c r="M42">
-        <f>J42+2</f>
+        <f t="shared" si="8"/>
         <v>9</v>
       </c>
       <c r="N42">
-        <f>M42-L42</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="O42" t="s">
@@ -5058,11 +5050,11 @@
       <c r="R42">
         <v>2</v>
       </c>
-      <c r="S42" s="4">
+      <c r="S42" s="3">
         <v>30060.7</v>
       </c>
       <c r="T42">
-        <f>D42/S42</f>
+        <f t="shared" si="14"/>
         <v>170.47879789891786</v>
       </c>
       <c r="U42">
@@ -5080,11 +5072,11 @@
       <c r="Y42">
         <v>33</v>
       </c>
-      <c r="Z42" s="5">
-        <v>0</v>
-      </c>
-      <c r="AA42" s="6">
-        <f>Z42/D42</f>
+      <c r="Z42" s="4">
+        <v>0</v>
+      </c>
+      <c r="AA42" s="5">
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
@@ -5105,15 +5097,15 @@
         <v>892717</v>
       </c>
       <c r="F43">
-        <f>D43-C43</f>
+        <f t="shared" si="10"/>
         <v>68009</v>
       </c>
       <c r="G43">
-        <f>F43/C43*100</f>
+        <f t="shared" si="11"/>
         <v>8.2961985261557949</v>
       </c>
       <c r="H43" s="2">
-        <f>(D43-E43)/E43</f>
+        <f t="shared" si="12"/>
         <v>-5.5415097953774826E-3</v>
       </c>
       <c r="I43">
@@ -5123,18 +5115,18 @@
         <v>1</v>
       </c>
       <c r="K43">
-        <f>J43-I43</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="L43">
         <v>3</v>
       </c>
       <c r="M43">
-        <f>J43+2</f>
+        <f t="shared" si="8"/>
         <v>3</v>
       </c>
       <c r="N43">
-        <f>M43-L43</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="O43" t="s">
@@ -5149,11 +5141,11 @@
       <c r="R43">
         <v>1</v>
       </c>
-      <c r="S43" s="4">
+      <c r="S43" s="3">
         <v>75811</v>
       </c>
       <c r="T43">
-        <f>D43/S43</f>
+        <f t="shared" si="14"/>
         <v>11.710305892284762</v>
       </c>
       <c r="U43">
@@ -5171,11 +5163,11 @@
       <c r="Y43">
         <v>45</v>
       </c>
-      <c r="Z43" s="5">
-        <v>0</v>
-      </c>
-      <c r="AA43" s="6">
-        <f>Z43/D43</f>
+      <c r="Z43" s="4">
+        <v>0</v>
+      </c>
+      <c r="AA43" s="5">
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
@@ -5196,15 +5188,15 @@
         <v>6886834</v>
       </c>
       <c r="F44">
-        <f>D44-C44</f>
+        <f t="shared" si="10"/>
         <v>541466</v>
       </c>
       <c r="G44">
-        <f>F44/C44*100</f>
+        <f t="shared" si="11"/>
         <v>8.4930101196295578</v>
       </c>
       <c r="H44" s="2">
-        <f>(D44-E44)/E44</f>
+        <f t="shared" si="12"/>
         <v>4.3652859935349106E-3</v>
       </c>
       <c r="I44">
@@ -5214,18 +5206,18 @@
         <v>9</v>
       </c>
       <c r="K44">
-        <f>J44-I44</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="L44">
         <v>11</v>
       </c>
       <c r="M44">
-        <f>J44+2</f>
+        <f t="shared" si="8"/>
         <v>11</v>
       </c>
       <c r="N44">
-        <f>M44-L44</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="O44" t="s">
@@ -5240,11 +5232,11 @@
       <c r="R44">
         <v>0</v>
       </c>
-      <c r="S44" s="4">
+      <c r="S44" s="3">
         <v>41234.9</v>
       </c>
       <c r="T44">
-        <f>D44/S44</f>
+        <f t="shared" si="14"/>
         <v>167.74375589609772</v>
       </c>
       <c r="U44">
@@ -5262,11 +5254,11 @@
       <c r="Y44">
         <v>42</v>
       </c>
-      <c r="Z44" s="5">
-        <v>0</v>
-      </c>
-      <c r="AA44" s="6">
-        <f>Z44/D44</f>
+      <c r="Z44" s="4">
+        <v>0</v>
+      </c>
+      <c r="AA44" s="5">
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
@@ -5287,15 +5279,15 @@
         <v>29360759</v>
       </c>
       <c r="F45">
-        <f>D45-C45</f>
+        <f t="shared" si="10"/>
         <v>3914872</v>
       </c>
       <c r="G45">
-        <f>F45/C45*100</f>
+        <f t="shared" si="11"/>
         <v>15.493142467407338</v>
       </c>
       <c r="H45" s="2">
-        <f>(D45-E45)/E45</f>
+        <f t="shared" si="12"/>
         <v>-6.0444282111371851E-3</v>
       </c>
       <c r="I45">
@@ -5305,18 +5297,18 @@
         <v>38</v>
       </c>
       <c r="K45">
-        <f>J45-I45</f>
+        <f t="shared" si="13"/>
         <v>2</v>
       </c>
       <c r="L45">
         <v>38</v>
       </c>
       <c r="M45">
-        <f>J45+2</f>
+        <f t="shared" si="8"/>
         <v>40</v>
       </c>
       <c r="N45">
-        <f>M45-L45</f>
+        <f t="shared" si="9"/>
         <v>2</v>
       </c>
       <c r="O45" t="s">
@@ -5331,11 +5323,11 @@
       <c r="R45">
         <v>21</v>
       </c>
-      <c r="S45" s="4">
+      <c r="S45" s="3">
         <v>261231.71</v>
       </c>
       <c r="T45">
-        <f>D45/S45</f>
+        <f t="shared" si="14"/>
         <v>111.71419426837576</v>
       </c>
       <c r="U45">
@@ -5353,11 +5345,11 @@
       <c r="Y45">
         <v>29</v>
       </c>
-      <c r="Z45" s="5">
-        <v>0</v>
-      </c>
-      <c r="AA45" s="6">
-        <f>Z45/D45</f>
+      <c r="Z45" s="4">
+        <v>0</v>
+      </c>
+      <c r="AA45" s="5">
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
@@ -5378,15 +5370,15 @@
         <v>3249879</v>
       </c>
       <c r="F46">
-        <f>D46-C46</f>
+        <f t="shared" si="10"/>
         <v>504487</v>
       </c>
       <c r="G46">
-        <f>F46/C46*100</f>
+        <f t="shared" si="11"/>
         <v>18.207498651094554</v>
       </c>
       <c r="H46" s="2">
-        <f>(D46-E46)/E46</f>
+        <f t="shared" si="12"/>
         <v>7.8073675973782406E-3</v>
       </c>
       <c r="I46">
@@ -5396,18 +5388,18 @@
         <v>4</v>
       </c>
       <c r="K46">
-        <f>J46-I46</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="L46">
         <v>6</v>
       </c>
       <c r="M46">
-        <f>J46+2</f>
+        <f t="shared" si="8"/>
         <v>6</v>
       </c>
       <c r="N46">
-        <f>M46-L46</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="O46" t="s">
@@ -5422,11 +5414,11 @@
       <c r="R46">
         <v>2</v>
       </c>
-      <c r="S46" s="4">
+      <c r="S46" s="3">
         <v>82169.62</v>
       </c>
       <c r="T46">
-        <f>D46/S46</f>
+        <f t="shared" si="14"/>
         <v>39.859646424067684</v>
       </c>
       <c r="U46">
@@ -5444,11 +5436,11 @@
       <c r="Y46">
         <v>41</v>
       </c>
-      <c r="Z46" s="5">
+      <c r="Z46" s="4">
         <v>1000000</v>
       </c>
-      <c r="AA46" s="6">
-        <f>Z46/D46</f>
+      <c r="AA46" s="5">
+        <f t="shared" si="15"/>
         <v>0.30532001812379628</v>
       </c>
     </row>
@@ -5457,7 +5449,7 @@
         <v>55</v>
       </c>
       <c r="B47" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C47">
         <v>630337</v>
@@ -5469,15 +5461,15 @@
         <v>623347</v>
       </c>
       <c r="F47">
-        <f>D47-C47</f>
+        <f t="shared" si="10"/>
         <v>13166</v>
       </c>
       <c r="G47">
-        <f>F47/C47*100</f>
+        <f t="shared" si="11"/>
         <v>2.0887239682899783</v>
       </c>
       <c r="H47" s="2">
-        <f>(D47-E47)/E47</f>
+        <f t="shared" si="12"/>
         <v>3.233511992517811E-2</v>
       </c>
       <c r="I47">
@@ -5487,37 +5479,37 @@
         <v>1</v>
       </c>
       <c r="K47">
-        <f>J47-I47</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="L47">
         <v>3</v>
       </c>
       <c r="M47">
-        <f>J47+2</f>
+        <f t="shared" si="8"/>
         <v>3</v>
       </c>
       <c r="N47">
-        <f>M47-L47</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="O47" t="s">
         <v>12</v>
       </c>
       <c r="P47">
-        <v>1706</v>
+        <v>321</v>
       </c>
       <c r="Q47">
-        <v>41</v>
+        <v>16</v>
       </c>
       <c r="R47">
-        <v>7</v>
-      </c>
-      <c r="S47" s="4">
+        <v>3</v>
+      </c>
+      <c r="S47" s="3">
         <v>9216.66</v>
       </c>
       <c r="T47">
-        <f>D47/S47</f>
+        <f t="shared" si="14"/>
         <v>69.819544173268838</v>
       </c>
       <c r="U47">
@@ -5535,11 +5527,11 @@
       <c r="Y47">
         <v>2</v>
       </c>
-      <c r="Z47" s="5">
-        <v>0</v>
-      </c>
-      <c r="AA47" s="6">
-        <f>Z47/D47</f>
+      <c r="Z47" s="4">
+        <v>0</v>
+      </c>
+      <c r="AA47" s="5">
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>
@@ -5548,7 +5540,7 @@
         <v>56</v>
       </c>
       <c r="B48" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C48">
         <v>8037736</v>
@@ -5560,15 +5552,15 @@
         <v>8590563</v>
       </c>
       <c r="F48">
-        <f>D48-C48</f>
+        <f t="shared" si="10"/>
         <v>616806</v>
       </c>
       <c r="G48">
-        <f>F48/C48*100</f>
+        <f t="shared" si="11"/>
         <v>7.6738773206783604</v>
       </c>
       <c r="H48" s="2">
-        <f>(D48-E48)/E48</f>
+        <f t="shared" si="12"/>
         <v>7.4475910368156312E-3</v>
       </c>
       <c r="I48">
@@ -5578,37 +5570,37 @@
         <v>11</v>
       </c>
       <c r="K48">
-        <f>J48-I48</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="L48">
         <v>13</v>
       </c>
       <c r="M48">
-        <f>J48+2</f>
+        <f t="shared" si="8"/>
         <v>13</v>
       </c>
       <c r="N48">
-        <f>M48-L48</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="O48" t="s">
         <v>12</v>
       </c>
       <c r="P48">
-        <v>321</v>
+        <v>1706</v>
       </c>
       <c r="Q48">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="R48">
-        <v>3</v>
-      </c>
-      <c r="S48" s="4">
+        <v>7</v>
+      </c>
+      <c r="S48" s="3">
         <v>39490.089999999997</v>
       </c>
       <c r="T48">
-        <f>D48/S48</f>
+        <f t="shared" si="14"/>
         <v>219.15731263210594</v>
       </c>
       <c r="U48">
@@ -5626,11 +5618,11 @@
       <c r="Y48">
         <v>17</v>
       </c>
-      <c r="Z48" s="5">
+      <c r="Z48" s="4">
         <v>1500000</v>
       </c>
-      <c r="AA48" s="6">
-        <f>Z48/D48</f>
+      <c r="AA48" s="5">
+        <f t="shared" si="15"/>
         <v>0.17331939691320464</v>
       </c>
     </row>
@@ -5651,15 +5643,15 @@
         <v>7693612</v>
       </c>
       <c r="F49">
-        <f>D49-C49</f>
+        <f t="shared" si="10"/>
         <v>962577</v>
       </c>
       <c r="G49">
-        <f>F49/C49*100</f>
+        <f t="shared" si="11"/>
         <v>14.25328602657429</v>
       </c>
       <c r="H49" s="2">
-        <f>(D49-E49)/E49</f>
+        <f t="shared" si="12"/>
         <v>2.9029277795656967E-3</v>
       </c>
       <c r="I49">
@@ -5669,18 +5661,18 @@
         <v>10</v>
       </c>
       <c r="K49">
-        <f>J49-I49</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="L49">
         <v>12</v>
       </c>
       <c r="M49">
-        <f>J49+2</f>
+        <f t="shared" si="8"/>
         <v>12</v>
       </c>
       <c r="N49">
-        <f>M49-L49</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="O49" t="s">
@@ -5695,11 +5687,11 @@
       <c r="R49">
         <v>51</v>
       </c>
-      <c r="S49" s="4">
+      <c r="S49" s="3">
         <v>66455.520000000004</v>
       </c>
       <c r="T49">
-        <f>D49/S49</f>
+        <f t="shared" si="14"/>
         <v>116.10692384921522</v>
       </c>
       <c r="U49">
@@ -5717,11 +5709,11 @@
       <c r="Y49">
         <v>10</v>
       </c>
-      <c r="Z49" s="5">
+      <c r="Z49" s="4">
         <v>15464000</v>
       </c>
-      <c r="AA49" s="6">
-        <f>Z49/D49</f>
+      <c r="AA49" s="5">
+        <f t="shared" si="15"/>
         <v>2.0041612525541264</v>
       </c>
     </row>
@@ -5742,15 +5734,15 @@
         <v>1784787</v>
       </c>
       <c r="F50">
-        <f>D50-C50</f>
+        <f t="shared" si="10"/>
         <v>-64770</v>
       </c>
       <c r="G50">
-        <f>F50/C50*100</f>
+        <f t="shared" si="11"/>
         <v>-3.4826044525934035</v>
       </c>
       <c r="H50" s="2">
-        <f>(D50-E50)/E50</f>
+        <f t="shared" si="12"/>
         <v>5.7474645433880905E-3</v>
       </c>
       <c r="I50">
@@ -5760,18 +5752,18 @@
         <v>2</v>
       </c>
       <c r="K50">
-        <f>J50-I50</f>
+        <f t="shared" si="13"/>
         <v>-1</v>
       </c>
       <c r="L50">
         <v>5</v>
       </c>
       <c r="M50">
-        <f>J50+2</f>
+        <f t="shared" si="8"/>
         <v>4</v>
       </c>
       <c r="N50">
-        <f>M50-L50</f>
+        <f t="shared" si="9"/>
         <v>-1</v>
       </c>
       <c r="O50" t="s">
@@ -5786,11 +5778,11 @@
       <c r="R50">
         <v>1</v>
       </c>
-      <c r="S50" s="4">
+      <c r="S50" s="3">
         <v>24038.21</v>
       </c>
       <c r="T50">
-        <f>D50/S50</f>
+        <f t="shared" si="14"/>
         <v>74.674653395573131</v>
       </c>
       <c r="U50">
@@ -5808,11 +5800,11 @@
       <c r="Y50">
         <v>50</v>
       </c>
-      <c r="Z50" s="5">
+      <c r="Z50" s="4">
         <v>1000000</v>
       </c>
-      <c r="AA50" s="6">
-        <f>Z50/D50</f>
+      <c r="AA50" s="5">
+        <f t="shared" si="15"/>
         <v>0.55708909804489581</v>
       </c>
     </row>
@@ -5833,15 +5825,15 @@
         <v>5832655</v>
       </c>
       <c r="F51">
-        <f>D51-C51</f>
+        <f t="shared" si="10"/>
         <v>199243</v>
       </c>
       <c r="G51">
-        <f>F51/C51*100</f>
+        <f t="shared" si="11"/>
         <v>3.4965770072461098</v>
       </c>
       <c r="H51" s="2">
-        <f>(D51-E51)/E51</f>
+        <f t="shared" si="12"/>
         <v>1.1112949420118283E-2</v>
       </c>
       <c r="I51">
@@ -5851,18 +5843,18 @@
         <v>8</v>
       </c>
       <c r="K51">
-        <f>J51-I51</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="L51">
         <v>10</v>
       </c>
       <c r="M51">
-        <f>J51+2</f>
+        <f t="shared" si="8"/>
         <v>10</v>
       </c>
       <c r="N51">
-        <f>M51-L51</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="O51" t="s">
@@ -5877,11 +5869,11 @@
       <c r="R51">
         <v>8</v>
       </c>
-      <c r="S51" s="4">
+      <c r="S51" s="3">
         <v>54157.8</v>
       </c>
       <c r="T51">
-        <f>D51/S51</f>
+        <f t="shared" si="14"/>
         <v>108.8942497664233</v>
       </c>
       <c r="U51">
@@ -5899,11 +5891,11 @@
       <c r="Y51">
         <v>24</v>
       </c>
-      <c r="Z51" s="5">
+      <c r="Z51" s="4">
         <v>1000000</v>
       </c>
-      <c r="AA51" s="6">
-        <f>Z51/D51</f>
+      <c r="AA51" s="5">
+        <f t="shared" si="15"/>
         <v>0.16956415061162636</v>
       </c>
     </row>
@@ -5924,15 +5916,15 @@
         <v>582328</v>
       </c>
       <c r="F52">
-        <f>D52-C52</f>
+        <f t="shared" si="10"/>
         <v>9419</v>
       </c>
       <c r="G52">
-        <f>F52/C52*100</f>
+        <f t="shared" si="11"/>
         <v>1.6573992609537216</v>
       </c>
       <c r="H52" s="2">
-        <f>(D52-E52)/E52</f>
+        <f t="shared" si="12"/>
         <v>-7.914783421027324E-3</v>
       </c>
       <c r="I52">
@@ -5942,18 +5934,18 @@
         <v>1</v>
       </c>
       <c r="K52">
-        <f>J52-I52</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="L52">
         <v>3</v>
       </c>
       <c r="M52">
-        <f>J52+2</f>
+        <f t="shared" si="8"/>
         <v>3</v>
       </c>
       <c r="N52">
-        <f>M52-L52</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="O52" t="s">
@@ -5968,11 +5960,11 @@
       <c r="R52">
         <v>0</v>
       </c>
-      <c r="S52" s="4">
+      <c r="S52" s="3">
         <v>97093.14</v>
       </c>
       <c r="T52">
-        <f>D52/S52</f>
+        <f t="shared" si="14"/>
         <v>5.9501526060440524</v>
       </c>
       <c r="U52">
@@ -5990,11 +5982,11 @@
       <c r="Y52">
         <v>51</v>
       </c>
-      <c r="Z52" s="5">
-        <v>0</v>
-      </c>
-      <c r="AA52" s="6">
-        <f>Z52/D52</f>
+      <c r="Z52" s="4">
+        <v>0</v>
+      </c>
+      <c r="AA52" s="5">
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
     </row>

--- a/apportion/pop.xlsx
+++ b/apportion/pop.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/user/Google Drive/GitHub/R Functions/apportion/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83A3C4D6-0D34-2043-B0CF-EBDF49C09E7B}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E73B2A34-0126-C447-98C1-44D560DC460D}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="35840" windowHeight="21900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1373,15 +1373,15 @@
         <v>4921532</v>
       </c>
       <c r="F2">
-        <f t="shared" ref="F2:F33" si="0">D2-C2</f>
+        <f>D2-C2</f>
         <v>227071</v>
       </c>
       <c r="G2">
-        <f t="shared" ref="G2:G33" si="1">F2/C2*100</f>
+        <f>F2/C2*100</f>
         <v>4.7277087442759518</v>
       </c>
       <c r="H2" s="2">
-        <f t="shared" ref="H2:H33" si="2">(D2-E2)/E2</f>
+        <f>(D2-E2)/E2</f>
         <v>2.2050247768377815E-2</v>
       </c>
       <c r="I2">
@@ -1391,18 +1391,18 @@
         <v>7</v>
       </c>
       <c r="K2">
-        <f t="shared" ref="K2:K33" si="3">J2-I2</f>
+        <f>J2-I2</f>
         <v>0</v>
       </c>
       <c r="L2">
         <v>9</v>
       </c>
       <c r="M2">
-        <f t="shared" ref="M2:M9" si="4">J2+2</f>
+        <f>J2+2</f>
         <v>9</v>
       </c>
       <c r="N2">
-        <f t="shared" ref="N2:N9" si="5">M2-L2</f>
+        <f>M2-L2</f>
         <v>0</v>
       </c>
       <c r="O2" t="s">
@@ -1421,7 +1421,7 @@
         <v>50645.33</v>
       </c>
       <c r="T2">
-        <f t="shared" ref="T2:T33" si="6">D2/S2</f>
+        <f>D2/S2</f>
         <v>99.319186981307055</v>
       </c>
       <c r="U2">
@@ -1443,7 +1443,7 @@
         <v>1240000</v>
       </c>
       <c r="AA2" s="5">
-        <f t="shared" ref="AA2:AA33" si="7">Z2/D2</f>
+        <f>Z2/D2</f>
         <v>0.2465182772428044</v>
       </c>
     </row>
@@ -1464,15 +1464,15 @@
         <v>731158</v>
       </c>
       <c r="F3">
-        <f t="shared" si="0"/>
+        <f>D3-C3</f>
         <v>14558</v>
       </c>
       <c r="G3">
-        <f t="shared" si="1"/>
+        <f>F3/C3*100</f>
         <v>2.0176764981850894</v>
       </c>
       <c r="H3" s="2">
-        <f t="shared" si="2"/>
+        <f>(D3-E3)/E3</f>
         <v>6.7331548037496683E-3</v>
       </c>
       <c r="I3">
@@ -1482,18 +1482,18 @@
         <v>1</v>
       </c>
       <c r="K3">
-        <f t="shared" si="3"/>
+        <f>J3-I3</f>
         <v>0</v>
       </c>
       <c r="L3">
         <v>3</v>
       </c>
       <c r="M3">
-        <f t="shared" si="4"/>
+        <f>J3+2</f>
         <v>3</v>
       </c>
       <c r="N3">
-        <f t="shared" si="5"/>
+        <f>M3-L3</f>
         <v>0</v>
       </c>
       <c r="O3" t="s">
@@ -1512,7 +1512,7 @@
         <v>570640.94999999995</v>
       </c>
       <c r="T3">
-        <f t="shared" si="6"/>
+        <f>D3/S3</f>
         <v>1.289919694687176</v>
       </c>
       <c r="U3">
@@ -1534,7 +1534,7 @@
         <v>600000</v>
       </c>
       <c r="AA3" s="5">
-        <f t="shared" si="7"/>
+        <f>Z3/D3</f>
         <v>0.81512768295880478</v>
       </c>
     </row>
@@ -1555,15 +1555,15 @@
         <v>7421401</v>
       </c>
       <c r="F4">
-        <f t="shared" si="0"/>
+        <f>D4-C4</f>
         <v>746223</v>
       </c>
       <c r="G4">
-        <f t="shared" si="1"/>
+        <f>F4/C4*100</f>
         <v>11.636642911722053</v>
       </c>
       <c r="H4" s="2">
-        <f t="shared" si="2"/>
+        <f>(D4-E4)/E4</f>
         <v>-3.5367715610570026E-2</v>
       </c>
       <c r="I4">
@@ -1573,18 +1573,18 @@
         <v>9</v>
       </c>
       <c r="K4">
-        <f t="shared" si="3"/>
+        <f>J4-I4</f>
         <v>0</v>
       </c>
       <c r="L4">
         <v>11</v>
       </c>
       <c r="M4">
-        <f t="shared" si="4"/>
+        <f>J4+2</f>
         <v>11</v>
       </c>
       <c r="N4">
-        <f t="shared" si="5"/>
+        <f>M4-L4</f>
         <v>0</v>
       </c>
       <c r="O4" t="s">
@@ -1603,7 +1603,7 @@
         <v>113594.08</v>
       </c>
       <c r="T4">
-        <f t="shared" si="6"/>
+        <f>D4/S4</f>
         <v>63.021972623925471</v>
       </c>
       <c r="U4">
@@ -1625,7 +1625,7 @@
         <v>0</v>
       </c>
       <c r="AA4" s="5">
-        <f t="shared" si="7"/>
+        <f>Z4/D4</f>
         <v>0</v>
       </c>
     </row>
@@ -1646,15 +1646,15 @@
         <v>3030522</v>
       </c>
       <c r="F5">
-        <f t="shared" si="0"/>
+        <f>D5-C5</f>
         <v>87527</v>
       </c>
       <c r="G5">
-        <f t="shared" si="1"/>
+        <f>F5/C5*100</f>
         <v>2.9911192869730976</v>
       </c>
       <c r="H5" s="2">
-        <f t="shared" si="2"/>
+        <f>(D5-E5)/E5</f>
         <v>-5.5323802302045654E-3</v>
       </c>
       <c r="I5">
@@ -1664,18 +1664,18 @@
         <v>4</v>
       </c>
       <c r="K5">
-        <f t="shared" si="3"/>
+        <f>J5-I5</f>
         <v>0</v>
       </c>
       <c r="L5">
         <v>6</v>
       </c>
       <c r="M5">
-        <f t="shared" si="4"/>
+        <f>J5+2</f>
         <v>6</v>
       </c>
       <c r="N5">
-        <f t="shared" si="5"/>
+        <f>M5-L5</f>
         <v>0</v>
       </c>
       <c r="O5" t="s">
@@ -1694,7 +1694,7 @@
         <v>52035.48</v>
       </c>
       <c r="T5">
-        <f t="shared" si="6"/>
+        <f>D5/S5</f>
         <v>57.917328714946031</v>
       </c>
       <c r="U5">
@@ -1716,7 +1716,7 @@
         <v>0</v>
       </c>
       <c r="AA5" s="5">
-        <f t="shared" si="7"/>
+        <f>Z5/D5</f>
         <v>0</v>
       </c>
     </row>
@@ -1737,15 +1737,15 @@
         <v>39368078</v>
       </c>
       <c r="F6">
-        <f t="shared" si="0"/>
+        <f>D6-C6</f>
         <v>2234768</v>
       </c>
       <c r="G6">
-        <f t="shared" si="1"/>
+        <f>F6/C6*100</f>
         <v>5.9845981958807819</v>
       </c>
       <c r="H6" s="2">
-        <f t="shared" si="2"/>
+        <f>(D6-E6)/E6</f>
         <v>5.3007159760250422E-3</v>
       </c>
       <c r="I6">
@@ -1755,18 +1755,18 @@
         <v>52</v>
       </c>
       <c r="K6">
-        <f t="shared" si="3"/>
+        <f>J6-I6</f>
         <v>-1</v>
       </c>
       <c r="L6">
         <v>55</v>
       </c>
       <c r="M6">
-        <f t="shared" si="4"/>
+        <f>J6+2</f>
         <v>54</v>
       </c>
       <c r="N6">
-        <f t="shared" si="5"/>
+        <f>M6-L6</f>
         <v>-1</v>
       </c>
       <c r="O6" t="s">
@@ -1785,7 +1785,7 @@
         <v>155779.22</v>
       </c>
       <c r="T6">
-        <f t="shared" si="6"/>
+        <f>D6/S6</f>
         <v>254.05671565180515</v>
       </c>
       <c r="U6">
@@ -1807,7 +1807,7 @@
         <v>187000000</v>
       </c>
       <c r="AA6" s="5">
-        <f t="shared" si="7"/>
+        <f>Z6/D6</f>
         <v>4.7249955320998129</v>
       </c>
     </row>
@@ -1828,15 +1828,15 @@
         <v>5807719</v>
       </c>
       <c r="F7">
-        <f t="shared" si="0"/>
+        <f>D7-C7</f>
         <v>737241</v>
       </c>
       <c r="G7">
-        <f t="shared" si="1"/>
+        <f>F7/C7*100</f>
         <v>14.613503061489455</v>
       </c>
       <c r="H7" s="2">
-        <f t="shared" si="2"/>
+        <f>(D7-E7)/E7</f>
         <v>-4.3989731596862725E-3</v>
       </c>
       <c r="I7">
@@ -1846,18 +1846,18 @@
         <v>8</v>
       </c>
       <c r="K7">
-        <f t="shared" si="3"/>
+        <f>J7-I7</f>
         <v>1</v>
       </c>
       <c r="L7">
         <v>9</v>
       </c>
       <c r="M7">
-        <f t="shared" si="4"/>
+        <f>J7+2</f>
         <v>10</v>
       </c>
       <c r="N7">
-        <f t="shared" si="5"/>
+        <f>M7-L7</f>
         <v>1</v>
       </c>
       <c r="O7" t="s">
@@ -1876,7 +1876,7 @@
         <v>103641.89</v>
       </c>
       <c r="T7">
-        <f t="shared" si="6"/>
+        <f>D7/S7</f>
         <v>55.789903098061991</v>
       </c>
       <c r="U7">
@@ -1898,7 +1898,7 @@
         <v>6000000</v>
       </c>
       <c r="AA7" s="5">
-        <f t="shared" si="7"/>
+        <f>Z7/D7</f>
         <v>1.0376725281905361</v>
       </c>
     </row>
@@ -1919,15 +1919,15 @@
         <v>3557006</v>
       </c>
       <c r="F8">
-        <f t="shared" si="0"/>
+        <f>D8-C8</f>
         <v>26670</v>
       </c>
       <c r="G8">
-        <f t="shared" si="1"/>
+        <f>F8/C8*100</f>
         <v>0.74463344601951964</v>
       </c>
       <c r="H8" s="2">
-        <f t="shared" si="2"/>
+        <f>(D8-E8)/E8</f>
         <v>1.4419992544291464E-2</v>
       </c>
       <c r="I8">
@@ -1937,18 +1937,18 @@
         <v>5</v>
       </c>
       <c r="K8">
-        <f t="shared" si="3"/>
+        <f>J8-I8</f>
         <v>0</v>
       </c>
       <c r="L8">
         <v>7</v>
       </c>
       <c r="M8">
-        <f t="shared" si="4"/>
+        <f>J8+2</f>
         <v>7</v>
       </c>
       <c r="N8">
-        <f t="shared" si="5"/>
+        <f>M8-L8</f>
         <v>0</v>
       </c>
       <c r="O8" t="s">
@@ -1967,7 +1967,7 @@
         <v>4842.3599999999997</v>
       </c>
       <c r="T8">
-        <f t="shared" si="6"/>
+        <f>D8/S8</f>
         <v>745.15277674522349</v>
       </c>
       <c r="U8">
@@ -1989,7 +1989,7 @@
         <v>500000</v>
       </c>
       <c r="AA8" s="5">
-        <f t="shared" si="7"/>
+        <f>Z8/D8</f>
         <v>0.13856948622314455</v>
       </c>
     </row>
@@ -2010,15 +2010,15 @@
         <v>986809</v>
       </c>
       <c r="F9">
-        <f t="shared" si="0"/>
+        <f>D9-C9</f>
         <v>89960</v>
       </c>
       <c r="G9">
-        <f t="shared" si="1"/>
+        <f>F9/C9*100</f>
         <v>9.9858249239352332</v>
       </c>
       <c r="H9" s="2">
-        <f t="shared" si="2"/>
+        <f>(D9-E9)/E9</f>
         <v>4.0818435989132653E-3</v>
       </c>
       <c r="I9">
@@ -2028,18 +2028,18 @@
         <v>1</v>
       </c>
       <c r="K9">
-        <f t="shared" si="3"/>
+        <f>J9-I9</f>
         <v>0</v>
       </c>
       <c r="L9">
         <v>3</v>
       </c>
       <c r="M9">
-        <f t="shared" si="4"/>
+        <f>J9+2</f>
         <v>3</v>
       </c>
       <c r="N9">
-        <f t="shared" si="5"/>
+        <f>M9-L9</f>
         <v>0</v>
       </c>
       <c r="O9" t="s">
@@ -2058,7 +2058,7 @@
         <v>1948.54</v>
       </c>
       <c r="T9">
-        <f t="shared" si="6"/>
+        <f>D9/S9</f>
         <v>508.50226323298472</v>
       </c>
       <c r="U9">
@@ -2080,7 +2080,7 @@
         <v>0</v>
       </c>
       <c r="AA9" s="5">
-        <f t="shared" si="7"/>
+        <f>Z9/D9</f>
         <v>0</v>
       </c>
     </row>
@@ -2102,15 +2102,15 @@
         <v>712816</v>
       </c>
       <c r="F10">
-        <f t="shared" si="0"/>
+        <f>D10-C10</f>
         <v>89810</v>
       </c>
       <c r="G10">
-        <f t="shared" si="1"/>
+        <f>F10/C10*100</f>
         <v>14.925472351896138</v>
       </c>
       <c r="H10" s="2">
-        <f t="shared" si="2"/>
+        <f>(D10-E10)/E10</f>
         <v>-2.9857635069919865E-2</v>
       </c>
       <c r="I10">
@@ -2120,7 +2120,7 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <f t="shared" si="3"/>
+        <f>J10-I10</f>
         <v>0</v>
       </c>
       <c r="L10">
@@ -2148,7 +2148,7 @@
         <v>61.05</v>
       </c>
       <c r="T10">
-        <f t="shared" si="6"/>
+        <f>D10/S10</f>
         <v>11327.321867321867</v>
       </c>
       <c r="U10">
@@ -2170,7 +2170,7 @@
         <v>0</v>
       </c>
       <c r="AA10" s="5">
-        <f t="shared" si="7"/>
+        <f>Z10/D10</f>
         <v>0</v>
       </c>
     </row>
@@ -2191,15 +2191,15 @@
         <v>21733312</v>
       </c>
       <c r="F11">
-        <f t="shared" si="0"/>
+        <f>D11-C11</f>
         <v>2669754</v>
       </c>
       <c r="G11">
-        <f t="shared" si="1"/>
+        <f>F11/C11*100</f>
         <v>14.12510483036858</v>
       </c>
       <c r="H11" s="2">
-        <f t="shared" si="2"/>
+        <f>(D11-E11)/E11</f>
         <v>-7.4901147142230323E-3</v>
       </c>
       <c r="I11">
@@ -2209,18 +2209,18 @@
         <v>28</v>
       </c>
       <c r="K11">
-        <f t="shared" si="3"/>
+        <f>J11-I11</f>
         <v>1</v>
       </c>
       <c r="L11">
         <v>29</v>
       </c>
       <c r="M11">
-        <f t="shared" ref="M11:M52" si="8">J11+2</f>
+        <f>J11+2</f>
         <v>30</v>
       </c>
       <c r="N11">
-        <f t="shared" ref="N11:N52" si="9">M11-L11</f>
+        <f>M11-L11</f>
         <v>1</v>
       </c>
       <c r="O11" t="s">
@@ -2239,7 +2239,7 @@
         <v>53624.76</v>
       </c>
       <c r="T11">
-        <f t="shared" si="6"/>
+        <f>D11/S11</f>
         <v>402.24939002058005</v>
       </c>
       <c r="U11">
@@ -2261,7 +2261,7 @@
         <v>0</v>
       </c>
       <c r="AA11" s="5">
-        <f t="shared" si="7"/>
+        <f>Z11/D11</f>
         <v>0</v>
       </c>
     </row>
@@ -2282,15 +2282,15 @@
         <v>10710017</v>
       </c>
       <c r="F12">
-        <f t="shared" si="0"/>
+        <f>D12-C12</f>
         <v>997708</v>
       </c>
       <c r="G12">
-        <f t="shared" si="1"/>
+        <f>F12/C12*100</f>
         <v>10.256501986211145</v>
       </c>
       <c r="H12" s="2">
-        <f t="shared" si="2"/>
+        <f>(D12-E12)/E12</f>
         <v>1.4245542280651841E-3</v>
       </c>
       <c r="I12">
@@ -2300,18 +2300,18 @@
         <v>14</v>
       </c>
       <c r="K12">
-        <f t="shared" si="3"/>
+        <f>J12-I12</f>
         <v>0</v>
       </c>
       <c r="L12">
         <v>16</v>
       </c>
       <c r="M12">
-        <f t="shared" si="8"/>
+        <f>J12+2</f>
         <v>16</v>
       </c>
       <c r="N12">
-        <f t="shared" si="9"/>
+        <f>M12-L12</f>
         <v>0</v>
       </c>
       <c r="O12" t="s">
@@ -2330,7 +2330,7 @@
         <v>57513.49</v>
       </c>
       <c r="T12">
-        <f t="shared" si="6"/>
+        <f>D12/S12</f>
         <v>186.48275387217851</v>
       </c>
       <c r="U12">
@@ -2352,7 +2352,7 @@
         <v>3750886</v>
       </c>
       <c r="AA12" s="5">
-        <f t="shared" si="7"/>
+        <f>Z12/D12</f>
         <v>0.34972402569855093</v>
       </c>
     </row>
@@ -2373,15 +2373,15 @@
         <v>1407006</v>
       </c>
       <c r="F13">
-        <f t="shared" si="0"/>
+        <f>D13-C13</f>
         <v>93275</v>
       </c>
       <c r="G13">
-        <f t="shared" si="1"/>
+        <f>F13/C13*100</f>
         <v>6.8240246637919553</v>
       </c>
       <c r="H13" s="2">
-        <f t="shared" si="2"/>
+        <f>(D13-E13)/E13</f>
         <v>3.7761743731014652E-2</v>
       </c>
       <c r="I13">
@@ -2391,18 +2391,18 @@
         <v>2</v>
       </c>
       <c r="K13">
-        <f t="shared" si="3"/>
+        <f>J13-I13</f>
         <v>0</v>
       </c>
       <c r="L13">
         <v>4</v>
       </c>
       <c r="M13">
-        <f t="shared" si="8"/>
+        <f>J13+2</f>
         <v>4</v>
       </c>
       <c r="N13">
-        <f t="shared" si="9"/>
+        <f>M13-L13</f>
         <v>0</v>
       </c>
       <c r="O13" t="s">
@@ -2421,7 +2421,7 @@
         <v>6422.63</v>
       </c>
       <c r="T13">
-        <f t="shared" si="6"/>
+        <f>D13/S13</f>
         <v>227.34253724720247</v>
       </c>
       <c r="U13">
@@ -2443,7 +2443,7 @@
         <v>750000</v>
       </c>
       <c r="AA13" s="5">
-        <f t="shared" si="7"/>
+        <f>Z13/D13</f>
         <v>0.51365043143211908</v>
       </c>
     </row>
@@ -2464,15 +2464,15 @@
         <v>1826913</v>
       </c>
       <c r="F14">
-        <f t="shared" si="0"/>
+        <f>D14-C14</f>
         <v>267878</v>
       </c>
       <c r="G14">
-        <f t="shared" si="1"/>
+        <f>F14/C14*100</f>
         <v>17.024351461297403</v>
       </c>
       <c r="H14" s="2">
-        <f t="shared" si="2"/>
+        <f>(D14-E14)/E14</f>
         <v>7.9171805116061908E-3</v>
       </c>
       <c r="I14">
@@ -2482,18 +2482,18 @@
         <v>2</v>
       </c>
       <c r="K14">
-        <f t="shared" si="3"/>
+        <f>J14-I14</f>
         <v>0</v>
       </c>
       <c r="L14">
         <v>4</v>
       </c>
       <c r="M14">
-        <f t="shared" si="8"/>
+        <f>J14+2</f>
         <v>4</v>
       </c>
       <c r="N14">
-        <f t="shared" si="9"/>
+        <f>M14-L14</f>
         <v>0</v>
       </c>
       <c r="O14" t="s">
@@ -2512,7 +2512,7 @@
         <v>82643.12</v>
       </c>
       <c r="T14">
-        <f t="shared" si="6"/>
+        <f>D14/S14</f>
         <v>22.281068284934065</v>
       </c>
       <c r="U14">
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="AA14" s="5">
-        <f t="shared" si="7"/>
+        <f>Z14/D14</f>
         <v>0</v>
       </c>
     </row>
@@ -2555,15 +2555,15 @@
         <v>12587530</v>
       </c>
       <c r="F15">
-        <f t="shared" si="0"/>
+        <f>D15-C15</f>
         <v>-41641</v>
       </c>
       <c r="G15">
-        <f t="shared" si="1"/>
+        <f>F15/C15*100</f>
         <v>-0.32369224167818428</v>
       </c>
       <c r="H15" s="2">
-        <f t="shared" si="2"/>
+        <f>(D15-E15)/E15</f>
         <v>1.8685874035652746E-2</v>
       </c>
       <c r="I15">
@@ -2573,18 +2573,18 @@
         <v>17</v>
       </c>
       <c r="K15">
-        <f t="shared" si="3"/>
+        <f>J15-I15</f>
         <v>-1</v>
       </c>
       <c r="L15">
         <v>20</v>
       </c>
       <c r="M15">
-        <f t="shared" si="8"/>
+        <f>J15+2</f>
         <v>19</v>
       </c>
       <c r="N15">
-        <f t="shared" si="9"/>
+        <f>M15-L15</f>
         <v>-1</v>
       </c>
       <c r="O15" t="s">
@@ -2603,7 +2603,7 @@
         <v>55518.93</v>
       </c>
       <c r="T15">
-        <f t="shared" si="6"/>
+        <f>D15/S15</f>
         <v>230.96156572181778</v>
       </c>
       <c r="U15">
@@ -2625,7 +2625,7 @@
         <v>30500000</v>
       </c>
       <c r="AA15" s="5">
-        <f t="shared" si="7"/>
+        <f>Z15/D15</f>
         <v>2.3785869774000701</v>
       </c>
     </row>
@@ -2646,15 +2646,15 @@
         <v>6754953</v>
       </c>
       <c r="F16">
-        <f t="shared" si="0"/>
+        <f>D16-C16</f>
         <v>288698</v>
       </c>
       <c r="G16">
-        <f t="shared" si="1"/>
+        <f>F16/C16*100</f>
         <v>4.4404269606997193</v>
       </c>
       <c r="H16" s="2">
-        <f t="shared" si="2"/>
+        <f>(D16-E16)/E16</f>
         <v>5.2297921243863576E-3</v>
       </c>
       <c r="I16">
@@ -2664,18 +2664,18 @@
         <v>9</v>
       </c>
       <c r="K16">
-        <f t="shared" si="3"/>
+        <f>J16-I16</f>
         <v>0</v>
       </c>
       <c r="L16">
         <v>11</v>
       </c>
       <c r="M16">
-        <f t="shared" si="8"/>
+        <f>J16+2</f>
         <v>11</v>
       </c>
       <c r="N16">
-        <f t="shared" si="9"/>
+        <f>M16-L16</f>
         <v>0</v>
       </c>
       <c r="O16" t="s">
@@ -2694,7 +2694,7 @@
         <v>35826.11</v>
       </c>
       <c r="T16">
-        <f t="shared" si="6"/>
+        <f>D16/S16</f>
         <v>189.53439265384938</v>
       </c>
       <c r="U16">
@@ -2716,7 +2716,7 @@
         <v>0</v>
       </c>
       <c r="AA16" s="5">
-        <f t="shared" si="7"/>
+        <f>Z16/D16</f>
         <v>0</v>
       </c>
     </row>
@@ -2737,15 +2737,15 @@
         <v>3163561</v>
       </c>
       <c r="F17">
-        <f t="shared" si="0"/>
+        <f>D17-C17</f>
         <v>138619</v>
       </c>
       <c r="G17">
-        <f t="shared" si="1"/>
+        <f>F17/C17*100</f>
         <v>4.5392491355814926</v>
       </c>
       <c r="H17" s="2">
-        <f t="shared" si="2"/>
+        <f>(D17-E17)/E17</f>
         <v>9.1178896186923531E-3</v>
       </c>
       <c r="I17">
@@ -2755,18 +2755,18 @@
         <v>4</v>
       </c>
       <c r="K17">
-        <f t="shared" si="3"/>
+        <f>J17-I17</f>
         <v>0</v>
       </c>
       <c r="L17">
         <v>6</v>
       </c>
       <c r="M17">
-        <f t="shared" si="8"/>
+        <f>J17+2</f>
         <v>6</v>
       </c>
       <c r="N17">
-        <f t="shared" si="9"/>
+        <f>M17-L17</f>
         <v>0</v>
       </c>
       <c r="O17" t="s">
@@ -2785,7 +2785,7 @@
         <v>55857.13</v>
       </c>
       <c r="T17">
-        <f t="shared" si="6"/>
+        <f>D17/S17</f>
         <v>57.153061748786591</v>
       </c>
       <c r="U17">
@@ -2807,7 +2807,7 @@
         <v>0</v>
       </c>
       <c r="AA17" s="5">
-        <f t="shared" si="7"/>
+        <f>Z17/D17</f>
         <v>0</v>
       </c>
     </row>
@@ -2828,15 +2828,15 @@
         <v>2913805</v>
       </c>
       <c r="F18">
-        <f t="shared" si="0"/>
+        <f>D18-C18</f>
         <v>77052</v>
       </c>
       <c r="G18">
-        <f t="shared" si="1"/>
+        <f>F18/C18*100</f>
         <v>2.6905388026383008</v>
       </c>
       <c r="H18" s="2">
-        <f t="shared" si="2"/>
+        <f>(D18-E18)/E18</f>
         <v>9.2868259886986267E-3</v>
       </c>
       <c r="I18">
@@ -2846,18 +2846,18 @@
         <v>4</v>
       </c>
       <c r="K18">
-        <f t="shared" si="3"/>
+        <f>J18-I18</f>
         <v>0</v>
       </c>
       <c r="L18">
         <v>6</v>
       </c>
       <c r="M18">
-        <f t="shared" si="8"/>
+        <f>J18+2</f>
         <v>6</v>
       </c>
       <c r="N18">
-        <f t="shared" si="9"/>
+        <f>M18-L18</f>
         <v>0</v>
       </c>
       <c r="O18" t="s">
@@ -2876,7 +2876,7 @@
         <v>81758.720000000001</v>
       </c>
       <c r="T18">
-        <f t="shared" si="6"/>
+        <f>D18/S18</f>
         <v>35.97004698703698</v>
       </c>
       <c r="U18">
@@ -2898,7 +2898,7 @@
         <v>0</v>
       </c>
       <c r="AA18" s="5">
-        <f t="shared" si="7"/>
+        <f>Z18/D18</f>
         <v>0</v>
       </c>
     </row>
@@ -2919,15 +2919,15 @@
         <v>4477251</v>
       </c>
       <c r="F19">
-        <f t="shared" si="0"/>
+        <f>D19-C19</f>
         <v>158736</v>
       </c>
       <c r="G19">
-        <f t="shared" si="1"/>
+        <f>F19/C19*100</f>
         <v>3.6485951612258156</v>
       </c>
       <c r="H19" s="2">
-        <f t="shared" si="2"/>
+        <f>(D19-E19)/E19</f>
         <v>7.1675677776385557E-3</v>
       </c>
       <c r="I19">
@@ -2937,18 +2937,18 @@
         <v>6</v>
       </c>
       <c r="K19">
-        <f t="shared" si="3"/>
+        <f>J19-I19</f>
         <v>0</v>
       </c>
       <c r="L19">
         <v>8</v>
       </c>
       <c r="M19">
-        <f t="shared" si="8"/>
+        <f>J19+2</f>
         <v>8</v>
       </c>
       <c r="N19">
-        <f t="shared" si="9"/>
+        <f>M19-L19</f>
         <v>0</v>
       </c>
       <c r="O19" t="s">
@@ -2967,7 +2967,7 @@
         <v>39486.339999999997</v>
       </c>
       <c r="T19">
-        <f t="shared" si="6"/>
+        <f>D19/S19</f>
         <v>114.2000499413215</v>
       </c>
       <c r="U19">
@@ -2989,7 +2989,7 @@
         <v>0</v>
       </c>
       <c r="AA19" s="5">
-        <f t="shared" si="7"/>
+        <f>Z19/D19</f>
         <v>0</v>
       </c>
     </row>
@@ -3010,15 +3010,15 @@
         <v>4645318</v>
       </c>
       <c r="F20">
-        <f t="shared" si="0"/>
+        <f>D20-C20</f>
         <v>107506</v>
       </c>
       <c r="G20">
-        <f t="shared" si="1"/>
+        <f>F20/C20*100</f>
         <v>2.3607135940089092</v>
       </c>
       <c r="H20" s="2">
-        <f t="shared" si="2"/>
+        <f>(D20-E20)/E20</f>
         <v>3.4766188235121902E-3</v>
       </c>
       <c r="I20">
@@ -3028,18 +3028,18 @@
         <v>6</v>
       </c>
       <c r="K20">
-        <f t="shared" si="3"/>
+        <f>J20-I20</f>
         <v>0</v>
       </c>
       <c r="L20">
         <v>8</v>
       </c>
       <c r="M20">
-        <f t="shared" si="8"/>
+        <f>J20+2</f>
         <v>8</v>
       </c>
       <c r="N20">
-        <f t="shared" si="9"/>
+        <f>M20-L20</f>
         <v>0</v>
       </c>
       <c r="O20" t="s">
@@ -3058,7 +3058,7 @@
         <v>43203.9</v>
       </c>
       <c r="T20">
-        <f t="shared" si="6"/>
+        <f>D20/S20</f>
         <v>107.89461136610352</v>
       </c>
       <c r="U20">
@@ -3080,7 +3080,7 @@
         <v>0</v>
       </c>
       <c r="AA20" s="5">
-        <f t="shared" si="7"/>
+        <f>Z20/D20</f>
         <v>0</v>
       </c>
     </row>
@@ -3101,15 +3101,15 @@
         <v>1350141</v>
       </c>
       <c r="F21">
-        <f t="shared" si="0"/>
+        <f>D21-C21</f>
         <v>30508</v>
       </c>
       <c r="G21">
-        <f t="shared" si="1"/>
+        <f>F21/C21*100</f>
         <v>2.2885451220262341</v>
       </c>
       <c r="H21" s="2">
-        <f t="shared" si="2"/>
+        <f>(D21-E21)/E21</f>
         <v>9.9552565250592348E-3</v>
       </c>
       <c r="I21">
@@ -3119,18 +3119,18 @@
         <v>2</v>
       </c>
       <c r="K21">
-        <f t="shared" si="3"/>
+        <f>J21-I21</f>
         <v>0</v>
       </c>
       <c r="L21">
         <v>4</v>
       </c>
       <c r="M21">
-        <f t="shared" si="8"/>
+        <f>J21+2</f>
         <v>4</v>
       </c>
       <c r="N21">
-        <f t="shared" si="9"/>
+        <f>M21-L21</f>
         <v>0</v>
       </c>
       <c r="O21" t="s">
@@ -3149,7 +3149,7 @@
         <v>30842.92</v>
       </c>
       <c r="T21">
-        <f t="shared" si="6"/>
+        <f>D21/S21</f>
         <v>44.210535189275205</v>
       </c>
       <c r="U21">
@@ -3171,7 +3171,7 @@
         <v>0</v>
       </c>
       <c r="AA21" s="5">
-        <f t="shared" si="7"/>
+        <f>Z21/D21</f>
         <v>0</v>
       </c>
     </row>
@@ -3192,15 +3192,15 @@
         <v>6055802</v>
       </c>
       <c r="F22">
-        <f t="shared" si="0"/>
+        <f>D22-C22</f>
         <v>395349</v>
       </c>
       <c r="G22">
-        <f t="shared" si="1"/>
+        <f>F22/C22*100</f>
         <v>6.8282184462020172</v>
       </c>
       <c r="H22" s="2">
-        <f t="shared" si="2"/>
+        <f>(D22-E22)/E22</f>
         <v>2.1380487671162299E-2</v>
       </c>
       <c r="I22">
@@ -3210,18 +3210,18 @@
         <v>8</v>
       </c>
       <c r="K22">
-        <f t="shared" si="3"/>
+        <f>J22-I22</f>
         <v>0</v>
       </c>
       <c r="L22">
         <v>10</v>
       </c>
       <c r="M22">
-        <f t="shared" si="8"/>
+        <f>J22+2</f>
         <v>10</v>
       </c>
       <c r="N22">
-        <f t="shared" si="9"/>
+        <f>M22-L22</f>
         <v>0</v>
       </c>
       <c r="O22" t="s">
@@ -3240,7 +3240,7 @@
         <v>9707.24</v>
       </c>
       <c r="T22">
-        <f t="shared" si="6"/>
+        <f>D22/S22</f>
         <v>637.18193842946096</v>
       </c>
       <c r="U22">
@@ -3262,7 +3262,7 @@
         <v>5000000</v>
       </c>
       <c r="AA22" s="5">
-        <f t="shared" si="7"/>
+        <f>Z22/D22</f>
         <v>0.80837110312584171</v>
       </c>
     </row>
@@ -3283,15 +3283,15 @@
         <v>6893574</v>
       </c>
       <c r="F23">
-        <f t="shared" si="0"/>
+        <f>D23-C23</f>
         <v>473825</v>
       </c>
       <c r="G23">
-        <f t="shared" si="1"/>
+        <f>F23/C23*100</f>
         <v>7.223334071178253</v>
       </c>
       <c r="H23" s="2">
-        <f t="shared" si="2"/>
+        <f>(D23-E23)/E23</f>
         <v>2.0293537140531167E-2</v>
       </c>
       <c r="I23">
@@ -3301,18 +3301,18 @@
         <v>9</v>
       </c>
       <c r="K23">
-        <f t="shared" si="3"/>
+        <f>J23-I23</f>
         <v>0</v>
       </c>
       <c r="L23">
         <v>11</v>
       </c>
       <c r="M23">
-        <f t="shared" si="8"/>
+        <f>J23+2</f>
         <v>11</v>
       </c>
       <c r="N23">
-        <f t="shared" si="9"/>
+        <f>M23-L23</f>
         <v>0</v>
       </c>
       <c r="O23" t="s">
@@ -3331,7 +3331,7 @@
         <v>7800.06</v>
       </c>
       <c r="T23">
-        <f t="shared" si="6"/>
+        <f>D23/S23</f>
         <v>901.71985856519052</v>
       </c>
       <c r="U23">
@@ -3353,7 +3353,7 @@
         <v>6650000</v>
       </c>
       <c r="AA23" s="5">
-        <f t="shared" si="7"/>
+        <f>Z23/D23</f>
         <v>0.94547939288564431</v>
       </c>
     </row>
@@ -3374,15 +3374,15 @@
         <v>9966555</v>
       </c>
       <c r="F24">
-        <f t="shared" si="0"/>
+        <f>D24-C24</f>
         <v>172816</v>
       </c>
       <c r="G24">
-        <f t="shared" si="1"/>
+        <f>F24/C24*100</f>
         <v>1.743568613262849</v>
       </c>
       <c r="H24" s="2">
-        <f t="shared" si="2"/>
+        <f>(D24-E24)/E24</f>
         <v>1.1828259614279959E-2</v>
       </c>
       <c r="I24">
@@ -3392,18 +3392,18 @@
         <v>13</v>
       </c>
       <c r="K24">
-        <f t="shared" si="3"/>
+        <f>J24-I24</f>
         <v>-1</v>
       </c>
       <c r="L24">
         <v>16</v>
       </c>
       <c r="M24">
-        <f t="shared" si="8"/>
+        <f>J24+2</f>
         <v>15</v>
       </c>
       <c r="N24">
-        <f t="shared" si="9"/>
+        <f>M24-L24</f>
         <v>-1</v>
       </c>
       <c r="O24" t="s">
@@ -3422,7 +3422,7 @@
         <v>56538.9</v>
       </c>
       <c r="T24">
-        <f t="shared" si="6"/>
+        <f>D24/S24</f>
         <v>178.36289704964193</v>
       </c>
       <c r="U24">
@@ -3444,7 +3444,7 @@
         <v>16000000</v>
       </c>
       <c r="AA24" s="5">
-        <f t="shared" si="7"/>
+        <f>Z24/D24</f>
         <v>1.5866024119133215</v>
       </c>
     </row>
@@ -3465,15 +3465,15 @@
         <v>5657342</v>
       </c>
       <c r="F25">
-        <f t="shared" si="0"/>
+        <f>D25-C25</f>
         <v>394873</v>
       </c>
       <c r="G25">
-        <f t="shared" si="1"/>
+        <f>F25/C25*100</f>
         <v>7.4295764776582871</v>
       </c>
       <c r="H25" s="2">
-        <f t="shared" si="2"/>
+        <f>(D25-E25)/E25</f>
         <v>9.2640678254911936E-3</v>
       </c>
       <c r="I25">
@@ -3483,18 +3483,18 @@
         <v>8</v>
       </c>
       <c r="K25">
-        <f t="shared" si="3"/>
+        <f>J25-I25</f>
         <v>0</v>
       </c>
       <c r="L25">
         <v>10</v>
       </c>
       <c r="M25">
-        <f t="shared" si="8"/>
+        <f>J25+2</f>
         <v>10</v>
       </c>
       <c r="N25">
-        <f t="shared" si="9"/>
+        <f>M25-L25</f>
         <v>0</v>
       </c>
       <c r="O25" t="s">
@@ -3513,7 +3513,7 @@
         <v>79626.740000000005</v>
       </c>
       <c r="T25">
-        <f t="shared" si="6"/>
+        <f>D25/S25</f>
         <v>71.706464436444335</v>
       </c>
       <c r="U25">
@@ -3535,7 +3535,7 @@
         <v>2170000</v>
       </c>
       <c r="AA25" s="5">
-        <f t="shared" si="7"/>
+        <f>Z25/D25</f>
         <v>0.38005153288619192</v>
       </c>
     </row>
@@ -3556,15 +3556,15 @@
         <v>2966786</v>
       </c>
       <c r="F26">
-        <f t="shared" si="0"/>
+        <f>D26-C26</f>
         <v>-14326</v>
       </c>
       <c r="G26">
-        <f t="shared" si="1"/>
+        <f>F26/C26*100</f>
         <v>-0.48102234876974315</v>
       </c>
       <c r="H26" s="2">
-        <f t="shared" si="2"/>
+        <f>(D26-E26)/E26</f>
         <v>-9.6805094806298806E-4</v>
       </c>
       <c r="I26">
@@ -3574,18 +3574,18 @@
         <v>4</v>
       </c>
       <c r="K26">
-        <f t="shared" si="3"/>
+        <f>J26-I26</f>
         <v>0</v>
       </c>
       <c r="L26">
         <v>6</v>
       </c>
       <c r="M26">
-        <f t="shared" si="8"/>
+        <f>J26+2</f>
         <v>6</v>
       </c>
       <c r="N26">
-        <f t="shared" si="9"/>
+        <f>M26-L26</f>
         <v>0</v>
       </c>
       <c r="O26" t="s">
@@ -3604,7 +3604,7 @@
         <v>46923.27</v>
       </c>
       <c r="T26">
-        <f t="shared" si="6"/>
+        <f>D26/S26</f>
         <v>63.165120418930741</v>
       </c>
       <c r="U26">
@@ -3626,7 +3626,7 @@
         <v>400000</v>
       </c>
       <c r="AA26" s="5">
-        <f t="shared" si="7"/>
+        <f>Z26/D26</f>
         <v>0.13495668227890553</v>
       </c>
     </row>
@@ -3647,15 +3647,15 @@
         <v>6151548</v>
       </c>
       <c r="F27">
-        <f t="shared" si="0"/>
+        <f>D27-C27</f>
         <v>148803</v>
       </c>
       <c r="G27">
-        <f t="shared" si="1"/>
+        <f>F27/C27*100</f>
         <v>2.4753147229350252</v>
       </c>
       <c r="H27" s="2">
-        <f t="shared" si="2"/>
+        <f>(D27-E27)/E27</f>
         <v>1.4196426655534509E-3</v>
       </c>
       <c r="I27">
@@ -3665,18 +3665,18 @@
         <v>8</v>
       </c>
       <c r="K27">
-        <f t="shared" si="3"/>
+        <f>J27-I27</f>
         <v>0</v>
       </c>
       <c r="L27">
         <v>10</v>
       </c>
       <c r="M27">
-        <f t="shared" si="8"/>
+        <f>J27+2</f>
         <v>10</v>
       </c>
       <c r="N27">
-        <f t="shared" si="9"/>
+        <f>M27-L27</f>
         <v>0</v>
       </c>
       <c r="O27" t="s">
@@ -3695,7 +3695,7 @@
         <v>68741.52</v>
       </c>
       <c r="T27">
-        <f t="shared" si="6"/>
+        <f>D27/S27</f>
         <v>89.615140893014868</v>
       </c>
       <c r="U27">
@@ -3717,7 +3717,7 @@
         <v>501650</v>
       </c>
       <c r="AA27" s="5">
-        <f t="shared" si="7"/>
+        <f>Z27/D27</f>
         <v>8.1432973593250052E-2</v>
       </c>
     </row>
@@ -3738,15 +3738,15 @@
         <v>1080577</v>
       </c>
       <c r="F28">
-        <f t="shared" si="0"/>
+        <f>D28-C28</f>
         <v>90991</v>
       </c>
       <c r="G28">
-        <f t="shared" si="1"/>
+        <f>F28/C28*100</f>
         <v>9.1501946871329505</v>
       </c>
       <c r="H28" s="2">
-        <f t="shared" si="2"/>
+        <f>(D28-E28)/E28</f>
         <v>4.4698341719285163E-3</v>
       </c>
       <c r="I28">
@@ -3756,18 +3756,18 @@
         <v>2</v>
       </c>
       <c r="K28">
-        <f t="shared" si="3"/>
+        <f>J28-I28</f>
         <v>1</v>
       </c>
       <c r="L28">
         <v>3</v>
       </c>
       <c r="M28">
-        <f t="shared" si="8"/>
+        <f>J28+2</f>
         <v>4</v>
       </c>
       <c r="N28">
-        <f t="shared" si="9"/>
+        <f>M28-L28</f>
         <v>1</v>
       </c>
       <c r="O28" t="s">
@@ -3786,7 +3786,7 @@
         <v>145545.79999999999</v>
       </c>
       <c r="T28">
-        <f t="shared" si="6"/>
+        <f>D28/S28</f>
         <v>7.4574944794009861</v>
       </c>
       <c r="U28">
@@ -3808,7 +3808,7 @@
         <v>635500</v>
       </c>
       <c r="AA28" s="5">
-        <f t="shared" si="7"/>
+        <f>Z28/D28</f>
         <v>0.58549465776432252</v>
       </c>
     </row>
@@ -3829,15 +3829,15 @@
         <v>1937552</v>
       </c>
       <c r="F29">
-        <f t="shared" si="0"/>
+        <f>D29-C29</f>
         <v>131508</v>
       </c>
       <c r="G29">
-        <f t="shared" si="1"/>
+        <f>F29/C29*100</f>
         <v>7.1790700530891334</v>
       </c>
       <c r="H29" s="2">
-        <f t="shared" si="2"/>
+        <f>(D29-E29)/E29</f>
         <v>1.330596546570105E-2</v>
       </c>
       <c r="I29">
@@ -3847,18 +3847,18 @@
         <v>3</v>
       </c>
       <c r="K29">
-        <f t="shared" si="3"/>
+        <f>J29-I29</f>
         <v>0</v>
       </c>
       <c r="L29">
         <v>5</v>
       </c>
       <c r="M29">
-        <f t="shared" si="8"/>
+        <f>J29+2</f>
         <v>5</v>
       </c>
       <c r="N29">
-        <f t="shared" si="9"/>
+        <f>M29-L29</f>
         <v>0</v>
       </c>
       <c r="O29" t="s">
@@ -3877,7 +3877,7 @@
         <v>76824.17</v>
       </c>
       <c r="T29">
-        <f t="shared" si="6"/>
+        <f>D29/S29</f>
         <v>25.556188892115593</v>
       </c>
       <c r="U29">
@@ -3896,7 +3896,7 @@
         <v>40</v>
       </c>
       <c r="AA29" s="5">
-        <f t="shared" si="7"/>
+        <f>Z29/D29</f>
         <v>0</v>
       </c>
     </row>
@@ -3917,15 +3917,15 @@
         <v>3138259</v>
       </c>
       <c r="F30">
-        <f t="shared" si="0"/>
+        <f>D30-C30</f>
         <v>399030</v>
       </c>
       <c r="G30">
-        <f t="shared" si="1"/>
+        <f>F30/C30*100</f>
         <v>14.72744102823027</v>
       </c>
       <c r="H30" s="2">
-        <f t="shared" si="2"/>
+        <f>(D30-E30)/E30</f>
         <v>-9.4947548943538438E-3</v>
       </c>
       <c r="I30">
@@ -3935,18 +3935,18 @@
         <v>4</v>
       </c>
       <c r="K30">
-        <f t="shared" si="3"/>
+        <f>J30-I30</f>
         <v>0</v>
       </c>
       <c r="L30">
         <v>6</v>
       </c>
       <c r="M30">
-        <f t="shared" si="8"/>
+        <f>J30+2</f>
         <v>6</v>
       </c>
       <c r="N30">
-        <f t="shared" si="9"/>
+        <f>M30-L30</f>
         <v>0</v>
       </c>
       <c r="O30" t="s">
@@ -3965,7 +3965,7 @@
         <v>109781.18</v>
       </c>
       <c r="T30">
-        <f t="shared" si="6"/>
+        <f>D30/S30</f>
         <v>28.315071854756891</v>
       </c>
       <c r="U30">
@@ -3987,7 +3987,7 @@
         <v>5000000</v>
       </c>
       <c r="AA30" s="5">
-        <f t="shared" si="7"/>
+        <f>Z30/D30</f>
         <v>1.6085125055413256</v>
       </c>
     </row>
@@ -4008,15 +4008,15 @@
         <v>1366275</v>
       </c>
       <c r="F31">
-        <f t="shared" si="0"/>
+        <f>D31-C31</f>
         <v>57644</v>
       </c>
       <c r="G31">
-        <f t="shared" si="1"/>
+        <f>F31/C31*100</f>
         <v>4.3621944159613149</v>
       </c>
       <c r="H31" s="2">
-        <f t="shared" si="2"/>
+        <f>(D31-E31)/E31</f>
         <v>9.3787853836160371E-3</v>
       </c>
       <c r="I31">
@@ -4026,18 +4026,18 @@
         <v>2</v>
       </c>
       <c r="K31">
-        <f t="shared" si="3"/>
+        <f>J31-I31</f>
         <v>0</v>
       </c>
       <c r="L31">
         <v>4</v>
       </c>
       <c r="M31">
-        <f t="shared" si="8"/>
+        <f>J31+2</f>
         <v>4</v>
       </c>
       <c r="N31">
-        <f t="shared" si="9"/>
+        <f>M31-L31</f>
         <v>0</v>
       </c>
       <c r="O31" t="s">
@@ -4056,7 +4056,7 @@
         <v>8952.65</v>
       </c>
       <c r="T31">
-        <f t="shared" si="6"/>
+        <f>D31/S31</f>
         <v>154.0425460617806</v>
       </c>
       <c r="U31">
@@ -4075,7 +4075,7 @@
         <v>19</v>
       </c>
       <c r="AA31" s="5">
-        <f t="shared" si="7"/>
+        <f>Z31/D31</f>
         <v>0</v>
       </c>
     </row>
@@ -4096,15 +4096,15 @@
         <v>8882371</v>
       </c>
       <c r="F32">
-        <f t="shared" si="0"/>
+        <f>D32-C32</f>
         <v>486992</v>
       </c>
       <c r="G32">
-        <f t="shared" si="1"/>
+        <f>F32/C32*100</f>
         <v>5.5292869112362295</v>
       </c>
       <c r="H32" s="2">
-        <f t="shared" si="2"/>
+        <f>(D32-E32)/E32</f>
         <v>4.6397746727759967E-2</v>
       </c>
       <c r="I32">
@@ -4114,18 +4114,18 @@
         <v>12</v>
       </c>
       <c r="K32">
-        <f t="shared" si="3"/>
+        <f>J32-I32</f>
         <v>0</v>
       </c>
       <c r="L32">
         <v>14</v>
       </c>
       <c r="M32">
-        <f t="shared" si="8"/>
+        <f>J32+2</f>
         <v>14</v>
       </c>
       <c r="N32">
-        <f t="shared" si="9"/>
+        <f>M32-L32</f>
         <v>0</v>
       </c>
       <c r="O32" t="s">
@@ -4144,7 +4144,7 @@
         <v>7354.22</v>
       </c>
       <c r="T32">
-        <f t="shared" si="6"/>
+        <f>D32/S32</f>
         <v>1263.8312424703095</v>
       </c>
       <c r="U32">
@@ -4166,7 +4166,7 @@
         <v>9000000</v>
       </c>
       <c r="AA32" s="5">
-        <f t="shared" si="7"/>
+        <f>Z32/D32</f>
         <v>0.96831532392353192</v>
       </c>
     </row>
@@ -4187,15 +4187,15 @@
         <v>2106319</v>
       </c>
       <c r="F33">
-        <f t="shared" si="0"/>
+        <f>D33-C33</f>
         <v>52947</v>
       </c>
       <c r="G33">
-        <f t="shared" si="1"/>
+        <f>F33/C33*100</f>
         <v>2.5612001898152785</v>
       </c>
       <c r="H33" s="2">
-        <f t="shared" si="2"/>
+        <f>(D33-E33)/E33</f>
         <v>6.5996651029592386E-3</v>
       </c>
       <c r="I33">
@@ -4205,18 +4205,18 @@
         <v>3</v>
       </c>
       <c r="K33">
-        <f t="shared" si="3"/>
+        <f>J33-I33</f>
         <v>0</v>
       </c>
       <c r="L33">
         <v>5</v>
       </c>
       <c r="M33">
-        <f t="shared" si="8"/>
+        <f>J33+2</f>
         <v>5</v>
       </c>
       <c r="N33">
-        <f t="shared" si="9"/>
+        <f>M33-L33</f>
         <v>0</v>
       </c>
       <c r="O33" t="s">
@@ -4235,7 +4235,7 @@
         <v>121298.15</v>
       </c>
       <c r="T33">
-        <f t="shared" si="6"/>
+        <f>D33/S33</f>
         <v>17.479409207807375</v>
       </c>
       <c r="U33">
@@ -4257,7 +4257,7 @@
         <v>11500000</v>
       </c>
       <c r="AA33" s="5">
-        <f t="shared" si="7"/>
+        <f>Z33/D33</f>
         <v>5.4239654375489339</v>
       </c>
     </row>
@@ -4278,15 +4278,15 @@
         <v>19336776</v>
       </c>
       <c r="F34">
-        <f t="shared" ref="F34:F52" si="10">D34-C34</f>
+        <f>D34-C34</f>
         <v>794696</v>
       </c>
       <c r="G34">
-        <f t="shared" ref="G34:G52" si="11">F34/C34*100</f>
+        <f>F34/C34*100</f>
         <v>4.0919301242903643</v>
       </c>
       <c r="H34" s="2">
-        <f t="shared" ref="H34:H52" si="12">(D34-E34)/E34</f>
+        <f>(D34-E34)/E34</f>
         <v>4.5456129811919009E-2</v>
       </c>
       <c r="I34">
@@ -4296,18 +4296,18 @@
         <v>26</v>
       </c>
       <c r="K34">
-        <f t="shared" ref="K34:K52" si="13">J34-I34</f>
+        <f>J34-I34</f>
         <v>-1</v>
       </c>
       <c r="L34">
         <v>29</v>
       </c>
       <c r="M34">
-        <f t="shared" si="8"/>
+        <f>J34+2</f>
         <v>28</v>
       </c>
       <c r="N34">
-        <f t="shared" si="9"/>
+        <f>M34-L34</f>
         <v>-1</v>
       </c>
       <c r="O34" t="s">
@@ -4326,7 +4326,7 @@
         <v>47126.400000000001</v>
       </c>
       <c r="T34">
-        <f t="shared" ref="T34:T52" si="14">D34/S34</f>
+        <f>D34/S34</f>
         <v>428.96870968289534</v>
       </c>
       <c r="U34">
@@ -4348,7 +4348,7 @@
         <v>20000000</v>
       </c>
       <c r="AA34" s="5">
-        <f t="shared" ref="AA34:AA52" si="15">Z34/D34</f>
+        <f>Z34/D34</f>
         <v>0.98932757927222192</v>
       </c>
     </row>
@@ -4369,15 +4369,15 @@
         <v>10600823</v>
       </c>
       <c r="F35">
-        <f t="shared" si="10"/>
+        <f>D35-C35</f>
         <v>888167</v>
       </c>
       <c r="G35">
-        <f t="shared" si="11"/>
+        <f>F35/C35*100</f>
         <v>9.2848351849159005</v>
       </c>
       <c r="H35" s="2">
-        <f t="shared" si="12"/>
+        <f>(D35-E35)/E35</f>
         <v>-1.3855056347983548E-2</v>
       </c>
       <c r="I35">
@@ -4387,18 +4387,18 @@
         <v>14</v>
       </c>
       <c r="K35">
-        <f t="shared" si="13"/>
+        <f>J35-I35</f>
         <v>1</v>
       </c>
       <c r="L35">
         <v>15</v>
       </c>
       <c r="M35">
-        <f t="shared" si="8"/>
+        <f>J35+2</f>
         <v>16</v>
       </c>
       <c r="N35">
-        <f t="shared" si="9"/>
+        <f>M35-L35</f>
         <v>1</v>
       </c>
       <c r="O35" t="s">
@@ -4417,7 +4417,7 @@
         <v>48617.91</v>
       </c>
       <c r="T35">
-        <f t="shared" si="14"/>
+        <f>D35/S35</f>
         <v>215.02257090031225</v>
       </c>
       <c r="U35">
@@ -4439,7 +4439,7 @@
         <v>0</v>
       </c>
       <c r="AA35" s="5">
-        <f t="shared" si="15"/>
+        <f>Z35/D35</f>
         <v>0</v>
       </c>
     </row>
@@ -4460,15 +4460,15 @@
         <v>765309</v>
       </c>
       <c r="F36">
-        <f t="shared" si="10"/>
+        <f>D36-C36</f>
         <v>103797</v>
       </c>
       <c r="G36">
-        <f t="shared" si="11"/>
+        <f>F36/C36*100</f>
         <v>15.356743921113175</v>
       </c>
       <c r="H36" s="2">
-        <f t="shared" si="12"/>
+        <f>(D36-E36)/E36</f>
         <v>1.8806782619830684E-2</v>
       </c>
       <c r="I36">
@@ -4478,18 +4478,18 @@
         <v>1</v>
       </c>
       <c r="K36">
-        <f t="shared" si="13"/>
+        <f>J36-I36</f>
         <v>0</v>
       </c>
       <c r="L36">
         <v>3</v>
       </c>
       <c r="M36">
-        <f t="shared" si="8"/>
+        <f>J36+2</f>
         <v>3</v>
       </c>
       <c r="N36">
-        <f t="shared" si="9"/>
+        <f>M36-L36</f>
         <v>0</v>
       </c>
       <c r="O36" t="s">
@@ -4508,7 +4508,7 @@
         <v>69000.800000000003</v>
       </c>
       <c r="T36">
-        <f t="shared" si="14"/>
+        <f>D36/S36</f>
         <v>11.299897972197423</v>
       </c>
       <c r="U36">
@@ -4530,7 +4530,7 @@
         <v>1000000</v>
       </c>
       <c r="AA36" s="5">
-        <f t="shared" si="15"/>
+        <f>Z36/D36</f>
         <v>1.2825412785910515</v>
       </c>
     </row>
@@ -4551,15 +4551,15 @@
         <v>11693217</v>
       </c>
       <c r="F37">
-        <f t="shared" si="10"/>
+        <f>D37-C37</f>
         <v>240353</v>
       </c>
       <c r="G37">
-        <f t="shared" si="11"/>
+        <f>F37/C37*100</f>
         <v>2.0776514144666183</v>
       </c>
       <c r="H37" s="2">
-        <f t="shared" si="12"/>
+        <f>(D37-E37)/E37</f>
         <v>9.8887243775600854E-3</v>
       </c>
       <c r="I37">
@@ -4569,18 +4569,18 @@
         <v>15</v>
       </c>
       <c r="K37">
-        <f t="shared" si="13"/>
+        <f>J37-I37</f>
         <v>-1</v>
       </c>
       <c r="L37">
         <v>18</v>
       </c>
       <c r="M37">
-        <f t="shared" si="8"/>
+        <f>J37+2</f>
         <v>17</v>
       </c>
       <c r="N37">
-        <f t="shared" si="9"/>
+        <f>M37-L37</f>
         <v>-1</v>
       </c>
       <c r="O37" t="s">
@@ -4599,7 +4599,7 @@
         <v>40860.69</v>
       </c>
       <c r="T37">
-        <f t="shared" si="14"/>
+        <f>D37/S37</f>
         <v>289.00265756647769</v>
       </c>
       <c r="U37">
@@ -4621,7 +4621,7 @@
         <v>0</v>
       </c>
       <c r="AA37" s="5">
-        <f t="shared" si="15"/>
+        <f>Z37/D37</f>
         <v>0</v>
       </c>
     </row>
@@ -4642,15 +4642,15 @@
         <v>3980783</v>
       </c>
       <c r="F38">
-        <f t="shared" si="10"/>
+        <f>D38-C38</f>
         <v>198634</v>
       </c>
       <c r="G38">
-        <f t="shared" si="11"/>
+        <f>F38/C38*100</f>
         <v>5.2759688085841736</v>
       </c>
       <c r="H38" s="2">
-        <f t="shared" si="12"/>
+        <f>(D38-E38)/E38</f>
         <v>-4.3375888612868377E-3</v>
       </c>
       <c r="I38">
@@ -4660,18 +4660,18 @@
         <v>5</v>
       </c>
       <c r="K38">
-        <f t="shared" si="13"/>
+        <f>J38-I38</f>
         <v>0</v>
       </c>
       <c r="L38">
         <v>7</v>
       </c>
       <c r="M38">
-        <f t="shared" si="8"/>
+        <f>J38+2</f>
         <v>7</v>
       </c>
       <c r="N38">
-        <f t="shared" si="9"/>
+        <f>M38-L38</f>
         <v>0</v>
       </c>
       <c r="O38" t="s">
@@ -4690,7 +4690,7 @@
         <v>68594.92</v>
       </c>
       <c r="T38">
-        <f t="shared" si="14"/>
+        <f>D38/S38</f>
         <v>57.781480027967085</v>
       </c>
       <c r="U38">
@@ -4712,7 +4712,7 @@
         <v>0</v>
       </c>
       <c r="AA38" s="5">
-        <f t="shared" si="15"/>
+        <f>Z38/D38</f>
         <v>0</v>
       </c>
     </row>
@@ -4733,15 +4733,15 @@
         <v>4241507</v>
       </c>
       <c r="F39">
-        <f t="shared" si="10"/>
+        <f>D39-C39</f>
         <v>392894</v>
       </c>
       <c r="G39">
-        <f t="shared" si="11"/>
+        <f>F39/C39*100</f>
         <v>10.208735318710204</v>
       </c>
       <c r="H39" s="2">
-        <f t="shared" si="12"/>
+        <f>(D39-E39)/E39</f>
         <v>-1.6503568189325161E-6</v>
       </c>
       <c r="I39">
@@ -4751,18 +4751,18 @@
         <v>6</v>
       </c>
       <c r="K39">
-        <f t="shared" si="13"/>
+        <f>J39-I39</f>
         <v>1</v>
       </c>
       <c r="L39">
         <v>7</v>
       </c>
       <c r="M39">
-        <f t="shared" si="8"/>
+        <f>J39+2</f>
         <v>8</v>
       </c>
       <c r="N39">
-        <f t="shared" si="9"/>
+        <f>M39-L39</f>
         <v>1</v>
       </c>
       <c r="O39" t="s">
@@ -4781,7 +4781,7 @@
         <v>95988.01</v>
       </c>
       <c r="T39">
-        <f t="shared" si="14"/>
+        <f>D39/S39</f>
         <v>44.187810540087249</v>
       </c>
       <c r="U39">
@@ -4803,7 +4803,7 @@
         <v>7730772</v>
       </c>
       <c r="AA39" s="5">
-        <f t="shared" si="15"/>
+        <f>Z39/D39</f>
         <v>1.8226504774254391</v>
       </c>
     </row>
@@ -4824,15 +4824,15 @@
         <v>12783254</v>
       </c>
       <c r="F40">
-        <f t="shared" si="10"/>
+        <f>D40-C40</f>
         <v>276939</v>
       </c>
       <c r="G40">
-        <f t="shared" si="11"/>
+        <f>F40/C40*100</f>
         <v>2.1746451975888319</v>
       </c>
       <c r="H40" s="2">
-        <f t="shared" si="12"/>
+        <f>(D40-E40)/E40</f>
         <v>1.7881988420162816E-2</v>
       </c>
       <c r="I40">
@@ -4842,18 +4842,18 @@
         <v>17</v>
       </c>
       <c r="K40">
-        <f t="shared" si="13"/>
+        <f>J40-I40</f>
         <v>-1</v>
       </c>
       <c r="L40">
         <v>20</v>
       </c>
       <c r="M40">
-        <f t="shared" si="8"/>
+        <f>J40+2</f>
         <v>19</v>
       </c>
       <c r="N40">
-        <f t="shared" si="9"/>
+        <f>M40-L40</f>
         <v>-1</v>
       </c>
       <c r="O40" t="s">
@@ -4872,7 +4872,7 @@
         <v>44742.7</v>
       </c>
       <c r="T40">
-        <f t="shared" si="14"/>
+        <f>D40/S40</f>
         <v>290.81490388376204</v>
       </c>
       <c r="U40">
@@ -4894,7 +4894,7 @@
         <v>4000000</v>
       </c>
       <c r="AA40" s="5">
-        <f t="shared" si="15"/>
+        <f>Z40/D40</f>
         <v>0.30741223150231434</v>
       </c>
     </row>
@@ -4915,15 +4915,15 @@
         <v>1057125</v>
       </c>
       <c r="F41">
-        <f t="shared" si="10"/>
+        <f>D41-C41</f>
         <v>42916</v>
       </c>
       <c r="G41">
-        <f t="shared" si="11"/>
+        <f>F41/C41*100</f>
         <v>4.0669151392991401</v>
       </c>
       <c r="H41" s="2">
-        <f t="shared" si="12"/>
+        <f>(D41-E41)/E41</f>
         <v>3.8820385479484451E-2</v>
       </c>
       <c r="I41">
@@ -4933,18 +4933,18 @@
         <v>2</v>
       </c>
       <c r="K41">
-        <f t="shared" si="13"/>
+        <f>J41-I41</f>
         <v>0</v>
       </c>
       <c r="L41">
         <v>4</v>
       </c>
       <c r="M41">
-        <f t="shared" si="8"/>
+        <f>J41+2</f>
         <v>4</v>
       </c>
       <c r="N41">
-        <f t="shared" si="9"/>
+        <f>M41-L41</f>
         <v>0</v>
       </c>
       <c r="O41" t="s">
@@ -4963,7 +4963,7 @@
         <v>1033.81</v>
       </c>
       <c r="T41">
-        <f t="shared" si="14"/>
+        <f>D41/S41</f>
         <v>1062.2483821978894</v>
       </c>
       <c r="U41">
@@ -4985,7 +4985,7 @@
         <v>500000</v>
       </c>
       <c r="AA41" s="5">
-        <f t="shared" si="15"/>
+        <f>Z41/D41</f>
         <v>0.45530581525693364</v>
       </c>
     </row>
@@ -5006,15 +5006,15 @@
         <v>5218040</v>
       </c>
       <c r="F42">
-        <f t="shared" si="10"/>
+        <f>D42-C42</f>
         <v>478737</v>
       </c>
       <c r="G42">
-        <f t="shared" si="11"/>
+        <f>F42/C42*100</f>
         <v>10.304338701779498</v>
       </c>
       <c r="H42" s="2">
-        <f t="shared" si="12"/>
+        <f>(D42-E42)/E42</f>
         <v>-1.7885642885067957E-2</v>
       </c>
       <c r="I42">
@@ -5024,18 +5024,18 @@
         <v>7</v>
       </c>
       <c r="K42">
-        <f t="shared" si="13"/>
+        <f>J42-I42</f>
         <v>0</v>
       </c>
       <c r="L42">
         <v>9</v>
       </c>
       <c r="M42">
-        <f t="shared" si="8"/>
+        <f>J42+2</f>
         <v>9</v>
       </c>
       <c r="N42">
-        <f t="shared" si="9"/>
+        <f>M42-L42</f>
         <v>0</v>
       </c>
       <c r="O42" t="s">
@@ -5054,7 +5054,7 @@
         <v>30060.7</v>
       </c>
       <c r="T42">
-        <f t="shared" si="14"/>
+        <f>D42/S42</f>
         <v>170.47879789891786</v>
       </c>
       <c r="U42">
@@ -5076,7 +5076,7 @@
         <v>0</v>
       </c>
       <c r="AA42" s="5">
-        <f t="shared" si="15"/>
+        <f>Z42/D42</f>
         <v>0</v>
       </c>
     </row>
@@ -5097,15 +5097,15 @@
         <v>892717</v>
       </c>
       <c r="F43">
-        <f t="shared" si="10"/>
+        <f>D43-C43</f>
         <v>68009</v>
       </c>
       <c r="G43">
-        <f t="shared" si="11"/>
+        <f>F43/C43*100</f>
         <v>8.2961985261557949</v>
       </c>
       <c r="H43" s="2">
-        <f t="shared" si="12"/>
+        <f>(D43-E43)/E43</f>
         <v>-5.5415097953774826E-3</v>
       </c>
       <c r="I43">
@@ -5115,18 +5115,18 @@
         <v>1</v>
       </c>
       <c r="K43">
-        <f t="shared" si="13"/>
+        <f>J43-I43</f>
         <v>0</v>
       </c>
       <c r="L43">
         <v>3</v>
       </c>
       <c r="M43">
-        <f t="shared" si="8"/>
+        <f>J43+2</f>
         <v>3</v>
       </c>
       <c r="N43">
-        <f t="shared" si="9"/>
+        <f>M43-L43</f>
         <v>0</v>
       </c>
       <c r="O43" t="s">
@@ -5145,7 +5145,7 @@
         <v>75811</v>
       </c>
       <c r="T43">
-        <f t="shared" si="14"/>
+        <f>D43/S43</f>
         <v>11.710305892284762</v>
       </c>
       <c r="U43">
@@ -5167,7 +5167,7 @@
         <v>0</v>
       </c>
       <c r="AA43" s="5">
-        <f t="shared" si="15"/>
+        <f>Z43/D43</f>
         <v>0</v>
       </c>
     </row>
@@ -5188,15 +5188,15 @@
         <v>6886834</v>
       </c>
       <c r="F44">
-        <f t="shared" si="10"/>
+        <f>D44-C44</f>
         <v>541466</v>
       </c>
       <c r="G44">
-        <f t="shared" si="11"/>
+        <f>F44/C44*100</f>
         <v>8.4930101196295578</v>
       </c>
       <c r="H44" s="2">
-        <f t="shared" si="12"/>
+        <f>(D44-E44)/E44</f>
         <v>4.3652859935349106E-3</v>
       </c>
       <c r="I44">
@@ -5206,18 +5206,18 @@
         <v>9</v>
       </c>
       <c r="K44">
-        <f t="shared" si="13"/>
+        <f>J44-I44</f>
         <v>0</v>
       </c>
       <c r="L44">
         <v>11</v>
       </c>
       <c r="M44">
-        <f t="shared" si="8"/>
+        <f>J44+2</f>
         <v>11</v>
       </c>
       <c r="N44">
-        <f t="shared" si="9"/>
+        <f>M44-L44</f>
         <v>0</v>
       </c>
       <c r="O44" t="s">
@@ -5236,7 +5236,7 @@
         <v>41234.9</v>
       </c>
       <c r="T44">
-        <f t="shared" si="14"/>
+        <f>D44/S44</f>
         <v>167.74375589609772</v>
       </c>
       <c r="U44">
@@ -5258,7 +5258,7 @@
         <v>0</v>
       </c>
       <c r="AA44" s="5">
-        <f t="shared" si="15"/>
+        <f>Z44/D44</f>
         <v>0</v>
       </c>
     </row>
@@ -5279,15 +5279,15 @@
         <v>29360759</v>
       </c>
       <c r="F45">
-        <f t="shared" si="10"/>
+        <f>D45-C45</f>
         <v>3914872</v>
       </c>
       <c r="G45">
-        <f t="shared" si="11"/>
+        <f>F45/C45*100</f>
         <v>15.493142467407338</v>
       </c>
       <c r="H45" s="2">
-        <f t="shared" si="12"/>
+        <f>(D45-E45)/E45</f>
         <v>-6.0444282111371851E-3</v>
       </c>
       <c r="I45">
@@ -5297,18 +5297,18 @@
         <v>38</v>
       </c>
       <c r="K45">
-        <f t="shared" si="13"/>
+        <f>J45-I45</f>
         <v>2</v>
       </c>
       <c r="L45">
         <v>38</v>
       </c>
       <c r="M45">
-        <f t="shared" si="8"/>
+        <f>J45+2</f>
         <v>40</v>
       </c>
       <c r="N45">
-        <f t="shared" si="9"/>
+        <f>M45-L45</f>
         <v>2</v>
       </c>
       <c r="O45" t="s">
@@ -5327,7 +5327,7 @@
         <v>261231.71</v>
       </c>
       <c r="T45">
-        <f t="shared" si="14"/>
+        <f>D45/S45</f>
         <v>111.71419426837576</v>
       </c>
       <c r="U45">
@@ -5349,7 +5349,7 @@
         <v>0</v>
       </c>
       <c r="AA45" s="5">
-        <f t="shared" si="15"/>
+        <f>Z45/D45</f>
         <v>0</v>
       </c>
     </row>
@@ -5370,15 +5370,15 @@
         <v>3249879</v>
       </c>
       <c r="F46">
-        <f t="shared" si="10"/>
+        <f>D46-C46</f>
         <v>504487</v>
       </c>
       <c r="G46">
-        <f t="shared" si="11"/>
+        <f>F46/C46*100</f>
         <v>18.207498651094554</v>
       </c>
       <c r="H46" s="2">
-        <f t="shared" si="12"/>
+        <f>(D46-E46)/E46</f>
         <v>7.8073675973782406E-3</v>
       </c>
       <c r="I46">
@@ -5388,18 +5388,18 @@
         <v>4</v>
       </c>
       <c r="K46">
-        <f t="shared" si="13"/>
+        <f>J46-I46</f>
         <v>0</v>
       </c>
       <c r="L46">
         <v>6</v>
       </c>
       <c r="M46">
-        <f t="shared" si="8"/>
+        <f>J46+2</f>
         <v>6</v>
       </c>
       <c r="N46">
-        <f t="shared" si="9"/>
+        <f>M46-L46</f>
         <v>0</v>
       </c>
       <c r="O46" t="s">
@@ -5418,7 +5418,7 @@
         <v>82169.62</v>
       </c>
       <c r="T46">
-        <f t="shared" si="14"/>
+        <f>D46/S46</f>
         <v>39.859646424067684</v>
       </c>
       <c r="U46">
@@ -5440,7 +5440,7 @@
         <v>1000000</v>
       </c>
       <c r="AA46" s="5">
-        <f t="shared" si="15"/>
+        <f>Z46/D46</f>
         <v>0.30532001812379628</v>
       </c>
     </row>
@@ -5461,15 +5461,15 @@
         <v>623347</v>
       </c>
       <c r="F47">
-        <f t="shared" si="10"/>
+        <f>D47-C47</f>
         <v>13166</v>
       </c>
       <c r="G47">
-        <f t="shared" si="11"/>
+        <f>F47/C47*100</f>
         <v>2.0887239682899783</v>
       </c>
       <c r="H47" s="2">
-        <f t="shared" si="12"/>
+        <f>(D47-E47)/E47</f>
         <v>3.233511992517811E-2</v>
       </c>
       <c r="I47">
@@ -5479,18 +5479,18 @@
         <v>1</v>
       </c>
       <c r="K47">
-        <f t="shared" si="13"/>
+        <f>J47-I47</f>
         <v>0</v>
       </c>
       <c r="L47">
         <v>3</v>
       </c>
       <c r="M47">
-        <f t="shared" si="8"/>
+        <f>J47+2</f>
         <v>3</v>
       </c>
       <c r="N47">
-        <f t="shared" si="9"/>
+        <f>M47-L47</f>
         <v>0</v>
       </c>
       <c r="O47" t="s">
@@ -5509,7 +5509,7 @@
         <v>9216.66</v>
       </c>
       <c r="T47">
-        <f t="shared" si="14"/>
+        <f>D47/S47</f>
         <v>69.819544173268838</v>
       </c>
       <c r="U47">
@@ -5531,7 +5531,7 @@
         <v>0</v>
       </c>
       <c r="AA47" s="5">
-        <f t="shared" si="15"/>
+        <f>Z47/D47</f>
         <v>0</v>
       </c>
     </row>
@@ -5552,15 +5552,15 @@
         <v>8590563</v>
       </c>
       <c r="F48">
-        <f t="shared" si="10"/>
+        <f>D48-C48</f>
         <v>616806</v>
       </c>
       <c r="G48">
-        <f t="shared" si="11"/>
+        <f>F48/C48*100</f>
         <v>7.6738773206783604</v>
       </c>
       <c r="H48" s="2">
-        <f t="shared" si="12"/>
+        <f>(D48-E48)/E48</f>
         <v>7.4475910368156312E-3</v>
       </c>
       <c r="I48">
@@ -5570,18 +5570,18 @@
         <v>11</v>
       </c>
       <c r="K48">
-        <f t="shared" si="13"/>
+        <f>J48-I48</f>
         <v>0</v>
       </c>
       <c r="L48">
         <v>13</v>
       </c>
       <c r="M48">
-        <f t="shared" si="8"/>
+        <f>J48+2</f>
         <v>13</v>
       </c>
       <c r="N48">
-        <f t="shared" si="9"/>
+        <f>M48-L48</f>
         <v>0</v>
       </c>
       <c r="O48" t="s">
@@ -5600,7 +5600,7 @@
         <v>39490.089999999997</v>
       </c>
       <c r="T48">
-        <f t="shared" si="14"/>
+        <f>D48/S48</f>
         <v>219.15731263210594</v>
       </c>
       <c r="U48">
@@ -5622,7 +5622,7 @@
         <v>1500000</v>
       </c>
       <c r="AA48" s="5">
-        <f t="shared" si="15"/>
+        <f>Z48/D48</f>
         <v>0.17331939691320464</v>
       </c>
     </row>
@@ -5643,15 +5643,15 @@
         <v>7693612</v>
       </c>
       <c r="F49">
-        <f t="shared" si="10"/>
+        <f>D49-C49</f>
         <v>962577</v>
       </c>
       <c r="G49">
-        <f t="shared" si="11"/>
+        <f>F49/C49*100</f>
         <v>14.25328602657429</v>
       </c>
       <c r="H49" s="2">
-        <f t="shared" si="12"/>
+        <f>(D49-E49)/E49</f>
         <v>2.9029277795656967E-3</v>
       </c>
       <c r="I49">
@@ -5661,18 +5661,18 @@
         <v>10</v>
       </c>
       <c r="K49">
-        <f t="shared" si="13"/>
+        <f>J49-I49</f>
         <v>0</v>
       </c>
       <c r="L49">
         <v>12</v>
       </c>
       <c r="M49">
-        <f t="shared" si="8"/>
+        <f>J49+2</f>
         <v>12</v>
       </c>
       <c r="N49">
-        <f t="shared" si="9"/>
+        <f>M49-L49</f>
         <v>0</v>
       </c>
       <c r="O49" t="s">
@@ -5691,7 +5691,7 @@
         <v>66455.520000000004</v>
       </c>
       <c r="T49">
-        <f t="shared" si="14"/>
+        <f>D49/S49</f>
         <v>116.10692384921522</v>
       </c>
       <c r="U49">
@@ -5713,7 +5713,7 @@
         <v>15464000</v>
       </c>
       <c r="AA49" s="5">
-        <f t="shared" si="15"/>
+        <f>Z49/D49</f>
         <v>2.0041612525541264</v>
       </c>
     </row>
@@ -5734,15 +5734,15 @@
         <v>1784787</v>
       </c>
       <c r="F50">
-        <f t="shared" si="10"/>
+        <f>D50-C50</f>
         <v>-64770</v>
       </c>
       <c r="G50">
-        <f t="shared" si="11"/>
+        <f>F50/C50*100</f>
         <v>-3.4826044525934035</v>
       </c>
       <c r="H50" s="2">
-        <f t="shared" si="12"/>
+        <f>(D50-E50)/E50</f>
         <v>5.7474645433880905E-3</v>
       </c>
       <c r="I50">
@@ -5752,18 +5752,18 @@
         <v>2</v>
       </c>
       <c r="K50">
-        <f t="shared" si="13"/>
+        <f>J50-I50</f>
         <v>-1</v>
       </c>
       <c r="L50">
         <v>5</v>
       </c>
       <c r="M50">
-        <f t="shared" si="8"/>
+        <f>J50+2</f>
         <v>4</v>
       </c>
       <c r="N50">
-        <f t="shared" si="9"/>
+        <f>M50-L50</f>
         <v>-1</v>
       </c>
       <c r="O50" t="s">
@@ -5782,7 +5782,7 @@
         <v>24038.21</v>
       </c>
       <c r="T50">
-        <f t="shared" si="14"/>
+        <f>D50/S50</f>
         <v>74.674653395573131</v>
       </c>
       <c r="U50">
@@ -5804,7 +5804,7 @@
         <v>1000000</v>
       </c>
       <c r="AA50" s="5">
-        <f t="shared" si="15"/>
+        <f>Z50/D50</f>
         <v>0.55708909804489581</v>
       </c>
     </row>
@@ -5825,15 +5825,15 @@
         <v>5832655</v>
       </c>
       <c r="F51">
-        <f t="shared" si="10"/>
+        <f>D51-C51</f>
         <v>199243</v>
       </c>
       <c r="G51">
-        <f t="shared" si="11"/>
+        <f>F51/C51*100</f>
         <v>3.4965770072461098</v>
       </c>
       <c r="H51" s="2">
-        <f t="shared" si="12"/>
+        <f>(D51-E51)/E51</f>
         <v>1.1112949420118283E-2</v>
       </c>
       <c r="I51">
@@ -5843,18 +5843,18 @@
         <v>8</v>
       </c>
       <c r="K51">
-        <f t="shared" si="13"/>
+        <f>J51-I51</f>
         <v>0</v>
       </c>
       <c r="L51">
         <v>10</v>
       </c>
       <c r="M51">
-        <f t="shared" si="8"/>
+        <f>J51+2</f>
         <v>10</v>
       </c>
       <c r="N51">
-        <f t="shared" si="9"/>
+        <f>M51-L51</f>
         <v>0</v>
       </c>
       <c r="O51" t="s">
@@ -5873,7 +5873,7 @@
         <v>54157.8</v>
       </c>
       <c r="T51">
-        <f t="shared" si="14"/>
+        <f>D51/S51</f>
         <v>108.8942497664233</v>
       </c>
       <c r="U51">
@@ -5895,7 +5895,7 @@
         <v>1000000</v>
       </c>
       <c r="AA51" s="5">
-        <f t="shared" si="15"/>
+        <f>Z51/D51</f>
         <v>0.16956415061162636</v>
       </c>
     </row>
@@ -5916,15 +5916,15 @@
         <v>582328</v>
       </c>
       <c r="F52">
-        <f t="shared" si="10"/>
+        <f>D52-C52</f>
         <v>9419</v>
       </c>
       <c r="G52">
-        <f t="shared" si="11"/>
+        <f>F52/C52*100</f>
         <v>1.6573992609537216</v>
       </c>
       <c r="H52" s="2">
-        <f t="shared" si="12"/>
+        <f>(D52-E52)/E52</f>
         <v>-7.914783421027324E-3</v>
       </c>
       <c r="I52">
@@ -5934,18 +5934,18 @@
         <v>1</v>
       </c>
       <c r="K52">
-        <f t="shared" si="13"/>
+        <f>J52-I52</f>
         <v>0</v>
       </c>
       <c r="L52">
         <v>3</v>
       </c>
       <c r="M52">
-        <f t="shared" si="8"/>
+        <f>J52+2</f>
         <v>3</v>
       </c>
       <c r="N52">
-        <f t="shared" si="9"/>
+        <f>M52-L52</f>
         <v>0</v>
       </c>
       <c r="O52" t="s">
@@ -5964,7 +5964,7 @@
         <v>97093.14</v>
       </c>
       <c r="T52">
-        <f t="shared" si="14"/>
+        <f>D52/S52</f>
         <v>5.9501526060440524</v>
       </c>
       <c r="U52">
@@ -5986,7 +5986,7 @@
         <v>0</v>
       </c>
       <c r="AA52" s="5">
-        <f t="shared" si="15"/>
+        <f>Z52/D52</f>
         <v>0</v>
       </c>
     </row>

--- a/apportion/pop.xlsx
+++ b/apportion/pop.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/user/Google Drive/GitHub/R Functions/apportion/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E73B2A34-0126-C447-98C1-44D560DC460D}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9AA455F-17E2-A34D-B9BC-7FDF45F7DEC1}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="35840" windowHeight="21900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38400" yWindow="500" windowWidth="38400" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="pop" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="136">
   <si>
     <t>state</t>
   </si>
@@ -412,16 +412,33 @@
     <t>hispanic_per</t>
   </si>
   <si>
-    <t>hispnaic_rank</t>
+    <t>undoc_pop</t>
+  </si>
+  <si>
+    <t>undoc_per</t>
+  </si>
+  <si>
+    <t>hispanic_rank</t>
+  </si>
+  <si>
+    <t>black_pop</t>
+  </si>
+  <si>
+    <t>black_error</t>
+  </si>
+  <si>
+    <t>black_per</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="0.000"/>
+    <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="166" formatCode="0.0%"/>
   </numFmts>
   <fonts count="18" x14ac:knownFonts="1">
     <font>
@@ -902,13 +919,15 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="43" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="44">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1266,14 +1285,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AA52"/>
+  <dimension ref="A1:AF52"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="26" max="26" width="17.1640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="10.83203125" style="5"/>
+    <col min="22" max="22" width="17.1640625" style="4" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="10.83203125" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1341,22 +1360,37 @@
         <v>129</v>
       </c>
       <c r="W1" t="s">
+        <v>132</v>
+      </c>
+      <c r="X1" t="s">
         <v>130</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Y1" t="s">
+        <v>131</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>133</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>134</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>135</v>
+      </c>
+      <c r="AC1" t="s">
         <v>123</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="AD1" t="s">
         <v>124</v>
       </c>
-      <c r="Z1" s="4" t="s">
+      <c r="AE1" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="AA1" s="5" t="s">
+      <c r="AF1" s="5" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -1373,15 +1407,15 @@
         <v>4921532</v>
       </c>
       <c r="F2">
-        <f>D2-C2</f>
+        <f t="shared" ref="F2:F33" si="0">D2-C2</f>
         <v>227071</v>
       </c>
       <c r="G2">
-        <f>F2/C2*100</f>
+        <f t="shared" ref="G2:G33" si="1">F2/C2*100</f>
         <v>4.7277087442759518</v>
       </c>
       <c r="H2" s="2">
-        <f>(D2-E2)/E2</f>
+        <f t="shared" ref="H2:H33" si="2">(D2-E2)/E2</f>
         <v>2.2050247768377815E-2</v>
       </c>
       <c r="I2">
@@ -1391,18 +1425,18 @@
         <v>7</v>
       </c>
       <c r="K2">
-        <f>J2-I2</f>
+        <f t="shared" ref="K2:K33" si="3">J2-I2</f>
         <v>0</v>
       </c>
       <c r="L2">
         <v>9</v>
       </c>
       <c r="M2">
-        <f>J2+2</f>
+        <f t="shared" ref="M2:M9" si="4">J2+2</f>
         <v>9</v>
       </c>
       <c r="N2">
-        <f>M2-L2</f>
+        <f t="shared" ref="N2:N9" si="5">M2-L2</f>
         <v>0</v>
       </c>
       <c r="O2" t="s">
@@ -1421,7 +1455,7 @@
         <v>50645.33</v>
       </c>
       <c r="T2">
-        <f>D2/S2</f>
+        <f t="shared" ref="T2:T33" si="6">D2/S2</f>
         <v>99.319186981307055</v>
       </c>
       <c r="U2">
@@ -1433,21 +1467,36 @@
       <c r="W2">
         <v>40</v>
       </c>
-      <c r="X2">
+      <c r="X2" s="6">
+        <v>60000</v>
+      </c>
+      <c r="Y2" s="7">
+        <v>5.4854633708831318E-3</v>
+      </c>
+      <c r="Z2">
+        <v>1319551</v>
+      </c>
+      <c r="AA2">
+        <v>8216</v>
+      </c>
+      <c r="AB2">
+        <v>26.9</v>
+      </c>
+      <c r="AC2">
         <v>0.3708863</v>
       </c>
-      <c r="Y2">
+      <c r="AD2">
         <v>43</v>
       </c>
-      <c r="Z2" s="4">
+      <c r="AE2" s="4">
         <v>1240000</v>
       </c>
-      <c r="AA2" s="5">
-        <f>Z2/D2</f>
+      <c r="AF2" s="5">
+        <f>AE2/D2</f>
         <v>0.2465182772428044</v>
       </c>
     </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -1464,15 +1513,15 @@
         <v>731158</v>
       </c>
       <c r="F3">
-        <f>D3-C3</f>
+        <f t="shared" si="0"/>
         <v>14558</v>
       </c>
       <c r="G3">
-        <f>F3/C3*100</f>
+        <f t="shared" si="1"/>
         <v>2.0176764981850894</v>
       </c>
       <c r="H3" s="2">
-        <f>(D3-E3)/E3</f>
+        <f t="shared" si="2"/>
         <v>6.7331548037496683E-3</v>
       </c>
       <c r="I3">
@@ -1482,18 +1531,18 @@
         <v>1</v>
       </c>
       <c r="K3">
-        <f>J3-I3</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L3">
         <v>3</v>
       </c>
       <c r="M3">
-        <f>J3+2</f>
+        <f t="shared" si="4"/>
         <v>3</v>
       </c>
       <c r="N3">
-        <f>M3-L3</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="O3" t="s">
@@ -1512,7 +1561,7 @@
         <v>570640.94999999995</v>
       </c>
       <c r="T3">
-        <f>D3/S3</f>
+        <f t="shared" si="6"/>
         <v>1.289919694687176</v>
       </c>
       <c r="U3">
@@ -1524,21 +1573,36 @@
       <c r="W3">
         <v>31</v>
       </c>
-      <c r="X3">
+      <c r="X3" s="6">
+        <v>9000</v>
+      </c>
+      <c r="Y3" s="7">
+        <v>8.1422119017382423E-4</v>
+      </c>
+      <c r="Z3">
+        <v>22551</v>
+      </c>
+      <c r="AA3">
+        <v>1965</v>
+      </c>
+      <c r="AB3">
+        <v>3.1</v>
+      </c>
+      <c r="AC3">
         <v>0.44738149999999999</v>
       </c>
-      <c r="Y3">
+      <c r="AD3">
         <v>32</v>
       </c>
-      <c r="Z3" s="4">
+      <c r="AE3" s="4">
         <v>600000</v>
       </c>
-      <c r="AA3" s="5">
-        <f>Z3/D3</f>
+      <c r="AF3" s="5">
+        <f>AE3/D3</f>
         <v>0.81512768295880478</v>
       </c>
     </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -1555,15 +1619,15 @@
         <v>7421401</v>
       </c>
       <c r="F4">
-        <f>D4-C4</f>
+        <f t="shared" si="0"/>
         <v>746223</v>
       </c>
       <c r="G4">
-        <f>F4/C4*100</f>
+        <f t="shared" si="1"/>
         <v>11.636642911722053</v>
       </c>
       <c r="H4" s="2">
-        <f>(D4-E4)/E4</f>
+        <f t="shared" si="2"/>
         <v>-3.5367715610570026E-2</v>
       </c>
       <c r="I4">
@@ -1573,18 +1637,18 @@
         <v>9</v>
       </c>
       <c r="K4">
-        <f>J4-I4</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L4">
         <v>11</v>
       </c>
       <c r="M4">
-        <f>J4+2</f>
+        <f t="shared" si="4"/>
         <v>11</v>
       </c>
       <c r="N4">
-        <f>M4-L4</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="O4" t="s">
@@ -1603,7 +1667,7 @@
         <v>113594.08</v>
       </c>
       <c r="T4">
-        <f>D4/S4</f>
+        <f t="shared" si="6"/>
         <v>63.021972623925471</v>
       </c>
       <c r="U4">
@@ -1615,21 +1679,36 @@
       <c r="W4">
         <v>4</v>
       </c>
-      <c r="X4">
+      <c r="X4" s="6">
+        <v>281000</v>
+      </c>
+      <c r="Y4" s="7">
+        <v>2.5634192618307336E-2</v>
+      </c>
+      <c r="Z4">
+        <v>343729</v>
+      </c>
+      <c r="AA4">
+        <v>7680</v>
+      </c>
+      <c r="AB4">
+        <v>4.7</v>
+      </c>
+      <c r="AC4">
         <v>0.50156829999999997</v>
       </c>
-      <c r="Y4">
+      <c r="AD4">
         <v>25</v>
       </c>
-      <c r="Z4" s="4">
-        <v>0</v>
-      </c>
-      <c r="AA4" s="5">
-        <f>Z4/D4</f>
+      <c r="AE4" s="4">
+        <v>0</v>
+      </c>
+      <c r="AF4" s="5">
+        <f>AE4/D4</f>
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -1646,15 +1725,15 @@
         <v>3030522</v>
       </c>
       <c r="F5">
-        <f>D5-C5</f>
+        <f t="shared" si="0"/>
         <v>87527</v>
       </c>
       <c r="G5">
-        <f>F5/C5*100</f>
+        <f t="shared" si="1"/>
         <v>2.9911192869730976</v>
       </c>
       <c r="H5" s="2">
-        <f>(D5-E5)/E5</f>
+        <f t="shared" si="2"/>
         <v>-5.5323802302045654E-3</v>
       </c>
       <c r="I5">
@@ -1664,18 +1743,18 @@
         <v>4</v>
       </c>
       <c r="K5">
-        <f>J5-I5</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L5">
         <v>6</v>
       </c>
       <c r="M5">
-        <f>J5+2</f>
+        <f t="shared" si="4"/>
         <v>6</v>
       </c>
       <c r="N5">
-        <f>M5-L5</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="O5" t="s">
@@ -1694,7 +1773,7 @@
         <v>52035.48</v>
       </c>
       <c r="T5">
-        <f>D5/S5</f>
+        <f t="shared" si="6"/>
         <v>57.917328714946031</v>
       </c>
       <c r="U5">
@@ -1706,21 +1785,36 @@
       <c r="W5">
         <v>30</v>
       </c>
-      <c r="X5">
+      <c r="X5" s="6">
+        <v>58000</v>
+      </c>
+      <c r="Y5" s="7">
+        <v>5.3074451728820585E-3</v>
+      </c>
+      <c r="Z5">
+        <v>467468</v>
+      </c>
+      <c r="AA5">
+        <v>6259</v>
+      </c>
+      <c r="AB5">
+        <v>15.5</v>
+      </c>
+      <c r="AC5">
         <v>0.35787570000000002</v>
       </c>
-      <c r="Y5">
+      <c r="AD5">
         <v>46</v>
       </c>
-      <c r="Z5" s="4">
-        <v>0</v>
-      </c>
-      <c r="AA5" s="5">
-        <f>Z5/D5</f>
+      <c r="AE5" s="4">
+        <v>0</v>
+      </c>
+      <c r="AF5" s="5">
+        <f>AE5/D5</f>
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -1737,15 +1831,15 @@
         <v>39368078</v>
       </c>
       <c r="F6">
-        <f>D6-C6</f>
+        <f t="shared" si="0"/>
         <v>2234768</v>
       </c>
       <c r="G6">
-        <f>F6/C6*100</f>
+        <f t="shared" si="1"/>
         <v>5.9845981958807819</v>
       </c>
       <c r="H6" s="2">
-        <f>(D6-E6)/E6</f>
+        <f t="shared" si="2"/>
         <v>5.3007159760250422E-3</v>
       </c>
       <c r="I6">
@@ -1755,18 +1849,18 @@
         <v>52</v>
       </c>
       <c r="K6">
-        <f>J6-I6</f>
+        <f t="shared" si="3"/>
         <v>-1</v>
       </c>
       <c r="L6">
         <v>55</v>
       </c>
       <c r="M6">
-        <f>J6+2</f>
+        <f t="shared" si="4"/>
         <v>54</v>
       </c>
       <c r="N6">
-        <f>M6-L6</f>
+        <f t="shared" si="5"/>
         <v>-1</v>
       </c>
       <c r="O6" t="s">
@@ -1785,7 +1879,7 @@
         <v>155779.22</v>
       </c>
       <c r="T6">
-        <f>D6/S6</f>
+        <f t="shared" si="6"/>
         <v>254.05671565180515</v>
       </c>
       <c r="U6">
@@ -1797,21 +1891,36 @@
       <c r="W6">
         <v>3</v>
       </c>
-      <c r="X6">
+      <c r="X6" s="6">
+        <v>2625000</v>
+      </c>
+      <c r="Y6" s="7">
+        <v>0.23912001877298844</v>
+      </c>
+      <c r="Z6">
+        <v>2282144</v>
+      </c>
+      <c r="AA6">
+        <v>17125</v>
+      </c>
+      <c r="AB6">
+        <v>5.8</v>
+      </c>
+      <c r="AC6">
         <v>0.64908909999999997</v>
       </c>
-      <c r="Y6">
+      <c r="AD6">
         <v>6</v>
       </c>
-      <c r="Z6" s="4">
+      <c r="AE6" s="4">
         <v>187000000</v>
       </c>
-      <c r="AA6" s="5">
-        <f>Z6/D6</f>
+      <c r="AF6" s="5">
+        <f>AE6/D6</f>
         <v>4.7249955320998129</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>15</v>
       </c>
@@ -1828,15 +1937,15 @@
         <v>5807719</v>
       </c>
       <c r="F7">
-        <f>D7-C7</f>
+        <f t="shared" si="0"/>
         <v>737241</v>
       </c>
       <c r="G7">
-        <f>F7/C7*100</f>
+        <f t="shared" si="1"/>
         <v>14.613503061489455</v>
       </c>
       <c r="H7" s="2">
-        <f>(D7-E7)/E7</f>
+        <f t="shared" si="2"/>
         <v>-4.3989731596862725E-3</v>
       </c>
       <c r="I7">
@@ -1846,18 +1955,18 @@
         <v>8</v>
       </c>
       <c r="K7">
-        <f>J7-I7</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="L7">
         <v>9</v>
       </c>
       <c r="M7">
-        <f>J7+2</f>
+        <f t="shared" si="4"/>
         <v>10</v>
       </c>
       <c r="N7">
-        <f>M7-L7</f>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="O7" t="s">
@@ -1876,7 +1985,7 @@
         <v>103641.89</v>
       </c>
       <c r="T7">
-        <f>D7/S7</f>
+        <f t="shared" si="6"/>
         <v>55.789903098061991</v>
       </c>
       <c r="U7">
@@ -1888,21 +1997,36 @@
       <c r="W7">
         <v>7</v>
       </c>
-      <c r="X7">
+      <c r="X7" s="6">
+        <v>178000</v>
+      </c>
+      <c r="Y7" s="7">
+        <v>1.6207999032549474E-2</v>
+      </c>
+      <c r="Z7">
+        <v>240538</v>
+      </c>
+      <c r="AA7">
+        <v>6815</v>
+      </c>
+      <c r="AB7">
+        <v>4.2</v>
+      </c>
+      <c r="AC7">
         <v>0.56938319999999998</v>
       </c>
-      <c r="Y7">
+      <c r="AD7">
         <v>15</v>
       </c>
-      <c r="Z7" s="4">
+      <c r="AE7" s="4">
         <v>6000000</v>
       </c>
-      <c r="AA7" s="5">
-        <f>Z7/D7</f>
+      <c r="AF7" s="5">
+        <f>AE7/D7</f>
         <v>1.0376725281905361</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -1919,15 +2043,15 @@
         <v>3557006</v>
       </c>
       <c r="F8">
-        <f>D8-C8</f>
+        <f t="shared" si="0"/>
         <v>26670</v>
       </c>
       <c r="G8">
-        <f>F8/C8*100</f>
+        <f t="shared" si="1"/>
         <v>0.74463344601951964</v>
       </c>
       <c r="H8" s="2">
-        <f>(D8-E8)/E8</f>
+        <f t="shared" si="2"/>
         <v>1.4419992544291464E-2</v>
       </c>
       <c r="I8">
@@ -1937,18 +2061,18 @@
         <v>5</v>
       </c>
       <c r="K8">
-        <f>J8-I8</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L8">
         <v>7</v>
       </c>
       <c r="M8">
-        <f>J8+2</f>
+        <f t="shared" si="4"/>
         <v>7</v>
       </c>
       <c r="N8">
-        <f>M8-L8</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="O8" t="s">
@@ -1967,7 +2091,7 @@
         <v>4842.3599999999997</v>
       </c>
       <c r="T8">
-        <f>D8/S8</f>
+        <f t="shared" si="6"/>
         <v>745.15277674522349</v>
       </c>
       <c r="U8">
@@ -1979,21 +2103,36 @@
       <c r="W8">
         <v>11</v>
       </c>
-      <c r="X8">
+      <c r="X8" s="6">
+        <v>116000</v>
+      </c>
+      <c r="Y8" s="7">
+        <v>1.0581337524693493E-2</v>
+      </c>
+      <c r="Z8">
+        <v>396745</v>
+      </c>
+      <c r="AA8">
+        <v>7946</v>
+      </c>
+      <c r="AB8">
+        <v>11.1</v>
+      </c>
+      <c r="AC8">
         <v>0.60195050000000005</v>
       </c>
-      <c r="Y8">
+      <c r="AD8">
         <v>9</v>
       </c>
-      <c r="Z8" s="4">
+      <c r="AE8" s="4">
         <v>500000</v>
       </c>
-      <c r="AA8" s="5">
-        <f>Z8/D8</f>
+      <c r="AF8" s="5">
+        <f>AE8/D8</f>
         <v>0.13856948622314455</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>17</v>
       </c>
@@ -2010,15 +2149,15 @@
         <v>986809</v>
       </c>
       <c r="F9">
-        <f>D9-C9</f>
+        <f t="shared" si="0"/>
         <v>89960</v>
       </c>
       <c r="G9">
-        <f>F9/C9*100</f>
+        <f t="shared" si="1"/>
         <v>9.9858249239352332</v>
       </c>
       <c r="H9" s="2">
-        <f>(D9-E9)/E9</f>
+        <f t="shared" si="2"/>
         <v>4.0818435989132653E-3</v>
       </c>
       <c r="I9">
@@ -2028,18 +2167,18 @@
         <v>1</v>
       </c>
       <c r="K9">
-        <f>J9-I9</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L9">
         <v>3</v>
       </c>
       <c r="M9">
-        <f>J9+2</f>
+        <f t="shared" si="4"/>
         <v>3</v>
       </c>
       <c r="N9">
-        <f>M9-L9</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="O9" t="s">
@@ -2058,7 +2197,7 @@
         <v>1948.54</v>
       </c>
       <c r="T9">
-        <f>D9/S9</f>
+        <f t="shared" si="6"/>
         <v>508.50226323298472</v>
       </c>
       <c r="U9">
@@ -2070,21 +2209,36 @@
       <c r="W9">
         <v>28</v>
       </c>
-      <c r="X9">
+      <c r="X9" s="6">
+        <v>24000</v>
+      </c>
+      <c r="Y9" s="7">
+        <v>2.1447469365479806E-3</v>
+      </c>
+      <c r="Z9">
+        <v>219418</v>
+      </c>
+      <c r="AA9">
+        <v>3974</v>
+      </c>
+      <c r="AB9">
+        <v>22.5</v>
+      </c>
+      <c r="AC9">
         <v>0.5962674</v>
       </c>
-      <c r="Y9">
+      <c r="AD9">
         <v>11</v>
       </c>
-      <c r="Z9" s="4">
-        <v>0</v>
-      </c>
-      <c r="AA9" s="5">
-        <f>Z9/D9</f>
+      <c r="AE9" s="4">
+        <v>0</v>
+      </c>
+      <c r="AF9" s="5">
+        <f>AE9/D9</f>
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -2102,15 +2256,15 @@
         <v>712816</v>
       </c>
       <c r="F10">
-        <f>D10-C10</f>
+        <f t="shared" si="0"/>
         <v>89810</v>
       </c>
       <c r="G10">
-        <f>F10/C10*100</f>
+        <f t="shared" si="1"/>
         <v>14.925472351896138</v>
       </c>
       <c r="H10" s="2">
-        <f>(D10-E10)/E10</f>
+        <f t="shared" si="2"/>
         <v>-2.9857635069919865E-2</v>
       </c>
       <c r="I10">
@@ -2120,7 +2274,7 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <f>J10-I10</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L10">
@@ -2148,7 +2302,7 @@
         <v>61.05</v>
       </c>
       <c r="T10">
-        <f>D10/S10</f>
+        <f t="shared" si="6"/>
         <v>11327.321867321867</v>
       </c>
       <c r="U10">
@@ -2160,21 +2314,36 @@
       <c r="W10">
         <v>19</v>
       </c>
-      <c r="X10">
+      <c r="X10" s="6">
+        <v>25000</v>
+      </c>
+      <c r="Y10" s="7">
+        <v>2.3050032809033808E-3</v>
+      </c>
+      <c r="Z10">
+        <v>320704</v>
+      </c>
+      <c r="AA10">
+        <v>4929</v>
+      </c>
+      <c r="AB10">
+        <v>45.4</v>
+      </c>
+      <c r="AC10">
         <v>0.94466950000000005</v>
       </c>
-      <c r="Y10">
+      <c r="AD10">
         <v>1</v>
       </c>
-      <c r="Z10" s="4">
-        <v>0</v>
-      </c>
-      <c r="AA10" s="5">
-        <f>Z10/D10</f>
+      <c r="AE10" s="4">
+        <v>0</v>
+      </c>
+      <c r="AF10" s="5">
+        <f>AE10/D10</f>
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -2191,15 +2360,15 @@
         <v>21733312</v>
       </c>
       <c r="F11">
-        <f>D11-C11</f>
+        <f t="shared" si="0"/>
         <v>2669754</v>
       </c>
       <c r="G11">
-        <f>F11/C11*100</f>
+        <f t="shared" si="1"/>
         <v>14.12510483036858</v>
       </c>
       <c r="H11" s="2">
-        <f>(D11-E11)/E11</f>
+        <f t="shared" si="2"/>
         <v>-7.4901147142230323E-3</v>
       </c>
       <c r="I11">
@@ -2209,18 +2378,18 @@
         <v>28</v>
       </c>
       <c r="K11">
-        <f>J11-I11</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="L11">
         <v>29</v>
       </c>
       <c r="M11">
-        <f>J11+2</f>
+        <f t="shared" ref="M11:M52" si="7">J11+2</f>
         <v>30</v>
       </c>
       <c r="N11">
-        <f>M11-L11</f>
+        <f t="shared" ref="N11:N52" si="8">M11-L11</f>
         <v>1</v>
       </c>
       <c r="O11" t="s">
@@ -2239,7 +2408,7 @@
         <v>53624.76</v>
       </c>
       <c r="T11">
-        <f>D11/S11</f>
+        <f t="shared" si="6"/>
         <v>402.24939002058005</v>
       </c>
       <c r="U11">
@@ -2251,21 +2420,36 @@
       <c r="W11">
         <v>6</v>
       </c>
-      <c r="X11">
+      <c r="X11" s="6">
+        <v>732000</v>
+      </c>
+      <c r="Y11" s="7">
+        <v>6.665678324468978E-2</v>
+      </c>
+      <c r="Z11">
+        <v>3441062</v>
+      </c>
+      <c r="AA11">
+        <v>26501</v>
+      </c>
+      <c r="AB11">
+        <v>16</v>
+      </c>
+      <c r="AC11">
         <v>0.4830525</v>
       </c>
-      <c r="Y11">
+      <c r="AD11">
         <v>28</v>
       </c>
-      <c r="Z11" s="4">
-        <v>0</v>
-      </c>
-      <c r="AA11" s="5">
-        <f>Z11/D11</f>
+      <c r="AE11" s="4">
+        <v>0</v>
+      </c>
+      <c r="AF11" s="5">
+        <f>AE11/D11</f>
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>20</v>
       </c>
@@ -2282,15 +2466,15 @@
         <v>10710017</v>
       </c>
       <c r="F12">
-        <f>D12-C12</f>
+        <f t="shared" si="0"/>
         <v>997708</v>
       </c>
       <c r="G12">
-        <f>F12/C12*100</f>
+        <f t="shared" si="1"/>
         <v>10.256501986211145</v>
       </c>
       <c r="H12" s="2">
-        <f>(D12-E12)/E12</f>
+        <f t="shared" si="2"/>
         <v>1.4245542280651841E-3</v>
       </c>
       <c r="I12">
@@ -2300,18 +2484,18 @@
         <v>14</v>
       </c>
       <c r="K12">
-        <f>J12-I12</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L12">
         <v>16</v>
       </c>
       <c r="M12">
-        <f>J12+2</f>
+        <f t="shared" si="7"/>
         <v>16</v>
       </c>
       <c r="N12">
-        <f>M12-L12</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="O12" t="s">
@@ -2330,7 +2514,7 @@
         <v>57513.49</v>
       </c>
       <c r="T12">
-        <f>D12/S12</f>
+        <f t="shared" si="6"/>
         <v>186.48275387217851</v>
       </c>
       <c r="U12">
@@ -2342,21 +2526,36 @@
       <c r="W12">
         <v>25</v>
       </c>
-      <c r="X12">
+      <c r="X12" s="6">
+        <v>330000</v>
+      </c>
+      <c r="Y12" s="7">
+        <v>3.0036898545099215E-2</v>
+      </c>
+      <c r="Z12">
+        <v>3390968</v>
+      </c>
+      <c r="AA12">
+        <v>15987</v>
+      </c>
+      <c r="AB12">
+        <v>31.9</v>
+      </c>
+      <c r="AC12">
         <v>0.50119329999999995</v>
       </c>
-      <c r="Y12">
+      <c r="AD12">
         <v>26</v>
       </c>
-      <c r="Z12" s="4">
+      <c r="AE12" s="4">
         <v>3750886</v>
       </c>
-      <c r="AA12" s="5">
-        <f>Z12/D12</f>
+      <c r="AF12" s="5">
+        <f>AE12/D12</f>
         <v>0.34972402569855093</v>
       </c>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>21</v>
       </c>
@@ -2373,15 +2572,15 @@
         <v>1407006</v>
       </c>
       <c r="F13">
-        <f>D13-C13</f>
+        <f t="shared" si="0"/>
         <v>93275</v>
       </c>
       <c r="G13">
-        <f>F13/C13*100</f>
+        <f t="shared" si="1"/>
         <v>6.8240246637919553</v>
       </c>
       <c r="H13" s="2">
-        <f>(D13-E13)/E13</f>
+        <f t="shared" si="2"/>
         <v>3.7761743731014652E-2</v>
       </c>
       <c r="I13">
@@ -2391,18 +2590,18 @@
         <v>2</v>
       </c>
       <c r="K13">
-        <f>J13-I13</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L13">
         <v>4</v>
       </c>
       <c r="M13">
-        <f>J13+2</f>
+        <f t="shared" si="7"/>
         <v>4</v>
       </c>
       <c r="N13">
-        <f>M13-L13</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="O13" t="s">
@@ -2421,7 +2620,7 @@
         <v>6422.63</v>
       </c>
       <c r="T13">
-        <f>D13/S13</f>
+        <f t="shared" si="6"/>
         <v>227.34253724720247</v>
       </c>
       <c r="U13">
@@ -2433,21 +2632,36 @@
       <c r="W13">
         <v>22</v>
       </c>
-      <c r="X13">
+      <c r="X13" s="6">
+        <v>39000</v>
+      </c>
+      <c r="Y13" s="7">
+        <v>3.5846859659377519E-3</v>
+      </c>
+      <c r="Z13">
+        <v>26923</v>
+      </c>
+      <c r="AA13">
+        <v>2003</v>
+      </c>
+      <c r="AB13">
+        <v>1.9</v>
+      </c>
+      <c r="AC13">
         <v>0.65032659999999998</v>
       </c>
-      <c r="Y13">
+      <c r="AD13">
         <v>5</v>
       </c>
-      <c r="Z13" s="4">
+      <c r="AE13" s="4">
         <v>750000</v>
       </c>
-      <c r="AA13" s="5">
-        <f>Z13/D13</f>
+      <c r="AF13" s="5">
+        <f>AE13/D13</f>
         <v>0.51365043143211908</v>
       </c>
     </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>22</v>
       </c>
@@ -2464,15 +2678,15 @@
         <v>1826913</v>
       </c>
       <c r="F14">
-        <f>D14-C14</f>
+        <f t="shared" si="0"/>
         <v>267878</v>
       </c>
       <c r="G14">
-        <f>F14/C14*100</f>
+        <f t="shared" si="1"/>
         <v>17.024351461297403</v>
       </c>
       <c r="H14" s="2">
-        <f>(D14-E14)/E14</f>
+        <f t="shared" si="2"/>
         <v>7.9171805116061908E-3</v>
       </c>
       <c r="I14">
@@ -2482,18 +2696,18 @@
         <v>2</v>
       </c>
       <c r="K14">
-        <f>J14-I14</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L14">
         <v>4</v>
       </c>
       <c r="M14">
-        <f>J14+2</f>
+        <f t="shared" si="7"/>
         <v>4</v>
       </c>
       <c r="N14">
-        <f>M14-L14</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="O14" t="s">
@@ -2512,7 +2726,7 @@
         <v>82643.12</v>
       </c>
       <c r="T14">
-        <f>D14/S14</f>
+        <f t="shared" si="6"/>
         <v>22.281068284934065</v>
       </c>
       <c r="U14">
@@ -2524,21 +2738,36 @@
       <c r="W14">
         <v>16</v>
       </c>
-      <c r="X14">
+      <c r="X14" s="6">
+        <v>30000</v>
+      </c>
+      <c r="Y14" s="7">
+        <v>2.7473702600875104E-3</v>
+      </c>
+      <c r="Z14">
+        <v>12708</v>
+      </c>
+      <c r="AA14">
+        <v>2170</v>
+      </c>
+      <c r="AB14">
+        <v>0.7</v>
+      </c>
+      <c r="AC14">
         <v>0.34122859999999999</v>
       </c>
-      <c r="Y14">
+      <c r="AD14">
         <v>47</v>
       </c>
-      <c r="Z14" s="4">
-        <v>0</v>
-      </c>
-      <c r="AA14" s="5">
-        <f>Z14/D14</f>
+      <c r="AE14" s="4">
+        <v>0</v>
+      </c>
+      <c r="AF14" s="5">
+        <f>AE14/D14</f>
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>23</v>
       </c>
@@ -2555,15 +2784,15 @@
         <v>12587530</v>
       </c>
       <c r="F15">
-        <f>D15-C15</f>
+        <f t="shared" si="0"/>
         <v>-41641</v>
       </c>
       <c r="G15">
-        <f>F15/C15*100</f>
+        <f t="shared" si="1"/>
         <v>-0.32369224167818428</v>
       </c>
       <c r="H15" s="2">
-        <f>(D15-E15)/E15</f>
+        <f t="shared" si="2"/>
         <v>1.8685874035652746E-2</v>
       </c>
       <c r="I15">
@@ -2573,18 +2802,18 @@
         <v>17</v>
       </c>
       <c r="K15">
-        <f>J15-I15</f>
+        <f t="shared" si="3"/>
         <v>-1</v>
       </c>
       <c r="L15">
         <v>20</v>
       </c>
       <c r="M15">
-        <f>J15+2</f>
+        <f t="shared" si="7"/>
         <v>19</v>
       </c>
       <c r="N15">
-        <f>M15-L15</f>
+        <f t="shared" si="8"/>
         <v>-1</v>
       </c>
       <c r="O15" t="s">
@@ -2603,7 +2832,7 @@
         <v>55518.93</v>
       </c>
       <c r="T15">
-        <f>D15/S15</f>
+        <f t="shared" si="6"/>
         <v>230.96156572181778</v>
       </c>
       <c r="U15">
@@ -2615,21 +2844,36 @@
       <c r="W15">
         <v>10</v>
       </c>
-      <c r="X15">
+      <c r="X15" s="6">
+        <v>437000</v>
+      </c>
+      <c r="Y15" s="7">
+        <v>3.9819831027452048E-2</v>
+      </c>
+      <c r="Z15">
+        <v>1790212</v>
+      </c>
+      <c r="AA15">
+        <v>12139</v>
+      </c>
+      <c r="AB15">
+        <v>14.1</v>
+      </c>
+      <c r="AC15">
         <v>0.58659039999999996</v>
       </c>
-      <c r="Y15">
+      <c r="AD15">
         <v>12</v>
       </c>
-      <c r="Z15" s="4">
+      <c r="AE15" s="4">
         <v>30500000</v>
       </c>
-      <c r="AA15" s="5">
-        <f>Z15/D15</f>
+      <c r="AF15" s="5">
+        <f>AE15/D15</f>
         <v>2.3785869774000701</v>
       </c>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>24</v>
       </c>
@@ -2646,15 +2890,15 @@
         <v>6754953</v>
       </c>
       <c r="F16">
-        <f>D16-C16</f>
+        <f t="shared" si="0"/>
         <v>288698</v>
       </c>
       <c r="G16">
-        <f>F16/C16*100</f>
+        <f t="shared" si="1"/>
         <v>4.4404269606997193</v>
       </c>
       <c r="H16" s="2">
-        <f>(D16-E16)/E16</f>
+        <f t="shared" si="2"/>
         <v>5.2297921243863576E-3</v>
       </c>
       <c r="I16">
@@ -2664,18 +2908,18 @@
         <v>9</v>
       </c>
       <c r="K16">
-        <f>J16-I16</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L16">
         <v>11</v>
       </c>
       <c r="M16">
-        <f>J16+2</f>
+        <f t="shared" si="7"/>
         <v>11</v>
       </c>
       <c r="N16">
-        <f>M16-L16</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="O16" t="s">
@@ -2694,7 +2938,7 @@
         <v>35826.11</v>
       </c>
       <c r="T16">
-        <f>D16/S16</f>
+        <f t="shared" si="6"/>
         <v>189.53439265384938</v>
       </c>
       <c r="U16">
@@ -2706,21 +2950,36 @@
       <c r="W16">
         <v>32</v>
       </c>
-      <c r="X16">
+      <c r="X16" s="6">
+        <v>105000</v>
+      </c>
+      <c r="Y16" s="7">
+        <v>9.5839421108608464E-3</v>
+      </c>
+      <c r="Z16">
+        <v>643105</v>
+      </c>
+      <c r="AA16">
+        <v>8996</v>
+      </c>
+      <c r="AB16">
+        <v>9.6</v>
+      </c>
+      <c r="AC16">
         <v>0.41804950000000002</v>
       </c>
-      <c r="Y16">
+      <c r="AD16">
         <v>36</v>
       </c>
-      <c r="Z16" s="4">
-        <v>0</v>
-      </c>
-      <c r="AA16" s="5">
-        <f>Z16/D16</f>
+      <c r="AE16" s="4">
+        <v>0</v>
+      </c>
+      <c r="AF16" s="5">
+        <f>AE16/D16</f>
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>25</v>
       </c>
@@ -2737,15 +2996,15 @@
         <v>3163561</v>
       </c>
       <c r="F17">
-        <f>D17-C17</f>
+        <f t="shared" si="0"/>
         <v>138619</v>
       </c>
       <c r="G17">
-        <f>F17/C17*100</f>
+        <f t="shared" si="1"/>
         <v>4.5392491355814926</v>
       </c>
       <c r="H17" s="2">
-        <f>(D17-E17)/E17</f>
+        <f t="shared" si="2"/>
         <v>9.1178896186923531E-3</v>
       </c>
       <c r="I17">
@@ -2755,18 +3014,18 @@
         <v>4</v>
       </c>
       <c r="K17">
-        <f>J17-I17</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L17">
         <v>6</v>
       </c>
       <c r="M17">
-        <f>J17+2</f>
+        <f t="shared" si="7"/>
         <v>6</v>
       </c>
       <c r="N17">
-        <f>M17-L17</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="O17" t="s">
@@ -2785,7 +3044,7 @@
         <v>55857.13</v>
       </c>
       <c r="T17">
-        <f>D17/S17</f>
+        <f t="shared" si="6"/>
         <v>57.153061748786591</v>
       </c>
       <c r="U17">
@@ -2797,21 +3056,36 @@
       <c r="W17">
         <v>34</v>
       </c>
-      <c r="X17">
+      <c r="X17" s="6">
+        <v>40000</v>
+      </c>
+      <c r="Y17" s="7">
+        <v>3.6131851319176136E-3</v>
+      </c>
+      <c r="Z17">
+        <v>129335</v>
+      </c>
+      <c r="AA17">
+        <v>4761</v>
+      </c>
+      <c r="AB17">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="AC17">
         <v>0.4581674</v>
       </c>
-      <c r="Y17">
+      <c r="AD17">
         <v>31</v>
       </c>
-      <c r="Z17" s="4">
-        <v>0</v>
-      </c>
-      <c r="AA17" s="5">
-        <f>Z17/D17</f>
+      <c r="AE17" s="4">
+        <v>0</v>
+      </c>
+      <c r="AF17" s="5">
+        <f>AE17/D17</f>
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>26</v>
       </c>
@@ -2828,15 +3102,15 @@
         <v>2913805</v>
       </c>
       <c r="F18">
-        <f>D18-C18</f>
+        <f t="shared" si="0"/>
         <v>77052</v>
       </c>
       <c r="G18">
-        <f>F18/C18*100</f>
+        <f t="shared" si="1"/>
         <v>2.6905388026383008</v>
       </c>
       <c r="H18" s="2">
-        <f>(D18-E18)/E18</f>
+        <f t="shared" si="2"/>
         <v>9.2868259886986267E-3</v>
       </c>
       <c r="I18">
@@ -2846,18 +3120,18 @@
         <v>4</v>
       </c>
       <c r="K18">
-        <f>J18-I18</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L18">
         <v>6</v>
       </c>
       <c r="M18">
-        <f>J18+2</f>
+        <f t="shared" si="7"/>
         <v>6</v>
       </c>
       <c r="N18">
-        <f>M18-L18</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="O18" t="s">
@@ -2876,7 +3150,7 @@
         <v>81758.720000000001</v>
       </c>
       <c r="T18">
-        <f>D18/S18</f>
+        <f t="shared" si="6"/>
         <v>35.97004698703698</v>
       </c>
       <c r="U18">
@@ -2888,21 +3162,36 @@
       <c r="W18">
         <v>18</v>
       </c>
-      <c r="X18">
+      <c r="X18" s="6">
+        <v>70000</v>
+      </c>
+      <c r="Y18" s="7">
+        <v>6.4161028441482989E-3</v>
+      </c>
+      <c r="Z18">
+        <v>167237</v>
+      </c>
+      <c r="AA18">
+        <v>4802</v>
+      </c>
+      <c r="AB18">
+        <v>5.7</v>
+      </c>
+      <c r="AC18">
         <v>0.42506569999999999</v>
       </c>
-      <c r="Y18">
+      <c r="AD18">
         <v>34</v>
       </c>
-      <c r="Z18" s="4">
-        <v>0</v>
-      </c>
-      <c r="AA18" s="5">
-        <f>Z18/D18</f>
+      <c r="AE18" s="4">
+        <v>0</v>
+      </c>
+      <c r="AF18" s="5">
+        <f>AE18/D18</f>
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>27</v>
       </c>
@@ -2919,15 +3208,15 @@
         <v>4477251</v>
       </c>
       <c r="F19">
-        <f>D19-C19</f>
+        <f t="shared" si="0"/>
         <v>158736</v>
       </c>
       <c r="G19">
-        <f>F19/C19*100</f>
+        <f t="shared" si="1"/>
         <v>3.6485951612258156</v>
       </c>
       <c r="H19" s="2">
-        <f>(D19-E19)/E19</f>
+        <f t="shared" si="2"/>
         <v>7.1675677776385557E-3</v>
       </c>
       <c r="I19">
@@ -2937,18 +3226,18 @@
         <v>6</v>
       </c>
       <c r="K19">
-        <f>J19-I19</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L19">
         <v>8</v>
       </c>
       <c r="M19">
-        <f>J19+2</f>
+        <f t="shared" si="7"/>
         <v>8</v>
       </c>
       <c r="N19">
-        <f>M19-L19</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="O19" t="s">
@@ -2967,7 +3256,7 @@
         <v>39486.339999999997</v>
       </c>
       <c r="T19">
-        <f>D19/S19</f>
+        <f t="shared" si="6"/>
         <v>114.2000499413215</v>
       </c>
       <c r="U19">
@@ -2979,21 +3268,36 @@
       <c r="W19">
         <v>45</v>
       </c>
-      <c r="X19">
+      <c r="X19" s="6">
+        <v>48000</v>
+      </c>
+      <c r="Y19" s="7">
+        <v>4.4082292365805039E-3</v>
+      </c>
+      <c r="Z19">
+        <v>363167</v>
+      </c>
+      <c r="AA19">
+        <v>7961</v>
+      </c>
+      <c r="AB19">
+        <v>8.1</v>
+      </c>
+      <c r="AC19">
         <v>0.36799900000000002</v>
       </c>
-      <c r="Y19">
+      <c r="AD19">
         <v>44</v>
       </c>
-      <c r="Z19" s="4">
-        <v>0</v>
-      </c>
-      <c r="AA19" s="5">
-        <f>Z19/D19</f>
+      <c r="AE19" s="4">
+        <v>0</v>
+      </c>
+      <c r="AF19" s="5">
+        <f>AE19/D19</f>
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>28</v>
       </c>
@@ -3010,15 +3314,15 @@
         <v>4645318</v>
       </c>
       <c r="F20">
-        <f>D20-C20</f>
+        <f t="shared" si="0"/>
         <v>107506</v>
       </c>
       <c r="G20">
-        <f>F20/C20*100</f>
+        <f t="shared" si="1"/>
         <v>2.3607135940089092</v>
       </c>
       <c r="H20" s="2">
-        <f>(D20-E20)/E20</f>
+        <f t="shared" si="2"/>
         <v>3.4766188235121902E-3</v>
       </c>
       <c r="I20">
@@ -3028,18 +3332,18 @@
         <v>6</v>
       </c>
       <c r="K20">
-        <f>J20-I20</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L20">
         <v>8</v>
       </c>
       <c r="M20">
-        <f>J20+2</f>
+        <f t="shared" si="7"/>
         <v>8</v>
       </c>
       <c r="N20">
-        <f>M20-L20</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="O20" t="s">
@@ -3058,7 +3362,7 @@
         <v>43203.9</v>
       </c>
       <c r="T20">
-        <f>D20/S20</f>
+        <f t="shared" si="6"/>
         <v>107.89461136610352</v>
       </c>
       <c r="U20">
@@ -3070,21 +3374,36 @@
       <c r="W20">
         <v>38</v>
       </c>
-      <c r="X20">
+      <c r="X20" s="6">
+        <v>70000</v>
+      </c>
+      <c r="Y20" s="7">
+        <v>6.3682077308170361E-3</v>
+      </c>
+      <c r="Z20">
+        <v>1504017</v>
+      </c>
+      <c r="AA20">
+        <v>8676</v>
+      </c>
+      <c r="AB20">
+        <v>32.4</v>
+      </c>
+      <c r="AC20">
         <v>0.40535559999999998</v>
       </c>
-      <c r="Y20">
+      <c r="AD20">
         <v>39</v>
       </c>
-      <c r="Z20" s="4">
-        <v>0</v>
-      </c>
-      <c r="AA20" s="5">
-        <f>Z20/D20</f>
+      <c r="AE20" s="4">
+        <v>0</v>
+      </c>
+      <c r="AF20" s="5">
+        <f>AE20/D20</f>
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>29</v>
       </c>
@@ -3101,15 +3420,15 @@
         <v>1350141</v>
       </c>
       <c r="F21">
-        <f>D21-C21</f>
+        <f t="shared" si="0"/>
         <v>30508</v>
       </c>
       <c r="G21">
-        <f>F21/C21*100</f>
+        <f t="shared" si="1"/>
         <v>2.2885451220262341</v>
       </c>
       <c r="H21" s="2">
-        <f>(D21-E21)/E21</f>
+        <f t="shared" si="2"/>
         <v>9.9552565250592348E-3</v>
       </c>
       <c r="I21">
@@ -3119,18 +3438,18 @@
         <v>2</v>
       </c>
       <c r="K21">
-        <f>J21-I21</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L21">
         <v>4</v>
       </c>
       <c r="M21">
-        <f>J21+2</f>
+        <f t="shared" si="7"/>
         <v>4</v>
       </c>
       <c r="N21">
-        <f>M21-L21</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="O21" t="s">
@@ -3149,7 +3468,7 @@
         <v>30842.92</v>
       </c>
       <c r="T21">
-        <f>D21/S21</f>
+        <f t="shared" si="6"/>
         <v>44.210535189275205</v>
       </c>
       <c r="U21">
@@ -3161,21 +3480,36 @@
       <c r="W21">
         <v>50</v>
       </c>
-      <c r="X21">
+      <c r="X21" s="6">
+        <v>6000</v>
+      </c>
+      <c r="Y21" s="7">
+        <v>5.2123922384111258E-4</v>
+      </c>
+      <c r="Z21">
+        <v>21983</v>
+      </c>
+      <c r="AA21">
+        <v>2723</v>
+      </c>
+      <c r="AB21">
+        <v>1.6</v>
+      </c>
+      <c r="AC21">
         <v>0.54670399999999997</v>
       </c>
-      <c r="Y21">
+      <c r="AD21">
         <v>18</v>
       </c>
-      <c r="Z21" s="4">
-        <v>0</v>
-      </c>
-      <c r="AA21" s="5">
-        <f>Z21/D21</f>
+      <c r="AE21" s="4">
+        <v>0</v>
+      </c>
+      <c r="AF21" s="5">
+        <f>AE21/D21</f>
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>30</v>
       </c>
@@ -3192,15 +3526,15 @@
         <v>6055802</v>
       </c>
       <c r="F22">
-        <f>D22-C22</f>
+        <f t="shared" si="0"/>
         <v>395349</v>
       </c>
       <c r="G22">
-        <f>F22/C22*100</f>
+        <f t="shared" si="1"/>
         <v>6.8282184462020172</v>
       </c>
       <c r="H22" s="2">
-        <f>(D22-E22)/E22</f>
+        <f t="shared" si="2"/>
         <v>2.1380487671162299E-2</v>
       </c>
       <c r="I22">
@@ -3210,18 +3544,18 @@
         <v>8</v>
       </c>
       <c r="K22">
-        <f>J22-I22</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L22">
         <v>10</v>
       </c>
       <c r="M22">
-        <f>J22+2</f>
+        <f t="shared" si="7"/>
         <v>10</v>
       </c>
       <c r="N22">
-        <f>M22-L22</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="O22" t="s">
@@ -3240,7 +3574,7 @@
         <v>9707.24</v>
       </c>
       <c r="T22">
-        <f>D22/S22</f>
+        <f t="shared" si="6"/>
         <v>637.18193842946096</v>
       </c>
       <c r="U22">
@@ -3252,21 +3586,36 @@
       <c r="W22">
         <v>23</v>
       </c>
-      <c r="X22">
+      <c r="X22" s="6">
+        <v>226000</v>
+      </c>
+      <c r="Y22" s="7">
+        <v>2.0626662460001551E-2</v>
+      </c>
+      <c r="Z22">
+        <v>1830059</v>
+      </c>
+      <c r="AA22">
+        <v>9860</v>
+      </c>
+      <c r="AB22">
+        <v>30.3</v>
+      </c>
+      <c r="AC22">
         <v>0.67029050000000001</v>
       </c>
-      <c r="Y22">
+      <c r="AD22">
         <v>4</v>
       </c>
-      <c r="Z22" s="4">
+      <c r="AE22" s="4">
         <v>5000000</v>
       </c>
-      <c r="AA22" s="5">
-        <f>Z22/D22</f>
+      <c r="AF22" s="5">
+        <f>AE22/D22</f>
         <v>0.80837110312584171</v>
       </c>
     </row>
-    <row r="23" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>31</v>
       </c>
@@ -3283,15 +3632,15 @@
         <v>6893574</v>
       </c>
       <c r="F23">
-        <f>D23-C23</f>
+        <f t="shared" si="0"/>
         <v>473825</v>
       </c>
       <c r="G23">
-        <f>F23/C23*100</f>
+        <f t="shared" si="1"/>
         <v>7.223334071178253</v>
       </c>
       <c r="H23" s="2">
-        <f>(D23-E23)/E23</f>
+        <f t="shared" si="2"/>
         <v>2.0293537140531167E-2</v>
       </c>
       <c r="I23">
@@ -3301,18 +3650,18 @@
         <v>9</v>
       </c>
       <c r="K23">
-        <f>J23-I23</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L23">
         <v>11</v>
       </c>
       <c r="M23">
-        <f>J23+2</f>
+        <f t="shared" si="7"/>
         <v>11</v>
       </c>
       <c r="N23">
-        <f>M23-L23</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="O23" t="s">
@@ -3331,7 +3680,7 @@
         <v>7800.06</v>
       </c>
       <c r="T23">
-        <f>D23/S23</f>
+        <f t="shared" si="6"/>
         <v>901.71985856519052</v>
       </c>
       <c r="U23">
@@ -3343,21 +3692,36 @@
       <c r="W23">
         <v>17</v>
       </c>
-      <c r="X23">
+      <c r="X23" s="6">
+        <v>215000</v>
+      </c>
+      <c r="Y23" s="7">
+        <v>1.9543947332479099E-2</v>
+      </c>
+      <c r="Z23">
+        <v>543629</v>
+      </c>
+      <c r="AA23">
+        <v>9985</v>
+      </c>
+      <c r="AB23">
+        <v>7.9</v>
+      </c>
+      <c r="AC23">
         <v>0.67115550000000002</v>
       </c>
-      <c r="Y23">
+      <c r="AD23">
         <v>3</v>
       </c>
-      <c r="Z23" s="4">
+      <c r="AE23" s="4">
         <v>6650000</v>
       </c>
-      <c r="AA23" s="5">
-        <f>Z23/D23</f>
+      <c r="AF23" s="5">
+        <f>AE23/D23</f>
         <v>0.94547939288564431</v>
       </c>
     </row>
-    <row r="24" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>32</v>
       </c>
@@ -3374,15 +3738,15 @@
         <v>9966555</v>
       </c>
       <c r="F24">
-        <f>D24-C24</f>
+        <f t="shared" si="0"/>
         <v>172816</v>
       </c>
       <c r="G24">
-        <f>F24/C24*100</f>
+        <f t="shared" si="1"/>
         <v>1.743568613262849</v>
       </c>
       <c r="H24" s="2">
-        <f>(D24-E24)/E24</f>
+        <f t="shared" si="2"/>
         <v>1.1828259614279959E-2</v>
       </c>
       <c r="I24">
@@ -3392,18 +3756,18 @@
         <v>13</v>
       </c>
       <c r="K24">
-        <f>J24-I24</f>
+        <f t="shared" si="3"/>
         <v>-1</v>
       </c>
       <c r="L24">
         <v>16</v>
       </c>
       <c r="M24">
-        <f>J24+2</f>
+        <f t="shared" si="7"/>
         <v>15</v>
       </c>
       <c r="N24">
-        <f>M24-L24</f>
+        <f t="shared" si="8"/>
         <v>-1</v>
       </c>
       <c r="O24" t="s">
@@ -3422,7 +3786,7 @@
         <v>56538.9</v>
       </c>
       <c r="T24">
-        <f>D24/S24</f>
+        <f t="shared" si="6"/>
         <v>178.36289704964193</v>
       </c>
       <c r="U24">
@@ -3434,21 +3798,36 @@
       <c r="W24">
         <v>39</v>
       </c>
-      <c r="X24">
+      <c r="X24" s="6">
+        <v>102000</v>
+      </c>
+      <c r="Y24" s="7">
+        <v>9.3105623088550939E-3</v>
+      </c>
+      <c r="Z24">
+        <v>1371069</v>
+      </c>
+      <c r="AA24">
+        <v>10424</v>
+      </c>
+      <c r="AB24">
+        <v>13.7</v>
+      </c>
+      <c r="AC24">
         <v>0.51413560000000003</v>
       </c>
-      <c r="Y24">
+      <c r="AD24">
         <v>21</v>
       </c>
-      <c r="Z24" s="4">
+      <c r="AE24" s="4">
         <v>16000000</v>
       </c>
-      <c r="AA24" s="5">
-        <f>Z24/D24</f>
+      <c r="AF24" s="5">
+        <f>AE24/D24</f>
         <v>1.5866024119133215</v>
       </c>
     </row>
-    <row r="25" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>33</v>
       </c>
@@ -3465,15 +3844,15 @@
         <v>5657342</v>
       </c>
       <c r="F25">
-        <f>D25-C25</f>
+        <f t="shared" si="0"/>
         <v>394873</v>
       </c>
       <c r="G25">
-        <f>F25/C25*100</f>
+        <f t="shared" si="1"/>
         <v>7.4295764776582871</v>
       </c>
       <c r="H25" s="2">
-        <f>(D25-E25)/E25</f>
+        <f t="shared" si="2"/>
         <v>9.2640678254911936E-3</v>
       </c>
       <c r="I25">
@@ -3483,18 +3862,18 @@
         <v>8</v>
       </c>
       <c r="K25">
-        <f>J25-I25</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L25">
         <v>10</v>
       </c>
       <c r="M25">
-        <f>J25+2</f>
+        <f t="shared" si="7"/>
         <v>10</v>
       </c>
       <c r="N25">
-        <f>M25-L25</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="O25" t="s">
@@ -3513,7 +3892,7 @@
         <v>79626.740000000005</v>
       </c>
       <c r="T25">
-        <f>D25/S25</f>
+        <f t="shared" si="6"/>
         <v>71.706464436444335</v>
       </c>
       <c r="U25">
@@ -3525,21 +3904,36 @@
       <c r="W25">
         <v>37</v>
       </c>
-      <c r="X25">
+      <c r="X25" s="6">
+        <v>92000</v>
+      </c>
+      <c r="Y25" s="7">
+        <v>8.3464036035804864E-3</v>
+      </c>
+      <c r="Z25">
+        <v>370291</v>
+      </c>
+      <c r="AA25">
+        <v>8173</v>
+      </c>
+      <c r="AB25">
+        <v>6.6</v>
+      </c>
+      <c r="AC25">
         <v>0.53639510000000001</v>
       </c>
-      <c r="Y25">
+      <c r="AD25">
         <v>20</v>
       </c>
-      <c r="Z25" s="4">
+      <c r="AE25" s="4">
         <v>2170000</v>
       </c>
-      <c r="AA25" s="5">
-        <f>Z25/D25</f>
+      <c r="AF25" s="5">
+        <f>AE25/D25</f>
         <v>0.38005153288619192</v>
       </c>
     </row>
-    <row r="26" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>34</v>
       </c>
@@ -3556,15 +3950,15 @@
         <v>2966786</v>
       </c>
       <c r="F26">
-        <f>D26-C26</f>
+        <f t="shared" si="0"/>
         <v>-14326</v>
       </c>
       <c r="G26">
-        <f>F26/C26*100</f>
+        <f t="shared" si="1"/>
         <v>-0.48102234876974315</v>
       </c>
       <c r="H26" s="2">
-        <f>(D26-E26)/E26</f>
+        <f t="shared" si="2"/>
         <v>-9.6805094806298806E-4</v>
       </c>
       <c r="I26">
@@ -3574,18 +3968,18 @@
         <v>4</v>
       </c>
       <c r="K26">
-        <f>J26-I26</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L26">
         <v>6</v>
       </c>
       <c r="M26">
-        <f>J26+2</f>
+        <f t="shared" si="7"/>
         <v>6</v>
       </c>
       <c r="N26">
-        <f>M26-L26</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="O26" t="s">
@@ -3604,7 +3998,7 @@
         <v>46923.27</v>
       </c>
       <c r="T26">
-        <f>D26/S26</f>
+        <f t="shared" si="6"/>
         <v>63.165120418930741</v>
       </c>
       <c r="U26">
@@ -3616,21 +4010,36 @@
       <c r="W26">
         <v>48</v>
       </c>
-      <c r="X26">
+      <c r="X26" s="6">
+        <v>27000</v>
+      </c>
+      <c r="Y26" s="7">
+        <v>2.4263958971555422E-3</v>
+      </c>
+      <c r="Z26">
+        <v>1130608</v>
+      </c>
+      <c r="AA26">
+        <v>7506</v>
+      </c>
+      <c r="AB26">
+        <v>38</v>
+      </c>
+      <c r="AC26">
         <v>0.41615010000000002</v>
       </c>
-      <c r="Y26">
+      <c r="AD26">
         <v>37</v>
       </c>
-      <c r="Z26" s="4">
+      <c r="AE26" s="4">
         <v>400000</v>
       </c>
-      <c r="AA26" s="5">
-        <f>Z26/D26</f>
+      <c r="AF26" s="5">
+        <f>AE26/D26</f>
         <v>0.13495668227890553</v>
       </c>
     </row>
-    <row r="27" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>35</v>
       </c>
@@ -3647,15 +4056,15 @@
         <v>6151548</v>
       </c>
       <c r="F27">
-        <f>D27-C27</f>
+        <f t="shared" si="0"/>
         <v>148803</v>
       </c>
       <c r="G27">
-        <f>F27/C27*100</f>
+        <f t="shared" si="1"/>
         <v>2.4753147229350252</v>
       </c>
       <c r="H27" s="2">
-        <f>(D27-E27)/E27</f>
+        <f t="shared" si="2"/>
         <v>1.4196426655534509E-3</v>
       </c>
       <c r="I27">
@@ -3665,18 +4074,18 @@
         <v>8</v>
       </c>
       <c r="K27">
-        <f>J27-I27</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L27">
         <v>10</v>
       </c>
       <c r="M27">
-        <f>J27+2</f>
+        <f t="shared" si="7"/>
         <v>10</v>
       </c>
       <c r="N27">
-        <f>M27-L27</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="O27" t="s">
@@ -3695,7 +4104,7 @@
         <v>68741.52</v>
       </c>
       <c r="T27">
-        <f>D27/S27</f>
+        <f t="shared" si="6"/>
         <v>89.615140893014868</v>
       </c>
       <c r="U27">
@@ -3707,21 +4116,36 @@
       <c r="W27">
         <v>41</v>
       </c>
-      <c r="X27">
+      <c r="X27" s="6">
+        <v>54000</v>
+      </c>
+      <c r="Y27" s="7">
+        <v>4.9513267401302703E-3</v>
+      </c>
+      <c r="Z27">
+        <v>703058</v>
+      </c>
+      <c r="AA27">
+        <v>8638</v>
+      </c>
+      <c r="AB27">
+        <v>11.5</v>
+      </c>
+      <c r="AC27">
         <v>0.42164180000000001</v>
       </c>
-      <c r="Y27">
+      <c r="AD27">
         <v>35</v>
       </c>
-      <c r="Z27" s="4">
+      <c r="AE27" s="4">
         <v>501650</v>
       </c>
-      <c r="AA27" s="5">
-        <f>Z27/D27</f>
+      <c r="AF27" s="5">
+        <f>AE27/D27</f>
         <v>8.1432973593250052E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>36</v>
       </c>
@@ -3738,15 +4162,15 @@
         <v>1080577</v>
       </c>
       <c r="F28">
-        <f>D28-C28</f>
+        <f t="shared" si="0"/>
         <v>90991</v>
       </c>
       <c r="G28">
-        <f>F28/C28*100</f>
+        <f t="shared" si="1"/>
         <v>9.1501946871329505</v>
       </c>
       <c r="H28" s="2">
-        <f>(D28-E28)/E28</f>
+        <f t="shared" si="2"/>
         <v>4.4698341719285163E-3</v>
       </c>
       <c r="I28">
@@ -3756,18 +4180,18 @@
         <v>2</v>
       </c>
       <c r="K28">
-        <f>J28-I28</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="L28">
         <v>3</v>
       </c>
       <c r="M28">
-        <f>J28+2</f>
+        <f t="shared" si="7"/>
         <v>4</v>
       </c>
       <c r="N28">
-        <f>M28-L28</f>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="O28" t="s">
@@ -3786,7 +4210,7 @@
         <v>145545.79999999999</v>
       </c>
       <c r="T28">
-        <f>D28/S28</f>
+        <f t="shared" si="6"/>
         <v>7.4574944794009861</v>
       </c>
       <c r="U28">
@@ -3798,21 +4222,36 @@
       <c r="W28">
         <v>46</v>
       </c>
-      <c r="X28">
+      <c r="X28" s="6">
+        <v>4000</v>
+      </c>
+      <c r="Y28" s="7">
+        <v>3.4862345327097891E-4</v>
+      </c>
+      <c r="Z28">
+        <v>7787</v>
+      </c>
+      <c r="AA28">
+        <v>1893</v>
+      </c>
+      <c r="AB28">
+        <v>0.7</v>
+      </c>
+      <c r="AC28">
         <v>0.41602820000000001</v>
       </c>
-      <c r="Y28">
+      <c r="AD28">
         <v>38</v>
       </c>
-      <c r="Z28" s="4">
+      <c r="AE28" s="4">
         <v>635500</v>
       </c>
-      <c r="AA28" s="5">
-        <f>Z28/D28</f>
+      <c r="AF28" s="5">
+        <f>AE28/D28</f>
         <v>0.58549465776432252</v>
       </c>
     </row>
-    <row r="29" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>37</v>
       </c>
@@ -3829,15 +4268,15 @@
         <v>1937552</v>
       </c>
       <c r="F29">
-        <f>D29-C29</f>
+        <f t="shared" si="0"/>
         <v>131508</v>
       </c>
       <c r="G29">
-        <f>F29/C29*100</f>
+        <f t="shared" si="1"/>
         <v>7.1790700530891334</v>
       </c>
       <c r="H29" s="2">
-        <f>(D29-E29)/E29</f>
+        <f t="shared" si="2"/>
         <v>1.330596546570105E-2</v>
       </c>
       <c r="I29">
@@ -3847,18 +4286,18 @@
         <v>3</v>
       </c>
       <c r="K29">
-        <f>J29-I29</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L29">
         <v>5</v>
       </c>
       <c r="M29">
-        <f>J29+2</f>
+        <f t="shared" si="7"/>
         <v>5</v>
       </c>
       <c r="N29">
-        <f>M29-L29</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="O29" t="s">
@@ -3877,7 +4316,7 @@
         <v>76824.17</v>
       </c>
       <c r="T29">
-        <f>D29/S29</f>
+        <f t="shared" si="6"/>
         <v>25.556188892115593</v>
       </c>
       <c r="U29">
@@ -3889,18 +4328,34 @@
       <c r="W29">
         <v>20</v>
       </c>
-      <c r="X29">
+      <c r="X29" s="6">
+        <v>41000</v>
+      </c>
+      <c r="Y29" s="7">
+        <v>3.7471223651725965E-3</v>
+      </c>
+      <c r="Z29">
+        <v>94659</v>
+      </c>
+      <c r="AA29">
+        <v>3635</v>
+      </c>
+      <c r="AB29">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="AC29">
         <v>0.4021595</v>
       </c>
-      <c r="Y29">
+      <c r="AD29">
         <v>40</v>
       </c>
-      <c r="AA29" s="5">
-        <f>Z29/D29</f>
+      <c r="AE29" s="4"/>
+      <c r="AF29" s="5">
+        <f>AE29/D29</f>
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>38</v>
       </c>
@@ -3917,15 +4372,15 @@
         <v>3138259</v>
       </c>
       <c r="F30">
-        <f>D30-C30</f>
+        <f t="shared" si="0"/>
         <v>399030</v>
       </c>
       <c r="G30">
-        <f>F30/C30*100</f>
+        <f t="shared" si="1"/>
         <v>14.72744102823027</v>
       </c>
       <c r="H30" s="2">
-        <f>(D30-E30)/E30</f>
+        <f t="shared" si="2"/>
         <v>-9.4947548943538438E-3</v>
       </c>
       <c r="I30">
@@ -3935,18 +4390,18 @@
         <v>4</v>
       </c>
       <c r="K30">
-        <f>J30-I30</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L30">
         <v>6</v>
       </c>
       <c r="M30">
-        <f>J30+2</f>
+        <f t="shared" si="7"/>
         <v>6</v>
       </c>
       <c r="N30">
-        <f>M30-L30</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="O30" t="s">
@@ -3965,7 +4420,7 @@
         <v>109781.18</v>
       </c>
       <c r="T30">
-        <f>D30/S30</f>
+        <f t="shared" si="6"/>
         <v>28.315071854756891</v>
       </c>
       <c r="U30">
@@ -3977,21 +4432,36 @@
       <c r="W30">
         <v>5</v>
       </c>
-      <c r="X30">
+      <c r="X30" s="6">
+        <v>162000</v>
+      </c>
+      <c r="Y30" s="7">
+        <v>1.4781831764217334E-2</v>
+      </c>
+      <c r="Z30">
+        <v>296184</v>
+      </c>
+      <c r="AA30">
+        <v>5444</v>
+      </c>
+      <c r="AB30">
+        <v>9.6</v>
+      </c>
+      <c r="AC30">
         <v>0.5122312</v>
       </c>
-      <c r="Y30">
+      <c r="AD30">
         <v>22</v>
       </c>
-      <c r="Z30" s="4">
+      <c r="AE30" s="4">
         <v>5000000</v>
       </c>
-      <c r="AA30" s="5">
-        <f>Z30/D30</f>
+      <c r="AF30" s="5">
+        <f>AE30/D30</f>
         <v>1.6085125055413256</v>
       </c>
     </row>
-    <row r="31" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>39</v>
       </c>
@@ -4008,15 +4478,15 @@
         <v>1366275</v>
       </c>
       <c r="F31">
-        <f>D31-C31</f>
+        <f t="shared" si="0"/>
         <v>57644</v>
       </c>
       <c r="G31">
-        <f>F31/C31*100</f>
+        <f t="shared" si="1"/>
         <v>4.3621944159613149</v>
       </c>
       <c r="H31" s="2">
-        <f>(D31-E31)/E31</f>
+        <f t="shared" si="2"/>
         <v>9.3787853836160371E-3</v>
       </c>
       <c r="I31">
@@ -4026,18 +4496,18 @@
         <v>2</v>
       </c>
       <c r="K31">
-        <f>J31-I31</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L31">
         <v>4</v>
       </c>
       <c r="M31">
-        <f>J31+2</f>
+        <f t="shared" si="7"/>
         <v>4</v>
       </c>
       <c r="N31">
-        <f>M31-L31</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="O31" t="s">
@@ -4056,7 +4526,7 @@
         <v>8952.65</v>
       </c>
       <c r="T31">
-        <f>D31/S31</f>
+        <f t="shared" si="6"/>
         <v>154.0425460617806</v>
       </c>
       <c r="U31">
@@ -4068,18 +4538,34 @@
       <c r="W31">
         <v>42</v>
       </c>
-      <c r="X31">
+      <c r="X31" s="6">
+        <v>11000</v>
+      </c>
+      <c r="Y31" s="7">
+        <v>1.0264600366713149E-3</v>
+      </c>
+      <c r="Z31">
+        <v>22000</v>
+      </c>
+      <c r="AA31">
+        <v>1840</v>
+      </c>
+      <c r="AB31">
+        <v>1.6</v>
+      </c>
+      <c r="AC31">
         <v>0.53748879999999999</v>
       </c>
-      <c r="Y31">
+      <c r="AD31">
         <v>19</v>
       </c>
-      <c r="AA31" s="5">
-        <f>Z31/D31</f>
+      <c r="AE31" s="4"/>
+      <c r="AF31" s="5">
+        <f>AE31/D31</f>
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>40</v>
       </c>
@@ -4096,15 +4582,15 @@
         <v>8882371</v>
       </c>
       <c r="F32">
-        <f>D32-C32</f>
+        <f t="shared" si="0"/>
         <v>486992</v>
       </c>
       <c r="G32">
-        <f>F32/C32*100</f>
+        <f t="shared" si="1"/>
         <v>5.5292869112362295</v>
       </c>
       <c r="H32" s="2">
-        <f>(D32-E32)/E32</f>
+        <f t="shared" si="2"/>
         <v>4.6397746727759967E-2</v>
       </c>
       <c r="I32">
@@ -4114,18 +4600,18 @@
         <v>12</v>
       </c>
       <c r="K32">
-        <f>J32-I32</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L32">
         <v>14</v>
       </c>
       <c r="M32">
-        <f>J32+2</f>
+        <f t="shared" si="7"/>
         <v>14</v>
       </c>
       <c r="N32">
-        <f>M32-L32</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="O32" t="s">
@@ -4144,7 +4630,7 @@
         <v>7354.22</v>
       </c>
       <c r="T32">
-        <f>D32/S32</f>
+        <f t="shared" si="6"/>
         <v>1263.8312424703095</v>
       </c>
       <c r="U32">
@@ -4156,21 +4642,36 @@
       <c r="W32">
         <v>8</v>
       </c>
-      <c r="X32">
+      <c r="X32" s="6">
+        <v>425000</v>
+      </c>
+      <c r="Y32" s="7">
+        <v>3.8706204889950788E-2</v>
+      </c>
+      <c r="Z32">
+        <v>1203843</v>
+      </c>
+      <c r="AA32">
+        <v>10689</v>
+      </c>
+      <c r="AB32">
+        <v>13.6</v>
+      </c>
+      <c r="AC32">
         <v>0.58071280000000003</v>
       </c>
-      <c r="Y32">
+      <c r="AD32">
         <v>14</v>
       </c>
-      <c r="Z32" s="4">
+      <c r="AE32" s="4">
         <v>9000000</v>
       </c>
-      <c r="AA32" s="5">
-        <f>Z32/D32</f>
+      <c r="AF32" s="5">
+        <f>AE32/D32</f>
         <v>0.96831532392353192</v>
       </c>
     </row>
-    <row r="33" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>41</v>
       </c>
@@ -4187,15 +4688,15 @@
         <v>2106319</v>
       </c>
       <c r="F33">
-        <f>D33-C33</f>
+        <f t="shared" si="0"/>
         <v>52947</v>
       </c>
       <c r="G33">
-        <f>F33/C33*100</f>
+        <f t="shared" si="1"/>
         <v>2.5612001898152785</v>
       </c>
       <c r="H33" s="2">
-        <f>(D33-E33)/E33</f>
+        <f t="shared" si="2"/>
         <v>6.5996651029592386E-3</v>
       </c>
       <c r="I33">
@@ -4205,18 +4706,18 @@
         <v>3</v>
       </c>
       <c r="K33">
-        <f>J33-I33</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L33">
         <v>5</v>
       </c>
       <c r="M33">
-        <f>J33+2</f>
+        <f t="shared" si="7"/>
         <v>5</v>
       </c>
       <c r="N33">
-        <f>M33-L33</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="O33" t="s">
@@ -4235,7 +4736,7 @@
         <v>121298.15</v>
       </c>
       <c r="T33">
-        <f>D33/S33</f>
+        <f t="shared" si="6"/>
         <v>17.479409207807375</v>
       </c>
       <c r="U33">
@@ -4247,21 +4748,36 @@
       <c r="W33">
         <v>1</v>
       </c>
-      <c r="X33">
+      <c r="X33" s="6">
+        <v>71000</v>
+      </c>
+      <c r="Y33" s="7">
+        <v>6.4332024548798411E-3</v>
+      </c>
+      <c r="Z33">
+        <v>48337</v>
+      </c>
+      <c r="AA33">
+        <v>3861</v>
+      </c>
+      <c r="AB33">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="AC33">
         <v>0.55518489999999998</v>
       </c>
-      <c r="Y33">
+      <c r="AD33">
         <v>16</v>
       </c>
-      <c r="Z33" s="4">
+      <c r="AE33" s="4">
         <v>11500000</v>
       </c>
-      <c r="AA33" s="5">
-        <f>Z33/D33</f>
+      <c r="AF33" s="5">
+        <f>AE33/D33</f>
         <v>5.4239654375489339</v>
       </c>
     </row>
-    <row r="34" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>42</v>
       </c>
@@ -4278,15 +4794,15 @@
         <v>19336776</v>
       </c>
       <c r="F34">
-        <f>D34-C34</f>
+        <f t="shared" ref="F34:F52" si="9">D34-C34</f>
         <v>794696</v>
       </c>
       <c r="G34">
-        <f>F34/C34*100</f>
+        <f t="shared" ref="G34:G52" si="10">F34/C34*100</f>
         <v>4.0919301242903643</v>
       </c>
       <c r="H34" s="2">
-        <f>(D34-E34)/E34</f>
+        <f t="shared" ref="H34:H52" si="11">(D34-E34)/E34</f>
         <v>4.5456129811919009E-2</v>
       </c>
       <c r="I34">
@@ -4296,18 +4812,18 @@
         <v>26</v>
       </c>
       <c r="K34">
-        <f>J34-I34</f>
+        <f t="shared" ref="K34:K52" si="12">J34-I34</f>
         <v>-1</v>
       </c>
       <c r="L34">
         <v>29</v>
       </c>
       <c r="M34">
-        <f>J34+2</f>
+        <f t="shared" si="7"/>
         <v>28</v>
       </c>
       <c r="N34">
-        <f>M34-L34</f>
+        <f t="shared" si="8"/>
         <v>-1</v>
       </c>
       <c r="O34" t="s">
@@ -4326,7 +4842,7 @@
         <v>47126.400000000001</v>
       </c>
       <c r="T34">
-        <f>D34/S34</f>
+        <f t="shared" ref="T34:T52" si="13">D34/S34</f>
         <v>428.96870968289534</v>
       </c>
       <c r="U34">
@@ -4338,21 +4854,36 @@
       <c r="W34">
         <v>9</v>
       </c>
-      <c r="X34">
+      <c r="X34" s="6">
+        <v>866000</v>
+      </c>
+      <c r="Y34" s="7">
+        <v>7.8852265943519587E-2</v>
+      </c>
+      <c r="Z34">
+        <v>3084304</v>
+      </c>
+      <c r="AA34">
+        <v>17635</v>
+      </c>
+      <c r="AB34">
+        <v>15.9</v>
+      </c>
+      <c r="AC34">
         <v>0.6171683</v>
       </c>
-      <c r="Y34">
+      <c r="AD34">
         <v>7</v>
       </c>
-      <c r="Z34" s="4">
+      <c r="AE34" s="4">
         <v>20000000</v>
       </c>
-      <c r="AA34" s="5">
-        <f>Z34/D34</f>
+      <c r="AF34" s="5">
+        <f>AE34/D34</f>
         <v>0.98932757927222192</v>
       </c>
     </row>
-    <row r="35" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>43</v>
       </c>
@@ -4369,15 +4900,15 @@
         <v>10600823</v>
       </c>
       <c r="F35">
-        <f>D35-C35</f>
+        <f t="shared" si="9"/>
         <v>888167</v>
       </c>
       <c r="G35">
-        <f>F35/C35*100</f>
+        <f t="shared" si="10"/>
         <v>9.2848351849159005</v>
       </c>
       <c r="H35" s="2">
-        <f>(D35-E35)/E35</f>
+        <f t="shared" si="11"/>
         <v>-1.3855056347983548E-2</v>
       </c>
       <c r="I35">
@@ -4387,18 +4918,18 @@
         <v>14</v>
       </c>
       <c r="K35">
-        <f>J35-I35</f>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="L35">
         <v>15</v>
       </c>
       <c r="M35">
-        <f>J35+2</f>
+        <f t="shared" si="7"/>
         <v>16</v>
       </c>
       <c r="N35">
-        <f>M35-L35</f>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="O35" t="s">
@@ -4417,7 +4948,7 @@
         <v>48617.91</v>
       </c>
       <c r="T35">
-        <f>D35/S35</f>
+        <f t="shared" si="13"/>
         <v>215.02257090031225</v>
       </c>
       <c r="U35">
@@ -4429,21 +4960,36 @@
       <c r="W35">
         <v>26</v>
       </c>
-      <c r="X35">
+      <c r="X35" s="6">
+        <v>298000</v>
+      </c>
+      <c r="Y35" s="7">
+        <v>2.7137862459207431E-2</v>
+      </c>
+      <c r="Z35">
+        <v>2253481</v>
+      </c>
+      <c r="AA35">
+        <v>14903</v>
+      </c>
+      <c r="AB35">
+        <v>21.5</v>
+      </c>
+      <c r="AC35">
         <v>0.49315799999999999</v>
       </c>
-      <c r="Y35">
+      <c r="AD35">
         <v>27</v>
       </c>
-      <c r="Z35" s="4">
-        <v>0</v>
-      </c>
-      <c r="AA35" s="5">
-        <f>Z35/D35</f>
+      <c r="AE35" s="4">
+        <v>0</v>
+      </c>
+      <c r="AF35" s="5">
+        <f>AE35/D35</f>
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>44</v>
       </c>
@@ -4460,15 +5006,15 @@
         <v>765309</v>
       </c>
       <c r="F36">
-        <f>D36-C36</f>
+        <f t="shared" si="9"/>
         <v>103797</v>
       </c>
       <c r="G36">
-        <f>F36/C36*100</f>
+        <f t="shared" si="10"/>
         <v>15.356743921113175</v>
       </c>
       <c r="H36" s="2">
-        <f>(D36-E36)/E36</f>
+        <f t="shared" si="11"/>
         <v>1.8806782619830684E-2</v>
       </c>
       <c r="I36">
@@ -4478,18 +5024,18 @@
         <v>1</v>
       </c>
       <c r="K36">
-        <f>J36-I36</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="L36">
         <v>3</v>
       </c>
       <c r="M36">
-        <f>J36+2</f>
+        <f t="shared" si="7"/>
         <v>3</v>
       </c>
       <c r="N36">
-        <f>M36-L36</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="O36" t="s">
@@ -4508,7 +5054,7 @@
         <v>69000.800000000003</v>
       </c>
       <c r="T36">
-        <f>D36/S36</f>
+        <f t="shared" si="13"/>
         <v>11.299897972197423</v>
       </c>
       <c r="U36">
@@ -4520,21 +5066,36 @@
       <c r="W36">
         <v>43</v>
       </c>
-      <c r="X36">
+      <c r="X36" s="6">
+        <v>5000</v>
+      </c>
+      <c r="Y36" s="7">
+        <v>4.8200798385366272E-4</v>
+      </c>
+      <c r="Z36">
+        <v>22256</v>
+      </c>
+      <c r="AA36">
+        <v>2558</v>
+      </c>
+      <c r="AB36">
+        <v>2.9</v>
+      </c>
+      <c r="AC36">
         <v>0.3278259</v>
       </c>
-      <c r="Y36">
+      <c r="AD36">
         <v>49</v>
       </c>
-      <c r="Z36" s="4">
+      <c r="AE36" s="4">
         <v>1000000</v>
       </c>
-      <c r="AA36" s="5">
-        <f>Z36/D36</f>
+      <c r="AF36" s="5">
+        <f>AE36/D36</f>
         <v>1.2825412785910515</v>
       </c>
     </row>
-    <row r="37" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>45</v>
       </c>
@@ -4551,15 +5112,15 @@
         <v>11693217</v>
       </c>
       <c r="F37">
-        <f>D37-C37</f>
+        <f t="shared" si="9"/>
         <v>240353</v>
       </c>
       <c r="G37">
-        <f>F37/C37*100</f>
+        <f t="shared" si="10"/>
         <v>2.0776514144666183</v>
       </c>
       <c r="H37" s="2">
-        <f>(D37-E37)/E37</f>
+        <f t="shared" si="11"/>
         <v>9.8887243775600854E-3</v>
       </c>
       <c r="I37">
@@ -4569,18 +5130,18 @@
         <v>15</v>
       </c>
       <c r="K37">
-        <f>J37-I37</f>
+        <f t="shared" si="12"/>
         <v>-1</v>
       </c>
       <c r="L37">
         <v>18</v>
       </c>
       <c r="M37">
-        <f>J37+2</f>
+        <f t="shared" si="7"/>
         <v>17</v>
       </c>
       <c r="N37">
-        <f>M37-L37</f>
+        <f t="shared" si="8"/>
         <v>-1</v>
       </c>
       <c r="O37" t="s">
@@ -4599,7 +5160,7 @@
         <v>40860.69</v>
       </c>
       <c r="T37">
-        <f>D37/S37</f>
+        <f t="shared" si="13"/>
         <v>289.00265756647769</v>
       </c>
       <c r="U37">
@@ -4611,21 +5172,36 @@
       <c r="W37">
         <v>44</v>
       </c>
-      <c r="X37">
+      <c r="X37" s="6">
+        <v>87000</v>
+      </c>
+      <c r="Y37" s="7">
+        <v>7.9600360029181538E-3</v>
+      </c>
+      <c r="Z37">
+        <v>1467331</v>
+      </c>
+      <c r="AA37">
+        <v>13248</v>
+      </c>
+      <c r="AB37">
+        <v>12.6</v>
+      </c>
+      <c r="AC37">
         <v>0.459233</v>
       </c>
-      <c r="Y37">
+      <c r="AD37">
         <v>30</v>
       </c>
-      <c r="Z37" s="4">
-        <v>0</v>
-      </c>
-      <c r="AA37" s="5">
-        <f>Z37/D37</f>
+      <c r="AE37" s="4">
+        <v>0</v>
+      </c>
+      <c r="AF37" s="5">
+        <f>AE37/D37</f>
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>46</v>
       </c>
@@ -4642,15 +5218,15 @@
         <v>3980783</v>
       </c>
       <c r="F38">
-        <f>D38-C38</f>
+        <f t="shared" si="9"/>
         <v>198634</v>
       </c>
       <c r="G38">
-        <f>F38/C38*100</f>
+        <f t="shared" si="10"/>
         <v>5.2759688085841736</v>
       </c>
       <c r="H38" s="2">
-        <f>(D38-E38)/E38</f>
+        <f t="shared" si="11"/>
         <v>-4.3375888612868377E-3</v>
       </c>
       <c r="I38">
@@ -4660,18 +5236,18 @@
         <v>5</v>
       </c>
       <c r="K38">
-        <f>J38-I38</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="L38">
         <v>7</v>
       </c>
       <c r="M38">
-        <f>J38+2</f>
+        <f t="shared" si="7"/>
         <v>7</v>
       </c>
       <c r="N38">
-        <f>M38-L38</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="O38" t="s">
@@ -4690,7 +5266,7 @@
         <v>68594.92</v>
       </c>
       <c r="T38">
-        <f>D38/S38</f>
+        <f t="shared" si="13"/>
         <v>57.781480027967085</v>
       </c>
       <c r="U38">
@@ -4702,21 +5278,36 @@
       <c r="W38">
         <v>21</v>
       </c>
-      <c r="X38">
+      <c r="X38" s="6">
+        <v>92000</v>
+      </c>
+      <c r="Y38" s="7">
+        <v>8.3754220653741284E-3</v>
+      </c>
+      <c r="Z38">
+        <v>287414</v>
+      </c>
+      <c r="AA38">
+        <v>6538</v>
+      </c>
+      <c r="AB38">
+        <v>7.3</v>
+      </c>
+      <c r="AC38">
         <v>0.33059959999999999</v>
       </c>
-      <c r="Y38">
+      <c r="AD38">
         <v>48</v>
       </c>
-      <c r="Z38" s="4">
-        <v>0</v>
-      </c>
-      <c r="AA38" s="5">
-        <f>Z38/D38</f>
+      <c r="AE38" s="4">
+        <v>0</v>
+      </c>
+      <c r="AF38" s="5">
+        <f>AE38/D38</f>
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>47</v>
       </c>
@@ -4733,15 +5324,15 @@
         <v>4241507</v>
       </c>
       <c r="F39">
-        <f>D39-C39</f>
+        <f t="shared" si="9"/>
         <v>392894</v>
       </c>
       <c r="G39">
-        <f>F39/C39*100</f>
+        <f t="shared" si="10"/>
         <v>10.208735318710204</v>
       </c>
       <c r="H39" s="2">
-        <f>(D39-E39)/E39</f>
+        <f t="shared" si="11"/>
         <v>-1.6503568189325161E-6</v>
       </c>
       <c r="I39">
@@ -4751,18 +5342,18 @@
         <v>6</v>
       </c>
       <c r="K39">
-        <f>J39-I39</f>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="L39">
         <v>7</v>
       </c>
       <c r="M39">
-        <f>J39+2</f>
+        <f t="shared" si="7"/>
         <v>8</v>
       </c>
       <c r="N39">
-        <f>M39-L39</f>
+        <f t="shared" si="8"/>
         <v>1</v>
       </c>
       <c r="O39" t="s">
@@ -4781,7 +5372,7 @@
         <v>95988.01</v>
       </c>
       <c r="T39">
-        <f>D39/S39</f>
+        <f t="shared" si="13"/>
         <v>44.187810540087249</v>
       </c>
       <c r="U39">
@@ -4793,21 +5384,36 @@
       <c r="W39">
         <v>14</v>
       </c>
-      <c r="X39">
+      <c r="X39" s="6">
+        <v>110000</v>
+      </c>
+      <c r="Y39" s="7">
+        <v>1.0018798796430226E-2</v>
+      </c>
+      <c r="Z39">
+        <v>77918</v>
+      </c>
+      <c r="AA39">
+        <v>5485</v>
+      </c>
+      <c r="AB39">
+        <v>1.8</v>
+      </c>
+      <c r="AC39">
         <v>0.58307160000000002</v>
       </c>
-      <c r="Y39">
+      <c r="AD39">
         <v>13</v>
       </c>
-      <c r="Z39" s="4">
+      <c r="AE39" s="4">
         <v>7730772</v>
       </c>
-      <c r="AA39" s="5">
-        <f>Z39/D39</f>
+      <c r="AF39" s="5">
+        <f>AE39/D39</f>
         <v>1.8226504774254391</v>
       </c>
     </row>
-    <row r="40" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>48</v>
       </c>
@@ -4824,15 +5430,15 @@
         <v>12783254</v>
       </c>
       <c r="F40">
-        <f>D40-C40</f>
+        <f t="shared" si="9"/>
         <v>276939</v>
       </c>
       <c r="G40">
-        <f>F40/C40*100</f>
+        <f t="shared" si="10"/>
         <v>2.1746451975888319</v>
       </c>
       <c r="H40" s="2">
-        <f>(D40-E40)/E40</f>
+        <f t="shared" si="11"/>
         <v>1.7881988420162816E-2</v>
       </c>
       <c r="I40">
@@ -4842,18 +5448,18 @@
         <v>17</v>
       </c>
       <c r="K40">
-        <f>J40-I40</f>
+        <f t="shared" si="12"/>
         <v>-1</v>
       </c>
       <c r="L40">
         <v>20</v>
       </c>
       <c r="M40">
-        <f>J40+2</f>
+        <f t="shared" si="7"/>
         <v>19</v>
       </c>
       <c r="N40">
-        <f>M40-L40</f>
+        <f t="shared" si="8"/>
         <v>-1</v>
       </c>
       <c r="O40" t="s">
@@ -4872,7 +5478,7 @@
         <v>44742.7</v>
       </c>
       <c r="T40">
-        <f>D40/S40</f>
+        <f t="shared" si="13"/>
         <v>290.81490388376204</v>
       </c>
       <c r="U40">
@@ -4884,21 +5490,36 @@
       <c r="W40">
         <v>29</v>
       </c>
-      <c r="X40">
+      <c r="X40" s="6">
+        <v>157000</v>
+      </c>
+      <c r="Y40" s="7">
+        <v>1.434764606728998E-2</v>
+      </c>
+      <c r="Z40">
+        <v>1454753</v>
+      </c>
+      <c r="AA40">
+        <v>14506</v>
+      </c>
+      <c r="AB40">
+        <v>11.4</v>
+      </c>
+      <c r="AC40">
         <v>0.50589209999999996</v>
       </c>
-      <c r="Y40">
+      <c r="AD40">
         <v>23</v>
       </c>
-      <c r="Z40" s="4">
+      <c r="AE40" s="4">
         <v>4000000</v>
       </c>
-      <c r="AA40" s="5">
-        <f>Z40/D40</f>
+      <c r="AF40" s="5">
+        <f>AE40/D40</f>
         <v>0.30741223150231434</v>
       </c>
     </row>
-    <row r="41" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>49</v>
       </c>
@@ -4915,15 +5536,15 @@
         <v>1057125</v>
       </c>
       <c r="F41">
-        <f>D41-C41</f>
+        <f t="shared" si="9"/>
         <v>42916</v>
       </c>
       <c r="G41">
-        <f>F41/C41*100</f>
+        <f t="shared" si="10"/>
         <v>4.0669151392991401</v>
       </c>
       <c r="H41" s="2">
-        <f>(D41-E41)/E41</f>
+        <f t="shared" si="11"/>
         <v>3.8820385479484451E-2</v>
       </c>
       <c r="I41">
@@ -4933,18 +5554,18 @@
         <v>2</v>
       </c>
       <c r="K41">
-        <f>J41-I41</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="L41">
         <v>4</v>
       </c>
       <c r="M41">
-        <f>J41+2</f>
+        <f t="shared" si="7"/>
         <v>4</v>
       </c>
       <c r="N41">
-        <f>M41-L41</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="O41" t="s">
@@ -4963,7 +5584,7 @@
         <v>1033.81</v>
       </c>
       <c r="T41">
-        <f>D41/S41</f>
+        <f t="shared" si="13"/>
         <v>1062.2483821978894</v>
       </c>
       <c r="U41">
@@ -4975,21 +5596,36 @@
       <c r="W41">
         <v>12</v>
       </c>
-      <c r="X41">
+      <c r="X41" s="6">
+        <v>25000</v>
+      </c>
+      <c r="Y41" s="7">
+        <v>2.2709345985391992E-3</v>
+      </c>
+      <c r="Z41">
+        <v>78143</v>
+      </c>
+      <c r="AA41">
+        <v>6572</v>
+      </c>
+      <c r="AB41">
+        <v>7.4</v>
+      </c>
+      <c r="AC41">
         <v>0.60599360000000002</v>
       </c>
-      <c r="Y41">
+      <c r="AD41">
         <v>8</v>
       </c>
-      <c r="Z41" s="4">
+      <c r="AE41" s="4">
         <v>500000</v>
       </c>
-      <c r="AA41" s="5">
-        <f>Z41/D41</f>
+      <c r="AF41" s="5">
+        <f>AE41/D41</f>
         <v>0.45530581525693364</v>
       </c>
     </row>
-    <row r="42" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>50</v>
       </c>
@@ -5006,15 +5642,15 @@
         <v>5218040</v>
       </c>
       <c r="F42">
-        <f>D42-C42</f>
+        <f t="shared" si="9"/>
         <v>478737</v>
       </c>
       <c r="G42">
-        <f>F42/C42*100</f>
+        <f t="shared" si="10"/>
         <v>10.304338701779498</v>
       </c>
       <c r="H42" s="2">
-        <f>(D42-E42)/E42</f>
+        <f t="shared" si="11"/>
         <v>-1.7885642885067957E-2</v>
       </c>
       <c r="I42">
@@ -5024,18 +5660,18 @@
         <v>7</v>
       </c>
       <c r="K42">
-        <f>J42-I42</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="L42">
         <v>9</v>
       </c>
       <c r="M42">
-        <f>J42+2</f>
+        <f t="shared" si="7"/>
         <v>9</v>
       </c>
       <c r="N42">
-        <f>M42-L42</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="O42" t="s">
@@ -5054,7 +5690,7 @@
         <v>30060.7</v>
       </c>
       <c r="T42">
-        <f>D42/S42</f>
+        <f t="shared" si="13"/>
         <v>170.47879789891786</v>
       </c>
       <c r="U42">
@@ -5066,21 +5702,36 @@
       <c r="W42">
         <v>35</v>
       </c>
-      <c r="X42">
+      <c r="X42" s="6">
+        <v>88000</v>
+      </c>
+      <c r="Y42" s="7">
+        <v>8.0353984685408303E-3</v>
+      </c>
+      <c r="Z42">
+        <v>1362917</v>
+      </c>
+      <c r="AA42">
+        <v>8396</v>
+      </c>
+      <c r="AB42">
+        <v>26.5</v>
+      </c>
+      <c r="AC42">
         <v>0.44073390000000001</v>
       </c>
-      <c r="Y42">
+      <c r="AD42">
         <v>33</v>
       </c>
-      <c r="Z42" s="4">
-        <v>0</v>
-      </c>
-      <c r="AA42" s="5">
-        <f>Z42/D42</f>
+      <c r="AE42" s="4">
+        <v>0</v>
+      </c>
+      <c r="AF42" s="5">
+        <f>AE42/D42</f>
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>51</v>
       </c>
@@ -5097,15 +5748,15 @@
         <v>892717</v>
       </c>
       <c r="F43">
-        <f>D43-C43</f>
+        <f t="shared" si="9"/>
         <v>68009</v>
       </c>
       <c r="G43">
-        <f>F43/C43*100</f>
+        <f t="shared" si="10"/>
         <v>8.2961985261557949</v>
       </c>
       <c r="H43" s="2">
-        <f>(D43-E43)/E43</f>
+        <f t="shared" si="11"/>
         <v>-5.5415097953774826E-3</v>
       </c>
       <c r="I43">
@@ -5115,18 +5766,18 @@
         <v>1</v>
       </c>
       <c r="K43">
-        <f>J43-I43</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="L43">
         <v>3</v>
       </c>
       <c r="M43">
-        <f>J43+2</f>
+        <f t="shared" si="7"/>
         <v>3</v>
       </c>
       <c r="N43">
-        <f>M43-L43</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="O43" t="s">
@@ -5145,7 +5796,7 @@
         <v>75811</v>
       </c>
       <c r="T43">
-        <f>D43/S43</f>
+        <f t="shared" si="13"/>
         <v>11.710305892284762</v>
       </c>
       <c r="U43">
@@ -5157,21 +5808,36 @@
       <c r="W43">
         <v>47</v>
       </c>
-      <c r="X43">
+      <c r="X43" s="6">
+        <v>6000</v>
+      </c>
+      <c r="Y43" s="7">
+        <v>5.8496170868967167E-4</v>
+      </c>
+      <c r="Z43">
+        <v>20866</v>
+      </c>
+      <c r="AA43">
+        <v>2182</v>
+      </c>
+      <c r="AB43">
+        <v>2.4</v>
+      </c>
+      <c r="AC43">
         <v>0.36565219999999998</v>
       </c>
-      <c r="Y43">
+      <c r="AD43">
         <v>45</v>
       </c>
-      <c r="Z43" s="4">
-        <v>0</v>
-      </c>
-      <c r="AA43" s="5">
-        <f>Z43/D43</f>
+      <c r="AE43" s="4">
+        <v>0</v>
+      </c>
+      <c r="AF43" s="5">
+        <f>AE43/D43</f>
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>52</v>
       </c>
@@ -5188,15 +5854,15 @@
         <v>6886834</v>
       </c>
       <c r="F44">
-        <f>D44-C44</f>
+        <f t="shared" si="9"/>
         <v>541466</v>
       </c>
       <c r="G44">
-        <f>F44/C44*100</f>
+        <f t="shared" si="10"/>
         <v>8.4930101196295578</v>
       </c>
       <c r="H44" s="2">
-        <f>(D44-E44)/E44</f>
+        <f t="shared" si="11"/>
         <v>4.3652859935349106E-3</v>
       </c>
       <c r="I44">
@@ -5206,18 +5872,18 @@
         <v>9</v>
       </c>
       <c r="K44">
-        <f>J44-I44</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="L44">
         <v>11</v>
       </c>
       <c r="M44">
-        <f>J44+2</f>
+        <f t="shared" si="7"/>
         <v>11</v>
       </c>
       <c r="N44">
-        <f>M44-L44</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="O44" t="s">
@@ -5236,7 +5902,7 @@
         <v>41234.9</v>
       </c>
       <c r="T44">
-        <f>D44/S44</f>
+        <f t="shared" si="13"/>
         <v>167.74375589609772</v>
       </c>
       <c r="U44">
@@ -5248,21 +5914,36 @@
       <c r="W44">
         <v>36</v>
       </c>
-      <c r="X44">
+      <c r="X44" s="6">
+        <v>124000</v>
+      </c>
+      <c r="Y44" s="7">
+        <v>1.1310102995998677E-2</v>
+      </c>
+      <c r="Z44">
+        <v>1141304</v>
+      </c>
+      <c r="AA44">
+        <v>8527</v>
+      </c>
+      <c r="AB44">
+        <v>16.7</v>
+      </c>
+      <c r="AC44">
         <v>0.38172230000000001</v>
       </c>
-      <c r="Y44">
+      <c r="AD44">
         <v>42</v>
       </c>
-      <c r="Z44" s="4">
-        <v>0</v>
-      </c>
-      <c r="AA44" s="5">
-        <f>Z44/D44</f>
+      <c r="AE44" s="4">
+        <v>0</v>
+      </c>
+      <c r="AF44" s="5">
+        <f>AE44/D44</f>
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>53</v>
       </c>
@@ -5279,15 +5960,15 @@
         <v>29360759</v>
       </c>
       <c r="F45">
-        <f>D45-C45</f>
+        <f t="shared" si="9"/>
         <v>3914872</v>
       </c>
       <c r="G45">
-        <f>F45/C45*100</f>
+        <f t="shared" si="10"/>
         <v>15.493142467407338</v>
       </c>
       <c r="H45" s="2">
-        <f>(D45-E45)/E45</f>
+        <f t="shared" si="11"/>
         <v>-6.0444282111371851E-3</v>
       </c>
       <c r="I45">
@@ -5297,18 +5978,18 @@
         <v>38</v>
       </c>
       <c r="K45">
-        <f>J45-I45</f>
+        <f t="shared" si="12"/>
         <v>2</v>
       </c>
       <c r="L45">
         <v>38</v>
       </c>
       <c r="M45">
-        <f>J45+2</f>
+        <f t="shared" si="7"/>
         <v>40</v>
       </c>
       <c r="N45">
-        <f>M45-L45</f>
+        <f t="shared" si="8"/>
         <v>2</v>
       </c>
       <c r="O45" t="s">
@@ -5327,7 +6008,7 @@
         <v>261231.71</v>
       </c>
       <c r="T45">
-        <f>D45/S45</f>
+        <f t="shared" si="13"/>
         <v>111.71419426837576</v>
       </c>
       <c r="U45">
@@ -5339,21 +6020,36 @@
       <c r="W45">
         <v>2</v>
       </c>
-      <c r="X45">
+      <c r="X45" s="6">
+        <v>1730000</v>
+      </c>
+      <c r="Y45" s="7">
+        <v>0.1576112344387991</v>
+      </c>
+      <c r="Z45">
+        <v>3553922</v>
+      </c>
+      <c r="AA45">
+        <v>23163</v>
+      </c>
+      <c r="AB45">
+        <v>12.3</v>
+      </c>
+      <c r="AC45">
         <v>0.47169280000000002</v>
       </c>
-      <c r="Y45">
+      <c r="AD45">
         <v>29</v>
       </c>
-      <c r="Z45" s="4">
-        <v>0</v>
-      </c>
-      <c r="AA45" s="5">
-        <f>Z45/D45</f>
+      <c r="AE45" s="4">
+        <v>0</v>
+      </c>
+      <c r="AF45" s="5">
+        <f>AE45/D45</f>
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>54</v>
       </c>
@@ -5370,15 +6066,15 @@
         <v>3249879</v>
       </c>
       <c r="F46">
-        <f>D46-C46</f>
+        <f t="shared" si="9"/>
         <v>504487</v>
       </c>
       <c r="G46">
-        <f>F46/C46*100</f>
+        <f t="shared" si="10"/>
         <v>18.207498651094554</v>
       </c>
       <c r="H46" s="2">
-        <f>(D46-E46)/E46</f>
+        <f t="shared" si="11"/>
         <v>7.8073675973782406E-3</v>
       </c>
       <c r="I46">
@@ -5388,18 +6084,18 @@
         <v>4</v>
       </c>
       <c r="K46">
-        <f>J46-I46</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="L46">
         <v>6</v>
       </c>
       <c r="M46">
-        <f>J46+2</f>
+        <f t="shared" si="7"/>
         <v>6</v>
       </c>
       <c r="N46">
-        <f>M46-L46</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="O46" t="s">
@@ -5418,7 +6114,7 @@
         <v>82169.62</v>
       </c>
       <c r="T46">
-        <f>D46/S46</f>
+        <f t="shared" si="13"/>
         <v>39.859646424067684</v>
       </c>
       <c r="U46">
@@ -5430,21 +6126,36 @@
       <c r="W46">
         <v>13</v>
       </c>
-      <c r="X46">
+      <c r="X46" s="6">
+        <v>92000</v>
+      </c>
+      <c r="Y46" s="7">
+        <v>8.3393736326296021E-3</v>
+      </c>
+      <c r="Z46">
+        <v>36918</v>
+      </c>
+      <c r="AA46">
+        <v>2748</v>
+      </c>
+      <c r="AB46">
+        <v>1.2</v>
+      </c>
+      <c r="AC46">
         <v>0.39306390000000002</v>
       </c>
-      <c r="Y46">
+      <c r="AD46">
         <v>41</v>
       </c>
-      <c r="Z46" s="4">
+      <c r="AE46" s="4">
         <v>1000000</v>
       </c>
-      <c r="AA46" s="5">
-        <f>Z46/D46</f>
+      <c r="AF46" s="5">
+        <f>AE46/D46</f>
         <v>0.30532001812379628</v>
       </c>
     </row>
-    <row r="47" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>55</v>
       </c>
@@ -5461,15 +6172,15 @@
         <v>623347</v>
       </c>
       <c r="F47">
-        <f>D47-C47</f>
+        <f t="shared" si="9"/>
         <v>13166</v>
       </c>
       <c r="G47">
-        <f>F47/C47*100</f>
+        <f t="shared" si="10"/>
         <v>2.0887239682899783</v>
       </c>
       <c r="H47" s="2">
-        <f>(D47-E47)/E47</f>
+        <f t="shared" si="11"/>
         <v>3.233511992517811E-2</v>
       </c>
       <c r="I47">
@@ -5479,18 +6190,18 @@
         <v>1</v>
       </c>
       <c r="K47">
-        <f>J47-I47</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="L47">
         <v>3</v>
       </c>
       <c r="M47">
-        <f>J47+2</f>
+        <f t="shared" si="7"/>
         <v>3</v>
       </c>
       <c r="N47">
-        <f>M47-L47</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="O47" t="s">
@@ -5509,7 +6220,7 @@
         <v>9216.66</v>
       </c>
       <c r="T47">
-        <f>D47/S47</f>
+        <f t="shared" si="13"/>
         <v>69.819544173268838</v>
       </c>
       <c r="U47">
@@ -5521,21 +6232,36 @@
       <c r="W47">
         <v>49</v>
       </c>
-      <c r="X47">
+      <c r="X47" s="6">
+        <v>3000</v>
+      </c>
+      <c r="Y47" s="7">
+        <v>2.6588542379373502E-4</v>
+      </c>
+      <c r="Z47">
+        <v>9435</v>
+      </c>
+      <c r="AA47">
+        <v>1109</v>
+      </c>
+      <c r="AB47">
+        <v>1.5</v>
+      </c>
+      <c r="AC47">
         <v>0.68299189999999999</v>
       </c>
-      <c r="Y47">
+      <c r="AD47">
         <v>2</v>
       </c>
-      <c r="Z47" s="4">
-        <v>0</v>
-      </c>
-      <c r="AA47" s="5">
-        <f>Z47/D47</f>
+      <c r="AE47" s="4">
+        <v>0</v>
+      </c>
+      <c r="AF47" s="5">
+        <f>AE47/D47</f>
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>56</v>
       </c>
@@ -5552,15 +6278,15 @@
         <v>8590563</v>
       </c>
       <c r="F48">
-        <f>D48-C48</f>
+        <f t="shared" si="9"/>
         <v>616806</v>
       </c>
       <c r="G48">
-        <f>F48/C48*100</f>
+        <f t="shared" si="10"/>
         <v>7.6738773206783604</v>
       </c>
       <c r="H48" s="2">
-        <f>(D48-E48)/E48</f>
+        <f t="shared" si="11"/>
         <v>7.4475910368156312E-3</v>
       </c>
       <c r="I48">
@@ -5570,18 +6296,18 @@
         <v>11</v>
       </c>
       <c r="K48">
-        <f>J48-I48</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="L48">
         <v>13</v>
       </c>
       <c r="M48">
-        <f>J48+2</f>
+        <f t="shared" si="7"/>
         <v>13</v>
       </c>
       <c r="N48">
-        <f>M48-L48</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="O48" t="s">
@@ -5600,7 +6326,7 @@
         <v>39490.089999999997</v>
       </c>
       <c r="T48">
-        <f>D48/S48</f>
+        <f t="shared" si="13"/>
         <v>219.15731263210594</v>
       </c>
       <c r="U48">
@@ -5612,21 +6338,36 @@
       <c r="W48">
         <v>27</v>
       </c>
-      <c r="X48">
+      <c r="X48" s="6">
+        <v>251000</v>
+      </c>
+      <c r="Y48" s="7">
+        <v>2.2902440797941868E-2</v>
+      </c>
+      <c r="Z48">
+        <v>1659908</v>
+      </c>
+      <c r="AA48">
+        <v>12568</v>
+      </c>
+      <c r="AB48">
+        <v>19.399999999999999</v>
+      </c>
+      <c r="AC48">
         <v>0.55154689999999995</v>
       </c>
-      <c r="Y48">
+      <c r="AD48">
         <v>17</v>
       </c>
-      <c r="Z48" s="4">
+      <c r="AE48" s="4">
         <v>1500000</v>
       </c>
-      <c r="AA48" s="5">
-        <f>Z48/D48</f>
+      <c r="AF48" s="5">
+        <f>AE48/D48</f>
         <v>0.17331939691320464</v>
       </c>
     </row>
-    <row r="49" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>57</v>
       </c>
@@ -5643,15 +6384,15 @@
         <v>7693612</v>
       </c>
       <c r="F49">
-        <f>D49-C49</f>
+        <f t="shared" si="9"/>
         <v>962577</v>
       </c>
       <c r="G49">
-        <f>F49/C49*100</f>
+        <f t="shared" si="10"/>
         <v>14.25328602657429</v>
       </c>
       <c r="H49" s="2">
-        <f>(D49-E49)/E49</f>
+        <f t="shared" si="11"/>
         <v>2.9029277795656967E-3</v>
       </c>
       <c r="I49">
@@ -5661,18 +6402,18 @@
         <v>10</v>
       </c>
       <c r="K49">
-        <f>J49-I49</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="L49">
         <v>12</v>
       </c>
       <c r="M49">
-        <f>J49+2</f>
+        <f t="shared" si="7"/>
         <v>12</v>
       </c>
       <c r="N49">
-        <f>M49-L49</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="O49" t="s">
@@ -5691,7 +6432,7 @@
         <v>66455.520000000004</v>
       </c>
       <c r="T49">
-        <f>D49/S49</f>
+        <f t="shared" si="13"/>
         <v>116.10692384921522</v>
       </c>
       <c r="U49">
@@ -5703,21 +6444,36 @@
       <c r="W49">
         <v>15</v>
       </c>
-      <c r="X49">
+      <c r="X49" s="6">
+        <v>240000</v>
+      </c>
+      <c r="Y49" s="7">
+        <v>2.1875828694926852E-2</v>
+      </c>
+      <c r="Z49">
+        <v>305924</v>
+      </c>
+      <c r="AA49">
+        <v>7176</v>
+      </c>
+      <c r="AB49">
+        <v>4</v>
+      </c>
+      <c r="AC49">
         <v>0.59925499999999998</v>
       </c>
-      <c r="Y49">
+      <c r="AD49">
         <v>10</v>
       </c>
-      <c r="Z49" s="4">
+      <c r="AE49" s="4">
         <v>15464000</v>
       </c>
-      <c r="AA49" s="5">
-        <f>Z49/D49</f>
+      <c r="AF49" s="5">
+        <f>AE49/D49</f>
         <v>2.0041612525541264</v>
       </c>
     </row>
-    <row r="50" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>58</v>
       </c>
@@ -5734,15 +6490,15 @@
         <v>1784787</v>
       </c>
       <c r="F50">
-        <f>D50-C50</f>
+        <f t="shared" si="9"/>
         <v>-64770</v>
       </c>
       <c r="G50">
-        <f>F50/C50*100</f>
+        <f t="shared" si="10"/>
         <v>-3.4826044525934035</v>
       </c>
       <c r="H50" s="2">
-        <f>(D50-E50)/E50</f>
+        <f t="shared" si="11"/>
         <v>5.7474645433880905E-3</v>
       </c>
       <c r="I50">
@@ -5752,18 +6508,18 @@
         <v>2</v>
       </c>
       <c r="K50">
-        <f>J50-I50</f>
+        <f t="shared" si="12"/>
         <v>-1</v>
       </c>
       <c r="L50">
         <v>5</v>
       </c>
       <c r="M50">
-        <f>J50+2</f>
+        <f t="shared" si="7"/>
         <v>4</v>
       </c>
       <c r="N50">
-        <f>M50-L50</f>
+        <f t="shared" si="8"/>
         <v>-1</v>
       </c>
       <c r="O50" t="s">
@@ -5782,7 +6538,7 @@
         <v>24038.21</v>
       </c>
       <c r="T50">
-        <f>D50/S50</f>
+        <f t="shared" si="13"/>
         <v>74.674653395573131</v>
       </c>
       <c r="U50">
@@ -5794,21 +6550,36 @@
       <c r="W50">
         <v>51</v>
       </c>
-      <c r="X50">
+      <c r="X50" s="6">
+        <v>6000</v>
+      </c>
+      <c r="Y50" s="7">
+        <v>5.1273037763429653E-4</v>
+      </c>
+      <c r="Z50">
+        <v>65925</v>
+      </c>
+      <c r="AA50">
+        <v>3478</v>
+      </c>
+      <c r="AB50">
+        <v>3.7</v>
+      </c>
+      <c r="AC50">
         <v>0.30201470000000002</v>
       </c>
-      <c r="Y50">
+      <c r="AD50">
         <v>50</v>
       </c>
-      <c r="Z50" s="4">
+      <c r="AE50" s="4">
         <v>1000000</v>
       </c>
-      <c r="AA50" s="5">
-        <f>Z50/D50</f>
+      <c r="AF50" s="5">
+        <f>AE50/D50</f>
         <v>0.55708909804489581</v>
       </c>
     </row>
-    <row r="51" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>59</v>
       </c>
@@ -5825,15 +6596,15 @@
         <v>5832655</v>
       </c>
       <c r="F51">
-        <f>D51-C51</f>
+        <f t="shared" si="9"/>
         <v>199243</v>
       </c>
       <c r="G51">
-        <f>F51/C51*100</f>
+        <f t="shared" si="10"/>
         <v>3.4965770072461098</v>
       </c>
       <c r="H51" s="2">
-        <f>(D51-E51)/E51</f>
+        <f t="shared" si="11"/>
         <v>1.1112949420118283E-2</v>
       </c>
       <c r="I51">
@@ -5843,18 +6614,18 @@
         <v>8</v>
       </c>
       <c r="K51">
-        <f>J51-I51</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="L51">
         <v>10</v>
       </c>
       <c r="M51">
-        <f>J51+2</f>
+        <f t="shared" si="7"/>
         <v>10</v>
       </c>
       <c r="N51">
-        <f>M51-L51</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="O51" t="s">
@@ -5873,7 +6644,7 @@
         <v>54157.8</v>
       </c>
       <c r="T51">
-        <f>D51/S51</f>
+        <f t="shared" si="13"/>
         <v>108.8942497664233</v>
       </c>
       <c r="U51">
@@ -5885,21 +6656,36 @@
       <c r="W51">
         <v>33</v>
       </c>
-      <c r="X51">
+      <c r="X51" s="6">
+        <v>74000</v>
+      </c>
+      <c r="Y51" s="7">
+        <v>6.7595759382643901E-3</v>
+      </c>
+      <c r="Z51">
+        <v>374747</v>
+      </c>
+      <c r="AA51">
+        <v>5775</v>
+      </c>
+      <c r="AB51">
+        <v>6.4</v>
+      </c>
+      <c r="AC51">
         <v>0.50319060000000004</v>
       </c>
-      <c r="Y51">
+      <c r="AD51">
         <v>24</v>
       </c>
-      <c r="Z51" s="4">
+      <c r="AE51" s="4">
         <v>1000000</v>
       </c>
-      <c r="AA51" s="5">
-        <f>Z51/D51</f>
+      <c r="AF51" s="5">
+        <f>AE51/D51</f>
         <v>0.16956415061162636</v>
       </c>
     </row>
-    <row r="52" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>60</v>
       </c>
@@ -5916,15 +6702,15 @@
         <v>582328</v>
       </c>
       <c r="F52">
-        <f>D52-C52</f>
+        <f t="shared" si="9"/>
         <v>9419</v>
       </c>
       <c r="G52">
-        <f>F52/C52*100</f>
+        <f t="shared" si="10"/>
         <v>1.6573992609537216</v>
       </c>
       <c r="H52" s="2">
-        <f>(D52-E52)/E52</f>
+        <f t="shared" si="11"/>
         <v>-7.914783421027324E-3</v>
       </c>
       <c r="I52">
@@ -5934,18 +6720,18 @@
         <v>1</v>
       </c>
       <c r="K52">
-        <f>J52-I52</f>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="L52">
         <v>3</v>
       </c>
       <c r="M52">
-        <f>J52+2</f>
+        <f t="shared" si="7"/>
         <v>3</v>
       </c>
       <c r="N52">
-        <f>M52-L52</f>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="O52" t="s">
@@ -5964,7 +6750,7 @@
         <v>97093.14</v>
       </c>
       <c r="T52">
-        <f>D52/S52</f>
+        <f t="shared" si="13"/>
         <v>5.9501526060440524</v>
       </c>
       <c r="U52">
@@ -5976,22 +6762,28 @@
       <c r="W52">
         <v>24</v>
       </c>
-      <c r="X52">
-        <v>0.27519569999999999</v>
-      </c>
-      <c r="Y52">
-        <v>51</v>
-      </c>
-      <c r="Z52" s="4">
-        <v>0</v>
-      </c>
-      <c r="AA52" s="5">
-        <f>Z52/D52</f>
-        <v>0</v>
+      <c r="X52" s="6">
+        <v>8000</v>
+      </c>
+      <c r="Y52" s="7">
+        <v>7.5184707792282806E-4</v>
+      </c>
+      <c r="Z52">
+        <v>7116</v>
+      </c>
+      <c r="AA52">
+        <v>1901</v>
+      </c>
+      <c r="AB52">
+        <v>1.2</v>
+      </c>
+      <c r="AC52" s="5" t="e">
+        <f>#REF!/D52</f>
+        <v>#REF!</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AA52">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AC52">
     <sortCondition ref="A2:A52"/>
   </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/apportion/pop.xlsx
+++ b/apportion/pop.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/user/Google Drive/GitHub/R Functions/apportion/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9AA455F-17E2-A34D-B9BC-7FDF45F7DEC1}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{234137D1-13F8-6C49-8A76-D68FFAD45B61}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38400" yWindow="500" windowWidth="38400" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -434,10 +434,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="4">
+  <numFmts count="3">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="0.000"/>
-    <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
   </numFmts>
   <fonts count="18" x14ac:knownFonts="1">
@@ -919,14 +918,13 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="43" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="44">
@@ -1290,6 +1288,7 @@
   <cols>
     <col min="22" max="22" width="17.1640625" style="4" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="10.83203125" style="5"/>
+    <col min="24" max="24" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:32" x14ac:dyDescent="0.2">
@@ -1362,7 +1361,7 @@
       <c r="W1" t="s">
         <v>132</v>
       </c>
-      <c r="X1" t="s">
+      <c r="X1" s="1" t="s">
         <v>130</v>
       </c>
       <c r="Y1" t="s">
@@ -1467,10 +1466,10 @@
       <c r="W2">
         <v>40</v>
       </c>
-      <c r="X2" s="6">
+      <c r="X2" s="1">
         <v>60000</v>
       </c>
-      <c r="Y2" s="7">
+      <c r="Y2" s="6">
         <v>5.4854633708831318E-3</v>
       </c>
       <c r="Z2">
@@ -1573,10 +1572,10 @@
       <c r="W3">
         <v>31</v>
       </c>
-      <c r="X3" s="6">
+      <c r="X3" s="1">
         <v>9000</v>
       </c>
-      <c r="Y3" s="7">
+      <c r="Y3" s="6">
         <v>8.1422119017382423E-4</v>
       </c>
       <c r="Z3">
@@ -1679,10 +1678,10 @@
       <c r="W4">
         <v>4</v>
       </c>
-      <c r="X4" s="6">
+      <c r="X4" s="1">
         <v>281000</v>
       </c>
-      <c r="Y4" s="7">
+      <c r="Y4" s="6">
         <v>2.5634192618307336E-2</v>
       </c>
       <c r="Z4">
@@ -1785,10 +1784,10 @@
       <c r="W5">
         <v>30</v>
       </c>
-      <c r="X5" s="6">
+      <c r="X5" s="1">
         <v>58000</v>
       </c>
-      <c r="Y5" s="7">
+      <c r="Y5" s="6">
         <v>5.3074451728820585E-3</v>
       </c>
       <c r="Z5">
@@ -1891,10 +1890,10 @@
       <c r="W6">
         <v>3</v>
       </c>
-      <c r="X6" s="6">
+      <c r="X6" s="1">
         <v>2625000</v>
       </c>
-      <c r="Y6" s="7">
+      <c r="Y6" s="6">
         <v>0.23912001877298844</v>
       </c>
       <c r="Z6">
@@ -1997,10 +1996,10 @@
       <c r="W7">
         <v>7</v>
       </c>
-      <c r="X7" s="6">
+      <c r="X7" s="1">
         <v>178000</v>
       </c>
-      <c r="Y7" s="7">
+      <c r="Y7" s="6">
         <v>1.6207999032549474E-2</v>
       </c>
       <c r="Z7">
@@ -2103,10 +2102,10 @@
       <c r="W8">
         <v>11</v>
       </c>
-      <c r="X8" s="6">
+      <c r="X8" s="1">
         <v>116000</v>
       </c>
-      <c r="Y8" s="7">
+      <c r="Y8" s="6">
         <v>1.0581337524693493E-2</v>
       </c>
       <c r="Z8">
@@ -2209,10 +2208,10 @@
       <c r="W9">
         <v>28</v>
       </c>
-      <c r="X9" s="6">
+      <c r="X9" s="1">
         <v>24000</v>
       </c>
-      <c r="Y9" s="7">
+      <c r="Y9" s="6">
         <v>2.1447469365479806E-3</v>
       </c>
       <c r="Z9">
@@ -2314,10 +2313,10 @@
       <c r="W10">
         <v>19</v>
       </c>
-      <c r="X10" s="6">
+      <c r="X10" s="1">
         <v>25000</v>
       </c>
-      <c r="Y10" s="7">
+      <c r="Y10" s="6">
         <v>2.3050032809033808E-3</v>
       </c>
       <c r="Z10">
@@ -2420,10 +2419,10 @@
       <c r="W11">
         <v>6</v>
       </c>
-      <c r="X11" s="6">
+      <c r="X11" s="1">
         <v>732000</v>
       </c>
-      <c r="Y11" s="7">
+      <c r="Y11" s="6">
         <v>6.665678324468978E-2</v>
       </c>
       <c r="Z11">
@@ -2526,10 +2525,10 @@
       <c r="W12">
         <v>25</v>
       </c>
-      <c r="X12" s="6">
+      <c r="X12" s="1">
         <v>330000</v>
       </c>
-      <c r="Y12" s="7">
+      <c r="Y12" s="6">
         <v>3.0036898545099215E-2</v>
       </c>
       <c r="Z12">
@@ -2632,10 +2631,10 @@
       <c r="W13">
         <v>22</v>
       </c>
-      <c r="X13" s="6">
+      <c r="X13" s="1">
         <v>39000</v>
       </c>
-      <c r="Y13" s="7">
+      <c r="Y13" s="6">
         <v>3.5846859659377519E-3</v>
       </c>
       <c r="Z13">
@@ -2738,10 +2737,10 @@
       <c r="W14">
         <v>16</v>
       </c>
-      <c r="X14" s="6">
+      <c r="X14" s="1">
         <v>30000</v>
       </c>
-      <c r="Y14" s="7">
+      <c r="Y14" s="6">
         <v>2.7473702600875104E-3</v>
       </c>
       <c r="Z14">
@@ -2844,10 +2843,10 @@
       <c r="W15">
         <v>10</v>
       </c>
-      <c r="X15" s="6">
+      <c r="X15" s="1">
         <v>437000</v>
       </c>
-      <c r="Y15" s="7">
+      <c r="Y15" s="6">
         <v>3.9819831027452048E-2</v>
       </c>
       <c r="Z15">
@@ -2950,10 +2949,10 @@
       <c r="W16">
         <v>32</v>
       </c>
-      <c r="X16" s="6">
+      <c r="X16" s="1">
         <v>105000</v>
       </c>
-      <c r="Y16" s="7">
+      <c r="Y16" s="6">
         <v>9.5839421108608464E-3</v>
       </c>
       <c r="Z16">
@@ -3056,10 +3055,10 @@
       <c r="W17">
         <v>34</v>
       </c>
-      <c r="X17" s="6">
+      <c r="X17" s="1">
         <v>40000</v>
       </c>
-      <c r="Y17" s="7">
+      <c r="Y17" s="6">
         <v>3.6131851319176136E-3</v>
       </c>
       <c r="Z17">
@@ -3162,10 +3161,10 @@
       <c r="W18">
         <v>18</v>
       </c>
-      <c r="X18" s="6">
+      <c r="X18" s="1">
         <v>70000</v>
       </c>
-      <c r="Y18" s="7">
+      <c r="Y18" s="6">
         <v>6.4161028441482989E-3</v>
       </c>
       <c r="Z18">
@@ -3268,10 +3267,10 @@
       <c r="W19">
         <v>45</v>
       </c>
-      <c r="X19" s="6">
+      <c r="X19" s="1">
         <v>48000</v>
       </c>
-      <c r="Y19" s="7">
+      <c r="Y19" s="6">
         <v>4.4082292365805039E-3</v>
       </c>
       <c r="Z19">
@@ -3374,10 +3373,10 @@
       <c r="W20">
         <v>38</v>
       </c>
-      <c r="X20" s="6">
+      <c r="X20" s="1">
         <v>70000</v>
       </c>
-      <c r="Y20" s="7">
+      <c r="Y20" s="6">
         <v>6.3682077308170361E-3</v>
       </c>
       <c r="Z20">
@@ -3480,10 +3479,10 @@
       <c r="W21">
         <v>50</v>
       </c>
-      <c r="X21" s="6">
+      <c r="X21" s="1">
         <v>6000</v>
       </c>
-      <c r="Y21" s="7">
+      <c r="Y21" s="6">
         <v>5.2123922384111258E-4</v>
       </c>
       <c r="Z21">
@@ -3586,10 +3585,10 @@
       <c r="W22">
         <v>23</v>
       </c>
-      <c r="X22" s="6">
+      <c r="X22" s="1">
         <v>226000</v>
       </c>
-      <c r="Y22" s="7">
+      <c r="Y22" s="6">
         <v>2.0626662460001551E-2</v>
       </c>
       <c r="Z22">
@@ -3692,10 +3691,10 @@
       <c r="W23">
         <v>17</v>
       </c>
-      <c r="X23" s="6">
+      <c r="X23" s="1">
         <v>215000</v>
       </c>
-      <c r="Y23" s="7">
+      <c r="Y23" s="6">
         <v>1.9543947332479099E-2</v>
       </c>
       <c r="Z23">
@@ -3798,10 +3797,10 @@
       <c r="W24">
         <v>39</v>
       </c>
-      <c r="X24" s="6">
+      <c r="X24" s="1">
         <v>102000</v>
       </c>
-      <c r="Y24" s="7">
+      <c r="Y24" s="6">
         <v>9.3105623088550939E-3</v>
       </c>
       <c r="Z24">
@@ -3904,10 +3903,10 @@
       <c r="W25">
         <v>37</v>
       </c>
-      <c r="X25" s="6">
+      <c r="X25" s="1">
         <v>92000</v>
       </c>
-      <c r="Y25" s="7">
+      <c r="Y25" s="6">
         <v>8.3464036035804864E-3</v>
       </c>
       <c r="Z25">
@@ -4010,10 +4009,10 @@
       <c r="W26">
         <v>48</v>
       </c>
-      <c r="X26" s="6">
+      <c r="X26" s="1">
         <v>27000</v>
       </c>
-      <c r="Y26" s="7">
+      <c r="Y26" s="6">
         <v>2.4263958971555422E-3</v>
       </c>
       <c r="Z26">
@@ -4116,10 +4115,10 @@
       <c r="W27">
         <v>41</v>
       </c>
-      <c r="X27" s="6">
+      <c r="X27" s="1">
         <v>54000</v>
       </c>
-      <c r="Y27" s="7">
+      <c r="Y27" s="6">
         <v>4.9513267401302703E-3</v>
       </c>
       <c r="Z27">
@@ -4222,10 +4221,10 @@
       <c r="W28">
         <v>46</v>
       </c>
-      <c r="X28" s="6">
+      <c r="X28" s="1">
         <v>4000</v>
       </c>
-      <c r="Y28" s="7">
+      <c r="Y28" s="6">
         <v>3.4862345327097891E-4</v>
       </c>
       <c r="Z28">
@@ -4328,10 +4327,10 @@
       <c r="W29">
         <v>20</v>
       </c>
-      <c r="X29" s="6">
+      <c r="X29" s="1">
         <v>41000</v>
       </c>
-      <c r="Y29" s="7">
+      <c r="Y29" s="6">
         <v>3.7471223651725965E-3</v>
       </c>
       <c r="Z29">
@@ -4432,10 +4431,10 @@
       <c r="W30">
         <v>5</v>
       </c>
-      <c r="X30" s="6">
+      <c r="X30" s="1">
         <v>162000</v>
       </c>
-      <c r="Y30" s="7">
+      <c r="Y30" s="6">
         <v>1.4781831764217334E-2</v>
       </c>
       <c r="Z30">
@@ -4538,10 +4537,10 @@
       <c r="W31">
         <v>42</v>
       </c>
-      <c r="X31" s="6">
+      <c r="X31" s="1">
         <v>11000</v>
       </c>
-      <c r="Y31" s="7">
+      <c r="Y31" s="6">
         <v>1.0264600366713149E-3</v>
       </c>
       <c r="Z31">
@@ -4642,10 +4641,10 @@
       <c r="W32">
         <v>8</v>
       </c>
-      <c r="X32" s="6">
+      <c r="X32" s="1">
         <v>425000</v>
       </c>
-      <c r="Y32" s="7">
+      <c r="Y32" s="6">
         <v>3.8706204889950788E-2</v>
       </c>
       <c r="Z32">
@@ -4748,10 +4747,10 @@
       <c r="W33">
         <v>1</v>
       </c>
-      <c r="X33" s="6">
+      <c r="X33" s="1">
         <v>71000</v>
       </c>
-      <c r="Y33" s="7">
+      <c r="Y33" s="6">
         <v>6.4332024548798411E-3</v>
       </c>
       <c r="Z33">
@@ -4854,10 +4853,10 @@
       <c r="W34">
         <v>9</v>
       </c>
-      <c r="X34" s="6">
+      <c r="X34" s="1">
         <v>866000</v>
       </c>
-      <c r="Y34" s="7">
+      <c r="Y34" s="6">
         <v>7.8852265943519587E-2</v>
       </c>
       <c r="Z34">
@@ -4960,10 +4959,10 @@
       <c r="W35">
         <v>26</v>
       </c>
-      <c r="X35" s="6">
+      <c r="X35" s="1">
         <v>298000</v>
       </c>
-      <c r="Y35" s="7">
+      <c r="Y35" s="6">
         <v>2.7137862459207431E-2</v>
       </c>
       <c r="Z35">
@@ -5066,10 +5065,10 @@
       <c r="W36">
         <v>43</v>
       </c>
-      <c r="X36" s="6">
+      <c r="X36" s="1">
         <v>5000</v>
       </c>
-      <c r="Y36" s="7">
+      <c r="Y36" s="6">
         <v>4.8200798385366272E-4</v>
       </c>
       <c r="Z36">
@@ -5172,10 +5171,10 @@
       <c r="W37">
         <v>44</v>
       </c>
-      <c r="X37" s="6">
+      <c r="X37" s="1">
         <v>87000</v>
       </c>
-      <c r="Y37" s="7">
+      <c r="Y37" s="6">
         <v>7.9600360029181538E-3</v>
       </c>
       <c r="Z37">
@@ -5278,10 +5277,10 @@
       <c r="W38">
         <v>21</v>
       </c>
-      <c r="X38" s="6">
+      <c r="X38" s="1">
         <v>92000</v>
       </c>
-      <c r="Y38" s="7">
+      <c r="Y38" s="6">
         <v>8.3754220653741284E-3</v>
       </c>
       <c r="Z38">
@@ -5384,10 +5383,10 @@
       <c r="W39">
         <v>14</v>
       </c>
-      <c r="X39" s="6">
+      <c r="X39" s="1">
         <v>110000</v>
       </c>
-      <c r="Y39" s="7">
+      <c r="Y39" s="6">
         <v>1.0018798796430226E-2</v>
       </c>
       <c r="Z39">
@@ -5490,10 +5489,10 @@
       <c r="W40">
         <v>29</v>
       </c>
-      <c r="X40" s="6">
+      <c r="X40" s="1">
         <v>157000</v>
       </c>
-      <c r="Y40" s="7">
+      <c r="Y40" s="6">
         <v>1.434764606728998E-2</v>
       </c>
       <c r="Z40">
@@ -5596,10 +5595,10 @@
       <c r="W41">
         <v>12</v>
       </c>
-      <c r="X41" s="6">
+      <c r="X41" s="1">
         <v>25000</v>
       </c>
-      <c r="Y41" s="7">
+      <c r="Y41" s="6">
         <v>2.2709345985391992E-3</v>
       </c>
       <c r="Z41">
@@ -5702,10 +5701,10 @@
       <c r="W42">
         <v>35</v>
       </c>
-      <c r="X42" s="6">
+      <c r="X42" s="1">
         <v>88000</v>
       </c>
-      <c r="Y42" s="7">
+      <c r="Y42" s="6">
         <v>8.0353984685408303E-3</v>
       </c>
       <c r="Z42">
@@ -5808,10 +5807,10 @@
       <c r="W43">
         <v>47</v>
       </c>
-      <c r="X43" s="6">
+      <c r="X43" s="1">
         <v>6000</v>
       </c>
-      <c r="Y43" s="7">
+      <c r="Y43" s="6">
         <v>5.8496170868967167E-4</v>
       </c>
       <c r="Z43">
@@ -5914,10 +5913,10 @@
       <c r="W44">
         <v>36</v>
       </c>
-      <c r="X44" s="6">
+      <c r="X44" s="1">
         <v>124000</v>
       </c>
-      <c r="Y44" s="7">
+      <c r="Y44" s="6">
         <v>1.1310102995998677E-2</v>
       </c>
       <c r="Z44">
@@ -6020,10 +6019,10 @@
       <c r="W45">
         <v>2</v>
       </c>
-      <c r="X45" s="6">
+      <c r="X45" s="1">
         <v>1730000</v>
       </c>
-      <c r="Y45" s="7">
+      <c r="Y45" s="6">
         <v>0.1576112344387991</v>
       </c>
       <c r="Z45">
@@ -6126,10 +6125,10 @@
       <c r="W46">
         <v>13</v>
       </c>
-      <c r="X46" s="6">
+      <c r="X46" s="1">
         <v>92000</v>
       </c>
-      <c r="Y46" s="7">
+      <c r="Y46" s="6">
         <v>8.3393736326296021E-3</v>
       </c>
       <c r="Z46">
@@ -6232,10 +6231,10 @@
       <c r="W47">
         <v>49</v>
       </c>
-      <c r="X47" s="6">
+      <c r="X47" s="1">
         <v>3000</v>
       </c>
-      <c r="Y47" s="7">
+      <c r="Y47" s="6">
         <v>2.6588542379373502E-4</v>
       </c>
       <c r="Z47">
@@ -6338,10 +6337,10 @@
       <c r="W48">
         <v>27</v>
       </c>
-      <c r="X48" s="6">
+      <c r="X48" s="1">
         <v>251000</v>
       </c>
-      <c r="Y48" s="7">
+      <c r="Y48" s="6">
         <v>2.2902440797941868E-2</v>
       </c>
       <c r="Z48">
@@ -6444,10 +6443,10 @@
       <c r="W49">
         <v>15</v>
       </c>
-      <c r="X49" s="6">
+      <c r="X49" s="1">
         <v>240000</v>
       </c>
-      <c r="Y49" s="7">
+      <c r="Y49" s="6">
         <v>2.1875828694926852E-2</v>
       </c>
       <c r="Z49">
@@ -6550,10 +6549,10 @@
       <c r="W50">
         <v>51</v>
       </c>
-      <c r="X50" s="6">
+      <c r="X50" s="1">
         <v>6000</v>
       </c>
-      <c r="Y50" s="7">
+      <c r="Y50" s="6">
         <v>5.1273037763429653E-4</v>
       </c>
       <c r="Z50">
@@ -6656,10 +6655,10 @@
       <c r="W51">
         <v>33</v>
       </c>
-      <c r="X51" s="6">
+      <c r="X51" s="1">
         <v>74000</v>
       </c>
-      <c r="Y51" s="7">
+      <c r="Y51" s="6">
         <v>6.7595759382643901E-3</v>
       </c>
       <c r="Z51">
@@ -6762,10 +6761,10 @@
       <c r="W52">
         <v>24</v>
       </c>
-      <c r="X52" s="6">
+      <c r="X52" s="1">
         <v>8000</v>
       </c>
-      <c r="Y52" s="7">
+      <c r="Y52" s="6">
         <v>7.5184707792282806E-4</v>
       </c>
       <c r="Z52">

--- a/apportion/pop.xlsx
+++ b/apportion/pop.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/user/Google Drive/GitHub/R Functions/apportion/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{234137D1-13F8-6C49-8A76-D68FFAD45B61}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{440BB53F-5830-9C4A-BAEE-630AFF9EB549}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38400" yWindow="500" windowWidth="38400" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="141">
   <si>
     <t>state</t>
   </si>
@@ -428,6 +428,21 @@
   </si>
   <si>
     <t>black_per</t>
+  </si>
+  <si>
+    <t>gov_party</t>
+  </si>
+  <si>
+    <t>R</t>
+  </si>
+  <si>
+    <t>D</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>L</t>
   </si>
 </sst>
 </file>
@@ -1283,7 +1298,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AF52"/>
+  <dimension ref="A1:AG52"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="22" max="22" width="17.1640625" style="4" bestFit="1" customWidth="1"/>
@@ -1291,7 +1306,7 @@
     <col min="24" max="24" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1382,14 +1397,17 @@
       <c r="AD1" t="s">
         <v>124</v>
       </c>
-      <c r="AE1" s="4" t="s">
+      <c r="AE1" t="s">
+        <v>136</v>
+      </c>
+      <c r="AF1" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="AF1" s="5" t="s">
+      <c r="AG1" s="5" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -1487,15 +1505,18 @@
       <c r="AD2">
         <v>43</v>
       </c>
-      <c r="AE2" s="4">
+      <c r="AE2" t="s">
+        <v>137</v>
+      </c>
+      <c r="AF2" s="4">
         <v>1240000</v>
       </c>
-      <c r="AF2" s="5">
-        <f>AE2/D2</f>
+      <c r="AG2" s="5">
+        <f>AF2/D2</f>
         <v>0.2465182772428044</v>
       </c>
     </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -1593,15 +1614,18 @@
       <c r="AD3">
         <v>32</v>
       </c>
-      <c r="AE3" s="4">
+      <c r="AE3" t="s">
+        <v>137</v>
+      </c>
+      <c r="AF3" s="4">
         <v>600000</v>
       </c>
-      <c r="AF3" s="5">
-        <f>AE3/D3</f>
+      <c r="AG3" s="5">
+        <f>AF3/D3</f>
         <v>0.81512768295880478</v>
       </c>
     </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -1699,15 +1723,18 @@
       <c r="AD4">
         <v>25</v>
       </c>
-      <c r="AE4" s="4">
-        <v>0</v>
-      </c>
-      <c r="AF4" s="5">
-        <f>AE4/D4</f>
+      <c r="AE4" t="s">
+        <v>137</v>
+      </c>
+      <c r="AF4" s="4">
+        <v>0</v>
+      </c>
+      <c r="AG4" s="5">
+        <f>AF4/D4</f>
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -1805,15 +1832,18 @@
       <c r="AD5">
         <v>46</v>
       </c>
-      <c r="AE5" s="4">
-        <v>0</v>
-      </c>
-      <c r="AF5" s="5">
-        <f>AE5/D5</f>
+      <c r="AE5" t="s">
+        <v>137</v>
+      </c>
+      <c r="AF5" s="4">
+        <v>0</v>
+      </c>
+      <c r="AG5" s="5">
+        <f>AF5/D5</f>
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -1911,15 +1941,18 @@
       <c r="AD6">
         <v>6</v>
       </c>
-      <c r="AE6" s="4">
+      <c r="AE6" t="s">
+        <v>138</v>
+      </c>
+      <c r="AF6" s="4">
         <v>187000000</v>
       </c>
-      <c r="AF6" s="5">
-        <f>AE6/D6</f>
+      <c r="AG6" s="5">
+        <f>AF6/D6</f>
         <v>4.7249955320998129</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>15</v>
       </c>
@@ -2017,15 +2050,18 @@
       <c r="AD7">
         <v>15</v>
       </c>
-      <c r="AE7" s="4">
+      <c r="AE7" t="s">
+        <v>138</v>
+      </c>
+      <c r="AF7" s="4">
         <v>6000000</v>
       </c>
-      <c r="AF7" s="5">
-        <f>AE7/D7</f>
+      <c r="AG7" s="5">
+        <f>AF7/D7</f>
         <v>1.0376725281905361</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -2123,15 +2159,18 @@
       <c r="AD8">
         <v>9</v>
       </c>
-      <c r="AE8" s="4">
+      <c r="AE8" t="s">
+        <v>138</v>
+      </c>
+      <c r="AF8" s="4">
         <v>500000</v>
       </c>
-      <c r="AF8" s="5">
-        <f>AE8/D8</f>
+      <c r="AG8" s="5">
+        <f>AF8/D8</f>
         <v>0.13856948622314455</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>17</v>
       </c>
@@ -2229,15 +2268,18 @@
       <c r="AD9">
         <v>11</v>
       </c>
-      <c r="AE9" s="4">
-        <v>0</v>
-      </c>
-      <c r="AF9" s="5">
-        <f>AE9/D9</f>
+      <c r="AE9" t="s">
+        <v>138</v>
+      </c>
+      <c r="AF9" s="4">
+        <v>0</v>
+      </c>
+      <c r="AG9" s="5">
+        <f>AF9/D9</f>
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -2334,15 +2376,18 @@
       <c r="AD10">
         <v>1</v>
       </c>
-      <c r="AE10" s="4">
-        <v>0</v>
-      </c>
-      <c r="AF10" s="5">
-        <f>AE10/D10</f>
+      <c r="AE10" t="s">
+        <v>139</v>
+      </c>
+      <c r="AF10" s="4">
+        <v>0</v>
+      </c>
+      <c r="AG10" s="5">
+        <f>AF10/D10</f>
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -2440,15 +2485,18 @@
       <c r="AD11">
         <v>28</v>
       </c>
-      <c r="AE11" s="4">
-        <v>0</v>
-      </c>
-      <c r="AF11" s="5">
-        <f>AE11/D11</f>
+      <c r="AE11" t="s">
+        <v>137</v>
+      </c>
+      <c r="AF11" s="4">
+        <v>0</v>
+      </c>
+      <c r="AG11" s="5">
+        <f>AF11/D11</f>
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>20</v>
       </c>
@@ -2546,15 +2594,18 @@
       <c r="AD12">
         <v>26</v>
       </c>
-      <c r="AE12" s="4">
+      <c r="AE12" t="s">
+        <v>137</v>
+      </c>
+      <c r="AF12" s="4">
         <v>3750886</v>
       </c>
-      <c r="AF12" s="5">
-        <f>AE12/D12</f>
+      <c r="AG12" s="5">
+        <f>AF12/D12</f>
         <v>0.34972402569855093</v>
       </c>
     </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>21</v>
       </c>
@@ -2652,15 +2703,18 @@
       <c r="AD13">
         <v>5</v>
       </c>
-      <c r="AE13" s="4">
+      <c r="AE13" t="s">
+        <v>138</v>
+      </c>
+      <c r="AF13" s="4">
         <v>750000</v>
       </c>
-      <c r="AF13" s="5">
-        <f>AE13/D13</f>
+      <c r="AG13" s="5">
+        <f>AF13/D13</f>
         <v>0.51365043143211908</v>
       </c>
     </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>22</v>
       </c>
@@ -2758,15 +2812,18 @@
       <c r="AD14">
         <v>47</v>
       </c>
-      <c r="AE14" s="4">
-        <v>0</v>
-      </c>
-      <c r="AF14" s="5">
-        <f>AE14/D14</f>
+      <c r="AE14" t="s">
+        <v>137</v>
+      </c>
+      <c r="AF14" s="4">
+        <v>0</v>
+      </c>
+      <c r="AG14" s="5">
+        <f>AF14/D14</f>
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>23</v>
       </c>
@@ -2864,15 +2921,18 @@
       <c r="AD15">
         <v>12</v>
       </c>
-      <c r="AE15" s="4">
+      <c r="AE15" t="s">
+        <v>138</v>
+      </c>
+      <c r="AF15" s="4">
         <v>30500000</v>
       </c>
-      <c r="AF15" s="5">
-        <f>AE15/D15</f>
+      <c r="AG15" s="5">
+        <f>AF15/D15</f>
         <v>2.3785869774000701</v>
       </c>
     </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>24</v>
       </c>
@@ -2970,15 +3030,18 @@
       <c r="AD16">
         <v>36</v>
       </c>
-      <c r="AE16" s="4">
-        <v>0</v>
-      </c>
-      <c r="AF16" s="5">
-        <f>AE16/D16</f>
+      <c r="AE16" t="s">
+        <v>137</v>
+      </c>
+      <c r="AF16" s="4">
+        <v>0</v>
+      </c>
+      <c r="AG16" s="5">
+        <f>AF16/D16</f>
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>25</v>
       </c>
@@ -3076,15 +3139,18 @@
       <c r="AD17">
         <v>31</v>
       </c>
-      <c r="AE17" s="4">
-        <v>0</v>
-      </c>
-      <c r="AF17" s="5">
-        <f>AE17/D17</f>
+      <c r="AE17" t="s">
+        <v>137</v>
+      </c>
+      <c r="AF17" s="4">
+        <v>0</v>
+      </c>
+      <c r="AG17" s="5">
+        <f>AF17/D17</f>
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>26</v>
       </c>
@@ -3182,15 +3248,18 @@
       <c r="AD18">
         <v>34</v>
       </c>
-      <c r="AE18" s="4">
-        <v>0</v>
-      </c>
-      <c r="AF18" s="5">
-        <f>AE18/D18</f>
+      <c r="AE18" t="s">
+        <v>138</v>
+      </c>
+      <c r="AF18" s="4">
+        <v>0</v>
+      </c>
+      <c r="AG18" s="5">
+        <f>AF18/D18</f>
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>27</v>
       </c>
@@ -3288,15 +3357,18 @@
       <c r="AD19">
         <v>44</v>
       </c>
-      <c r="AE19" s="4">
-        <v>0</v>
-      </c>
-      <c r="AF19" s="5">
-        <f>AE19/D19</f>
+      <c r="AE19" t="s">
+        <v>138</v>
+      </c>
+      <c r="AF19" s="4">
+        <v>0</v>
+      </c>
+      <c r="AG19" s="5">
+        <f>AF19/D19</f>
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>28</v>
       </c>
@@ -3394,15 +3466,18 @@
       <c r="AD20">
         <v>39</v>
       </c>
-      <c r="AE20" s="4">
-        <v>0</v>
-      </c>
-      <c r="AF20" s="5">
-        <f>AE20/D20</f>
+      <c r="AE20" t="s">
+        <v>140</v>
+      </c>
+      <c r="AF20" s="4">
+        <v>0</v>
+      </c>
+      <c r="AG20" s="5">
+        <f>AF20/D20</f>
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>29</v>
       </c>
@@ -3500,15 +3575,18 @@
       <c r="AD21">
         <v>18</v>
       </c>
-      <c r="AE21" s="4">
-        <v>0</v>
-      </c>
-      <c r="AF21" s="5">
-        <f>AE21/D21</f>
+      <c r="AE21" t="s">
+        <v>138</v>
+      </c>
+      <c r="AF21" s="4">
+        <v>0</v>
+      </c>
+      <c r="AG21" s="5">
+        <f>AF21/D21</f>
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>30</v>
       </c>
@@ -3606,15 +3684,18 @@
       <c r="AD22">
         <v>4</v>
       </c>
-      <c r="AE22" s="4">
+      <c r="AE22" t="s">
+        <v>137</v>
+      </c>
+      <c r="AF22" s="4">
         <v>5000000</v>
       </c>
-      <c r="AF22" s="5">
-        <f>AE22/D22</f>
+      <c r="AG22" s="5">
+        <f>AF22/D22</f>
         <v>0.80837110312584171</v>
       </c>
     </row>
-    <row r="23" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>31</v>
       </c>
@@ -3712,15 +3793,18 @@
       <c r="AD23">
         <v>3</v>
       </c>
-      <c r="AE23" s="4">
+      <c r="AE23" t="s">
+        <v>137</v>
+      </c>
+      <c r="AF23" s="4">
         <v>6650000</v>
       </c>
-      <c r="AF23" s="5">
-        <f>AE23/D23</f>
+      <c r="AG23" s="5">
+        <f>AF23/D23</f>
         <v>0.94547939288564431</v>
       </c>
     </row>
-    <row r="24" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>32</v>
       </c>
@@ -3818,15 +3902,18 @@
       <c r="AD24">
         <v>21</v>
       </c>
-      <c r="AE24" s="4">
+      <c r="AE24" t="s">
+        <v>138</v>
+      </c>
+      <c r="AF24" s="4">
         <v>16000000</v>
       </c>
-      <c r="AF24" s="5">
-        <f>AE24/D24</f>
+      <c r="AG24" s="5">
+        <f>AF24/D24</f>
         <v>1.5866024119133215</v>
       </c>
     </row>
-    <row r="25" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>33</v>
       </c>
@@ -3924,15 +4011,18 @@
       <c r="AD25">
         <v>20</v>
       </c>
-      <c r="AE25" s="4">
+      <c r="AE25" t="s">
+        <v>138</v>
+      </c>
+      <c r="AF25" s="4">
         <v>2170000</v>
       </c>
-      <c r="AF25" s="5">
-        <f>AE25/D25</f>
+      <c r="AG25" s="5">
+        <f>AF25/D25</f>
         <v>0.38005153288619192</v>
       </c>
     </row>
-    <row r="26" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>34</v>
       </c>
@@ -4030,15 +4120,18 @@
       <c r="AD26">
         <v>37</v>
       </c>
-      <c r="AE26" s="4">
+      <c r="AE26" t="s">
+        <v>137</v>
+      </c>
+      <c r="AF26" s="4">
         <v>400000</v>
       </c>
-      <c r="AF26" s="5">
-        <f>AE26/D26</f>
+      <c r="AG26" s="5">
+        <f>AF26/D26</f>
         <v>0.13495668227890553</v>
       </c>
     </row>
-    <row r="27" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>35</v>
       </c>
@@ -4136,15 +4229,18 @@
       <c r="AD27">
         <v>35</v>
       </c>
-      <c r="AE27" s="4">
+      <c r="AE27" t="s">
+        <v>137</v>
+      </c>
+      <c r="AF27" s="4">
         <v>501650</v>
       </c>
-      <c r="AF27" s="5">
-        <f>AE27/D27</f>
+      <c r="AG27" s="5">
+        <f>AF27/D27</f>
         <v>8.1432973593250052E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>36</v>
       </c>
@@ -4242,15 +4338,18 @@
       <c r="AD28">
         <v>38</v>
       </c>
-      <c r="AE28" s="4">
+      <c r="AE28" t="s">
+        <v>138</v>
+      </c>
+      <c r="AF28" s="4">
         <v>635500</v>
       </c>
-      <c r="AF28" s="5">
-        <f>AE28/D28</f>
+      <c r="AG28" s="5">
+        <f>AF28/D28</f>
         <v>0.58549465776432252</v>
       </c>
     </row>
-    <row r="29" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>37</v>
       </c>
@@ -4348,13 +4447,16 @@
       <c r="AD29">
         <v>40</v>
       </c>
-      <c r="AE29" s="4"/>
-      <c r="AF29" s="5">
-        <f>AE29/D29</f>
+      <c r="AE29" t="s">
+        <v>137</v>
+      </c>
+      <c r="AF29" s="4"/>
+      <c r="AG29" s="5">
+        <f>AF29/D29</f>
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>38</v>
       </c>
@@ -4452,15 +4554,18 @@
       <c r="AD30">
         <v>22</v>
       </c>
-      <c r="AE30" s="4">
+      <c r="AE30" t="s">
+        <v>138</v>
+      </c>
+      <c r="AF30" s="4">
         <v>5000000</v>
       </c>
-      <c r="AF30" s="5">
-        <f>AE30/D30</f>
+      <c r="AG30" s="5">
+        <f>AF30/D30</f>
         <v>1.6085125055413256</v>
       </c>
     </row>
-    <row r="31" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>39</v>
       </c>
@@ -4558,13 +4663,16 @@
       <c r="AD31">
         <v>19</v>
       </c>
-      <c r="AE31" s="4"/>
-      <c r="AF31" s="5">
-        <f>AE31/D31</f>
+      <c r="AE31" t="s">
+        <v>137</v>
+      </c>
+      <c r="AF31" s="4"/>
+      <c r="AG31" s="5">
+        <f>AF31/D31</f>
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>40</v>
       </c>
@@ -4662,15 +4770,18 @@
       <c r="AD32">
         <v>14</v>
       </c>
-      <c r="AE32" s="4">
+      <c r="AE32" t="s">
+        <v>138</v>
+      </c>
+      <c r="AF32" s="4">
         <v>9000000</v>
       </c>
-      <c r="AF32" s="5">
-        <f>AE32/D32</f>
+      <c r="AG32" s="5">
+        <f>AF32/D32</f>
         <v>0.96831532392353192</v>
       </c>
     </row>
-    <row r="33" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>41</v>
       </c>
@@ -4768,15 +4879,18 @@
       <c r="AD33">
         <v>16</v>
       </c>
-      <c r="AE33" s="4">
+      <c r="AE33" t="s">
+        <v>138</v>
+      </c>
+      <c r="AF33" s="4">
         <v>11500000</v>
       </c>
-      <c r="AF33" s="5">
-        <f>AE33/D33</f>
+      <c r="AG33" s="5">
+        <f>AF33/D33</f>
         <v>5.4239654375489339</v>
       </c>
     </row>
-    <row r="34" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>42</v>
       </c>
@@ -4874,15 +4988,18 @@
       <c r="AD34">
         <v>7</v>
       </c>
-      <c r="AE34" s="4">
+      <c r="AE34" t="s">
+        <v>138</v>
+      </c>
+      <c r="AF34" s="4">
         <v>20000000</v>
       </c>
-      <c r="AF34" s="5">
-        <f>AE34/D34</f>
+      <c r="AG34" s="5">
+        <f>AF34/D34</f>
         <v>0.98932757927222192</v>
       </c>
     </row>
-    <row r="35" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>43</v>
       </c>
@@ -4980,15 +5097,18 @@
       <c r="AD35">
         <v>27</v>
       </c>
-      <c r="AE35" s="4">
-        <v>0</v>
-      </c>
-      <c r="AF35" s="5">
-        <f>AE35/D35</f>
+      <c r="AE35" t="s">
+        <v>138</v>
+      </c>
+      <c r="AF35" s="4">
+        <v>0</v>
+      </c>
+      <c r="AG35" s="5">
+        <f>AF35/D35</f>
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>44</v>
       </c>
@@ -5086,15 +5206,18 @@
       <c r="AD36">
         <v>49</v>
       </c>
-      <c r="AE36" s="4">
+      <c r="AE36" t="s">
+        <v>137</v>
+      </c>
+      <c r="AF36" s="4">
         <v>1000000</v>
       </c>
-      <c r="AF36" s="5">
-        <f>AE36/D36</f>
+      <c r="AG36" s="5">
+        <f>AF36/D36</f>
         <v>1.2825412785910515</v>
       </c>
     </row>
-    <row r="37" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>45</v>
       </c>
@@ -5192,15 +5315,18 @@
       <c r="AD37">
         <v>30</v>
       </c>
-      <c r="AE37" s="4">
-        <v>0</v>
-      </c>
-      <c r="AF37" s="5">
-        <f>AE37/D37</f>
+      <c r="AE37" t="s">
+        <v>137</v>
+      </c>
+      <c r="AF37" s="4">
+        <v>0</v>
+      </c>
+      <c r="AG37" s="5">
+        <f>AF37/D37</f>
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>46</v>
       </c>
@@ -5298,15 +5424,18 @@
       <c r="AD38">
         <v>48</v>
       </c>
-      <c r="AE38" s="4">
-        <v>0</v>
-      </c>
-      <c r="AF38" s="5">
-        <f>AE38/D38</f>
+      <c r="AE38" t="s">
+        <v>137</v>
+      </c>
+      <c r="AF38" s="4">
+        <v>0</v>
+      </c>
+      <c r="AG38" s="5">
+        <f>AF38/D38</f>
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>47</v>
       </c>
@@ -5404,15 +5533,18 @@
       <c r="AD39">
         <v>13</v>
       </c>
-      <c r="AE39" s="4">
+      <c r="AE39" t="s">
+        <v>138</v>
+      </c>
+      <c r="AF39" s="4">
         <v>7730772</v>
       </c>
-      <c r="AF39" s="5">
-        <f>AE39/D39</f>
+      <c r="AG39" s="5">
+        <f>AF39/D39</f>
         <v>1.8226504774254391</v>
       </c>
     </row>
-    <row r="40" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>48</v>
       </c>
@@ -5510,15 +5642,18 @@
       <c r="AD40">
         <v>23</v>
       </c>
-      <c r="AE40" s="4">
+      <c r="AE40" t="s">
+        <v>138</v>
+      </c>
+      <c r="AF40" s="4">
         <v>4000000</v>
       </c>
-      <c r="AF40" s="5">
-        <f>AE40/D40</f>
+      <c r="AG40" s="5">
+        <f>AF40/D40</f>
         <v>0.30741223150231434</v>
       </c>
     </row>
-    <row r="41" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>49</v>
       </c>
@@ -5616,15 +5751,18 @@
       <c r="AD41">
         <v>8</v>
       </c>
-      <c r="AE41" s="4">
+      <c r="AE41" t="s">
+        <v>138</v>
+      </c>
+      <c r="AF41" s="4">
         <v>500000</v>
       </c>
-      <c r="AF41" s="5">
-        <f>AE41/D41</f>
+      <c r="AG41" s="5">
+        <f>AF41/D41</f>
         <v>0.45530581525693364</v>
       </c>
     </row>
-    <row r="42" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>50</v>
       </c>
@@ -5722,15 +5860,18 @@
       <c r="AD42">
         <v>33</v>
       </c>
-      <c r="AE42" s="4">
-        <v>0</v>
-      </c>
-      <c r="AF42" s="5">
-        <f>AE42/D42</f>
+      <c r="AE42" t="s">
+        <v>137</v>
+      </c>
+      <c r="AF42" s="4">
+        <v>0</v>
+      </c>
+      <c r="AG42" s="5">
+        <f>AF42/D42</f>
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>51</v>
       </c>
@@ -5828,15 +5969,18 @@
       <c r="AD43">
         <v>45</v>
       </c>
-      <c r="AE43" s="4">
-        <v>0</v>
-      </c>
-      <c r="AF43" s="5">
-        <f>AE43/D43</f>
+      <c r="AE43" t="s">
+        <v>137</v>
+      </c>
+      <c r="AF43" s="4">
+        <v>0</v>
+      </c>
+      <c r="AG43" s="5">
+        <f>AF43/D43</f>
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>52</v>
       </c>
@@ -5934,15 +6078,18 @@
       <c r="AD44">
         <v>42</v>
       </c>
-      <c r="AE44" s="4">
-        <v>0</v>
-      </c>
-      <c r="AF44" s="5">
-        <f>AE44/D44</f>
+      <c r="AE44" t="s">
+        <v>137</v>
+      </c>
+      <c r="AF44" s="4">
+        <v>0</v>
+      </c>
+      <c r="AG44" s="5">
+        <f>AF44/D44</f>
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>53</v>
       </c>
@@ -6040,15 +6187,18 @@
       <c r="AD45">
         <v>29</v>
       </c>
-      <c r="AE45" s="4">
-        <v>0</v>
-      </c>
-      <c r="AF45" s="5">
-        <f>AE45/D45</f>
+      <c r="AE45" t="s">
+        <v>137</v>
+      </c>
+      <c r="AF45" s="4">
+        <v>0</v>
+      </c>
+      <c r="AG45" s="5">
+        <f>AF45/D45</f>
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>54</v>
       </c>
@@ -6146,15 +6296,18 @@
       <c r="AD46">
         <v>41</v>
       </c>
-      <c r="AE46" s="4">
+      <c r="AE46" t="s">
+        <v>137</v>
+      </c>
+      <c r="AF46" s="4">
         <v>1000000</v>
       </c>
-      <c r="AF46" s="5">
-        <f>AE46/D46</f>
+      <c r="AG46" s="5">
+        <f>AF46/D46</f>
         <v>0.30532001812379628</v>
       </c>
     </row>
-    <row r="47" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>55</v>
       </c>
@@ -6252,15 +6405,18 @@
       <c r="AD47">
         <v>2</v>
       </c>
-      <c r="AE47" s="4">
-        <v>0</v>
-      </c>
-      <c r="AF47" s="5">
-        <f>AE47/D47</f>
+      <c r="AE47" t="s">
+        <v>137</v>
+      </c>
+      <c r="AF47" s="4">
+        <v>0</v>
+      </c>
+      <c r="AG47" s="5">
+        <f>AF47/D47</f>
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>56</v>
       </c>
@@ -6358,15 +6514,18 @@
       <c r="AD48">
         <v>17</v>
       </c>
-      <c r="AE48" s="4">
+      <c r="AE48" t="s">
+        <v>138</v>
+      </c>
+      <c r="AF48" s="4">
         <v>1500000</v>
       </c>
-      <c r="AF48" s="5">
-        <f>AE48/D48</f>
+      <c r="AG48" s="5">
+        <f>AF48/D48</f>
         <v>0.17331939691320464</v>
       </c>
     </row>
-    <row r="49" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>57</v>
       </c>
@@ -6464,15 +6623,18 @@
       <c r="AD49">
         <v>10</v>
       </c>
-      <c r="AE49" s="4">
+      <c r="AE49" t="s">
+        <v>138</v>
+      </c>
+      <c r="AF49" s="4">
         <v>15464000</v>
       </c>
-      <c r="AF49" s="5">
-        <f>AE49/D49</f>
+      <c r="AG49" s="5">
+        <f>AF49/D49</f>
         <v>2.0041612525541264</v>
       </c>
     </row>
-    <row r="50" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>58</v>
       </c>
@@ -6570,15 +6732,18 @@
       <c r="AD50">
         <v>50</v>
       </c>
-      <c r="AE50" s="4">
+      <c r="AE50" t="s">
+        <v>137</v>
+      </c>
+      <c r="AF50" s="4">
         <v>1000000</v>
       </c>
-      <c r="AF50" s="5">
-        <f>AE50/D50</f>
+      <c r="AG50" s="5">
+        <f>AF50/D50</f>
         <v>0.55708909804489581</v>
       </c>
     </row>
-    <row r="51" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>59</v>
       </c>
@@ -6676,15 +6841,18 @@
       <c r="AD51">
         <v>24</v>
       </c>
-      <c r="AE51" s="4">
+      <c r="AE51" t="s">
+        <v>138</v>
+      </c>
+      <c r="AF51" s="4">
         <v>1000000</v>
       </c>
-      <c r="AF51" s="5">
-        <f>AE51/D51</f>
+      <c r="AG51" s="5">
+        <f>AF51/D51</f>
         <v>0.16956415061162636</v>
       </c>
     </row>
-    <row r="52" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>60</v>
       </c>
@@ -6779,6 +6947,9 @@
       <c r="AC52" s="5" t="e">
         <f>#REF!/D52</f>
         <v>#REF!</v>
+      </c>
+      <c r="AE52" t="s">
+        <v>137</v>
       </c>
     </row>
   </sheetData>

--- a/apportion/pop.xlsx
+++ b/apportion/pop.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/user/Google Drive/GitHub/R Functions/apportion/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{440BB53F-5830-9C4A-BAEE-630AFF9EB549}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F370DB1-A421-2345-9BC1-F456D1A0699A}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38400" yWindow="500" windowWidth="38400" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="35840" windowHeight="21900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="pop" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="142">
   <si>
     <t>state</t>
   </si>
@@ -443,6 +443,9 @@
   </si>
   <si>
     <t>L</t>
+  </si>
+  <si>
+    <t>pep_census_diff</t>
   </si>
 </sst>
 </file>
@@ -452,7 +455,7 @@
   <numFmts count="3">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="0.000"/>
-    <numFmt numFmtId="166" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
   <fonts count="18" x14ac:knownFonts="1">
     <font>
@@ -940,7 +943,7 @@
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="43" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="44">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1298,15 +1301,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AG52"/>
+  <dimension ref="A1:AH53"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="22" max="22" width="17.1640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="10.83203125" style="5"/>
-    <col min="24" max="24" width="10.83203125" style="1"/>
+    <col min="23" max="23" width="17.1640625" style="4" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="10.83203125" style="5"/>
+    <col min="25" max="25" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1323,91 +1326,94 @@
         <v>117</v>
       </c>
       <c r="F1" t="s">
+        <v>141</v>
+      </c>
+      <c r="G1" t="s">
         <v>7</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>114</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>61</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>116</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>115</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>118</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>3</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>4</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>5</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>6</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>119</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>125</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>126</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>120</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U1" t="s">
         <v>121</v>
       </c>
-      <c r="U1" t="s">
+      <c r="V1" t="s">
         <v>122</v>
       </c>
-      <c r="V1" t="s">
+      <c r="W1" t="s">
         <v>129</v>
       </c>
-      <c r="W1" t="s">
+      <c r="X1" t="s">
         <v>132</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="Z1" t="s">
         <v>131</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AA1" t="s">
         <v>133</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AB1" t="s">
         <v>134</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AC1" t="s">
         <v>135</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AD1" t="s">
         <v>123</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AE1" t="s">
         <v>124</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AF1" t="s">
         <v>136</v>
       </c>
-      <c r="AF1" s="4" t="s">
+      <c r="AG1" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="AG1" s="5" t="s">
+      <c r="AH1" s="5" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="2" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -1424,99 +1430,103 @@
         <v>4921532</v>
       </c>
       <c r="F2">
-        <f t="shared" ref="F2:F33" si="0">D2-C2</f>
+        <f>D2-E2</f>
+        <v>108521</v>
+      </c>
+      <c r="G2">
+        <f t="shared" ref="G2:G33" si="0">D2-C2</f>
         <v>227071</v>
       </c>
-      <c r="G2">
-        <f t="shared" ref="G2:G33" si="1">F2/C2*100</f>
+      <c r="H2">
+        <f t="shared" ref="H2:H33" si="1">G2/C2*100</f>
         <v>4.7277087442759518</v>
       </c>
-      <c r="H2" s="2">
-        <f t="shared" ref="H2:H33" si="2">(D2-E2)/E2</f>
+      <c r="I2" s="2">
+        <f t="shared" ref="I2:I33" si="2">(D2-E2)/E2</f>
         <v>2.2050247768377815E-2</v>
-      </c>
-      <c r="I2">
-        <v>7</v>
       </c>
       <c r="J2">
         <v>7</v>
       </c>
       <c r="K2">
-        <f t="shared" ref="K2:K33" si="3">J2-I2</f>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L2">
+        <f t="shared" ref="L2:L33" si="3">K2-J2</f>
+        <v>0</v>
+      </c>
+      <c r="M2">
         <v>9</v>
       </c>
-      <c r="M2">
-        <f t="shared" ref="M2:M9" si="4">J2+2</f>
+      <c r="N2">
+        <f t="shared" ref="N2:N9" si="4">K2+2</f>
         <v>9</v>
       </c>
-      <c r="N2">
-        <f t="shared" ref="N2:N9" si="5">M2-L2</f>
-        <v>0</v>
-      </c>
-      <c r="O2" t="s">
+      <c r="O2">
+        <f t="shared" ref="O2:O9" si="5">N2-M2</f>
+        <v>0</v>
+      </c>
+      <c r="P2" t="s">
         <v>9</v>
       </c>
-      <c r="P2">
+      <c r="Q2">
         <v>3364</v>
       </c>
-      <c r="Q2">
+      <c r="R2">
         <v>56</v>
       </c>
-      <c r="R2">
+      <c r="S2">
         <v>7</v>
       </c>
-      <c r="S2" s="3">
+      <c r="T2" s="3">
         <v>50645.33</v>
       </c>
-      <c r="T2">
-        <f t="shared" ref="T2:T33" si="6">D2/S2</f>
+      <c r="U2">
+        <f t="shared" ref="U2:U33" si="6">D2/T2</f>
         <v>99.319186981307055</v>
       </c>
-      <c r="U2">
+      <c r="V2">
         <v>28</v>
       </c>
-      <c r="V2">
+      <c r="W2">
         <v>4.5</v>
       </c>
-      <c r="W2">
+      <c r="X2">
         <v>40</v>
       </c>
-      <c r="X2" s="1">
+      <c r="Y2" s="1">
         <v>60000</v>
       </c>
-      <c r="Y2" s="6">
+      <c r="Z2" s="6">
         <v>5.4854633708831318E-3</v>
       </c>
-      <c r="Z2">
+      <c r="AA2">
         <v>1319551</v>
       </c>
-      <c r="AA2">
+      <c r="AB2">
         <v>8216</v>
       </c>
-      <c r="AB2">
+      <c r="AC2">
         <v>26.9</v>
       </c>
-      <c r="AC2">
+      <c r="AD2">
         <v>0.3708863</v>
       </c>
-      <c r="AD2">
+      <c r="AE2">
         <v>43</v>
       </c>
-      <c r="AE2" t="s">
+      <c r="AF2" t="s">
         <v>137</v>
       </c>
-      <c r="AF2" s="4">
+      <c r="AG2" s="4">
         <v>1240000</v>
       </c>
-      <c r="AG2" s="5">
-        <f>AF2/D2</f>
+      <c r="AH2" s="5">
+        <f t="shared" ref="AH2:AH33" si="7">AG2/D2</f>
         <v>0.2465182772428044</v>
       </c>
     </row>
-    <row r="3" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -1533,99 +1543,103 @@
         <v>731158</v>
       </c>
       <c r="F3">
+        <f t="shared" ref="F3:F52" si="8">D3-E3</f>
+        <v>4923</v>
+      </c>
+      <c r="G3">
         <f t="shared" si="0"/>
         <v>14558</v>
       </c>
-      <c r="G3">
+      <c r="H3">
         <f t="shared" si="1"/>
         <v>2.0176764981850894</v>
       </c>
-      <c r="H3" s="2">
+      <c r="I3" s="2">
         <f t="shared" si="2"/>
         <v>6.7331548037496683E-3</v>
       </c>
-      <c r="I3">
-        <v>1</v>
-      </c>
       <c r="J3">
         <v>1</v>
       </c>
       <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L3">
+      <c r="M3">
         <v>3</v>
       </c>
-      <c r="M3">
+      <c r="N3">
         <f t="shared" si="4"/>
         <v>3</v>
       </c>
-      <c r="N3">
+      <c r="O3">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="O3" t="s">
+      <c r="P3" t="s">
         <v>9</v>
       </c>
-      <c r="P3">
+      <c r="Q3">
         <v>141</v>
       </c>
-      <c r="Q3">
+      <c r="R3">
         <v>6</v>
       </c>
-      <c r="R3">
-        <v>0</v>
-      </c>
-      <c r="S3" s="3">
+      <c r="S3">
+        <v>0</v>
+      </c>
+      <c r="T3" s="3">
         <v>570640.94999999995</v>
       </c>
-      <c r="T3">
+      <c r="U3">
         <f t="shared" si="6"/>
         <v>1.289919694687176</v>
       </c>
-      <c r="U3">
+      <c r="V3">
         <v>51</v>
       </c>
-      <c r="V3">
+      <c r="W3">
         <v>7.2</v>
       </c>
-      <c r="W3">
+      <c r="X3">
         <v>31</v>
       </c>
-      <c r="X3" s="1">
+      <c r="Y3" s="1">
         <v>9000</v>
       </c>
-      <c r="Y3" s="6">
+      <c r="Z3" s="6">
         <v>8.1422119017382423E-4</v>
       </c>
-      <c r="Z3">
+      <c r="AA3">
         <v>22551</v>
       </c>
-      <c r="AA3">
+      <c r="AB3">
         <v>1965</v>
       </c>
-      <c r="AB3">
+      <c r="AC3">
         <v>3.1</v>
       </c>
-      <c r="AC3">
+      <c r="AD3">
         <v>0.44738149999999999</v>
       </c>
-      <c r="AD3">
+      <c r="AE3">
         <v>32</v>
       </c>
-      <c r="AE3" t="s">
+      <c r="AF3" t="s">
         <v>137</v>
       </c>
-      <c r="AF3" s="4">
+      <c r="AG3" s="4">
         <v>600000</v>
       </c>
-      <c r="AG3" s="5">
-        <f>AF3/D3</f>
+      <c r="AH3" s="5">
+        <f t="shared" si="7"/>
         <v>0.81512768295880478</v>
       </c>
     </row>
-    <row r="4" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -1642,99 +1656,103 @@
         <v>7421401</v>
       </c>
       <c r="F4">
+        <f t="shared" si="8"/>
+        <v>-262478</v>
+      </c>
+      <c r="G4">
         <f t="shared" si="0"/>
         <v>746223</v>
       </c>
-      <c r="G4">
+      <c r="H4">
         <f t="shared" si="1"/>
         <v>11.636642911722053</v>
       </c>
-      <c r="H4" s="2">
+      <c r="I4" s="2">
         <f t="shared" si="2"/>
         <v>-3.5367715610570026E-2</v>
       </c>
-      <c r="I4">
-        <v>9</v>
-      </c>
       <c r="J4">
         <v>9</v>
       </c>
       <c r="K4">
+        <v>9</v>
+      </c>
+      <c r="L4">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L4">
+      <c r="M4">
         <v>11</v>
       </c>
-      <c r="M4">
+      <c r="N4">
         <f t="shared" si="4"/>
         <v>11</v>
       </c>
-      <c r="N4">
+      <c r="O4">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="O4" t="s">
+      <c r="P4" t="s">
         <v>12</v>
       </c>
-      <c r="P4">
+      <c r="Q4">
         <v>1413</v>
       </c>
-      <c r="Q4">
+      <c r="R4">
         <v>29</v>
       </c>
-      <c r="R4">
+      <c r="S4">
         <v>5</v>
       </c>
-      <c r="S4" s="3">
+      <c r="T4" s="3">
         <v>113594.08</v>
       </c>
-      <c r="T4">
+      <c r="U4">
         <f t="shared" si="6"/>
         <v>63.021972623925471</v>
       </c>
-      <c r="U4">
+      <c r="V4">
         <v>34</v>
       </c>
-      <c r="V4">
+      <c r="W4">
         <v>31.7</v>
       </c>
-      <c r="W4">
+      <c r="X4">
         <v>4</v>
       </c>
-      <c r="X4" s="1">
+      <c r="Y4" s="1">
         <v>281000</v>
       </c>
-      <c r="Y4" s="6">
+      <c r="Z4" s="6">
         <v>2.5634192618307336E-2</v>
       </c>
-      <c r="Z4">
+      <c r="AA4">
         <v>343729</v>
       </c>
-      <c r="AA4">
+      <c r="AB4">
         <v>7680</v>
       </c>
-      <c r="AB4">
+      <c r="AC4">
         <v>4.7</v>
       </c>
-      <c r="AC4">
+      <c r="AD4">
         <v>0.50156829999999997</v>
       </c>
-      <c r="AD4">
+      <c r="AE4">
         <v>25</v>
       </c>
-      <c r="AE4" t="s">
+      <c r="AF4" t="s">
         <v>137</v>
       </c>
-      <c r="AF4" s="4">
-        <v>0</v>
-      </c>
-      <c r="AG4" s="5">
-        <f>AF4/D4</f>
+      <c r="AG4" s="4">
+        <v>0</v>
+      </c>
+      <c r="AH4" s="5">
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -1751,99 +1769,103 @@
         <v>3030522</v>
       </c>
       <c r="F5">
+        <f t="shared" si="8"/>
+        <v>-16766</v>
+      </c>
+      <c r="G5">
         <f t="shared" si="0"/>
         <v>87527</v>
       </c>
-      <c r="G5">
+      <c r="H5">
         <f t="shared" si="1"/>
         <v>2.9911192869730976</v>
       </c>
-      <c r="H5" s="2">
+      <c r="I5" s="2">
         <f t="shared" si="2"/>
         <v>-5.5323802302045654E-3</v>
       </c>
-      <c r="I5">
-        <v>4</v>
-      </c>
       <c r="J5">
         <v>4</v>
       </c>
       <c r="K5">
+        <v>4</v>
+      </c>
+      <c r="L5">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L5">
+      <c r="M5">
         <v>6</v>
       </c>
-      <c r="M5">
+      <c r="N5">
         <f t="shared" si="4"/>
         <v>6</v>
       </c>
-      <c r="N5">
+      <c r="O5">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="O5" t="s">
+      <c r="P5" t="s">
         <v>9</v>
       </c>
-      <c r="P5">
+      <c r="Q5">
         <v>614</v>
       </c>
-      <c r="Q5">
+      <c r="R5">
         <v>10</v>
       </c>
-      <c r="R5">
+      <c r="S5">
         <v>2</v>
       </c>
-      <c r="S5" s="3">
+      <c r="T5" s="3">
         <v>52035.48</v>
       </c>
-      <c r="T5">
+      <c r="U5">
         <f t="shared" si="6"/>
         <v>57.917328714946031</v>
       </c>
-      <c r="U5">
+      <c r="V5">
         <v>35</v>
       </c>
-      <c r="V5">
+      <c r="W5">
         <v>7.7</v>
       </c>
-      <c r="W5">
+      <c r="X5">
         <v>30</v>
       </c>
-      <c r="X5" s="1">
+      <c r="Y5" s="1">
         <v>58000</v>
       </c>
-      <c r="Y5" s="6">
+      <c r="Z5" s="6">
         <v>5.3074451728820585E-3</v>
       </c>
-      <c r="Z5">
+      <c r="AA5">
         <v>467468</v>
       </c>
-      <c r="AA5">
+      <c r="AB5">
         <v>6259</v>
       </c>
-      <c r="AB5">
+      <c r="AC5">
         <v>15.5</v>
       </c>
-      <c r="AC5">
+      <c r="AD5">
         <v>0.35787570000000002</v>
       </c>
-      <c r="AD5">
+      <c r="AE5">
         <v>46</v>
       </c>
-      <c r="AE5" t="s">
+      <c r="AF5" t="s">
         <v>137</v>
       </c>
-      <c r="AF5" s="4">
-        <v>0</v>
-      </c>
-      <c r="AG5" s="5">
-        <f>AF5/D5</f>
+      <c r="AG5" s="4">
+        <v>0</v>
+      </c>
+      <c r="AH5" s="5">
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -1860,99 +1882,103 @@
         <v>39368078</v>
       </c>
       <c r="F6">
+        <f t="shared" si="8"/>
+        <v>208679</v>
+      </c>
+      <c r="G6">
         <f t="shared" si="0"/>
         <v>2234768</v>
       </c>
-      <c r="G6">
+      <c r="H6">
         <f t="shared" si="1"/>
         <v>5.9845981958807819</v>
       </c>
-      <c r="H6" s="2">
+      <c r="I6" s="2">
         <f t="shared" si="2"/>
         <v>5.3007159760250422E-3</v>
       </c>
-      <c r="I6">
+      <c r="J6">
         <v>53</v>
       </c>
-      <c r="J6">
+      <c r="K6">
         <v>52</v>
       </c>
-      <c r="K6">
+      <c r="L6">
         <f t="shared" si="3"/>
         <v>-1</v>
       </c>
-      <c r="L6">
+      <c r="M6">
         <v>55</v>
       </c>
-      <c r="M6">
+      <c r="N6">
         <f t="shared" si="4"/>
         <v>54</v>
       </c>
-      <c r="N6">
+      <c r="O6">
         <f t="shared" si="5"/>
         <v>-1</v>
       </c>
-      <c r="O6" t="s">
+      <c r="P6" t="s">
         <v>12</v>
       </c>
-      <c r="P6">
+      <c r="Q6">
         <v>8155</v>
       </c>
-      <c r="Q6">
+      <c r="R6">
         <v>172</v>
       </c>
-      <c r="R6">
-        <v>0</v>
-      </c>
-      <c r="S6" s="3">
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="T6" s="3">
         <v>155779.22</v>
       </c>
-      <c r="T6">
+      <c r="U6">
         <f t="shared" si="6"/>
         <v>254.05671565180515</v>
       </c>
-      <c r="U6">
+      <c r="V6">
         <v>12</v>
       </c>
-      <c r="V6">
+      <c r="W6">
         <v>39.4</v>
       </c>
-      <c r="W6">
+      <c r="X6">
         <v>3</v>
       </c>
-      <c r="X6" s="1">
+      <c r="Y6" s="1">
         <v>2625000</v>
       </c>
-      <c r="Y6" s="6">
+      <c r="Z6" s="6">
         <v>0.23912001877298844</v>
       </c>
-      <c r="Z6">
+      <c r="AA6">
         <v>2282144</v>
       </c>
-      <c r="AA6">
+      <c r="AB6">
         <v>17125</v>
       </c>
-      <c r="AB6">
+      <c r="AC6">
         <v>5.8</v>
       </c>
-      <c r="AC6">
+      <c r="AD6">
         <v>0.64908909999999997</v>
       </c>
-      <c r="AD6">
+      <c r="AE6">
         <v>6</v>
       </c>
-      <c r="AE6" t="s">
+      <c r="AF6" t="s">
         <v>138</v>
       </c>
-      <c r="AF6" s="4">
+      <c r="AG6" s="4">
         <v>187000000</v>
       </c>
-      <c r="AG6" s="5">
-        <f>AF6/D6</f>
+      <c r="AH6" s="5">
+        <f t="shared" si="7"/>
         <v>4.7249955320998129</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>15</v>
       </c>
@@ -1969,99 +1995,103 @@
         <v>5807719</v>
       </c>
       <c r="F7">
+        <f t="shared" si="8"/>
+        <v>-25548</v>
+      </c>
+      <c r="G7">
         <f t="shared" si="0"/>
         <v>737241</v>
       </c>
-      <c r="G7">
+      <c r="H7">
         <f t="shared" si="1"/>
         <v>14.613503061489455</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <f t="shared" si="2"/>
         <v>-4.3989731596862725E-3</v>
       </c>
-      <c r="I7">
+      <c r="J7">
         <v>7</v>
       </c>
-      <c r="J7">
+      <c r="K7">
         <v>8</v>
       </c>
-      <c r="K7">
+      <c r="L7">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="L7">
+      <c r="M7">
         <v>9</v>
       </c>
-      <c r="M7">
+      <c r="N7">
         <f t="shared" si="4"/>
         <v>10</v>
       </c>
-      <c r="N7">
+      <c r="O7">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
-      <c r="O7" t="s">
+      <c r="P7" t="s">
         <v>12</v>
       </c>
-      <c r="P7">
+      <c r="Q7">
         <v>3342</v>
       </c>
-      <c r="Q7">
+      <c r="R7">
         <v>80</v>
       </c>
-      <c r="R7">
+      <c r="S7">
         <v>11</v>
       </c>
-      <c r="S7" s="3">
+      <c r="T7" s="3">
         <v>103641.89</v>
       </c>
-      <c r="T7">
+      <c r="U7">
         <f t="shared" si="6"/>
         <v>55.789903098061991</v>
       </c>
-      <c r="U7">
+      <c r="V7">
         <v>38</v>
       </c>
-      <c r="V7">
+      <c r="W7">
         <v>21.8</v>
       </c>
-      <c r="W7">
+      <c r="X7">
         <v>7</v>
       </c>
-      <c r="X7" s="1">
+      <c r="Y7" s="1">
         <v>178000</v>
       </c>
-      <c r="Y7" s="6">
+      <c r="Z7" s="6">
         <v>1.6207999032549474E-2</v>
       </c>
-      <c r="Z7">
+      <c r="AA7">
         <v>240538</v>
       </c>
-      <c r="AA7">
+      <c r="AB7">
         <v>6815</v>
       </c>
-      <c r="AB7">
+      <c r="AC7">
         <v>4.2</v>
       </c>
-      <c r="AC7">
+      <c r="AD7">
         <v>0.56938319999999998</v>
       </c>
-      <c r="AD7">
+      <c r="AE7">
         <v>15</v>
       </c>
-      <c r="AE7" t="s">
+      <c r="AF7" t="s">
         <v>138</v>
       </c>
-      <c r="AF7" s="4">
+      <c r="AG7" s="4">
         <v>6000000</v>
       </c>
-      <c r="AG7" s="5">
-        <f>AF7/D7</f>
+      <c r="AH7" s="5">
+        <f t="shared" si="7"/>
         <v>1.0376725281905361</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -2078,99 +2108,103 @@
         <v>3557006</v>
       </c>
       <c r="F8">
+        <f t="shared" si="8"/>
+        <v>51292</v>
+      </c>
+      <c r="G8">
         <f t="shared" si="0"/>
         <v>26670</v>
       </c>
-      <c r="G8">
+      <c r="H8">
         <f t="shared" si="1"/>
         <v>0.74463344601951964</v>
       </c>
-      <c r="H8" s="2">
+      <c r="I8" s="2">
         <f t="shared" si="2"/>
         <v>1.4419992544291464E-2</v>
       </c>
-      <c r="I8">
-        <v>5</v>
-      </c>
       <c r="J8">
         <v>5</v>
       </c>
       <c r="K8">
+        <v>5</v>
+      </c>
+      <c r="L8">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L8">
+      <c r="M8">
         <v>7</v>
       </c>
-      <c r="M8">
+      <c r="N8">
         <f t="shared" si="4"/>
         <v>7</v>
       </c>
-      <c r="N8">
+      <c r="O8">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="O8" t="s">
+      <c r="P8" t="s">
         <v>12</v>
       </c>
-      <c r="P8">
+      <c r="Q8">
         <v>3557</v>
       </c>
-      <c r="Q8">
+      <c r="R8">
         <v>85</v>
       </c>
-      <c r="R8">
+      <c r="S8">
         <v>16</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>4842.3599999999997</v>
       </c>
-      <c r="T8">
+      <c r="U8">
         <f t="shared" si="6"/>
         <v>745.15277674522349</v>
       </c>
-      <c r="U8">
+      <c r="V8">
         <v>5</v>
       </c>
-      <c r="V8">
+      <c r="W8">
         <v>16.899999999999999</v>
       </c>
-      <c r="W8">
+      <c r="X8">
         <v>11</v>
       </c>
-      <c r="X8" s="1">
+      <c r="Y8" s="1">
         <v>116000</v>
       </c>
-      <c r="Y8" s="6">
+      <c r="Z8" s="6">
         <v>1.0581337524693493E-2</v>
       </c>
-      <c r="Z8">
+      <c r="AA8">
         <v>396745</v>
       </c>
-      <c r="AA8">
+      <c r="AB8">
         <v>7946</v>
       </c>
-      <c r="AB8">
+      <c r="AC8">
         <v>11.1</v>
       </c>
-      <c r="AC8">
+      <c r="AD8">
         <v>0.60195050000000005</v>
       </c>
-      <c r="AD8">
+      <c r="AE8">
         <v>9</v>
       </c>
-      <c r="AE8" t="s">
+      <c r="AF8" t="s">
         <v>138</v>
       </c>
-      <c r="AF8" s="4">
+      <c r="AG8" s="4">
         <v>500000</v>
       </c>
-      <c r="AG8" s="5">
-        <f>AF8/D8</f>
+      <c r="AH8" s="5">
+        <f t="shared" si="7"/>
         <v>0.13856948622314455</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>17</v>
       </c>
@@ -2187,99 +2221,103 @@
         <v>986809</v>
       </c>
       <c r="F9">
+        <f t="shared" si="8"/>
+        <v>4028</v>
+      </c>
+      <c r="G9">
         <f t="shared" si="0"/>
         <v>89960</v>
       </c>
-      <c r="G9">
+      <c r="H9">
         <f t="shared" si="1"/>
         <v>9.9858249239352332</v>
       </c>
-      <c r="H9" s="2">
+      <c r="I9" s="2">
         <f t="shared" si="2"/>
         <v>4.0818435989132653E-3</v>
       </c>
-      <c r="I9">
-        <v>1</v>
-      </c>
       <c r="J9">
         <v>1</v>
       </c>
       <c r="K9">
+        <v>1</v>
+      </c>
+      <c r="L9">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L9">
+      <c r="M9">
         <v>3</v>
       </c>
-      <c r="M9">
+      <c r="N9">
         <f t="shared" si="4"/>
         <v>3</v>
       </c>
-      <c r="N9">
+      <c r="O9">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="O9" t="s">
+      <c r="P9" t="s">
         <v>12</v>
       </c>
-      <c r="P9">
+      <c r="Q9">
         <v>368</v>
       </c>
-      <c r="Q9">
+      <c r="R9">
         <v>11</v>
       </c>
-      <c r="R9">
+      <c r="S9">
         <v>1</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1948.54</v>
       </c>
-      <c r="T9">
+      <c r="U9">
         <f t="shared" si="6"/>
         <v>508.50226323298472</v>
       </c>
-      <c r="U9">
+      <c r="V9">
         <v>7</v>
       </c>
-      <c r="V9">
+      <c r="W9">
         <v>9.6</v>
       </c>
-      <c r="W9">
+      <c r="X9">
         <v>28</v>
       </c>
-      <c r="X9" s="1">
+      <c r="Y9" s="1">
         <v>24000</v>
       </c>
-      <c r="Y9" s="6">
+      <c r="Z9" s="6">
         <v>2.1447469365479806E-3</v>
       </c>
-      <c r="Z9">
+      <c r="AA9">
         <v>219418</v>
       </c>
-      <c r="AA9">
+      <c r="AB9">
         <v>3974</v>
       </c>
-      <c r="AB9">
+      <c r="AC9">
         <v>22.5</v>
       </c>
-      <c r="AC9">
+      <c r="AD9">
         <v>0.5962674</v>
       </c>
-      <c r="AD9">
+      <c r="AE9">
         <v>11</v>
       </c>
-      <c r="AE9" t="s">
+      <c r="AF9" t="s">
         <v>138</v>
       </c>
-      <c r="AF9" s="4">
-        <v>0</v>
-      </c>
-      <c r="AG9" s="5">
-        <f>AF9/D9</f>
+      <c r="AG9" s="4">
+        <v>0</v>
+      </c>
+      <c r="AH9" s="5">
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -2297,97 +2335,101 @@
         <v>712816</v>
       </c>
       <c r="F10">
+        <f t="shared" si="8"/>
+        <v>-21283</v>
+      </c>
+      <c r="G10">
         <f t="shared" si="0"/>
         <v>89810</v>
       </c>
-      <c r="G10">
+      <c r="H10">
         <f t="shared" si="1"/>
         <v>14.925472351896138</v>
       </c>
-      <c r="H10" s="2">
+      <c r="I10" s="2">
         <f t="shared" si="2"/>
         <v>-2.9857635069919865E-2</v>
       </c>
-      <c r="I10">
-        <v>0</v>
-      </c>
       <c r="J10">
         <v>0</v>
       </c>
       <c r="K10">
+        <v>0</v>
+      </c>
+      <c r="L10">
         <f t="shared" si="3"/>
         <v>0</v>
-      </c>
-      <c r="L10">
-        <v>3</v>
       </c>
       <c r="M10">
         <v>3</v>
       </c>
       <c r="N10">
-        <v>0</v>
-      </c>
-      <c r="O10" t="s">
+        <v>3</v>
+      </c>
+      <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="P10" t="s">
         <v>12</v>
       </c>
-      <c r="P10">
+      <c r="Q10">
         <v>586</v>
       </c>
-      <c r="Q10">
+      <c r="R10">
         <v>11</v>
       </c>
-      <c r="R10">
+      <c r="S10">
         <v>2</v>
       </c>
-      <c r="S10">
+      <c r="T10">
         <v>61.05</v>
       </c>
-      <c r="T10">
+      <c r="U10">
         <f t="shared" si="6"/>
         <v>11327.321867321867</v>
       </c>
-      <c r="U10">
+      <c r="V10">
         <v>1</v>
       </c>
-      <c r="V10">
+      <c r="W10">
         <v>11.3</v>
       </c>
-      <c r="W10">
+      <c r="X10">
         <v>19</v>
       </c>
-      <c r="X10" s="1">
+      <c r="Y10" s="1">
         <v>25000</v>
       </c>
-      <c r="Y10" s="6">
+      <c r="Z10" s="6">
         <v>2.3050032809033808E-3</v>
       </c>
-      <c r="Z10">
+      <c r="AA10">
         <v>320704</v>
       </c>
-      <c r="AA10">
+      <c r="AB10">
         <v>4929</v>
       </c>
-      <c r="AB10">
+      <c r="AC10">
         <v>45.4</v>
       </c>
-      <c r="AC10">
+      <c r="AD10">
         <v>0.94466950000000005</v>
       </c>
-      <c r="AD10">
+      <c r="AE10">
         <v>1</v>
       </c>
-      <c r="AE10" t="s">
+      <c r="AF10" t="s">
         <v>139</v>
       </c>
-      <c r="AF10" s="4">
-        <v>0</v>
-      </c>
-      <c r="AG10" s="5">
-        <f>AF10/D10</f>
+      <c r="AG10" s="4">
+        <v>0</v>
+      </c>
+      <c r="AH10" s="5">
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -2404,99 +2446,103 @@
         <v>21733312</v>
       </c>
       <c r="F11">
+        <f t="shared" si="8"/>
+        <v>-162785</v>
+      </c>
+      <c r="G11">
         <f t="shared" si="0"/>
         <v>2669754</v>
       </c>
-      <c r="G11">
+      <c r="H11">
         <f t="shared" si="1"/>
         <v>14.12510483036858</v>
       </c>
-      <c r="H11" s="2">
+      <c r="I11" s="2">
         <f t="shared" si="2"/>
         <v>-7.4901147142230323E-3</v>
       </c>
-      <c r="I11">
+      <c r="J11">
         <v>27</v>
       </c>
-      <c r="J11">
+      <c r="K11">
         <v>28</v>
       </c>
-      <c r="K11">
+      <c r="L11">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="L11">
+      <c r="M11">
         <v>29</v>
       </c>
-      <c r="M11">
-        <f t="shared" ref="M11:M52" si="7">J11+2</f>
+      <c r="N11">
+        <f t="shared" ref="N11:N52" si="9">K11+2</f>
         <v>30</v>
       </c>
-      <c r="N11">
-        <f t="shared" ref="N11:N52" si="8">M11-L11</f>
+      <c r="O11">
+        <f t="shared" ref="O11:O52" si="10">N11-M11</f>
         <v>1</v>
       </c>
-      <c r="O11" t="s">
+      <c r="P11" t="s">
         <v>9</v>
       </c>
-      <c r="P11">
+      <c r="Q11">
         <v>7495</v>
       </c>
-      <c r="Q11">
+      <c r="R11">
         <v>101</v>
       </c>
-      <c r="R11">
+      <c r="S11">
         <v>16</v>
       </c>
-      <c r="S11" s="3">
+      <c r="T11" s="3">
         <v>53624.76</v>
       </c>
-      <c r="T11">
+      <c r="U11">
         <f t="shared" si="6"/>
         <v>402.24939002058005</v>
       </c>
-      <c r="U11">
+      <c r="V11">
         <v>9</v>
       </c>
-      <c r="V11">
+      <c r="W11">
         <v>26.4</v>
       </c>
-      <c r="W11">
+      <c r="X11">
         <v>6</v>
       </c>
-      <c r="X11" s="1">
+      <c r="Y11" s="1">
         <v>732000</v>
       </c>
-      <c r="Y11" s="6">
+      <c r="Z11" s="6">
         <v>6.665678324468978E-2</v>
       </c>
-      <c r="Z11">
+      <c r="AA11">
         <v>3441062</v>
       </c>
-      <c r="AA11">
+      <c r="AB11">
         <v>26501</v>
       </c>
-      <c r="AB11">
+      <c r="AC11">
         <v>16</v>
       </c>
-      <c r="AC11">
+      <c r="AD11">
         <v>0.4830525</v>
       </c>
-      <c r="AD11">
+      <c r="AE11">
         <v>28</v>
       </c>
-      <c r="AE11" t="s">
+      <c r="AF11" t="s">
         <v>137</v>
       </c>
-      <c r="AF11" s="4">
-        <v>0</v>
-      </c>
-      <c r="AG11" s="5">
-        <f>AF11/D11</f>
+      <c r="AG11" s="4">
+        <v>0</v>
+      </c>
+      <c r="AH11" s="5">
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>20</v>
       </c>
@@ -2513,99 +2559,103 @@
         <v>10710017</v>
       </c>
       <c r="F12">
+        <f t="shared" si="8"/>
+        <v>15257</v>
+      </c>
+      <c r="G12">
         <f t="shared" si="0"/>
         <v>997708</v>
       </c>
-      <c r="G12">
+      <c r="H12">
         <f t="shared" si="1"/>
         <v>10.256501986211145</v>
       </c>
-      <c r="H12" s="2">
+      <c r="I12" s="2">
         <f t="shared" si="2"/>
         <v>1.4245542280651841E-3</v>
       </c>
-      <c r="I12">
-        <v>14</v>
-      </c>
       <c r="J12">
         <v>14</v>
       </c>
       <c r="K12">
+        <v>14</v>
+      </c>
+      <c r="L12">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L12">
+      <c r="M12">
         <v>16</v>
       </c>
-      <c r="M12">
-        <f t="shared" si="7"/>
+      <c r="N12">
+        <f t="shared" si="9"/>
         <v>16</v>
       </c>
-      <c r="N12">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="O12" t="s">
+      <c r="O12">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="P12" t="s">
         <v>12</v>
       </c>
-      <c r="P12">
+      <c r="Q12">
         <v>4806</v>
       </c>
-      <c r="Q12">
+      <c r="R12">
         <v>154</v>
       </c>
-      <c r="R12">
+      <c r="S12">
         <v>24</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>57513.49</v>
       </c>
-      <c r="T12">
+      <c r="U12">
         <f t="shared" si="6"/>
         <v>186.48275387217851</v>
       </c>
-      <c r="U12">
+      <c r="V12">
         <v>18</v>
       </c>
-      <c r="V12">
+      <c r="W12">
         <v>9.8000000000000007</v>
       </c>
-      <c r="W12">
+      <c r="X12">
         <v>25</v>
       </c>
-      <c r="X12" s="1">
+      <c r="Y12" s="1">
         <v>330000</v>
       </c>
-      <c r="Y12" s="6">
+      <c r="Z12" s="6">
         <v>3.0036898545099215E-2</v>
       </c>
-      <c r="Z12">
+      <c r="AA12">
         <v>3390968</v>
       </c>
-      <c r="AA12">
+      <c r="AB12">
         <v>15987</v>
       </c>
-      <c r="AB12">
+      <c r="AC12">
         <v>31.9</v>
       </c>
-      <c r="AC12">
+      <c r="AD12">
         <v>0.50119329999999995</v>
       </c>
-      <c r="AD12">
+      <c r="AE12">
         <v>26</v>
       </c>
-      <c r="AE12" t="s">
+      <c r="AF12" t="s">
         <v>137</v>
       </c>
-      <c r="AF12" s="4">
+      <c r="AG12" s="4">
         <v>3750886</v>
       </c>
-      <c r="AG12" s="5">
-        <f>AF12/D12</f>
+      <c r="AH12" s="5">
+        <f t="shared" si="7"/>
         <v>0.34972402569855093</v>
       </c>
     </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>21</v>
       </c>
@@ -2622,99 +2672,103 @@
         <v>1407006</v>
       </c>
       <c r="F13">
+        <f t="shared" si="8"/>
+        <v>53131</v>
+      </c>
+      <c r="G13">
         <f t="shared" si="0"/>
         <v>93275</v>
       </c>
-      <c r="G13">
+      <c r="H13">
         <f t="shared" si="1"/>
         <v>6.8240246637919553</v>
       </c>
-      <c r="H13" s="2">
+      <c r="I13" s="2">
         <f t="shared" si="2"/>
         <v>3.7761743731014652E-2</v>
       </c>
-      <c r="I13">
-        <v>2</v>
-      </c>
       <c r="J13">
         <v>2</v>
       </c>
       <c r="K13">
+        <v>2</v>
+      </c>
+      <c r="L13">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L13">
+      <c r="M13">
         <v>4</v>
       </c>
-      <c r="M13">
-        <f t="shared" si="7"/>
+      <c r="N13">
+        <f t="shared" si="9"/>
         <v>4</v>
       </c>
-      <c r="N13">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="O13" t="s">
+      <c r="O13">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="P13" t="s">
         <v>12</v>
       </c>
-      <c r="P13">
+      <c r="Q13">
         <v>311</v>
       </c>
-      <c r="Q13">
+      <c r="R13">
         <v>1</v>
       </c>
-      <c r="R13">
-        <v>0</v>
-      </c>
-      <c r="S13" s="3">
+      <c r="S13">
+        <v>0</v>
+      </c>
+      <c r="T13" s="3">
         <v>6422.63</v>
       </c>
-      <c r="T13">
+      <c r="U13">
         <f t="shared" si="6"/>
         <v>227.34253724720247</v>
       </c>
-      <c r="U13">
+      <c r="V13">
         <v>14</v>
       </c>
-      <c r="V13">
+      <c r="W13">
         <v>10.7</v>
       </c>
-      <c r="W13">
+      <c r="X13">
         <v>22</v>
       </c>
-      <c r="X13" s="1">
+      <c r="Y13" s="1">
         <v>39000</v>
       </c>
-      <c r="Y13" s="6">
+      <c r="Z13" s="6">
         <v>3.5846859659377519E-3</v>
       </c>
-      <c r="Z13">
+      <c r="AA13">
         <v>26923</v>
       </c>
-      <c r="AA13">
+      <c r="AB13">
         <v>2003</v>
       </c>
-      <c r="AB13">
+      <c r="AC13">
         <v>1.9</v>
       </c>
-      <c r="AC13">
+      <c r="AD13">
         <v>0.65032659999999998</v>
       </c>
-      <c r="AD13">
+      <c r="AE13">
         <v>5</v>
       </c>
-      <c r="AE13" t="s">
+      <c r="AF13" t="s">
         <v>138</v>
       </c>
-      <c r="AF13" s="4">
+      <c r="AG13" s="4">
         <v>750000</v>
       </c>
-      <c r="AG13" s="5">
-        <f>AF13/D13</f>
+      <c r="AH13" s="5">
+        <f t="shared" si="7"/>
         <v>0.51365043143211908</v>
       </c>
     </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>22</v>
       </c>
@@ -2731,99 +2785,103 @@
         <v>1826913</v>
       </c>
       <c r="F14">
+        <f t="shared" si="8"/>
+        <v>14464</v>
+      </c>
+      <c r="G14">
         <f t="shared" si="0"/>
         <v>267878</v>
       </c>
-      <c r="G14">
+      <c r="H14">
         <f t="shared" si="1"/>
         <v>17.024351461297403</v>
       </c>
-      <c r="H14" s="2">
+      <c r="I14" s="2">
         <f t="shared" si="2"/>
         <v>7.9171805116061908E-3</v>
       </c>
-      <c r="I14">
-        <v>2</v>
-      </c>
       <c r="J14">
         <v>2</v>
       </c>
       <c r="K14">
+        <v>2</v>
+      </c>
+      <c r="L14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L14">
+      <c r="M14">
         <v>4</v>
       </c>
-      <c r="M14">
-        <f t="shared" si="7"/>
+      <c r="N14">
+        <f t="shared" si="9"/>
         <v>4</v>
       </c>
-      <c r="N14">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="O14" t="s">
+      <c r="O14">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="P14" t="s">
         <v>9</v>
       </c>
-      <c r="P14">
+      <c r="Q14">
         <v>669</v>
       </c>
-      <c r="Q14">
+      <c r="R14">
         <v>9</v>
       </c>
-      <c r="R14">
-        <v>0</v>
-      </c>
-      <c r="S14" s="3">
+      <c r="S14">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
         <v>82643.12</v>
       </c>
-      <c r="T14">
+      <c r="U14">
         <f t="shared" si="6"/>
         <v>22.281068284934065</v>
       </c>
-      <c r="U14">
+      <c r="V14">
         <v>45</v>
       </c>
-      <c r="V14">
+      <c r="W14">
         <v>12.8</v>
       </c>
-      <c r="W14">
+      <c r="X14">
         <v>16</v>
       </c>
-      <c r="X14" s="1">
+      <c r="Y14" s="1">
         <v>30000</v>
       </c>
-      <c r="Y14" s="6">
+      <c r="Z14" s="6">
         <v>2.7473702600875104E-3</v>
       </c>
-      <c r="Z14">
+      <c r="AA14">
         <v>12708</v>
       </c>
-      <c r="AA14">
+      <c r="AB14">
         <v>2170</v>
       </c>
-      <c r="AB14">
+      <c r="AC14">
         <v>0.7</v>
       </c>
-      <c r="AC14">
+      <c r="AD14">
         <v>0.34122859999999999</v>
       </c>
-      <c r="AD14">
+      <c r="AE14">
         <v>47</v>
       </c>
-      <c r="AE14" t="s">
+      <c r="AF14" t="s">
         <v>137</v>
       </c>
-      <c r="AF14" s="4">
-        <v>0</v>
-      </c>
-      <c r="AG14" s="5">
-        <f>AF14/D14</f>
+      <c r="AG14" s="4">
+        <v>0</v>
+      </c>
+      <c r="AH14" s="5">
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>23</v>
       </c>
@@ -2840,99 +2898,103 @@
         <v>12587530</v>
       </c>
       <c r="F15">
+        <f t="shared" si="8"/>
+        <v>235209</v>
+      </c>
+      <c r="G15">
         <f t="shared" si="0"/>
         <v>-41641</v>
       </c>
-      <c r="G15">
+      <c r="H15">
         <f t="shared" si="1"/>
         <v>-0.32369224167818428</v>
       </c>
-      <c r="H15" s="2">
+      <c r="I15" s="2">
         <f t="shared" si="2"/>
         <v>1.8685874035652746E-2</v>
       </c>
-      <c r="I15">
+      <c r="J15">
         <v>18</v>
       </c>
-      <c r="J15">
+      <c r="K15">
         <v>17</v>
       </c>
-      <c r="K15">
+      <c r="L15">
         <f t="shared" si="3"/>
         <v>-1</v>
       </c>
-      <c r="L15">
+      <c r="M15">
         <v>20</v>
       </c>
-      <c r="M15">
-        <f t="shared" si="7"/>
+      <c r="N15">
+        <f t="shared" si="9"/>
         <v>19</v>
       </c>
-      <c r="N15">
-        <f t="shared" si="8"/>
+      <c r="O15">
+        <f t="shared" si="10"/>
         <v>-1</v>
       </c>
-      <c r="O15" t="s">
+      <c r="P15" t="s">
         <v>12</v>
       </c>
-      <c r="P15">
+      <c r="Q15">
         <v>6980</v>
       </c>
-      <c r="Q15">
+      <c r="R15">
         <v>141</v>
       </c>
-      <c r="R15">
+      <c r="S15">
         <v>42</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>55518.93</v>
       </c>
-      <c r="T15">
+      <c r="U15">
         <f t="shared" si="6"/>
         <v>230.96156572181778</v>
       </c>
-      <c r="U15">
+      <c r="V15">
         <v>13</v>
       </c>
-      <c r="V15">
+      <c r="W15">
         <v>17.5</v>
       </c>
-      <c r="W15">
+      <c r="X15">
         <v>10</v>
       </c>
-      <c r="X15" s="1">
+      <c r="Y15" s="1">
         <v>437000</v>
       </c>
-      <c r="Y15" s="6">
+      <c r="Z15" s="6">
         <v>3.9819831027452048E-2</v>
       </c>
-      <c r="Z15">
+      <c r="AA15">
         <v>1790212</v>
       </c>
-      <c r="AA15">
+      <c r="AB15">
         <v>12139</v>
       </c>
-      <c r="AB15">
+      <c r="AC15">
         <v>14.1</v>
       </c>
-      <c r="AC15">
+      <c r="AD15">
         <v>0.58659039999999996</v>
       </c>
-      <c r="AD15">
+      <c r="AE15">
         <v>12</v>
       </c>
-      <c r="AE15" t="s">
+      <c r="AF15" t="s">
         <v>138</v>
       </c>
-      <c r="AF15" s="4">
+      <c r="AG15" s="4">
         <v>30500000</v>
       </c>
-      <c r="AG15" s="5">
-        <f>AF15/D15</f>
+      <c r="AH15" s="5">
+        <f t="shared" si="7"/>
         <v>2.3785869774000701</v>
       </c>
     </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>24</v>
       </c>
@@ -2949,99 +3011,103 @@
         <v>6754953</v>
       </c>
       <c r="F16">
+        <f t="shared" si="8"/>
+        <v>35327</v>
+      </c>
+      <c r="G16">
         <f t="shared" si="0"/>
         <v>288698</v>
       </c>
-      <c r="G16">
+      <c r="H16">
         <f t="shared" si="1"/>
         <v>4.4404269606997193</v>
       </c>
-      <c r="H16" s="2">
+      <c r="I16" s="2">
         <f t="shared" si="2"/>
         <v>5.2297921243863576E-3</v>
       </c>
-      <c r="I16">
-        <v>9</v>
-      </c>
       <c r="J16">
         <v>9</v>
       </c>
       <c r="K16">
+        <v>9</v>
+      </c>
+      <c r="L16">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L16">
+      <c r="M16">
         <v>11</v>
       </c>
-      <c r="M16">
-        <f t="shared" si="7"/>
+      <c r="N16">
+        <f t="shared" si="9"/>
         <v>11</v>
       </c>
-      <c r="N16">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="O16" t="s">
+      <c r="O16">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="P16" t="s">
         <v>9</v>
       </c>
-      <c r="P16">
+      <c r="Q16">
         <v>2565</v>
       </c>
-      <c r="Q16">
+      <c r="R16">
         <v>65</v>
       </c>
-      <c r="R16">
+      <c r="S16">
         <v>16</v>
       </c>
-      <c r="S16" s="3">
+      <c r="T16" s="3">
         <v>35826.11</v>
       </c>
-      <c r="T16">
+      <c r="U16">
         <f t="shared" si="6"/>
         <v>189.53439265384938</v>
       </c>
-      <c r="U16">
+      <c r="V16">
         <v>17</v>
       </c>
-      <c r="V16">
+      <c r="W16">
         <v>7.2</v>
       </c>
-      <c r="W16">
+      <c r="X16">
         <v>32</v>
       </c>
-      <c r="X16" s="1">
+      <c r="Y16" s="1">
         <v>105000</v>
       </c>
-      <c r="Y16" s="6">
+      <c r="Z16" s="6">
         <v>9.5839421108608464E-3</v>
       </c>
-      <c r="Z16">
+      <c r="AA16">
         <v>643105</v>
       </c>
-      <c r="AA16">
+      <c r="AB16">
         <v>8996</v>
       </c>
-      <c r="AB16">
+      <c r="AC16">
         <v>9.6</v>
       </c>
-      <c r="AC16">
+      <c r="AD16">
         <v>0.41804950000000002</v>
       </c>
-      <c r="AD16">
+      <c r="AE16">
         <v>36</v>
       </c>
-      <c r="AE16" t="s">
+      <c r="AF16" t="s">
         <v>137</v>
       </c>
-      <c r="AF16" s="4">
-        <v>0</v>
-      </c>
-      <c r="AG16" s="5">
-        <f>AF16/D16</f>
+      <c r="AG16" s="4">
+        <v>0</v>
+      </c>
+      <c r="AH16" s="5">
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>25</v>
       </c>
@@ -3058,99 +3124,103 @@
         <v>3163561</v>
       </c>
       <c r="F17">
+        <f t="shared" si="8"/>
+        <v>28845</v>
+      </c>
+      <c r="G17">
         <f t="shared" si="0"/>
         <v>138619</v>
       </c>
-      <c r="G17">
+      <c r="H17">
         <f t="shared" si="1"/>
         <v>4.5392491355814926</v>
       </c>
-      <c r="H17" s="2">
+      <c r="I17" s="2">
         <f t="shared" si="2"/>
         <v>9.1178896186923531E-3</v>
       </c>
-      <c r="I17">
-        <v>4</v>
-      </c>
       <c r="J17">
         <v>4</v>
       </c>
       <c r="K17">
+        <v>4</v>
+      </c>
+      <c r="L17">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L17">
+      <c r="M17">
         <v>6</v>
       </c>
-      <c r="M17">
-        <f t="shared" si="7"/>
+      <c r="N17">
+        <f t="shared" si="9"/>
         <v>6</v>
       </c>
-      <c r="N17">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="O17" t="s">
+      <c r="O17">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="P17" t="s">
         <v>9</v>
       </c>
-      <c r="P17">
+      <c r="Q17">
         <v>549</v>
       </c>
-      <c r="Q17">
+      <c r="R17">
         <v>9</v>
       </c>
-      <c r="R17">
+      <c r="S17">
         <v>2</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>55857.13</v>
       </c>
-      <c r="T17">
+      <c r="U17">
         <f t="shared" si="6"/>
         <v>57.153061748786591</v>
       </c>
-      <c r="U17">
+      <c r="V17">
         <v>37</v>
       </c>
-      <c r="V17">
+      <c r="W17">
         <v>6.3</v>
       </c>
-      <c r="W17">
+      <c r="X17">
         <v>34</v>
       </c>
-      <c r="X17" s="1">
+      <c r="Y17" s="1">
         <v>40000</v>
       </c>
-      <c r="Y17" s="6">
+      <c r="Z17" s="6">
         <v>3.6131851319176136E-3</v>
       </c>
-      <c r="Z17">
+      <c r="AA17">
         <v>129335</v>
       </c>
-      <c r="AA17">
+      <c r="AB17">
         <v>4761</v>
       </c>
-      <c r="AB17">
+      <c r="AC17">
         <v>4.0999999999999996</v>
       </c>
-      <c r="AC17">
+      <c r="AD17">
         <v>0.4581674</v>
       </c>
-      <c r="AD17">
+      <c r="AE17">
         <v>31</v>
       </c>
-      <c r="AE17" t="s">
+      <c r="AF17" t="s">
         <v>137</v>
       </c>
-      <c r="AF17" s="4">
-        <v>0</v>
-      </c>
-      <c r="AG17" s="5">
-        <f>AF17/D17</f>
+      <c r="AG17" s="4">
+        <v>0</v>
+      </c>
+      <c r="AH17" s="5">
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>26</v>
       </c>
@@ -3167,99 +3237,103 @@
         <v>2913805</v>
       </c>
       <c r="F18">
+        <f t="shared" si="8"/>
+        <v>27060</v>
+      </c>
+      <c r="G18">
         <f t="shared" si="0"/>
         <v>77052</v>
       </c>
-      <c r="G18">
+      <c r="H18">
         <f t="shared" si="1"/>
         <v>2.6905388026383008</v>
       </c>
-      <c r="H18" s="2">
+      <c r="I18" s="2">
         <f t="shared" si="2"/>
         <v>9.2868259886986267E-3</v>
       </c>
-      <c r="I18">
-        <v>4</v>
-      </c>
       <c r="J18">
         <v>4</v>
       </c>
       <c r="K18">
+        <v>4</v>
+      </c>
+      <c r="L18">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L18">
+      <c r="M18">
         <v>6</v>
       </c>
-      <c r="M18">
-        <f t="shared" si="7"/>
+      <c r="N18">
+        <f t="shared" si="9"/>
         <v>6</v>
       </c>
-      <c r="N18">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="O18" t="s">
+      <c r="O18">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="P18" t="s">
         <v>9</v>
       </c>
-      <c r="P18">
+      <c r="Q18">
         <v>482</v>
       </c>
-      <c r="Q18">
+      <c r="R18">
         <v>10</v>
       </c>
-      <c r="R18">
+      <c r="S18">
         <v>1</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>81758.720000000001</v>
       </c>
-      <c r="T18">
+      <c r="U18">
         <f t="shared" si="6"/>
         <v>35.97004698703698</v>
       </c>
-      <c r="U18">
+      <c r="V18">
         <v>42</v>
       </c>
-      <c r="V18">
+      <c r="W18">
         <v>12.2</v>
       </c>
-      <c r="W18">
+      <c r="X18">
         <v>18</v>
       </c>
-      <c r="X18" s="1">
+      <c r="Y18" s="1">
         <v>70000</v>
       </c>
-      <c r="Y18" s="6">
+      <c r="Z18" s="6">
         <v>6.4161028441482989E-3</v>
       </c>
-      <c r="Z18">
+      <c r="AA18">
         <v>167237</v>
       </c>
-      <c r="AA18">
+      <c r="AB18">
         <v>4802</v>
       </c>
-      <c r="AB18">
+      <c r="AC18">
         <v>5.7</v>
       </c>
-      <c r="AC18">
+      <c r="AD18">
         <v>0.42506569999999999</v>
       </c>
-      <c r="AD18">
+      <c r="AE18">
         <v>34</v>
       </c>
-      <c r="AE18" t="s">
+      <c r="AF18" t="s">
         <v>138</v>
       </c>
-      <c r="AF18" s="4">
-        <v>0</v>
-      </c>
-      <c r="AG18" s="5">
-        <f>AF18/D18</f>
+      <c r="AG18" s="4">
+        <v>0</v>
+      </c>
+      <c r="AH18" s="5">
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>27</v>
       </c>
@@ -3276,99 +3350,103 @@
         <v>4477251</v>
       </c>
       <c r="F19">
+        <f t="shared" si="8"/>
+        <v>32091</v>
+      </c>
+      <c r="G19">
         <f t="shared" si="0"/>
         <v>158736</v>
       </c>
-      <c r="G19">
+      <c r="H19">
         <f t="shared" si="1"/>
         <v>3.6485951612258156</v>
       </c>
-      <c r="H19" s="2">
+      <c r="I19" s="2">
         <f t="shared" si="2"/>
         <v>7.1675677776385557E-3</v>
       </c>
-      <c r="I19">
-        <v>6</v>
-      </c>
       <c r="J19">
         <v>6</v>
       </c>
       <c r="K19">
+        <v>6</v>
+      </c>
+      <c r="L19">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L19">
+      <c r="M19">
         <v>8</v>
       </c>
-      <c r="M19">
-        <f t="shared" si="7"/>
+      <c r="N19">
+        <f t="shared" si="9"/>
         <v>8</v>
       </c>
-      <c r="N19">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="O19" t="s">
+      <c r="O19">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="P19" t="s">
         <v>9</v>
       </c>
-      <c r="P19">
+      <c r="Q19">
         <v>680</v>
       </c>
-      <c r="Q19">
+      <c r="R19">
         <v>20</v>
       </c>
-      <c r="R19">
+      <c r="S19">
         <v>2</v>
       </c>
-      <c r="S19" s="3">
+      <c r="T19" s="3">
         <v>39486.339999999997</v>
       </c>
-      <c r="T19">
+      <c r="U19">
         <f t="shared" si="6"/>
         <v>114.2000499413215</v>
       </c>
-      <c r="U19">
+      <c r="V19">
         <v>24</v>
       </c>
-      <c r="V19">
+      <c r="W19">
         <v>3.8</v>
       </c>
-      <c r="W19">
+      <c r="X19">
         <v>45</v>
       </c>
-      <c r="X19" s="1">
+      <c r="Y19" s="1">
         <v>48000</v>
       </c>
-      <c r="Y19" s="6">
+      <c r="Z19" s="6">
         <v>4.4082292365805039E-3</v>
       </c>
-      <c r="Z19">
+      <c r="AA19">
         <v>363167</v>
       </c>
-      <c r="AA19">
+      <c r="AB19">
         <v>7961</v>
       </c>
-      <c r="AB19">
+      <c r="AC19">
         <v>8.1</v>
       </c>
-      <c r="AC19">
+      <c r="AD19">
         <v>0.36799900000000002</v>
       </c>
-      <c r="AD19">
+      <c r="AE19">
         <v>44</v>
       </c>
-      <c r="AE19" t="s">
+      <c r="AF19" t="s">
         <v>138</v>
       </c>
-      <c r="AF19" s="4">
-        <v>0</v>
-      </c>
-      <c r="AG19" s="5">
-        <f>AF19/D19</f>
+      <c r="AG19" s="4">
+        <v>0</v>
+      </c>
+      <c r="AH19" s="5">
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>28</v>
       </c>
@@ -3385,99 +3463,103 @@
         <v>4645318</v>
       </c>
       <c r="F20">
+        <f t="shared" si="8"/>
+        <v>16150</v>
+      </c>
+      <c r="G20">
         <f t="shared" si="0"/>
         <v>107506</v>
       </c>
-      <c r="G20">
+      <c r="H20">
         <f t="shared" si="1"/>
         <v>2.3607135940089092</v>
       </c>
-      <c r="H20" s="2">
+      <c r="I20" s="2">
         <f t="shared" si="2"/>
         <v>3.4766188235121902E-3</v>
       </c>
-      <c r="I20">
-        <v>6</v>
-      </c>
       <c r="J20">
         <v>6</v>
       </c>
       <c r="K20">
+        <v>6</v>
+      </c>
+      <c r="L20">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L20">
+      <c r="M20">
         <v>8</v>
       </c>
-      <c r="M20">
-        <f t="shared" si="7"/>
+      <c r="N20">
+        <f t="shared" si="9"/>
         <v>8</v>
       </c>
-      <c r="N20">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="O20" t="s">
+      <c r="O20">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="P20" t="s">
         <v>9</v>
       </c>
-      <c r="P20">
+      <c r="Q20">
         <v>6424</v>
       </c>
-      <c r="Q20">
+      <c r="R20">
         <v>273</v>
       </c>
-      <c r="R20">
+      <c r="S20">
         <v>34</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>43203.9</v>
       </c>
-      <c r="T20">
+      <c r="U20">
         <f t="shared" si="6"/>
         <v>107.89461136610352</v>
       </c>
-      <c r="U20">
+      <c r="V20">
         <v>27</v>
       </c>
-      <c r="V20">
+      <c r="W20">
         <v>5.4</v>
       </c>
-      <c r="W20">
+      <c r="X20">
         <v>38</v>
       </c>
-      <c r="X20" s="1">
+      <c r="Y20" s="1">
         <v>70000</v>
       </c>
-      <c r="Y20" s="6">
+      <c r="Z20" s="6">
         <v>6.3682077308170361E-3</v>
       </c>
-      <c r="Z20">
+      <c r="AA20">
         <v>1504017</v>
       </c>
-      <c r="AA20">
+      <c r="AB20">
         <v>8676</v>
       </c>
-      <c r="AB20">
+      <c r="AC20">
         <v>32.4</v>
       </c>
-      <c r="AC20">
+      <c r="AD20">
         <v>0.40535559999999998</v>
       </c>
-      <c r="AD20">
+      <c r="AE20">
         <v>39</v>
       </c>
-      <c r="AE20" t="s">
+      <c r="AF20" t="s">
         <v>140</v>
       </c>
-      <c r="AF20" s="4">
-        <v>0</v>
-      </c>
-      <c r="AG20" s="5">
-        <f>AF20/D20</f>
+      <c r="AG20" s="4">
+        <v>0</v>
+      </c>
+      <c r="AH20" s="5">
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>29</v>
       </c>
@@ -3494,99 +3576,103 @@
         <v>1350141</v>
       </c>
       <c r="F21">
+        <f t="shared" si="8"/>
+        <v>13441</v>
+      </c>
+      <c r="G21">
         <f t="shared" si="0"/>
         <v>30508</v>
       </c>
-      <c r="G21">
+      <c r="H21">
         <f t="shared" si="1"/>
         <v>2.2885451220262341</v>
       </c>
-      <c r="H21" s="2">
+      <c r="I21" s="2">
         <f t="shared" si="2"/>
         <v>9.9552565250592348E-3</v>
       </c>
-      <c r="I21">
-        <v>2</v>
-      </c>
       <c r="J21">
         <v>2</v>
       </c>
       <c r="K21">
+        <v>2</v>
+      </c>
+      <c r="L21">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L21">
+      <c r="M21">
         <v>4</v>
       </c>
-      <c r="M21">
-        <f t="shared" si="7"/>
+      <c r="N21">
+        <f t="shared" si="9"/>
         <v>4</v>
       </c>
-      <c r="N21">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="O21" t="s">
+      <c r="O21">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="P21" t="s">
         <v>12</v>
       </c>
-      <c r="P21">
+      <c r="Q21">
         <v>344</v>
       </c>
-      <c r="Q21">
+      <c r="R21">
         <v>7</v>
       </c>
-      <c r="R21">
+      <c r="S21">
         <v>2</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>30842.92</v>
       </c>
-      <c r="T21">
+      <c r="U21">
         <f t="shared" si="6"/>
         <v>44.210535189275205</v>
       </c>
-      <c r="U21">
+      <c r="V21">
         <v>39</v>
       </c>
-      <c r="V21">
+      <c r="W21">
         <v>1.7</v>
       </c>
-      <c r="W21">
+      <c r="X21">
         <v>50</v>
       </c>
-      <c r="X21" s="1">
+      <c r="Y21" s="1">
         <v>6000</v>
       </c>
-      <c r="Y21" s="6">
+      <c r="Z21" s="6">
         <v>5.2123922384111258E-4</v>
       </c>
-      <c r="Z21">
+      <c r="AA21">
         <v>21983</v>
       </c>
-      <c r="AA21">
+      <c r="AB21">
         <v>2723</v>
       </c>
-      <c r="AB21">
+      <c r="AC21">
         <v>1.6</v>
       </c>
-      <c r="AC21">
+      <c r="AD21">
         <v>0.54670399999999997</v>
       </c>
-      <c r="AD21">
+      <c r="AE21">
         <v>18</v>
       </c>
-      <c r="AE21" t="s">
+      <c r="AF21" t="s">
         <v>138</v>
       </c>
-      <c r="AF21" s="4">
-        <v>0</v>
-      </c>
-      <c r="AG21" s="5">
-        <f>AF21/D21</f>
+      <c r="AG21" s="4">
+        <v>0</v>
+      </c>
+      <c r="AH21" s="5">
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>30</v>
       </c>
@@ -3603,99 +3689,103 @@
         <v>6055802</v>
       </c>
       <c r="F22">
+        <f t="shared" si="8"/>
+        <v>129476</v>
+      </c>
+      <c r="G22">
         <f t="shared" si="0"/>
         <v>395349</v>
       </c>
-      <c r="G22">
+      <c r="H22">
         <f t="shared" si="1"/>
         <v>6.8282184462020172</v>
       </c>
-      <c r="H22" s="2">
+      <c r="I22" s="2">
         <f t="shared" si="2"/>
         <v>2.1380487671162299E-2</v>
       </c>
-      <c r="I22">
-        <v>8</v>
-      </c>
       <c r="J22">
         <v>8</v>
       </c>
       <c r="K22">
+        <v>8</v>
+      </c>
+      <c r="L22">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L22">
+      <c r="M22">
         <v>10</v>
       </c>
-      <c r="M22">
-        <f t="shared" si="7"/>
+      <c r="N22">
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
-      <c r="N22">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="O22" t="s">
+      <c r="O22">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="P22" t="s">
         <v>12</v>
       </c>
-      <c r="P22">
+      <c r="Q22">
         <v>1985</v>
       </c>
-      <c r="Q22">
+      <c r="R22">
         <v>31</v>
       </c>
-      <c r="R22">
+      <c r="S22">
         <v>13</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>9707.24</v>
       </c>
-      <c r="T22">
+      <c r="U22">
         <f t="shared" si="6"/>
         <v>637.18193842946096</v>
       </c>
-      <c r="U22">
+      <c r="V22">
         <v>6</v>
       </c>
-      <c r="V22">
+      <c r="W22">
         <v>10.6</v>
       </c>
-      <c r="W22">
+      <c r="X22">
         <v>23</v>
       </c>
-      <c r="X22" s="1">
+      <c r="Y22" s="1">
         <v>226000</v>
       </c>
-      <c r="Y22" s="6">
+      <c r="Z22" s="6">
         <v>2.0626662460001551E-2</v>
       </c>
-      <c r="Z22">
+      <c r="AA22">
         <v>1830059</v>
       </c>
-      <c r="AA22">
+      <c r="AB22">
         <v>9860</v>
       </c>
-      <c r="AB22">
+      <c r="AC22">
         <v>30.3</v>
       </c>
-      <c r="AC22">
+      <c r="AD22">
         <v>0.67029050000000001</v>
       </c>
-      <c r="AD22">
+      <c r="AE22">
         <v>4</v>
       </c>
-      <c r="AE22" t="s">
+      <c r="AF22" t="s">
         <v>137</v>
       </c>
-      <c r="AF22" s="4">
+      <c r="AG22" s="4">
         <v>5000000</v>
       </c>
-      <c r="AG22" s="5">
-        <f>AF22/D22</f>
+      <c r="AH22" s="5">
+        <f t="shared" si="7"/>
         <v>0.80837110312584171</v>
       </c>
     </row>
-    <row r="23" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>31</v>
       </c>
@@ -3712,99 +3802,103 @@
         <v>6893574</v>
       </c>
       <c r="F23">
+        <f t="shared" si="8"/>
+        <v>139895</v>
+      </c>
+      <c r="G23">
         <f t="shared" si="0"/>
         <v>473825</v>
       </c>
-      <c r="G23">
+      <c r="H23">
         <f t="shared" si="1"/>
         <v>7.223334071178253</v>
       </c>
-      <c r="H23" s="2">
+      <c r="I23" s="2">
         <f t="shared" si="2"/>
         <v>2.0293537140531167E-2</v>
       </c>
-      <c r="I23">
-        <v>9</v>
-      </c>
       <c r="J23">
         <v>9</v>
       </c>
       <c r="K23">
+        <v>9</v>
+      </c>
+      <c r="L23">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L23">
+      <c r="M23">
         <v>11</v>
       </c>
-      <c r="M23">
-        <f t="shared" si="7"/>
+      <c r="N23">
+        <f t="shared" si="9"/>
         <v>11</v>
       </c>
-      <c r="N23">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="O23" t="s">
+      <c r="O23">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="P23" t="s">
         <v>12</v>
       </c>
-      <c r="P23">
+      <c r="Q23">
         <v>7738</v>
       </c>
-      <c r="Q23">
+      <c r="R23">
         <v>122</v>
       </c>
-      <c r="R23">
+      <c r="S23">
         <v>33</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>7800.06</v>
       </c>
-      <c r="T23">
+      <c r="U23">
         <f t="shared" si="6"/>
         <v>901.71985856519052</v>
       </c>
-      <c r="U23">
+      <c r="V23">
         <v>4</v>
       </c>
-      <c r="V23">
+      <c r="W23">
         <v>12.4</v>
       </c>
-      <c r="W23">
+      <c r="X23">
         <v>17</v>
       </c>
-      <c r="X23" s="1">
+      <c r="Y23" s="1">
         <v>215000</v>
       </c>
-      <c r="Y23" s="6">
+      <c r="Z23" s="6">
         <v>1.9543947332479099E-2</v>
       </c>
-      <c r="Z23">
+      <c r="AA23">
         <v>543629</v>
       </c>
-      <c r="AA23">
+      <c r="AB23">
         <v>9985</v>
       </c>
-      <c r="AB23">
+      <c r="AC23">
         <v>7.9</v>
       </c>
-      <c r="AC23">
+      <c r="AD23">
         <v>0.67115550000000002</v>
       </c>
-      <c r="AD23">
+      <c r="AE23">
         <v>3</v>
       </c>
-      <c r="AE23" t="s">
+      <c r="AF23" t="s">
         <v>137</v>
       </c>
-      <c r="AF23" s="4">
+      <c r="AG23" s="4">
         <v>6650000</v>
       </c>
-      <c r="AG23" s="5">
-        <f>AF23/D23</f>
+      <c r="AH23" s="5">
+        <f t="shared" si="7"/>
         <v>0.94547939288564431</v>
       </c>
     </row>
-    <row r="24" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>32</v>
       </c>
@@ -3821,99 +3915,103 @@
         <v>9966555</v>
       </c>
       <c r="F24">
+        <f t="shared" si="8"/>
+        <v>117887</v>
+      </c>
+      <c r="G24">
         <f t="shared" si="0"/>
         <v>172816</v>
       </c>
-      <c r="G24">
+      <c r="H24">
         <f t="shared" si="1"/>
         <v>1.743568613262849</v>
       </c>
-      <c r="H24" s="2">
+      <c r="I24" s="2">
         <f t="shared" si="2"/>
         <v>1.1828259614279959E-2</v>
       </c>
-      <c r="I24">
+      <c r="J24">
         <v>14</v>
       </c>
-      <c r="J24">
+      <c r="K24">
         <v>13</v>
       </c>
-      <c r="K24">
+      <c r="L24">
         <f t="shared" si="3"/>
         <v>-1</v>
       </c>
-      <c r="L24">
+      <c r="M24">
         <v>16</v>
       </c>
-      <c r="M24">
-        <f t="shared" si="7"/>
+      <c r="N24">
+        <f t="shared" si="9"/>
         <v>15</v>
       </c>
-      <c r="N24">
-        <f t="shared" si="8"/>
+      <c r="O24">
+        <f t="shared" si="10"/>
         <v>-1</v>
       </c>
-      <c r="O24" t="s">
+      <c r="P24" t="s">
         <v>12</v>
       </c>
-      <c r="P24">
+      <c r="Q24">
         <v>9334</v>
       </c>
-      <c r="Q24">
+      <c r="R24">
         <v>337</v>
       </c>
-      <c r="R24">
+      <c r="S24">
         <v>78</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>56538.9</v>
       </c>
-      <c r="T24">
+      <c r="U24">
         <f t="shared" si="6"/>
         <v>178.36289704964193</v>
       </c>
-      <c r="U24">
+      <c r="V24">
         <v>19</v>
       </c>
-      <c r="V24">
+      <c r="W24">
         <v>5.3</v>
       </c>
-      <c r="W24">
+      <c r="X24">
         <v>39</v>
       </c>
-      <c r="X24" s="1">
+      <c r="Y24" s="1">
         <v>102000</v>
       </c>
-      <c r="Y24" s="6">
+      <c r="Z24" s="6">
         <v>9.3105623088550939E-3</v>
       </c>
-      <c r="Z24">
+      <c r="AA24">
         <v>1371069</v>
       </c>
-      <c r="AA24">
+      <c r="AB24">
         <v>10424</v>
       </c>
-      <c r="AB24">
+      <c r="AC24">
         <v>13.7</v>
       </c>
-      <c r="AC24">
+      <c r="AD24">
         <v>0.51413560000000003</v>
       </c>
-      <c r="AD24">
+      <c r="AE24">
         <v>21</v>
       </c>
-      <c r="AE24" t="s">
+      <c r="AF24" t="s">
         <v>138</v>
       </c>
-      <c r="AF24" s="4">
+      <c r="AG24" s="4">
         <v>16000000</v>
       </c>
-      <c r="AG24" s="5">
-        <f>AF24/D24</f>
+      <c r="AH24" s="5">
+        <f t="shared" si="7"/>
         <v>1.5866024119133215</v>
       </c>
     </row>
-    <row r="25" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>33</v>
       </c>
@@ -3930,99 +4028,103 @@
         <v>5657342</v>
       </c>
       <c r="F25">
+        <f t="shared" si="8"/>
+        <v>52410</v>
+      </c>
+      <c r="G25">
         <f t="shared" si="0"/>
         <v>394873</v>
       </c>
-      <c r="G25">
+      <c r="H25">
         <f t="shared" si="1"/>
         <v>7.4295764776582871</v>
       </c>
-      <c r="H25" s="2">
+      <c r="I25" s="2">
         <f t="shared" si="2"/>
         <v>9.2640678254911936E-3</v>
       </c>
-      <c r="I25">
-        <v>8</v>
-      </c>
       <c r="J25">
         <v>8</v>
       </c>
       <c r="K25">
+        <v>8</v>
+      </c>
+      <c r="L25">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L25">
+      <c r="M25">
         <v>10</v>
       </c>
-      <c r="M25">
-        <f t="shared" si="7"/>
+      <c r="N25">
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
-      <c r="N25">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="O25" t="s">
+      <c r="O25">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="P25" t="s">
         <v>12</v>
       </c>
-      <c r="P25">
+      <c r="Q25">
         <v>742</v>
       </c>
-      <c r="Q25">
+      <c r="R25">
         <v>18</v>
       </c>
-      <c r="R25">
+      <c r="S25">
         <v>1</v>
       </c>
-      <c r="S25" s="3">
+      <c r="T25" s="3">
         <v>79626.740000000005</v>
       </c>
-      <c r="T25">
+      <c r="U25">
         <f t="shared" si="6"/>
         <v>71.706464436444335</v>
       </c>
-      <c r="U25">
+      <c r="V25">
         <v>31</v>
       </c>
-      <c r="V25">
+      <c r="W25">
         <v>5.6</v>
       </c>
-      <c r="W25">
+      <c r="X25">
         <v>37</v>
       </c>
-      <c r="X25" s="1">
+      <c r="Y25" s="1">
         <v>92000</v>
       </c>
-      <c r="Y25" s="6">
+      <c r="Z25" s="6">
         <v>8.3464036035804864E-3</v>
       </c>
-      <c r="Z25">
+      <c r="AA25">
         <v>370291</v>
       </c>
-      <c r="AA25">
+      <c r="AB25">
         <v>8173</v>
       </c>
-      <c r="AB25">
+      <c r="AC25">
         <v>6.6</v>
       </c>
-      <c r="AC25">
+      <c r="AD25">
         <v>0.53639510000000001</v>
       </c>
-      <c r="AD25">
+      <c r="AE25">
         <v>20</v>
       </c>
-      <c r="AE25" t="s">
+      <c r="AF25" t="s">
         <v>138</v>
       </c>
-      <c r="AF25" s="4">
+      <c r="AG25" s="4">
         <v>2170000</v>
       </c>
-      <c r="AG25" s="5">
-        <f>AF25/D25</f>
+      <c r="AH25" s="5">
+        <f t="shared" si="7"/>
         <v>0.38005153288619192</v>
       </c>
     </row>
-    <row r="26" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>34</v>
       </c>
@@ -4039,99 +4141,103 @@
         <v>2966786</v>
       </c>
       <c r="F26">
+        <f t="shared" si="8"/>
+        <v>-2872</v>
+      </c>
+      <c r="G26">
         <f t="shared" si="0"/>
         <v>-14326</v>
       </c>
-      <c r="G26">
+      <c r="H26">
         <f t="shared" si="1"/>
         <v>-0.48102234876974315</v>
       </c>
-      <c r="H26" s="2">
+      <c r="I26" s="2">
         <f t="shared" si="2"/>
         <v>-9.6805094806298806E-4</v>
       </c>
-      <c r="I26">
-        <v>4</v>
-      </c>
       <c r="J26">
         <v>4</v>
       </c>
       <c r="K26">
+        <v>4</v>
+      </c>
+      <c r="L26">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L26">
+      <c r="M26">
         <v>6</v>
       </c>
-      <c r="M26">
-        <f t="shared" si="7"/>
+      <c r="N26">
+        <f t="shared" si="9"/>
         <v>6</v>
       </c>
-      <c r="N26">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="O26" t="s">
+      <c r="O26">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="P26" t="s">
         <v>9</v>
       </c>
-      <c r="P26">
+      <c r="Q26">
         <v>1177</v>
       </c>
-      <c r="Q26">
+      <c r="R26">
         <v>26</v>
       </c>
-      <c r="R26">
+      <c r="S26">
         <v>4</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>46923.27</v>
       </c>
-      <c r="T26">
+      <c r="U26">
         <f t="shared" si="6"/>
         <v>63.165120418930741</v>
       </c>
-      <c r="U26">
+      <c r="V26">
         <v>33</v>
       </c>
-      <c r="V26">
+      <c r="W26">
         <v>3</v>
       </c>
-      <c r="W26">
+      <c r="X26">
         <v>48</v>
       </c>
-      <c r="X26" s="1">
+      <c r="Y26" s="1">
         <v>27000</v>
       </c>
-      <c r="Y26" s="6">
+      <c r="Z26" s="6">
         <v>2.4263958971555422E-3</v>
       </c>
-      <c r="Z26">
+      <c r="AA26">
         <v>1130608</v>
       </c>
-      <c r="AA26">
+      <c r="AB26">
         <v>7506</v>
       </c>
-      <c r="AB26">
+      <c r="AC26">
         <v>38</v>
       </c>
-      <c r="AC26">
+      <c r="AD26">
         <v>0.41615010000000002</v>
       </c>
-      <c r="AD26">
+      <c r="AE26">
         <v>37</v>
       </c>
-      <c r="AE26" t="s">
+      <c r="AF26" t="s">
         <v>137</v>
       </c>
-      <c r="AF26" s="4">
+      <c r="AG26" s="4">
         <v>400000</v>
       </c>
-      <c r="AG26" s="5">
-        <f>AF26/D26</f>
+      <c r="AH26" s="5">
+        <f t="shared" si="7"/>
         <v>0.13495668227890553</v>
       </c>
     </row>
-    <row r="27" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>35</v>
       </c>
@@ -4148,99 +4254,103 @@
         <v>6151548</v>
       </c>
       <c r="F27">
+        <f t="shared" si="8"/>
+        <v>8733</v>
+      </c>
+      <c r="G27">
         <f t="shared" si="0"/>
         <v>148803</v>
       </c>
-      <c r="G27">
+      <c r="H27">
         <f t="shared" si="1"/>
         <v>2.4753147229350252</v>
       </c>
-      <c r="H27" s="2">
+      <c r="I27" s="2">
         <f t="shared" si="2"/>
         <v>1.4196426655534509E-3</v>
       </c>
-      <c r="I27">
-        <v>8</v>
-      </c>
       <c r="J27">
         <v>8</v>
       </c>
       <c r="K27">
+        <v>8</v>
+      </c>
+      <c r="L27">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L27">
+      <c r="M27">
         <v>10</v>
       </c>
-      <c r="M27">
-        <f t="shared" si="7"/>
+      <c r="N27">
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
-      <c r="N27">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="O27" t="s">
+      <c r="O27">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="P27" t="s">
         <v>9</v>
       </c>
-      <c r="P27">
+      <c r="Q27">
         <v>2819</v>
       </c>
-      <c r="Q27">
+      <c r="R27">
         <v>18</v>
       </c>
-      <c r="R27">
+      <c r="S27">
         <v>4</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>68741.52</v>
       </c>
-      <c r="T27">
+      <c r="U27">
         <f t="shared" si="6"/>
         <v>89.615140893014868</v>
       </c>
-      <c r="U27">
+      <c r="V27">
         <v>29</v>
       </c>
-      <c r="V27">
+      <c r="W27">
         <v>4.3</v>
       </c>
-      <c r="W27">
+      <c r="X27">
         <v>41</v>
       </c>
-      <c r="X27" s="1">
+      <c r="Y27" s="1">
         <v>54000</v>
       </c>
-      <c r="Y27" s="6">
+      <c r="Z27" s="6">
         <v>4.9513267401302703E-3</v>
       </c>
-      <c r="Z27">
+      <c r="AA27">
         <v>703058</v>
       </c>
-      <c r="AA27">
+      <c r="AB27">
         <v>8638</v>
       </c>
-      <c r="AB27">
+      <c r="AC27">
         <v>11.5</v>
       </c>
-      <c r="AC27">
+      <c r="AD27">
         <v>0.42164180000000001</v>
       </c>
-      <c r="AD27">
+      <c r="AE27">
         <v>35</v>
       </c>
-      <c r="AE27" t="s">
+      <c r="AF27" t="s">
         <v>137</v>
       </c>
-      <c r="AF27" s="4">
+      <c r="AG27" s="4">
         <v>501650</v>
       </c>
-      <c r="AG27" s="5">
-        <f>AF27/D27</f>
+      <c r="AH27" s="5">
+        <f t="shared" si="7"/>
         <v>8.1432973593250052E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>36</v>
       </c>
@@ -4257,99 +4367,103 @@
         <v>1080577</v>
       </c>
       <c r="F28">
+        <f t="shared" si="8"/>
+        <v>4830</v>
+      </c>
+      <c r="G28">
         <f t="shared" si="0"/>
         <v>90991</v>
       </c>
-      <c r="G28">
+      <c r="H28">
         <f t="shared" si="1"/>
         <v>9.1501946871329505</v>
       </c>
-      <c r="H28" s="2">
+      <c r="I28" s="2">
         <f t="shared" si="2"/>
         <v>4.4698341719285163E-3</v>
       </c>
-      <c r="I28">
+      <c r="J28">
         <v>1</v>
       </c>
-      <c r="J28">
+      <c r="K28">
         <v>2</v>
       </c>
-      <c r="K28">
+      <c r="L28">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
-      <c r="L28">
+      <c r="M28">
         <v>3</v>
       </c>
-      <c r="M28">
-        <f t="shared" si="7"/>
+      <c r="N28">
+        <f t="shared" si="9"/>
         <v>4</v>
       </c>
-      <c r="N28">
-        <f t="shared" si="8"/>
+      <c r="O28">
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
-      <c r="O28" t="s">
+      <c r="P28" t="s">
         <v>9</v>
       </c>
-      <c r="P28">
+      <c r="Q28">
         <v>228</v>
       </c>
-      <c r="Q28">
+      <c r="R28">
         <v>5</v>
       </c>
-      <c r="R28">
-        <v>0</v>
-      </c>
-      <c r="S28" s="3">
+      <c r="S28">
+        <v>0</v>
+      </c>
+      <c r="T28" s="3">
         <v>145545.79999999999</v>
       </c>
-      <c r="T28">
+      <c r="U28">
         <f t="shared" si="6"/>
         <v>7.4574944794009861</v>
       </c>
-      <c r="U28">
+      <c r="V28">
         <v>49</v>
       </c>
-      <c r="V28">
+      <c r="W28">
         <v>3.8</v>
       </c>
-      <c r="W28">
+      <c r="X28">
         <v>46</v>
       </c>
-      <c r="X28" s="1">
+      <c r="Y28" s="1">
         <v>4000</v>
       </c>
-      <c r="Y28" s="6">
+      <c r="Z28" s="6">
         <v>3.4862345327097891E-4</v>
       </c>
-      <c r="Z28">
+      <c r="AA28">
         <v>7787</v>
       </c>
-      <c r="AA28">
+      <c r="AB28">
         <v>1893</v>
       </c>
-      <c r="AB28">
+      <c r="AC28">
         <v>0.7</v>
       </c>
-      <c r="AC28">
+      <c r="AD28">
         <v>0.41602820000000001</v>
       </c>
-      <c r="AD28">
+      <c r="AE28">
         <v>38</v>
       </c>
-      <c r="AE28" t="s">
+      <c r="AF28" t="s">
         <v>138</v>
       </c>
-      <c r="AF28" s="4">
+      <c r="AG28" s="4">
         <v>635500</v>
       </c>
-      <c r="AG28" s="5">
-        <f>AF28/D28</f>
+      <c r="AH28" s="5">
+        <f t="shared" si="7"/>
         <v>0.58549465776432252</v>
       </c>
     </row>
-    <row r="29" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>37</v>
       </c>
@@ -4366,97 +4480,101 @@
         <v>1937552</v>
       </c>
       <c r="F29">
+        <f t="shared" si="8"/>
+        <v>25781</v>
+      </c>
+      <c r="G29">
         <f t="shared" si="0"/>
         <v>131508</v>
       </c>
-      <c r="G29">
+      <c r="H29">
         <f t="shared" si="1"/>
         <v>7.1790700530891334</v>
       </c>
-      <c r="H29" s="2">
+      <c r="I29" s="2">
         <f t="shared" si="2"/>
         <v>1.330596546570105E-2</v>
       </c>
-      <c r="I29">
-        <v>3</v>
-      </c>
       <c r="J29">
         <v>3</v>
       </c>
       <c r="K29">
+        <v>3</v>
+      </c>
+      <c r="L29">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L29">
+      <c r="M29">
         <v>5</v>
       </c>
-      <c r="M29">
-        <f t="shared" si="7"/>
+      <c r="N29">
+        <f t="shared" si="9"/>
         <v>5</v>
       </c>
-      <c r="N29">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="O29" t="s">
+      <c r="O29">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="P29" t="s">
         <v>9</v>
       </c>
-      <c r="P29">
+      <c r="Q29">
         <v>214</v>
       </c>
-      <c r="Q29">
+      <c r="R29">
         <v>4</v>
       </c>
-      <c r="R29">
+      <c r="S29">
         <v>1</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>76824.17</v>
       </c>
-      <c r="T29">
+      <c r="U29">
         <f t="shared" si="6"/>
         <v>25.556188892115593</v>
       </c>
-      <c r="U29">
+      <c r="V29">
         <v>44</v>
       </c>
-      <c r="V29">
+      <c r="W29">
         <v>11.3</v>
       </c>
-      <c r="W29">
+      <c r="X29">
         <v>20</v>
       </c>
-      <c r="X29" s="1">
+      <c r="Y29" s="1">
         <v>41000</v>
       </c>
-      <c r="Y29" s="6">
+      <c r="Z29" s="6">
         <v>3.7471223651725965E-3</v>
       </c>
-      <c r="Z29">
+      <c r="AA29">
         <v>94659</v>
       </c>
-      <c r="AA29">
+      <c r="AB29">
         <v>3635</v>
       </c>
-      <c r="AB29">
+      <c r="AC29">
         <v>4.9000000000000004</v>
       </c>
-      <c r="AC29">
+      <c r="AD29">
         <v>0.4021595</v>
       </c>
-      <c r="AD29">
+      <c r="AE29">
         <v>40</v>
       </c>
-      <c r="AE29" t="s">
+      <c r="AF29" t="s">
         <v>137</v>
       </c>
-      <c r="AF29" s="4"/>
-      <c r="AG29" s="5">
-        <f>AF29/D29</f>
+      <c r="AG29" s="4"/>
+      <c r="AH29" s="5">
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>38</v>
       </c>
@@ -4473,99 +4591,103 @@
         <v>3138259</v>
       </c>
       <c r="F30">
+        <f t="shared" si="8"/>
+        <v>-29797</v>
+      </c>
+      <c r="G30">
         <f t="shared" si="0"/>
         <v>399030</v>
       </c>
-      <c r="G30">
+      <c r="H30">
         <f t="shared" si="1"/>
         <v>14.72744102823027</v>
       </c>
-      <c r="H30" s="2">
+      <c r="I30" s="2">
         <f t="shared" si="2"/>
         <v>-9.4947548943538438E-3</v>
       </c>
-      <c r="I30">
-        <v>4</v>
-      </c>
       <c r="J30">
         <v>4</v>
       </c>
       <c r="K30">
+        <v>4</v>
+      </c>
+      <c r="L30">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L30">
+      <c r="M30">
         <v>6</v>
       </c>
-      <c r="M30">
-        <f t="shared" si="7"/>
+      <c r="N30">
+        <f t="shared" si="9"/>
         <v>6</v>
       </c>
-      <c r="N30">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="O30" t="s">
+      <c r="O30">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="P30" t="s">
         <v>12</v>
       </c>
-      <c r="P30">
+      <c r="Q30">
         <v>1279</v>
       </c>
-      <c r="Q30">
+      <c r="R30">
         <v>32</v>
       </c>
-      <c r="R30">
+      <c r="S30">
         <v>6</v>
       </c>
-      <c r="S30" s="3">
+      <c r="T30" s="3">
         <v>109781.18</v>
       </c>
-      <c r="T30">
+      <c r="U30">
         <f t="shared" si="6"/>
         <v>28.315071854756891</v>
       </c>
-      <c r="U30">
+      <c r="V30">
         <v>43</v>
       </c>
-      <c r="V30">
+      <c r="W30">
         <v>29.2</v>
       </c>
-      <c r="W30">
+      <c r="X30">
         <v>5</v>
       </c>
-      <c r="X30" s="1">
+      <c r="Y30" s="1">
         <v>162000</v>
       </c>
-      <c r="Y30" s="6">
+      <c r="Z30" s="6">
         <v>1.4781831764217334E-2</v>
       </c>
-      <c r="Z30">
+      <c r="AA30">
         <v>296184</v>
       </c>
-      <c r="AA30">
+      <c r="AB30">
         <v>5444</v>
       </c>
-      <c r="AB30">
+      <c r="AC30">
         <v>9.6</v>
       </c>
-      <c r="AC30">
+      <c r="AD30">
         <v>0.5122312</v>
       </c>
-      <c r="AD30">
+      <c r="AE30">
         <v>22</v>
       </c>
-      <c r="AE30" t="s">
+      <c r="AF30" t="s">
         <v>138</v>
       </c>
-      <c r="AF30" s="4">
+      <c r="AG30" s="4">
         <v>5000000</v>
       </c>
-      <c r="AG30" s="5">
-        <f>AF30/D30</f>
+      <c r="AH30" s="5">
+        <f t="shared" si="7"/>
         <v>1.6085125055413256</v>
       </c>
     </row>
-    <row r="31" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>39</v>
       </c>
@@ -4582,97 +4704,101 @@
         <v>1366275</v>
       </c>
       <c r="F31">
+        <f t="shared" si="8"/>
+        <v>12814</v>
+      </c>
+      <c r="G31">
         <f t="shared" si="0"/>
         <v>57644</v>
       </c>
-      <c r="G31">
+      <c r="H31">
         <f t="shared" si="1"/>
         <v>4.3621944159613149</v>
       </c>
-      <c r="H31" s="2">
+      <c r="I31" s="2">
         <f t="shared" si="2"/>
         <v>9.3787853836160371E-3</v>
       </c>
-      <c r="I31">
-        <v>2</v>
-      </c>
       <c r="J31">
         <v>2</v>
       </c>
       <c r="K31">
+        <v>2</v>
+      </c>
+      <c r="L31">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L31">
+      <c r="M31">
         <v>4</v>
       </c>
-      <c r="M31">
-        <f t="shared" si="7"/>
+      <c r="N31">
+        <f t="shared" si="9"/>
         <v>4</v>
       </c>
-      <c r="N31">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="O31" t="s">
+      <c r="O31">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="P31" t="s">
         <v>12</v>
       </c>
-      <c r="P31">
+      <c r="Q31">
         <v>415</v>
       </c>
-      <c r="Q31">
+      <c r="R31">
         <v>4</v>
       </c>
-      <c r="R31">
+      <c r="S31">
         <v>1</v>
       </c>
-      <c r="S31" s="3">
+      <c r="T31" s="3">
         <v>8952.65</v>
       </c>
-      <c r="T31">
+      <c r="U31">
         <f t="shared" si="6"/>
         <v>154.0425460617806</v>
       </c>
-      <c r="U31">
+      <c r="V31">
         <v>22</v>
       </c>
-      <c r="V31">
+      <c r="W31">
         <v>4</v>
       </c>
-      <c r="W31">
+      <c r="X31">
         <v>42</v>
       </c>
-      <c r="X31" s="1">
+      <c r="Y31" s="1">
         <v>11000</v>
       </c>
-      <c r="Y31" s="6">
+      <c r="Z31" s="6">
         <v>1.0264600366713149E-3</v>
       </c>
-      <c r="Z31">
+      <c r="AA31">
         <v>22000</v>
       </c>
-      <c r="AA31">
+      <c r="AB31">
         <v>1840</v>
       </c>
-      <c r="AB31">
+      <c r="AC31">
         <v>1.6</v>
       </c>
-      <c r="AC31">
+      <c r="AD31">
         <v>0.53748879999999999</v>
       </c>
-      <c r="AD31">
+      <c r="AE31">
         <v>19</v>
       </c>
-      <c r="AE31" t="s">
+      <c r="AF31" t="s">
         <v>137</v>
       </c>
-      <c r="AF31" s="4"/>
-      <c r="AG31" s="5">
-        <f>AF31/D31</f>
+      <c r="AG31" s="4"/>
+      <c r="AH31" s="5">
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>40</v>
       </c>
@@ -4689,99 +4815,103 @@
         <v>8882371</v>
       </c>
       <c r="F32">
+        <f t="shared" si="8"/>
+        <v>412122</v>
+      </c>
+      <c r="G32">
         <f t="shared" si="0"/>
         <v>486992</v>
       </c>
-      <c r="G32">
+      <c r="H32">
         <f t="shared" si="1"/>
         <v>5.5292869112362295</v>
       </c>
-      <c r="H32" s="2">
+      <c r="I32" s="2">
         <f t="shared" si="2"/>
         <v>4.6397746727759967E-2</v>
       </c>
-      <c r="I32">
-        <v>12</v>
-      </c>
       <c r="J32">
         <v>12</v>
       </c>
       <c r="K32">
+        <v>12</v>
+      </c>
+      <c r="L32">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L32">
+      <c r="M32">
         <v>14</v>
       </c>
-      <c r="M32">
-        <f t="shared" si="7"/>
+      <c r="N32">
+        <f t="shared" si="9"/>
         <v>14</v>
       </c>
-      <c r="N32">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="O32" t="s">
+      <c r="O32">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="P32" t="s">
         <v>12</v>
       </c>
-      <c r="P32">
+      <c r="Q32">
         <v>22255</v>
       </c>
-      <c r="Q32">
+      <c r="R32">
         <v>355</v>
       </c>
-      <c r="R32">
+      <c r="S32">
         <v>88</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>7354.22</v>
       </c>
-      <c r="T32">
+      <c r="U32">
         <f t="shared" si="6"/>
         <v>1263.8312424703095</v>
       </c>
-      <c r="U32">
+      <c r="V32">
         <v>2</v>
       </c>
-      <c r="V32">
+      <c r="W32">
         <v>20.9</v>
       </c>
-      <c r="W32">
+      <c r="X32">
         <v>8</v>
       </c>
-      <c r="X32" s="1">
+      <c r="Y32" s="1">
         <v>425000</v>
       </c>
-      <c r="Y32" s="6">
+      <c r="Z32" s="6">
         <v>3.8706204889950788E-2</v>
       </c>
-      <c r="Z32">
+      <c r="AA32">
         <v>1203843</v>
       </c>
-      <c r="AA32">
+      <c r="AB32">
         <v>10689</v>
       </c>
-      <c r="AB32">
+      <c r="AC32">
         <v>13.6</v>
       </c>
-      <c r="AC32">
+      <c r="AD32">
         <v>0.58071280000000003</v>
       </c>
-      <c r="AD32">
+      <c r="AE32">
         <v>14</v>
       </c>
-      <c r="AE32" t="s">
+      <c r="AF32" t="s">
         <v>138</v>
       </c>
-      <c r="AF32" s="4">
+      <c r="AG32" s="4">
         <v>9000000</v>
       </c>
-      <c r="AG32" s="5">
-        <f>AF32/D32</f>
+      <c r="AH32" s="5">
+        <f t="shared" si="7"/>
         <v>0.96831532392353192</v>
       </c>
     </row>
-    <row r="33" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>41</v>
       </c>
@@ -4798,99 +4928,103 @@
         <v>2106319</v>
       </c>
       <c r="F33">
+        <f t="shared" si="8"/>
+        <v>13901</v>
+      </c>
+      <c r="G33">
         <f t="shared" si="0"/>
         <v>52947</v>
       </c>
-      <c r="G33">
+      <c r="H33">
         <f t="shared" si="1"/>
         <v>2.5612001898152785</v>
       </c>
-      <c r="H33" s="2">
+      <c r="I33" s="2">
         <f t="shared" si="2"/>
         <v>6.5996651029592386E-3</v>
       </c>
-      <c r="I33">
-        <v>3</v>
-      </c>
       <c r="J33">
         <v>3</v>
       </c>
       <c r="K33">
+        <v>3</v>
+      </c>
+      <c r="L33">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="L33">
+      <c r="M33">
         <v>5</v>
       </c>
-      <c r="M33">
-        <f t="shared" si="7"/>
+      <c r="N33">
+        <f t="shared" si="9"/>
         <v>5</v>
       </c>
-      <c r="N33">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="O33" t="s">
+      <c r="O33">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="P33" t="s">
         <v>12</v>
       </c>
-      <c r="P33">
+      <c r="Q33">
         <v>363</v>
       </c>
-      <c r="Q33">
+      <c r="R33">
         <v>6</v>
       </c>
-      <c r="R33">
+      <c r="S33">
         <v>1</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>121298.15</v>
       </c>
-      <c r="T33">
+      <c r="U33">
         <f t="shared" si="6"/>
         <v>17.479409207807375</v>
       </c>
-      <c r="U33">
+      <c r="V33">
         <v>46</v>
       </c>
-      <c r="V33">
+      <c r="W33">
         <v>49.3</v>
       </c>
-      <c r="W33">
+      <c r="X33">
         <v>1</v>
       </c>
-      <c r="X33" s="1">
+      <c r="Y33" s="1">
         <v>71000</v>
       </c>
-      <c r="Y33" s="6">
+      <c r="Z33" s="6">
         <v>6.4332024548798411E-3</v>
       </c>
-      <c r="Z33">
+      <c r="AA33">
         <v>48337</v>
       </c>
-      <c r="AA33">
+      <c r="AB33">
         <v>3861</v>
       </c>
-      <c r="AB33">
+      <c r="AC33">
         <v>2.2999999999999998</v>
       </c>
-      <c r="AC33">
+      <c r="AD33">
         <v>0.55518489999999998</v>
       </c>
-      <c r="AD33">
+      <c r="AE33">
         <v>16</v>
       </c>
-      <c r="AE33" t="s">
+      <c r="AF33" t="s">
         <v>138</v>
       </c>
-      <c r="AF33" s="4">
+      <c r="AG33" s="4">
         <v>11500000</v>
       </c>
-      <c r="AG33" s="5">
-        <f>AF33/D33</f>
+      <c r="AH33" s="5">
+        <f t="shared" si="7"/>
         <v>5.4239654375489339</v>
       </c>
     </row>
-    <row r="34" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>42</v>
       </c>
@@ -4907,99 +5041,103 @@
         <v>19336776</v>
       </c>
       <c r="F34">
-        <f t="shared" ref="F34:F52" si="9">D34-C34</f>
+        <f t="shared" si="8"/>
+        <v>878975</v>
+      </c>
+      <c r="G34">
+        <f t="shared" ref="G34:G52" si="11">D34-C34</f>
         <v>794696</v>
       </c>
-      <c r="G34">
-        <f t="shared" ref="G34:G52" si="10">F34/C34*100</f>
+      <c r="H34">
+        <f t="shared" ref="H34:H52" si="12">G34/C34*100</f>
         <v>4.0919301242903643</v>
       </c>
-      <c r="H34" s="2">
-        <f t="shared" ref="H34:H52" si="11">(D34-E34)/E34</f>
+      <c r="I34" s="2">
+        <f t="shared" ref="I34:I52" si="13">(D34-E34)/E34</f>
         <v>4.5456129811919009E-2</v>
       </c>
-      <c r="I34">
+      <c r="J34">
         <v>27</v>
       </c>
-      <c r="J34">
+      <c r="K34">
         <v>26</v>
       </c>
-      <c r="K34">
-        <f t="shared" ref="K34:K52" si="12">J34-I34</f>
+      <c r="L34">
+        <f t="shared" ref="L34:L52" si="14">K34-J34</f>
         <v>-1</v>
       </c>
-      <c r="L34">
+      <c r="M34">
         <v>29</v>
       </c>
-      <c r="M34">
-        <f t="shared" si="7"/>
+      <c r="N34">
+        <f t="shared" si="9"/>
         <v>28</v>
       </c>
-      <c r="N34">
-        <f t="shared" si="8"/>
+      <c r="O34">
+        <f t="shared" si="10"/>
         <v>-1</v>
       </c>
-      <c r="O34" t="s">
+      <c r="P34" t="s">
         <v>12</v>
       </c>
-      <c r="P34">
+      <c r="Q34">
         <v>133197</v>
       </c>
-      <c r="Q34">
+      <c r="R34">
         <v>3069</v>
       </c>
-      <c r="R34">
+      <c r="S34">
         <v>666</v>
       </c>
-      <c r="S34" s="3">
+      <c r="T34" s="3">
         <v>47126.400000000001</v>
       </c>
-      <c r="T34">
-        <f t="shared" ref="T34:T52" si="13">D34/S34</f>
+      <c r="U34">
+        <f t="shared" ref="U34:U52" si="15">D34/T34</f>
         <v>428.96870968289534</v>
       </c>
-      <c r="U34">
+      <c r="V34">
         <v>8</v>
       </c>
-      <c r="V34">
+      <c r="W34">
         <v>19.3</v>
       </c>
-      <c r="W34">
+      <c r="X34">
         <v>9</v>
       </c>
-      <c r="X34" s="1">
+      <c r="Y34" s="1">
         <v>866000</v>
       </c>
-      <c r="Y34" s="6">
+      <c r="Z34" s="6">
         <v>7.8852265943519587E-2</v>
       </c>
-      <c r="Z34">
+      <c r="AA34">
         <v>3084304</v>
       </c>
-      <c r="AA34">
+      <c r="AB34">
         <v>17635</v>
       </c>
-      <c r="AB34">
+      <c r="AC34">
         <v>15.9</v>
       </c>
-      <c r="AC34">
+      <c r="AD34">
         <v>0.6171683</v>
       </c>
-      <c r="AD34">
+      <c r="AE34">
         <v>7</v>
       </c>
-      <c r="AE34" t="s">
+      <c r="AF34" t="s">
         <v>138</v>
       </c>
-      <c r="AF34" s="4">
+      <c r="AG34" s="4">
         <v>20000000</v>
       </c>
-      <c r="AG34" s="5">
-        <f>AF34/D34</f>
+      <c r="AH34" s="5">
+        <f t="shared" ref="AH34:AH65" si="16">AG34/D34</f>
         <v>0.98932757927222192</v>
       </c>
     </row>
-    <row r="35" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>43</v>
       </c>
@@ -5016,99 +5154,103 @@
         <v>10600823</v>
       </c>
       <c r="F35">
+        <f t="shared" si="8"/>
+        <v>-146875</v>
+      </c>
+      <c r="G35">
+        <f t="shared" si="11"/>
+        <v>888167</v>
+      </c>
+      <c r="H35">
+        <f t="shared" si="12"/>
+        <v>9.2848351849159005</v>
+      </c>
+      <c r="I35" s="2">
+        <f t="shared" si="13"/>
+        <v>-1.3855056347983548E-2</v>
+      </c>
+      <c r="J35">
+        <v>13</v>
+      </c>
+      <c r="K35">
+        <v>14</v>
+      </c>
+      <c r="L35">
+        <f t="shared" si="14"/>
+        <v>1</v>
+      </c>
+      <c r="M35">
+        <v>15</v>
+      </c>
+      <c r="N35">
         <f t="shared" si="9"/>
-        <v>888167</v>
-      </c>
-      <c r="G35">
+        <v>16</v>
+      </c>
+      <c r="O35">
         <f t="shared" si="10"/>
-        <v>9.2848351849159005</v>
-      </c>
-      <c r="H35" s="2">
-        <f t="shared" si="11"/>
-        <v>-1.3855056347983548E-2</v>
-      </c>
-      <c r="I35">
-        <v>13</v>
-      </c>
-      <c r="J35">
-        <v>14</v>
-      </c>
-      <c r="K35">
-        <f t="shared" si="12"/>
         <v>1</v>
       </c>
-      <c r="L35">
-        <v>15</v>
-      </c>
-      <c r="M35">
-        <f t="shared" si="7"/>
+      <c r="P35" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q35">
+        <v>1584</v>
+      </c>
+      <c r="R35">
+        <v>9</v>
+      </c>
+      <c r="S35">
+        <v>1</v>
+      </c>
+      <c r="T35" s="3">
+        <v>48617.91</v>
+      </c>
+      <c r="U35">
+        <f t="shared" si="15"/>
+        <v>215.02257090031225</v>
+      </c>
+      <c r="V35">
         <v>16</v>
       </c>
-      <c r="N35">
-        <f t="shared" si="8"/>
-        <v>1</v>
-      </c>
-      <c r="O35" t="s">
-        <v>9</v>
-      </c>
-      <c r="P35">
-        <v>1584</v>
-      </c>
-      <c r="Q35">
-        <v>9</v>
-      </c>
-      <c r="R35">
-        <v>1</v>
-      </c>
-      <c r="S35" s="3">
-        <v>48617.91</v>
-      </c>
-      <c r="T35">
-        <f t="shared" si="13"/>
-        <v>215.02257090031225</v>
-      </c>
-      <c r="U35">
-        <v>16</v>
-      </c>
-      <c r="V35">
+      <c r="W35">
         <v>9.8000000000000007</v>
       </c>
-      <c r="W35">
+      <c r="X35">
         <v>26</v>
       </c>
-      <c r="X35" s="1">
+      <c r="Y35" s="1">
         <v>298000</v>
       </c>
-      <c r="Y35" s="6">
+      <c r="Z35" s="6">
         <v>2.7137862459207431E-2</v>
       </c>
-      <c r="Z35">
+      <c r="AA35">
         <v>2253481</v>
       </c>
-      <c r="AA35">
+      <c r="AB35">
         <v>14903</v>
       </c>
-      <c r="AB35">
+      <c r="AC35">
         <v>21.5</v>
       </c>
-      <c r="AC35">
+      <c r="AD35">
         <v>0.49315799999999999</v>
       </c>
-      <c r="AD35">
+      <c r="AE35">
         <v>27</v>
       </c>
-      <c r="AE35" t="s">
+      <c r="AF35" t="s">
         <v>138</v>
       </c>
-      <c r="AF35" s="4">
-        <v>0</v>
-      </c>
-      <c r="AG35" s="5">
-        <f>AF35/D35</f>
+      <c r="AG35" s="4">
+        <v>0</v>
+      </c>
+      <c r="AH35" s="5">
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>44</v>
       </c>
@@ -5125,99 +5267,103 @@
         <v>765309</v>
       </c>
       <c r="F36">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
+        <v>14393</v>
+      </c>
+      <c r="G36">
+        <f t="shared" si="11"/>
         <v>103797</v>
       </c>
-      <c r="G36">
-        <f t="shared" si="10"/>
+      <c r="H36">
+        <f t="shared" si="12"/>
         <v>15.356743921113175</v>
       </c>
-      <c r="H36" s="2">
-        <f t="shared" si="11"/>
+      <c r="I36" s="2">
+        <f t="shared" si="13"/>
         <v>1.8806782619830684E-2</v>
-      </c>
-      <c r="I36">
-        <v>1</v>
       </c>
       <c r="J36">
         <v>1</v>
       </c>
       <c r="K36">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L36">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="M36">
         <v>3</v>
       </c>
-      <c r="M36">
-        <f t="shared" si="7"/>
+      <c r="N36">
+        <f t="shared" si="9"/>
         <v>3</v>
       </c>
-      <c r="N36">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="O36" t="s">
+      <c r="O36">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="P36" t="s">
         <v>9</v>
       </c>
-      <c r="P36">
+      <c r="Q36">
         <v>147</v>
       </c>
-      <c r="Q36">
+      <c r="R36">
         <v>3</v>
       </c>
-      <c r="R36">
-        <v>0</v>
-      </c>
-      <c r="S36" s="3">
+      <c r="S36">
+        <v>0</v>
+      </c>
+      <c r="T36" s="3">
         <v>69000.800000000003</v>
       </c>
-      <c r="T36">
-        <f t="shared" si="13"/>
+      <c r="U36">
+        <f t="shared" si="15"/>
         <v>11.299897972197423</v>
       </c>
-      <c r="U36">
+      <c r="V36">
         <v>48</v>
       </c>
-      <c r="V36">
+      <c r="W36">
         <v>4</v>
       </c>
-      <c r="W36">
+      <c r="X36">
         <v>43</v>
       </c>
-      <c r="X36" s="1">
+      <c r="Y36" s="1">
         <v>5000</v>
       </c>
-      <c r="Y36" s="6">
+      <c r="Z36" s="6">
         <v>4.8200798385366272E-4</v>
       </c>
-      <c r="Z36">
+      <c r="AA36">
         <v>22256</v>
       </c>
-      <c r="AA36">
+      <c r="AB36">
         <v>2558</v>
       </c>
-      <c r="AB36">
+      <c r="AC36">
         <v>2.9</v>
       </c>
-      <c r="AC36">
+      <c r="AD36">
         <v>0.3278259</v>
       </c>
-      <c r="AD36">
+      <c r="AE36">
         <v>49</v>
       </c>
-      <c r="AE36" t="s">
+      <c r="AF36" t="s">
         <v>137</v>
       </c>
-      <c r="AF36" s="4">
+      <c r="AG36" s="4">
         <v>1000000</v>
       </c>
-      <c r="AG36" s="5">
-        <f>AF36/D36</f>
+      <c r="AH36" s="5">
+        <f t="shared" si="16"/>
         <v>1.2825412785910515</v>
       </c>
     </row>
-    <row r="37" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>45</v>
       </c>
@@ -5234,99 +5380,103 @@
         <v>11693217</v>
       </c>
       <c r="F37">
+        <f t="shared" si="8"/>
+        <v>115631</v>
+      </c>
+      <c r="G37">
+        <f t="shared" si="11"/>
+        <v>240353</v>
+      </c>
+      <c r="H37">
+        <f t="shared" si="12"/>
+        <v>2.0776514144666183</v>
+      </c>
+      <c r="I37" s="2">
+        <f t="shared" si="13"/>
+        <v>9.8887243775600854E-3</v>
+      </c>
+      <c r="J37">
+        <v>16</v>
+      </c>
+      <c r="K37">
+        <v>15</v>
+      </c>
+      <c r="L37">
+        <f t="shared" si="14"/>
+        <v>-1</v>
+      </c>
+      <c r="M37">
+        <v>18</v>
+      </c>
+      <c r="N37">
         <f t="shared" si="9"/>
-        <v>240353</v>
-      </c>
-      <c r="G37">
+        <v>17</v>
+      </c>
+      <c r="O37">
         <f t="shared" si="10"/>
-        <v>2.0776514144666183</v>
-      </c>
-      <c r="H37" s="2">
-        <f t="shared" si="11"/>
-        <v>9.8887243775600854E-3</v>
-      </c>
-      <c r="I37">
-        <v>16</v>
-      </c>
-      <c r="J37">
-        <v>15</v>
-      </c>
-      <c r="K37">
-        <f t="shared" si="12"/>
         <v>-1</v>
       </c>
-      <c r="L37">
-        <v>18</v>
-      </c>
-      <c r="M37">
-        <f t="shared" si="7"/>
-        <v>17</v>
-      </c>
-      <c r="N37">
-        <f t="shared" si="8"/>
-        <v>-1</v>
-      </c>
-      <c r="O37" t="s">
+      <c r="P37" t="s">
         <v>9</v>
       </c>
-      <c r="P37">
+      <c r="Q37">
         <v>2547</v>
       </c>
-      <c r="Q37">
+      <c r="R37">
         <v>65</v>
       </c>
-      <c r="R37">
+      <c r="S37">
         <v>10</v>
       </c>
-      <c r="S37" s="3">
+      <c r="T37" s="3">
         <v>40860.69</v>
       </c>
-      <c r="T37">
-        <f t="shared" si="13"/>
+      <c r="U37">
+        <f t="shared" si="15"/>
         <v>289.00265756647769</v>
       </c>
-      <c r="U37">
+      <c r="V37">
         <v>11</v>
       </c>
-      <c r="V37">
+      <c r="W37">
         <v>4</v>
       </c>
-      <c r="W37">
+      <c r="X37">
         <v>44</v>
       </c>
-      <c r="X37" s="1">
+      <c r="Y37" s="1">
         <v>87000</v>
       </c>
-      <c r="Y37" s="6">
+      <c r="Z37" s="6">
         <v>7.9600360029181538E-3</v>
       </c>
-      <c r="Z37">
+      <c r="AA37">
         <v>1467331</v>
       </c>
-      <c r="AA37">
+      <c r="AB37">
         <v>13248</v>
       </c>
-      <c r="AB37">
+      <c r="AC37">
         <v>12.6</v>
       </c>
-      <c r="AC37">
+      <c r="AD37">
         <v>0.459233</v>
       </c>
-      <c r="AD37">
+      <c r="AE37">
         <v>30</v>
       </c>
-      <c r="AE37" t="s">
+      <c r="AF37" t="s">
         <v>137</v>
       </c>
-      <c r="AF37" s="4">
-        <v>0</v>
-      </c>
-      <c r="AG37" s="5">
-        <f>AF37/D37</f>
+      <c r="AG37" s="4">
+        <v>0</v>
+      </c>
+      <c r="AH37" s="5">
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>46</v>
       </c>
@@ -5343,99 +5493,103 @@
         <v>3980783</v>
       </c>
       <c r="F38">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
+        <v>-17267</v>
+      </c>
+      <c r="G38">
+        <f t="shared" si="11"/>
         <v>198634</v>
       </c>
-      <c r="G38">
-        <f t="shared" si="10"/>
+      <c r="H38">
+        <f t="shared" si="12"/>
         <v>5.2759688085841736</v>
       </c>
-      <c r="H38" s="2">
-        <f t="shared" si="11"/>
+      <c r="I38" s="2">
+        <f t="shared" si="13"/>
         <v>-4.3375888612868377E-3</v>
-      </c>
-      <c r="I38">
-        <v>5</v>
       </c>
       <c r="J38">
         <v>5</v>
       </c>
       <c r="K38">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L38">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="M38">
         <v>7</v>
       </c>
-      <c r="M38">
-        <f t="shared" si="7"/>
+      <c r="N38">
+        <f t="shared" si="9"/>
         <v>7</v>
       </c>
-      <c r="N38">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="O38" t="s">
+      <c r="O38">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="P38" t="s">
         <v>9</v>
       </c>
-      <c r="P38">
+      <c r="Q38">
         <v>1744</v>
       </c>
-      <c r="Q38">
+      <c r="R38">
         <v>36</v>
       </c>
-      <c r="R38">
+      <c r="S38">
         <v>5</v>
       </c>
-      <c r="S38" s="3">
+      <c r="T38" s="3">
         <v>68594.92</v>
       </c>
-      <c r="T38">
-        <f t="shared" si="13"/>
+      <c r="U38">
+        <f t="shared" si="15"/>
         <v>57.781480027967085</v>
       </c>
-      <c r="U38">
+      <c r="V38">
         <v>36</v>
       </c>
-      <c r="V38">
+      <c r="W38">
         <v>11.1</v>
       </c>
-      <c r="W38">
+      <c r="X38">
         <v>21</v>
       </c>
-      <c r="X38" s="1">
+      <c r="Y38" s="1">
         <v>92000</v>
       </c>
-      <c r="Y38" s="6">
+      <c r="Z38" s="6">
         <v>8.3754220653741284E-3</v>
       </c>
-      <c r="Z38">
+      <c r="AA38">
         <v>287414</v>
       </c>
-      <c r="AA38">
+      <c r="AB38">
         <v>6538</v>
       </c>
-      <c r="AB38">
+      <c r="AC38">
         <v>7.3</v>
       </c>
-      <c r="AC38">
+      <c r="AD38">
         <v>0.33059959999999999</v>
       </c>
-      <c r="AD38">
+      <c r="AE38">
         <v>48</v>
       </c>
-      <c r="AE38" t="s">
+      <c r="AF38" t="s">
         <v>137</v>
       </c>
-      <c r="AF38" s="4">
-        <v>0</v>
-      </c>
-      <c r="AG38" s="5">
-        <f>AF38/D38</f>
+      <c r="AG38" s="4">
+        <v>0</v>
+      </c>
+      <c r="AH38" s="5">
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>47</v>
       </c>
@@ -5452,99 +5606,103 @@
         <v>4241507</v>
       </c>
       <c r="F39">
+        <f t="shared" si="8"/>
+        <v>-7</v>
+      </c>
+      <c r="G39">
+        <f t="shared" si="11"/>
+        <v>392894</v>
+      </c>
+      <c r="H39">
+        <f t="shared" si="12"/>
+        <v>10.208735318710204</v>
+      </c>
+      <c r="I39" s="2">
+        <f t="shared" si="13"/>
+        <v>-1.6503568189325161E-6</v>
+      </c>
+      <c r="J39">
+        <v>5</v>
+      </c>
+      <c r="K39">
+        <v>6</v>
+      </c>
+      <c r="L39">
+        <f t="shared" si="14"/>
+        <v>1</v>
+      </c>
+      <c r="M39">
+        <v>7</v>
+      </c>
+      <c r="N39">
         <f t="shared" si="9"/>
-        <v>392894</v>
-      </c>
-      <c r="G39">
+        <v>8</v>
+      </c>
+      <c r="O39">
         <f t="shared" si="10"/>
-        <v>10.208735318710204</v>
-      </c>
-      <c r="H39" s="2">
-        <f t="shared" si="11"/>
-        <v>-1.6503568189325161E-6</v>
-      </c>
-      <c r="I39">
-        <v>5</v>
-      </c>
-      <c r="J39">
-        <v>6</v>
-      </c>
-      <c r="K39">
-        <f t="shared" si="12"/>
         <v>1</v>
       </c>
-      <c r="L39">
-        <v>7</v>
-      </c>
-      <c r="M39">
-        <f t="shared" si="7"/>
-        <v>8</v>
-      </c>
-      <c r="N39">
-        <f t="shared" si="8"/>
-        <v>1</v>
-      </c>
-      <c r="O39" t="s">
+      <c r="P39" t="s">
         <v>12</v>
       </c>
-      <c r="P39">
+      <c r="Q39">
         <v>736</v>
       </c>
-      <c r="Q39">
+      <c r="R39">
         <v>18</v>
       </c>
-      <c r="R39">
-        <v>0</v>
-      </c>
-      <c r="S39" s="3">
+      <c r="S39">
+        <v>0</v>
+      </c>
+      <c r="T39" s="3">
         <v>95988.01</v>
       </c>
-      <c r="T39">
-        <f t="shared" si="13"/>
+      <c r="U39">
+        <f t="shared" si="15"/>
         <v>44.187810540087249</v>
       </c>
-      <c r="U39">
+      <c r="V39">
         <v>40</v>
       </c>
-      <c r="V39">
+      <c r="W39">
         <v>13.4</v>
       </c>
-      <c r="W39">
+      <c r="X39">
         <v>14</v>
       </c>
-      <c r="X39" s="1">
+      <c r="Y39" s="1">
         <v>110000</v>
       </c>
-      <c r="Y39" s="6">
+      <c r="Z39" s="6">
         <v>1.0018798796430226E-2</v>
       </c>
-      <c r="Z39">
+      <c r="AA39">
         <v>77918</v>
       </c>
-      <c r="AA39">
+      <c r="AB39">
         <v>5485</v>
       </c>
-      <c r="AB39">
+      <c r="AC39">
         <v>1.8</v>
       </c>
-      <c r="AC39">
+      <c r="AD39">
         <v>0.58307160000000002</v>
       </c>
-      <c r="AD39">
+      <c r="AE39">
         <v>13</v>
       </c>
-      <c r="AE39" t="s">
+      <c r="AF39" t="s">
         <v>138</v>
       </c>
-      <c r="AF39" s="4">
+      <c r="AG39" s="4">
         <v>7730772</v>
       </c>
-      <c r="AG39" s="5">
-        <f>AF39/D39</f>
+      <c r="AH39" s="5">
+        <f t="shared" si="16"/>
         <v>1.8226504774254391</v>
       </c>
     </row>
-    <row r="40" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>48</v>
       </c>
@@ -5561,99 +5719,103 @@
         <v>12783254</v>
       </c>
       <c r="F40">
+        <f t="shared" si="8"/>
+        <v>228590</v>
+      </c>
+      <c r="G40">
+        <f t="shared" si="11"/>
+        <v>276939</v>
+      </c>
+      <c r="H40">
+        <f t="shared" si="12"/>
+        <v>2.1746451975888319</v>
+      </c>
+      <c r="I40" s="2">
+        <f t="shared" si="13"/>
+        <v>1.7881988420162816E-2</v>
+      </c>
+      <c r="J40">
+        <v>18</v>
+      </c>
+      <c r="K40">
+        <v>17</v>
+      </c>
+      <c r="L40">
+        <f t="shared" si="14"/>
+        <v>-1</v>
+      </c>
+      <c r="M40">
+        <v>20</v>
+      </c>
+      <c r="N40">
         <f t="shared" si="9"/>
-        <v>276939</v>
-      </c>
-      <c r="G40">
+        <v>19</v>
+      </c>
+      <c r="O40">
         <f t="shared" si="10"/>
-        <v>2.1746451975888319</v>
-      </c>
-      <c r="H40" s="2">
-        <f t="shared" si="11"/>
-        <v>1.7881988420162816E-2</v>
-      </c>
-      <c r="I40">
-        <v>18</v>
-      </c>
-      <c r="J40">
-        <v>17</v>
-      </c>
-      <c r="K40">
-        <f t="shared" si="12"/>
         <v>-1</v>
       </c>
-      <c r="L40">
-        <v>20</v>
-      </c>
-      <c r="M40">
-        <f t="shared" si="7"/>
-        <v>19</v>
-      </c>
-      <c r="N40">
-        <f t="shared" si="8"/>
-        <v>-1</v>
-      </c>
-      <c r="O40" t="s">
+      <c r="P40" t="s">
         <v>12</v>
       </c>
-      <c r="P40">
+      <c r="Q40">
         <v>5805</v>
       </c>
-      <c r="Q40">
+      <c r="R40">
         <v>74</v>
       </c>
-      <c r="R40">
+      <c r="S40">
         <v>11</v>
       </c>
-      <c r="S40" s="3">
+      <c r="T40" s="3">
         <v>44742.7</v>
       </c>
-      <c r="T40">
-        <f t="shared" si="13"/>
+      <c r="U40">
+        <f t="shared" si="15"/>
         <v>290.81490388376204</v>
       </c>
-      <c r="U40">
+      <c r="V40">
         <v>10</v>
       </c>
-      <c r="V40">
+      <c r="W40">
         <v>7.8</v>
       </c>
-      <c r="W40">
+      <c r="X40">
         <v>29</v>
       </c>
-      <c r="X40" s="1">
+      <c r="Y40" s="1">
         <v>157000</v>
       </c>
-      <c r="Y40" s="6">
+      <c r="Z40" s="6">
         <v>1.434764606728998E-2</v>
       </c>
-      <c r="Z40">
+      <c r="AA40">
         <v>1454753</v>
       </c>
-      <c r="AA40">
+      <c r="AB40">
         <v>14506</v>
       </c>
-      <c r="AB40">
+      <c r="AC40">
         <v>11.4</v>
       </c>
-      <c r="AC40">
+      <c r="AD40">
         <v>0.50589209999999996</v>
       </c>
-      <c r="AD40">
+      <c r="AE40">
         <v>23</v>
       </c>
-      <c r="AE40" t="s">
+      <c r="AF40" t="s">
         <v>138</v>
       </c>
-      <c r="AF40" s="4">
+      <c r="AG40" s="4">
         <v>4000000</v>
       </c>
-      <c r="AG40" s="5">
-        <f>AF40/D40</f>
+      <c r="AH40" s="5">
+        <f t="shared" si="16"/>
         <v>0.30741223150231434</v>
       </c>
     </row>
-    <row r="41" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>49</v>
       </c>
@@ -5670,99 +5832,103 @@
         <v>1057125</v>
       </c>
       <c r="F41">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
+        <v>41038</v>
+      </c>
+      <c r="G41">
+        <f t="shared" si="11"/>
         <v>42916</v>
       </c>
-      <c r="G41">
-        <f t="shared" si="10"/>
+      <c r="H41">
+        <f t="shared" si="12"/>
         <v>4.0669151392991401</v>
       </c>
-      <c r="H41" s="2">
-        <f t="shared" si="11"/>
+      <c r="I41" s="2">
+        <f t="shared" si="13"/>
         <v>3.8820385479484451E-2</v>
-      </c>
-      <c r="I41">
-        <v>2</v>
       </c>
       <c r="J41">
         <v>2</v>
       </c>
       <c r="K41">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L41">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="M41">
         <v>4</v>
       </c>
-      <c r="M41">
-        <f t="shared" si="7"/>
+      <c r="N41">
+        <f t="shared" si="9"/>
         <v>4</v>
       </c>
-      <c r="N41">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="O41" t="s">
+      <c r="O41">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="P41" t="s">
         <v>12</v>
       </c>
-      <c r="P41">
+      <c r="Q41">
         <v>682</v>
       </c>
-      <c r="Q41">
+      <c r="R41">
         <v>12</v>
       </c>
-      <c r="R41">
+      <c r="S41">
         <v>1</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1033.81</v>
       </c>
-      <c r="T41">
-        <f t="shared" si="13"/>
+      <c r="U41">
+        <f t="shared" si="15"/>
         <v>1062.2483821978894</v>
       </c>
-      <c r="U41">
+      <c r="V41">
         <v>3</v>
       </c>
-      <c r="V41">
+      <c r="W41">
         <v>16.3</v>
       </c>
-      <c r="W41">
+      <c r="X41">
         <v>12</v>
       </c>
-      <c r="X41" s="1">
+      <c r="Y41" s="1">
         <v>25000</v>
       </c>
-      <c r="Y41" s="6">
+      <c r="Z41" s="6">
         <v>2.2709345985391992E-3</v>
       </c>
-      <c r="Z41">
+      <c r="AA41">
         <v>78143</v>
       </c>
-      <c r="AA41">
+      <c r="AB41">
         <v>6572</v>
       </c>
-      <c r="AB41">
+      <c r="AC41">
         <v>7.4</v>
       </c>
-      <c r="AC41">
+      <c r="AD41">
         <v>0.60599360000000002</v>
       </c>
-      <c r="AD41">
+      <c r="AE41">
         <v>8</v>
       </c>
-      <c r="AE41" t="s">
+      <c r="AF41" t="s">
         <v>138</v>
       </c>
-      <c r="AF41" s="4">
+      <c r="AG41" s="4">
         <v>500000</v>
       </c>
-      <c r="AG41" s="5">
-        <f>AF41/D41</f>
+      <c r="AH41" s="5">
+        <f t="shared" si="16"/>
         <v>0.45530581525693364</v>
       </c>
     </row>
-    <row r="42" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>50</v>
       </c>
@@ -5779,99 +5945,103 @@
         <v>5218040</v>
       </c>
       <c r="F42">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
+        <v>-93328</v>
+      </c>
+      <c r="G42">
+        <f t="shared" si="11"/>
         <v>478737</v>
       </c>
-      <c r="G42">
-        <f t="shared" si="10"/>
+      <c r="H42">
+        <f t="shared" si="12"/>
         <v>10.304338701779498</v>
       </c>
-      <c r="H42" s="2">
-        <f t="shared" si="11"/>
+      <c r="I42" s="2">
+        <f t="shared" si="13"/>
         <v>-1.7885642885067957E-2</v>
-      </c>
-      <c r="I42">
-        <v>7</v>
       </c>
       <c r="J42">
         <v>7</v>
       </c>
       <c r="K42">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L42">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="M42">
         <v>9</v>
       </c>
-      <c r="M42">
-        <f t="shared" si="7"/>
+      <c r="N42">
+        <f t="shared" si="9"/>
         <v>9</v>
       </c>
-      <c r="N42">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="O42" t="s">
+      <c r="O42">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="P42" t="s">
         <v>9</v>
       </c>
-      <c r="P42">
+      <c r="Q42">
         <v>1349</v>
       </c>
-      <c r="Q42">
+      <c r="R42">
         <v>32</v>
       </c>
-      <c r="R42">
+      <c r="S42">
         <v>2</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>30060.7</v>
       </c>
-      <c r="T42">
-        <f t="shared" si="13"/>
+      <c r="U42">
+        <f t="shared" si="15"/>
         <v>170.47879789891786</v>
       </c>
-      <c r="U42">
+      <c r="V42">
         <v>20</v>
       </c>
-      <c r="V42">
+      <c r="W42">
         <v>5.8</v>
       </c>
-      <c r="W42">
+      <c r="X42">
         <v>35</v>
       </c>
-      <c r="X42" s="1">
+      <c r="Y42" s="1">
         <v>88000</v>
       </c>
-      <c r="Y42" s="6">
+      <c r="Z42" s="6">
         <v>8.0353984685408303E-3</v>
       </c>
-      <c r="Z42">
+      <c r="AA42">
         <v>1362917</v>
       </c>
-      <c r="AA42">
+      <c r="AB42">
         <v>8396</v>
       </c>
-      <c r="AB42">
+      <c r="AC42">
         <v>26.5</v>
       </c>
-      <c r="AC42">
+      <c r="AD42">
         <v>0.44073390000000001</v>
       </c>
-      <c r="AD42">
+      <c r="AE42">
         <v>33</v>
       </c>
-      <c r="AE42" t="s">
+      <c r="AF42" t="s">
         <v>137</v>
       </c>
-      <c r="AF42" s="4">
-        <v>0</v>
-      </c>
-      <c r="AG42" s="5">
-        <f>AF42/D42</f>
+      <c r="AG42" s="4">
+        <v>0</v>
+      </c>
+      <c r="AH42" s="5">
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>51</v>
       </c>
@@ -5888,99 +6058,103 @@
         <v>892717</v>
       </c>
       <c r="F43">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
+        <v>-4947</v>
+      </c>
+      <c r="G43">
+        <f t="shared" si="11"/>
         <v>68009</v>
       </c>
-      <c r="G43">
-        <f t="shared" si="10"/>
+      <c r="H43">
+        <f t="shared" si="12"/>
         <v>8.2961985261557949</v>
       </c>
-      <c r="H43" s="2">
-        <f t="shared" si="11"/>
+      <c r="I43" s="2">
+        <f t="shared" si="13"/>
         <v>-5.5415097953774826E-3</v>
-      </c>
-      <c r="I43">
-        <v>1</v>
       </c>
       <c r="J43">
         <v>1</v>
       </c>
       <c r="K43">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L43">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="M43">
         <v>3</v>
       </c>
-      <c r="M43">
-        <f t="shared" si="7"/>
+      <c r="N43">
+        <f t="shared" si="9"/>
         <v>3</v>
       </c>
-      <c r="N43">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="O43" t="s">
+      <c r="O43">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="P43" t="s">
         <v>9</v>
       </c>
-      <c r="P43">
+      <c r="Q43">
         <v>129</v>
       </c>
-      <c r="Q43">
+      <c r="R43">
         <v>2</v>
       </c>
-      <c r="R43">
+      <c r="S43">
         <v>1</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>75811</v>
       </c>
-      <c r="T43">
-        <f t="shared" si="13"/>
+      <c r="U43">
+        <f t="shared" si="15"/>
         <v>11.710305892284762</v>
       </c>
-      <c r="U43">
+      <c r="V43">
         <v>47</v>
       </c>
-      <c r="V43">
+      <c r="W43">
         <v>3.7</v>
       </c>
-      <c r="W43">
+      <c r="X43">
         <v>47</v>
       </c>
-      <c r="X43" s="1">
+      <c r="Y43" s="1">
         <v>6000</v>
       </c>
-      <c r="Y43" s="6">
+      <c r="Z43" s="6">
         <v>5.8496170868967167E-4</v>
       </c>
-      <c r="Z43">
+      <c r="AA43">
         <v>20866</v>
       </c>
-      <c r="AA43">
+      <c r="AB43">
         <v>2182</v>
       </c>
-      <c r="AB43">
+      <c r="AC43">
         <v>2.4</v>
       </c>
-      <c r="AC43">
+      <c r="AD43">
         <v>0.36565219999999998</v>
       </c>
-      <c r="AD43">
+      <c r="AE43">
         <v>45</v>
       </c>
-      <c r="AE43" t="s">
+      <c r="AF43" t="s">
         <v>137</v>
       </c>
-      <c r="AF43" s="4">
-        <v>0</v>
-      </c>
-      <c r="AG43" s="5">
-        <f>AF43/D43</f>
+      <c r="AG43" s="4">
+        <v>0</v>
+      </c>
+      <c r="AH43" s="5">
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>52</v>
       </c>
@@ -5997,99 +6171,103 @@
         <v>6886834</v>
       </c>
       <c r="F44">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
+        <v>30063</v>
+      </c>
+      <c r="G44">
+        <f t="shared" si="11"/>
         <v>541466</v>
       </c>
-      <c r="G44">
-        <f t="shared" si="10"/>
+      <c r="H44">
+        <f t="shared" si="12"/>
         <v>8.4930101196295578</v>
       </c>
-      <c r="H44" s="2">
-        <f t="shared" si="11"/>
+      <c r="I44" s="2">
+        <f t="shared" si="13"/>
         <v>4.3652859935349106E-3</v>
-      </c>
-      <c r="I44">
-        <v>9</v>
       </c>
       <c r="J44">
         <v>9</v>
       </c>
       <c r="K44">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L44">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="M44">
         <v>11</v>
       </c>
-      <c r="M44">
-        <f t="shared" si="7"/>
+      <c r="N44">
+        <f t="shared" si="9"/>
         <v>11</v>
       </c>
-      <c r="N44">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="O44" t="s">
+      <c r="O44">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="P44" t="s">
         <v>9</v>
       </c>
-      <c r="P44">
+      <c r="Q44">
         <v>2240</v>
       </c>
-      <c r="Q44">
+      <c r="R44">
         <v>23</v>
       </c>
-      <c r="R44">
-        <v>0</v>
-      </c>
-      <c r="S44" s="3">
+      <c r="S44">
+        <v>0</v>
+      </c>
+      <c r="T44" s="3">
         <v>41234.9</v>
       </c>
-      <c r="T44">
-        <f t="shared" si="13"/>
+      <c r="U44">
+        <f t="shared" si="15"/>
         <v>167.74375589609772</v>
       </c>
-      <c r="U44">
+      <c r="V44">
         <v>21</v>
       </c>
-      <c r="V44">
+      <c r="W44">
         <v>5.7</v>
       </c>
-      <c r="W44">
+      <c r="X44">
         <v>36</v>
       </c>
-      <c r="X44" s="1">
+      <c r="Y44" s="1">
         <v>124000</v>
       </c>
-      <c r="Y44" s="6">
+      <c r="Z44" s="6">
         <v>1.1310102995998677E-2</v>
       </c>
-      <c r="Z44">
+      <c r="AA44">
         <v>1141304</v>
       </c>
-      <c r="AA44">
+      <c r="AB44">
         <v>8527</v>
       </c>
-      <c r="AB44">
+      <c r="AC44">
         <v>16.7</v>
       </c>
-      <c r="AC44">
+      <c r="AD44">
         <v>0.38172230000000001</v>
       </c>
-      <c r="AD44">
+      <c r="AE44">
         <v>42</v>
       </c>
-      <c r="AE44" t="s">
+      <c r="AF44" t="s">
         <v>137</v>
       </c>
-      <c r="AF44" s="4">
-        <v>0</v>
-      </c>
-      <c r="AG44" s="5">
-        <f>AF44/D44</f>
+      <c r="AG44" s="4">
+        <v>0</v>
+      </c>
+      <c r="AH44" s="5">
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>53</v>
       </c>
@@ -6106,99 +6284,103 @@
         <v>29360759</v>
       </c>
       <c r="F45">
+        <f t="shared" si="8"/>
+        <v>-177469</v>
+      </c>
+      <c r="G45">
+        <f t="shared" si="11"/>
+        <v>3914872</v>
+      </c>
+      <c r="H45">
+        <f t="shared" si="12"/>
+        <v>15.493142467407338</v>
+      </c>
+      <c r="I45" s="2">
+        <f t="shared" si="13"/>
+        <v>-6.0444282111371851E-3</v>
+      </c>
+      <c r="J45">
+        <v>36</v>
+      </c>
+      <c r="K45">
+        <v>38</v>
+      </c>
+      <c r="L45">
+        <f t="shared" si="14"/>
+        <v>2</v>
+      </c>
+      <c r="M45">
+        <v>38</v>
+      </c>
+      <c r="N45">
         <f t="shared" si="9"/>
-        <v>3914872</v>
-      </c>
-      <c r="G45">
+        <v>40</v>
+      </c>
+      <c r="O45">
         <f t="shared" si="10"/>
-        <v>15.493142467407338</v>
-      </c>
-      <c r="H45" s="2">
-        <f t="shared" si="11"/>
-        <v>-6.0444282111371851E-3</v>
-      </c>
-      <c r="I45">
-        <v>36</v>
-      </c>
-      <c r="J45">
-        <v>38</v>
-      </c>
-      <c r="K45">
-        <f t="shared" si="12"/>
         <v>2</v>
       </c>
-      <c r="L45">
-        <v>38</v>
-      </c>
-      <c r="M45">
-        <f t="shared" si="7"/>
-        <v>40</v>
-      </c>
-      <c r="N45">
-        <f t="shared" si="8"/>
+      <c r="P45" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q45">
+        <v>3996</v>
+      </c>
+      <c r="R45">
+        <v>122</v>
+      </c>
+      <c r="S45">
+        <v>21</v>
+      </c>
+      <c r="T45" s="3">
+        <v>261231.71</v>
+      </c>
+      <c r="U45">
+        <f t="shared" si="15"/>
+        <v>111.71419426837576</v>
+      </c>
+      <c r="V45">
+        <v>25</v>
+      </c>
+      <c r="W45">
+        <v>39.700000000000003</v>
+      </c>
+      <c r="X45">
         <v>2</v>
       </c>
-      <c r="O45" t="s">
-        <v>9</v>
-      </c>
-      <c r="P45">
-        <v>3996</v>
-      </c>
-      <c r="Q45">
-        <v>122</v>
-      </c>
-      <c r="R45">
-        <v>21</v>
-      </c>
-      <c r="S45" s="3">
-        <v>261231.71</v>
-      </c>
-      <c r="T45">
-        <f t="shared" si="13"/>
-        <v>111.71419426837576</v>
-      </c>
-      <c r="U45">
-        <v>25</v>
-      </c>
-      <c r="V45">
-        <v>39.700000000000003</v>
-      </c>
-      <c r="W45">
-        <v>2</v>
-      </c>
-      <c r="X45" s="1">
+      <c r="Y45" s="1">
         <v>1730000</v>
       </c>
-      <c r="Y45" s="6">
+      <c r="Z45" s="6">
         <v>0.1576112344387991</v>
       </c>
-      <c r="Z45">
+      <c r="AA45">
         <v>3553922</v>
       </c>
-      <c r="AA45">
+      <c r="AB45">
         <v>23163</v>
       </c>
-      <c r="AB45">
+      <c r="AC45">
         <v>12.3</v>
       </c>
-      <c r="AC45">
+      <c r="AD45">
         <v>0.47169280000000002</v>
       </c>
-      <c r="AD45">
+      <c r="AE45">
         <v>29</v>
       </c>
-      <c r="AE45" t="s">
+      <c r="AF45" t="s">
         <v>137</v>
       </c>
-      <c r="AF45" s="4">
-        <v>0</v>
-      </c>
-      <c r="AG45" s="5">
-        <f>AF45/D45</f>
+      <c r="AG45" s="4">
+        <v>0</v>
+      </c>
+      <c r="AH45" s="5">
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>54</v>
       </c>
@@ -6215,99 +6397,103 @@
         <v>3249879</v>
       </c>
       <c r="F46">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
+        <v>25373</v>
+      </c>
+      <c r="G46">
+        <f t="shared" si="11"/>
         <v>504487</v>
       </c>
-      <c r="G46">
-        <f t="shared" si="10"/>
+      <c r="H46">
+        <f t="shared" si="12"/>
         <v>18.207498651094554</v>
       </c>
-      <c r="H46" s="2">
-        <f t="shared" si="11"/>
+      <c r="I46" s="2">
+        <f t="shared" si="13"/>
         <v>7.8073675973782406E-3</v>
-      </c>
-      <c r="I46">
-        <v>4</v>
       </c>
       <c r="J46">
         <v>4</v>
       </c>
       <c r="K46">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L46">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="M46">
         <v>6</v>
       </c>
-      <c r="M46">
-        <f t="shared" si="7"/>
+      <c r="N46">
+        <f t="shared" si="9"/>
         <v>6</v>
       </c>
-      <c r="N46">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="O46" t="s">
+      <c r="O46">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="P46" t="s">
         <v>9</v>
       </c>
-      <c r="P46">
+      <c r="Q46">
         <v>1012</v>
       </c>
-      <c r="Q46">
+      <c r="R46">
         <v>7</v>
       </c>
-      <c r="R46">
+      <c r="S46">
         <v>2</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>82169.62</v>
       </c>
-      <c r="T46">
-        <f t="shared" si="13"/>
+      <c r="U46">
+        <f t="shared" si="15"/>
         <v>39.859646424067684</v>
       </c>
-      <c r="U46">
+      <c r="V46">
         <v>41</v>
       </c>
-      <c r="V46">
+      <c r="W46">
         <v>14.4</v>
       </c>
-      <c r="W46">
+      <c r="X46">
         <v>13</v>
       </c>
-      <c r="X46" s="1">
+      <c r="Y46" s="1">
         <v>92000</v>
       </c>
-      <c r="Y46" s="6">
+      <c r="Z46" s="6">
         <v>8.3393736326296021E-3</v>
       </c>
-      <c r="Z46">
+      <c r="AA46">
         <v>36918</v>
       </c>
-      <c r="AA46">
+      <c r="AB46">
         <v>2748</v>
       </c>
-      <c r="AB46">
+      <c r="AC46">
         <v>1.2</v>
       </c>
-      <c r="AC46">
+      <c r="AD46">
         <v>0.39306390000000002</v>
       </c>
-      <c r="AD46">
+      <c r="AE46">
         <v>41</v>
       </c>
-      <c r="AE46" t="s">
+      <c r="AF46" t="s">
         <v>137</v>
       </c>
-      <c r="AF46" s="4">
+      <c r="AG46" s="4">
         <v>1000000</v>
       </c>
-      <c r="AG46" s="5">
-        <f>AF46/D46</f>
+      <c r="AH46" s="5">
+        <f t="shared" si="16"/>
         <v>0.30532001812379628</v>
       </c>
     </row>
-    <row r="47" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>55</v>
       </c>
@@ -6324,99 +6510,103 @@
         <v>623347</v>
       </c>
       <c r="F47">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
+        <v>20156</v>
+      </c>
+      <c r="G47">
+        <f t="shared" si="11"/>
         <v>13166</v>
       </c>
-      <c r="G47">
-        <f t="shared" si="10"/>
+      <c r="H47">
+        <f t="shared" si="12"/>
         <v>2.0887239682899783</v>
       </c>
-      <c r="H47" s="2">
-        <f t="shared" si="11"/>
+      <c r="I47" s="2">
+        <f t="shared" si="13"/>
         <v>3.233511992517811E-2</v>
-      </c>
-      <c r="I47">
-        <v>1</v>
       </c>
       <c r="J47">
         <v>1</v>
       </c>
       <c r="K47">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L47">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="M47">
         <v>3</v>
       </c>
-      <c r="M47">
-        <f t="shared" si="7"/>
+      <c r="N47">
+        <f t="shared" si="9"/>
         <v>3</v>
       </c>
-      <c r="N47">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="O47" t="s">
+      <c r="O47">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="P47" t="s">
         <v>12</v>
       </c>
-      <c r="P47">
+      <c r="Q47">
         <v>321</v>
       </c>
-      <c r="Q47">
+      <c r="R47">
         <v>16</v>
       </c>
-      <c r="R47">
+      <c r="S47">
         <v>3</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>9216.66</v>
       </c>
-      <c r="T47">
-        <f t="shared" si="13"/>
+      <c r="U47">
+        <f t="shared" si="15"/>
         <v>69.819544173268838</v>
       </c>
-      <c r="U47">
+      <c r="V47">
         <v>32</v>
       </c>
-      <c r="V47">
+      <c r="W47">
         <v>2</v>
       </c>
-      <c r="W47">
+      <c r="X47">
         <v>49</v>
       </c>
-      <c r="X47" s="1">
+      <c r="Y47" s="1">
         <v>3000</v>
       </c>
-      <c r="Y47" s="6">
+      <c r="Z47" s="6">
         <v>2.6588542379373502E-4</v>
       </c>
-      <c r="Z47">
+      <c r="AA47">
         <v>9435</v>
       </c>
-      <c r="AA47">
+      <c r="AB47">
         <v>1109</v>
       </c>
-      <c r="AB47">
+      <c r="AC47">
         <v>1.5</v>
       </c>
-      <c r="AC47">
+      <c r="AD47">
         <v>0.68299189999999999</v>
       </c>
-      <c r="AD47">
+      <c r="AE47">
         <v>2</v>
       </c>
-      <c r="AE47" t="s">
+      <c r="AF47" t="s">
         <v>137</v>
       </c>
-      <c r="AF47" s="4">
-        <v>0</v>
-      </c>
-      <c r="AG47" s="5">
-        <f>AF47/D47</f>
+      <c r="AG47" s="4">
+        <v>0</v>
+      </c>
+      <c r="AH47" s="5">
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>56</v>
       </c>
@@ -6433,99 +6623,103 @@
         <v>8590563</v>
       </c>
       <c r="F48">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
+        <v>63979</v>
+      </c>
+      <c r="G48">
+        <f t="shared" si="11"/>
         <v>616806</v>
       </c>
-      <c r="G48">
-        <f t="shared" si="10"/>
+      <c r="H48">
+        <f t="shared" si="12"/>
         <v>7.6738773206783604</v>
       </c>
-      <c r="H48" s="2">
-        <f t="shared" si="11"/>
+      <c r="I48" s="2">
+        <f t="shared" si="13"/>
         <v>7.4475910368156312E-3</v>
-      </c>
-      <c r="I48">
-        <v>11</v>
       </c>
       <c r="J48">
         <v>11</v>
       </c>
       <c r="K48">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="L48">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="M48">
         <v>13</v>
       </c>
-      <c r="M48">
-        <f t="shared" si="7"/>
+      <c r="N48">
+        <f t="shared" si="9"/>
         <v>13</v>
       </c>
-      <c r="N48">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="O48" t="s">
+      <c r="O48">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="P48" t="s">
         <v>12</v>
       </c>
-      <c r="P48">
+      <c r="Q48">
         <v>1706</v>
       </c>
-      <c r="Q48">
+      <c r="R48">
         <v>41</v>
       </c>
-      <c r="R48">
+      <c r="S48">
         <v>7</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>39490.089999999997</v>
       </c>
-      <c r="T48">
-        <f t="shared" si="13"/>
+      <c r="U48">
+        <f t="shared" si="15"/>
         <v>219.15731263210594</v>
       </c>
-      <c r="U48">
+      <c r="V48">
         <v>15</v>
       </c>
-      <c r="V48">
+      <c r="W48">
         <v>9.6999999999999993</v>
       </c>
-      <c r="W48">
+      <c r="X48">
         <v>27</v>
       </c>
-      <c r="X48" s="1">
+      <c r="Y48" s="1">
         <v>251000</v>
       </c>
-      <c r="Y48" s="6">
+      <c r="Z48" s="6">
         <v>2.2902440797941868E-2</v>
       </c>
-      <c r="Z48">
+      <c r="AA48">
         <v>1659908</v>
       </c>
-      <c r="AA48">
+      <c r="AB48">
         <v>12568</v>
       </c>
-      <c r="AB48">
+      <c r="AC48">
         <v>19.399999999999999</v>
       </c>
-      <c r="AC48">
+      <c r="AD48">
         <v>0.55154689999999995</v>
       </c>
-      <c r="AD48">
+      <c r="AE48">
         <v>17</v>
       </c>
-      <c r="AE48" t="s">
+      <c r="AF48" t="s">
         <v>138</v>
       </c>
-      <c r="AF48" s="4">
+      <c r="AG48" s="4">
         <v>1500000</v>
       </c>
-      <c r="AG48" s="5">
-        <f>AF48/D48</f>
+      <c r="AH48" s="5">
+        <f t="shared" si="16"/>
         <v>0.17331939691320464</v>
       </c>
     </row>
-    <row r="49" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>57</v>
       </c>
@@ -6542,99 +6736,103 @@
         <v>7693612</v>
       </c>
       <c r="F49">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
+        <v>22334</v>
+      </c>
+      <c r="G49">
+        <f t="shared" si="11"/>
         <v>962577</v>
       </c>
-      <c r="G49">
-        <f t="shared" si="10"/>
+      <c r="H49">
+        <f t="shared" si="12"/>
         <v>14.25328602657429</v>
       </c>
-      <c r="H49" s="2">
-        <f t="shared" si="11"/>
+      <c r="I49" s="2">
+        <f t="shared" si="13"/>
         <v>2.9029277795656967E-3</v>
-      </c>
-      <c r="I49">
-        <v>10</v>
       </c>
       <c r="J49">
         <v>10</v>
       </c>
       <c r="K49">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L49">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="M49">
         <v>12</v>
       </c>
-      <c r="M49">
-        <f t="shared" si="7"/>
+      <c r="N49">
+        <f t="shared" si="9"/>
         <v>12</v>
       </c>
-      <c r="N49">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="O49" t="s">
+      <c r="O49">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="P49" t="s">
         <v>9</v>
       </c>
-      <c r="P49">
+      <c r="Q49">
         <v>5319</v>
       </c>
-      <c r="Q49">
+      <c r="R49">
         <v>246</v>
       </c>
-      <c r="R49">
+      <c r="S49">
         <v>51</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>66455.520000000004</v>
       </c>
-      <c r="T49">
-        <f t="shared" si="13"/>
+      <c r="U49">
+        <f t="shared" si="15"/>
         <v>116.10692384921522</v>
       </c>
-      <c r="U49">
+      <c r="V49">
         <v>23</v>
       </c>
-      <c r="V49">
+      <c r="W49">
         <v>13</v>
       </c>
-      <c r="W49">
+      <c r="X49">
         <v>15</v>
       </c>
-      <c r="X49" s="1">
+      <c r="Y49" s="1">
         <v>240000</v>
       </c>
-      <c r="Y49" s="6">
+      <c r="Z49" s="6">
         <v>2.1875828694926852E-2</v>
       </c>
-      <c r="Z49">
+      <c r="AA49">
         <v>305924</v>
       </c>
-      <c r="AA49">
+      <c r="AB49">
         <v>7176</v>
       </c>
-      <c r="AB49">
+      <c r="AC49">
         <v>4</v>
       </c>
-      <c r="AC49">
+      <c r="AD49">
         <v>0.59925499999999998</v>
       </c>
-      <c r="AD49">
+      <c r="AE49">
         <v>10</v>
       </c>
-      <c r="AE49" t="s">
+      <c r="AF49" t="s">
         <v>138</v>
       </c>
-      <c r="AF49" s="4">
+      <c r="AG49" s="4">
         <v>15464000</v>
       </c>
-      <c r="AG49" s="5">
-        <f>AF49/D49</f>
+      <c r="AH49" s="5">
+        <f t="shared" si="16"/>
         <v>2.0041612525541264</v>
       </c>
     </row>
-    <row r="50" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>58</v>
       </c>
@@ -6651,99 +6849,103 @@
         <v>1784787</v>
       </c>
       <c r="F50">
+        <f t="shared" si="8"/>
+        <v>10258</v>
+      </c>
+      <c r="G50">
+        <f t="shared" si="11"/>
+        <v>-64770</v>
+      </c>
+      <c r="H50">
+        <f t="shared" si="12"/>
+        <v>-3.4826044525934035</v>
+      </c>
+      <c r="I50" s="2">
+        <f t="shared" si="13"/>
+        <v>5.7474645433880905E-3</v>
+      </c>
+      <c r="J50">
+        <v>3</v>
+      </c>
+      <c r="K50">
+        <v>2</v>
+      </c>
+      <c r="L50">
+        <f t="shared" si="14"/>
+        <v>-1</v>
+      </c>
+      <c r="M50">
+        <v>5</v>
+      </c>
+      <c r="N50">
         <f t="shared" si="9"/>
-        <v>-64770</v>
-      </c>
-      <c r="G50">
+        <v>4</v>
+      </c>
+      <c r="O50">
         <f t="shared" si="10"/>
-        <v>-3.4826044525934035</v>
-      </c>
-      <c r="H50" s="2">
-        <f t="shared" si="11"/>
-        <v>5.7474645433880905E-3</v>
-      </c>
-      <c r="I50">
-        <v>3</v>
-      </c>
-      <c r="J50">
+        <v>-1</v>
+      </c>
+      <c r="P50" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q50">
+        <v>191</v>
+      </c>
+      <c r="R50">
         <v>2</v>
       </c>
-      <c r="K50">
-        <f t="shared" si="12"/>
-        <v>-1</v>
-      </c>
-      <c r="L50">
-        <v>5</v>
-      </c>
-      <c r="M50">
-        <f t="shared" si="7"/>
-        <v>4</v>
-      </c>
-      <c r="N50">
-        <f t="shared" si="8"/>
-        <v>-1</v>
-      </c>
-      <c r="O50" t="s">
-        <v>9</v>
-      </c>
-      <c r="P50">
-        <v>191</v>
-      </c>
-      <c r="Q50">
-        <v>2</v>
-      </c>
-      <c r="R50">
+      <c r="S50">
         <v>1</v>
       </c>
-      <c r="S50" s="3">
+      <c r="T50" s="3">
         <v>24038.21</v>
       </c>
-      <c r="T50">
-        <f t="shared" si="13"/>
+      <c r="U50">
+        <f t="shared" si="15"/>
         <v>74.674653395573131</v>
       </c>
-      <c r="U50">
+      <c r="V50">
         <v>30</v>
       </c>
-      <c r="V50">
+      <c r="W50">
         <v>1.5</v>
       </c>
-      <c r="W50">
+      <c r="X50">
         <v>51</v>
       </c>
-      <c r="X50" s="1">
+      <c r="Y50" s="1">
         <v>6000</v>
       </c>
-      <c r="Y50" s="6">
+      <c r="Z50" s="6">
         <v>5.1273037763429653E-4</v>
       </c>
-      <c r="Z50">
+      <c r="AA50">
         <v>65925</v>
       </c>
-      <c r="AA50">
+      <c r="AB50">
         <v>3478</v>
       </c>
-      <c r="AB50">
+      <c r="AC50">
         <v>3.7</v>
       </c>
-      <c r="AC50">
+      <c r="AD50">
         <v>0.30201470000000002</v>
       </c>
-      <c r="AD50">
+      <c r="AE50">
         <v>50</v>
       </c>
-      <c r="AE50" t="s">
+      <c r="AF50" t="s">
         <v>137</v>
       </c>
-      <c r="AF50" s="4">
+      <c r="AG50" s="4">
         <v>1000000</v>
       </c>
-      <c r="AG50" s="5">
-        <f>AF50/D50</f>
+      <c r="AH50" s="5">
+        <f t="shared" si="16"/>
         <v>0.55708909804489581</v>
       </c>
     </row>
-    <row r="51" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>59</v>
       </c>
@@ -6760,99 +6962,103 @@
         <v>5832655</v>
       </c>
       <c r="F51">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
+        <v>64818</v>
+      </c>
+      <c r="G51">
+        <f t="shared" si="11"/>
         <v>199243</v>
       </c>
-      <c r="G51">
-        <f t="shared" si="10"/>
+      <c r="H51">
+        <f t="shared" si="12"/>
         <v>3.4965770072461098</v>
       </c>
-      <c r="H51" s="2">
-        <f t="shared" si="11"/>
+      <c r="I51" s="2">
+        <f t="shared" si="13"/>
         <v>1.1112949420118283E-2</v>
-      </c>
-      <c r="I51">
-        <v>8</v>
       </c>
       <c r="J51">
         <v>8</v>
       </c>
       <c r="K51">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L51">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="M51">
         <v>10</v>
       </c>
-      <c r="M51">
-        <f t="shared" si="7"/>
+      <c r="N51">
+        <f t="shared" si="9"/>
         <v>10</v>
       </c>
-      <c r="N51">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="O51" t="s">
+      <c r="O51">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="P51" t="s">
         <v>12</v>
       </c>
-      <c r="P51">
+      <c r="Q51">
         <v>1550</v>
       </c>
-      <c r="Q51">
+      <c r="R51">
         <v>24</v>
       </c>
-      <c r="R51">
+      <c r="S51">
         <v>8</v>
       </c>
-      <c r="S51" s="3">
+      <c r="T51" s="3">
         <v>54157.8</v>
       </c>
-      <c r="T51">
-        <f t="shared" si="13"/>
+      <c r="U51">
+        <f t="shared" si="15"/>
         <v>108.8942497664233</v>
       </c>
-      <c r="U51">
+      <c r="V51">
         <v>26</v>
       </c>
-      <c r="V51">
+      <c r="W51">
         <v>7.1</v>
       </c>
-      <c r="W51">
+      <c r="X51">
         <v>33</v>
       </c>
-      <c r="X51" s="1">
+      <c r="Y51" s="1">
         <v>74000</v>
       </c>
-      <c r="Y51" s="6">
+      <c r="Z51" s="6">
         <v>6.7595759382643901E-3</v>
       </c>
-      <c r="Z51">
+      <c r="AA51">
         <v>374747</v>
       </c>
-      <c r="AA51">
+      <c r="AB51">
         <v>5775</v>
       </c>
-      <c r="AB51">
+      <c r="AC51">
         <v>6.4</v>
       </c>
-      <c r="AC51">
+      <c r="AD51">
         <v>0.50319060000000004</v>
       </c>
-      <c r="AD51">
+      <c r="AE51">
         <v>24</v>
       </c>
-      <c r="AE51" t="s">
+      <c r="AF51" t="s">
         <v>138</v>
       </c>
-      <c r="AF51" s="4">
+      <c r="AG51" s="4">
         <v>1000000</v>
       </c>
-      <c r="AG51" s="5">
-        <f>AF51/D51</f>
+      <c r="AH51" s="5">
+        <f t="shared" si="16"/>
         <v>0.16956415061162636</v>
       </c>
     </row>
-    <row r="52" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>60</v>
       </c>
@@ -6869,91 +7075,105 @@
         <v>582328</v>
       </c>
       <c r="F52">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
+        <v>-4609</v>
+      </c>
+      <c r="G52">
+        <f t="shared" si="11"/>
         <v>9419</v>
       </c>
-      <c r="G52">
-        <f t="shared" si="10"/>
+      <c r="H52">
+        <f t="shared" si="12"/>
         <v>1.6573992609537216</v>
       </c>
-      <c r="H52" s="2">
-        <f t="shared" si="11"/>
+      <c r="I52" s="2">
+        <f t="shared" si="13"/>
         <v>-7.914783421027324E-3</v>
-      </c>
-      <c r="I52">
-        <v>1</v>
       </c>
       <c r="J52">
         <v>1</v>
       </c>
       <c r="K52">
-        <f t="shared" si="12"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L52">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="M52">
         <v>3</v>
       </c>
-      <c r="M52">
-        <f t="shared" si="7"/>
+      <c r="N52">
+        <f t="shared" si="9"/>
         <v>3</v>
       </c>
-      <c r="N52">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="O52" t="s">
+      <c r="O52">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="P52" t="s">
         <v>9</v>
       </c>
-      <c r="P52">
+      <c r="Q52">
         <v>137</v>
       </c>
-      <c r="Q52">
-        <v>0</v>
-      </c>
       <c r="R52">
         <v>0</v>
       </c>
-      <c r="S52" s="3">
+      <c r="S52">
+        <v>0</v>
+      </c>
+      <c r="T52" s="3">
         <v>97093.14</v>
       </c>
-      <c r="T52">
-        <f t="shared" si="13"/>
+      <c r="U52">
+        <f t="shared" si="15"/>
         <v>5.9501526060440524</v>
       </c>
-      <c r="U52">
+      <c r="V52">
         <v>50</v>
       </c>
-      <c r="V52">
+      <c r="W52">
         <v>10.1</v>
       </c>
-      <c r="W52">
+      <c r="X52">
         <v>24</v>
       </c>
-      <c r="X52" s="1">
+      <c r="Y52" s="1">
         <v>8000</v>
       </c>
-      <c r="Y52" s="6">
+      <c r="Z52" s="6">
         <v>7.5184707792282806E-4</v>
       </c>
-      <c r="Z52">
+      <c r="AA52">
         <v>7116</v>
       </c>
-      <c r="AA52">
+      <c r="AB52">
         <v>1901</v>
       </c>
-      <c r="AB52">
+      <c r="AC52">
         <v>1.2</v>
       </c>
-      <c r="AC52" s="5" t="e">
+      <c r="AD52" s="5" t="e">
         <f>#REF!/D52</f>
         <v>#REF!</v>
       </c>
-      <c r="AE52" t="s">
+      <c r="AF52" t="s">
         <v>137</v>
+      </c>
+    </row>
+    <row r="53" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="D53">
+        <f>SUM(D2:D52)</f>
+        <v>331799967</v>
+      </c>
+      <c r="E53">
+        <f>SUM(E2:E52)</f>
+        <v>329484123</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AC52">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AD52">
     <sortCondition ref="A2:A52"/>
   </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
